--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8034F616-89BF-4501-B9AF-86313972D0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33597F6A-7DB4-43D3-A75E-0B796240D426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="862">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -980,46 +980,184 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_013</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_solelc_spv_002</t>
@@ -1034,166 +1172,88 @@
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500</t>
+    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
   </si>
   <si>
-    <t>e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
   </si>
   <si>
     <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
@@ -1202,67 +1262,88 @@
     <t>e_w179863079-275,e_JP6-275</t>
   </si>
   <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w1037299172-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500</t>
-  </si>
-  <si>
-    <t>e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_wonelc_won_009</t>
@@ -1289,10 +1370,22 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wonelc_won_006</t>
@@ -1307,22 +1400,16 @@
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_015</t>
@@ -1331,64 +1418,22 @@
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1403,52 +1448,76 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
   </si>
   <si>
     <t>elc_won_009</t>
@@ -1466,16 +1535,28 @@
     <t>elc_won_025</t>
   </si>
   <si>
-    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
   </si>
   <si>
     <t>elc_won_030</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
   </si>
   <si>
     <t>elc_won_006</t>
@@ -1490,19 +1571,16 @@
     <t>e_w459476442-500,e_w150065045-500</t>
   </si>
   <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
   </si>
   <si>
     <t>elc_won_015</t>
@@ -1511,61 +1589,22 @@
     <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
   </si>
   <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -1580,46 +1619,214 @@
     <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_031</t>
@@ -1634,475 +1841,265 @@
     <t>connecting wind offshore to buses in cluster 39</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_018</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_023</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
   </si>
   <si>
     <t>elc_wof_031</t>
   </si>
   <si>
-    <t>e_JP117-500</t>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
   </si>
   <si>
     <t>elc_wof_039</t>
   </si>
   <si>
-    <t>e_w170247312-500,e_JP219-500</t>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
   </si>
   <si>
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
     <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7579,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8D64B8-E950-4E29-B93E-9D999A74BAEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E3DCEE-918C-4564-A09E-998D4F26F72E}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7817,25 +7814,25 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.99864771921475071</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB11">
-        <v>24.791814396238056</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
       </c>
       <c r="AE11" t="s">
+        <v>377</v>
+      </c>
+      <c r="AF11" t="s">
         <v>378</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>379</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -7850,28 +7847,28 @@
         <v>186</v>
       </c>
       <c r="AL11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AM11" t="s">
+        <v>439</v>
+      </c>
+      <c r="AN11" t="s">
         <v>440</v>
       </c>
-      <c r="AN11" t="s">
-        <v>441</v>
-      </c>
       <c r="AO11">
-        <v>0.99811838305018963</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP11">
-        <v>34.496310746523356</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
       </c>
       <c r="AS11" t="s">
+        <v>496</v>
+      </c>
+      <c r="AT11" t="s">
         <v>497</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>498</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -7886,19 +7883,19 @@
         <v>186</v>
       </c>
       <c r="AZ11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="BA11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>586</v>
+        <v>449</v>
       </c>
       <c r="BC11">
-        <v>0.98779966071713954</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD11">
-        <v>223.67288685244134</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7963,25 +7960,25 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.99628076912917996</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB12">
-        <v>68.185899298368355</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
       </c>
       <c r="AE12" t="s">
+        <v>379</v>
+      </c>
+      <c r="AF12" t="s">
         <v>380</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>381</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -7996,28 +7993,28 @@
         <v>186</v>
       </c>
       <c r="AL12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM12" t="s">
+        <v>441</v>
+      </c>
+      <c r="AN12" t="s">
         <v>442</v>
       </c>
-      <c r="AN12" t="s">
-        <v>443</v>
-      </c>
       <c r="AO12">
-        <v>0.9985928182686985</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP12">
-        <v>25.798331740528162</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
       </c>
       <c r="AS12" t="s">
+        <v>498</v>
+      </c>
+      <c r="AT12" t="s">
         <v>499</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>500</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -8032,19 +8029,19 @@
         <v>186</v>
       </c>
       <c r="AZ12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="BA12" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="BB12" t="s">
-        <v>588</v>
+        <v>491</v>
       </c>
       <c r="BC12">
-        <v>0.99681267676383467</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD12">
-        <v>58.434259329697142</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8109,25 +8106,25 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.99621285878087551</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB13">
-        <v>69.43092235061502</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
       </c>
       <c r="AE13" t="s">
+        <v>381</v>
+      </c>
+      <c r="AF13" t="s">
         <v>382</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>383</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -8142,28 +8139,28 @@
         <v>186</v>
       </c>
       <c r="AL13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AM13" t="s">
+        <v>443</v>
+      </c>
+      <c r="AN13" t="s">
         <v>444</v>
       </c>
-      <c r="AN13" t="s">
-        <v>445</v>
-      </c>
       <c r="AO13">
-        <v>0.99771335854027388</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP13">
-        <v>41.921760094978509</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
       </c>
       <c r="AS13" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT13" t="s">
         <v>501</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>502</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -8178,19 +8175,19 @@
         <v>186</v>
       </c>
       <c r="AZ13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="BA13" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="BB13" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="BC13">
-        <v>0.98627205860840139</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD13">
-        <v>251.67892551264018</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8255,25 +8252,25 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.9975431479552237</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB14">
-        <v>45.042287487565297</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
       </c>
       <c r="AE14" t="s">
+        <v>383</v>
+      </c>
+      <c r="AF14" t="s">
         <v>384</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>385</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -8288,28 +8285,28 @@
         <v>186</v>
       </c>
       <c r="AL14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AM14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AN14" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="AO14">
-        <v>0.98814178187791379</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP14">
-        <v>217.40066557158059</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
       </c>
       <c r="AS14" t="s">
+        <v>502</v>
+      </c>
+      <c r="AT14" t="s">
         <v>503</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>504</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -8324,19 +8321,19 @@
         <v>186</v>
       </c>
       <c r="AZ14" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="BA14" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="BB14" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="BC14">
-        <v>0.99302778580016682</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD14">
-        <v>127.82392699694152</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8401,25 +8398,25 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.99636728996375623</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB15">
-        <v>66.599683997802714</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
       </c>
       <c r="AE15" t="s">
+        <v>385</v>
+      </c>
+      <c r="AF15" t="s">
         <v>386</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>387</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -8434,28 +8431,28 @@
         <v>186</v>
       </c>
       <c r="AL15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AM15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AN15" t="s">
-        <v>448</v>
+        <v>370</v>
       </c>
       <c r="AO15">
-        <v>0.99869874972548245</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP15">
-        <v>23.856255032822389</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
       </c>
       <c r="AS15" t="s">
+        <v>504</v>
+      </c>
+      <c r="AT15" t="s">
         <v>505</v>
-      </c>
-      <c r="AT15" t="s">
-        <v>506</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -8470,19 +8467,19 @@
         <v>186</v>
       </c>
       <c r="AZ15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BA15" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="BB15" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="BC15">
-        <v>0.99504061303190972</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD15">
-        <v>90.922094414988095</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8562,10 +8559,10 @@
         <v>282</v>
       </c>
       <c r="AE16" t="s">
+        <v>387</v>
+      </c>
+      <c r="AF16" t="s">
         <v>388</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>389</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -8580,28 +8577,28 @@
         <v>186</v>
       </c>
       <c r="AL16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AM16" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AN16" t="s">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="AO16">
-        <v>0.99841760060377538</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP16">
-        <v>29.010655597451841</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
       </c>
       <c r="AS16" t="s">
+        <v>506</v>
+      </c>
+      <c r="AT16" t="s">
         <v>507</v>
-      </c>
-      <c r="AT16" t="s">
-        <v>508</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -8616,19 +8613,19 @@
         <v>186</v>
       </c>
       <c r="AZ16" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BA16" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="BB16" t="s">
-        <v>377</v>
+        <v>593</v>
       </c>
       <c r="BC16">
-        <v>0.97902641975794957</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD16">
-        <v>384.51563777092457</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8693,25 +8690,25 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.99410594174368461</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB17">
-        <v>108.05773469911641</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
       </c>
       <c r="AE17" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF17" t="s">
         <v>390</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>391</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -8726,28 +8723,28 @@
         <v>186</v>
       </c>
       <c r="AL17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AM17" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AN17" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AO17">
-        <v>0.99781438034778358</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP17">
-        <v>40.069693623967019</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
       </c>
       <c r="AS17" t="s">
+        <v>508</v>
+      </c>
+      <c r="AT17" t="s">
         <v>509</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>510</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -8762,19 +8759,19 @@
         <v>186</v>
       </c>
       <c r="AZ17" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="BA17" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="BB17" t="s">
-        <v>597</v>
+        <v>355</v>
       </c>
       <c r="BC17">
-        <v>0.99603667376986049</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD17">
-        <v>72.660980885890424</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8839,25 +8836,25 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.98968917222400854</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB18">
-        <v>189.03184255984442</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
       </c>
       <c r="AE18" t="s">
+        <v>391</v>
+      </c>
+      <c r="AF18" t="s">
         <v>392</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>393</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -8872,28 +8869,28 @@
         <v>186</v>
       </c>
       <c r="AL18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AM18" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AN18" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AO18">
-        <v>0.99750949182367343</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP18">
-        <v>45.659316565986806</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
       </c>
       <c r="AS18" t="s">
+        <v>510</v>
+      </c>
+      <c r="AT18" t="s">
         <v>511</v>
-      </c>
-      <c r="AT18" t="s">
-        <v>512</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -8908,19 +8905,19 @@
         <v>186</v>
       </c>
       <c r="AZ18" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="BB18" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="BC18">
-        <v>0.97589985979527272</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD18">
-        <v>441.83590375333313</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8985,25 +8982,25 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.99824350404965267</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB19">
-        <v>32.202425756367248</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
       </c>
       <c r="AE19" t="s">
+        <v>393</v>
+      </c>
+      <c r="AF19" t="s">
         <v>394</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>395</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -9018,28 +9015,28 @@
         <v>186</v>
       </c>
       <c r="AL19" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AM19" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AN19" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AO19">
-        <v>0.99827635377245738</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP19">
-        <v>31.600180838280902</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
       </c>
       <c r="AS19" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT19" t="s">
         <v>513</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>514</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -9054,19 +9051,19 @@
         <v>186</v>
       </c>
       <c r="AZ19" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="BB19" t="s">
-        <v>496</v>
+        <v>352</v>
       </c>
       <c r="BC19">
-        <v>0.9437657388784082</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD19">
-        <v>1030.9614538958492</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9131,25 +9128,25 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.99900168239190124</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB20">
-        <v>18.302489481810518</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
       </c>
       <c r="AE20" t="s">
+        <v>395</v>
+      </c>
+      <c r="AF20" t="s">
         <v>396</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>397</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -9164,28 +9161,28 @@
         <v>186</v>
       </c>
       <c r="AL20" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AM20" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AN20" t="s">
-        <v>367</v>
+        <v>455</v>
       </c>
       <c r="AO20">
-        <v>0.98949004263841422</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP20">
-        <v>192.68255162907312</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
       </c>
       <c r="AS20" t="s">
+        <v>514</v>
+      </c>
+      <c r="AT20" t="s">
         <v>515</v>
-      </c>
-      <c r="AT20" t="s">
-        <v>516</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -9200,19 +9197,19 @@
         <v>186</v>
       </c>
       <c r="AZ20" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="BA20" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="BB20" t="s">
-        <v>602</v>
+        <v>356</v>
       </c>
       <c r="BC20">
-        <v>0.99602290686668338</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD20">
-        <v>72.91337411080552</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9277,25 +9274,25 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="Z21" t="s">
         <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.99726055556014181</v>
+        <v>0.99809166649408687</v>
       </c>
       <c r="AB21">
-        <v>50.223148064066145</v>
+        <v>34.986114275074357</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
       </c>
       <c r="AE21" t="s">
+        <v>397</v>
+      </c>
+      <c r="AF21" t="s">
         <v>398</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>399</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -9310,28 +9307,28 @@
         <v>186</v>
       </c>
       <c r="AL21" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AM21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AN21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AO21">
-        <v>0.99686124252542985</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP21">
-        <v>57.543887033786262</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
       </c>
       <c r="AS21" t="s">
+        <v>516</v>
+      </c>
+      <c r="AT21" t="s">
         <v>517</v>
-      </c>
-      <c r="AT21" t="s">
-        <v>518</v>
       </c>
       <c r="AU21" t="s">
         <v>10</v>
@@ -9346,19 +9343,19 @@
         <v>186</v>
       </c>
       <c r="AZ21" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="BA21" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="BB21" t="s">
-        <v>604</v>
+        <v>356</v>
       </c>
       <c r="BC21">
-        <v>0.99519319222421976</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD21">
-        <v>88.124809222638589</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9423,25 +9420,25 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="Z22" t="s">
         <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.99116451092312863</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB22">
-        <v>161.98396640930775</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
       </c>
       <c r="AE22" t="s">
+        <v>399</v>
+      </c>
+      <c r="AF22" t="s">
         <v>400</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>401</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -9456,28 +9453,28 @@
         <v>186</v>
       </c>
       <c r="AL22" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AM22" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN22" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AO22">
-        <v>0.99863922747017897</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP22">
-        <v>24.947496380053089</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
       </c>
       <c r="AS22" t="s">
+        <v>518</v>
+      </c>
+      <c r="AT22" t="s">
         <v>519</v>
-      </c>
-      <c r="AT22" t="s">
-        <v>520</v>
       </c>
       <c r="AU22" t="s">
         <v>10</v>
@@ -9492,19 +9489,19 @@
         <v>186</v>
       </c>
       <c r="AZ22" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="BA22" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="BB22" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="BC22">
-        <v>0.99253849155603513</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD22">
-        <v>136.79432147269009</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9536,10 +9533,10 @@
         <v>262</v>
       </c>
       <c r="L23">
-        <v>9.0718124098924431</v>
+        <v>11.664406830498095</v>
       </c>
       <c r="M23">
-        <v>0.1955082967785822</v>
+        <v>0.20214793379564561</v>
       </c>
       <c r="O23" t="s">
         <v>282</v>
@@ -9569,25 +9566,25 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="Z23" t="s">
         <v>361</v>
       </c>
       <c r="AA23">
-        <v>0.99821686042936064</v>
+        <v>0.99621285878087551</v>
       </c>
       <c r="AB23">
-        <v>32.690892128388938</v>
+        <v>69.43092235061502</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
       </c>
       <c r="AE23" t="s">
+        <v>401</v>
+      </c>
+      <c r="AF23" t="s">
         <v>402</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>403</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -9602,28 +9599,28 @@
         <v>186</v>
       </c>
       <c r="AL23" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AM23" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AN23" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AO23">
-        <v>0.99762356494824644</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP23">
-        <v>43.567975948815601</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
       </c>
       <c r="AS23" t="s">
+        <v>520</v>
+      </c>
+      <c r="AT23" t="s">
         <v>521</v>
-      </c>
-      <c r="AT23" t="s">
-        <v>522</v>
       </c>
       <c r="AU23" t="s">
         <v>10</v>
@@ -9638,19 +9635,19 @@
         <v>186</v>
       </c>
       <c r="AZ23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="BA23" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="BB23" t="s">
-        <v>608</v>
+        <v>491</v>
       </c>
       <c r="BC23">
-        <v>0.99234935324205875</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD23">
-        <v>140.26185722892211</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9682,10 +9679,10 @@
         <v>263</v>
       </c>
       <c r="L24">
-        <v>11.664406830498095</v>
+        <v>11.049590277797785</v>
       </c>
       <c r="M24">
-        <v>0.20214793379564561</v>
+        <v>0.19454864451673889</v>
       </c>
       <c r="O24" t="s">
         <v>282</v>
@@ -9715,25 +9712,25 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="Z24" t="s">
         <v>362</v>
       </c>
       <c r="AA24">
-        <v>0.9981032549815434</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB24">
-        <v>34.773658671704098</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
       </c>
       <c r="AE24" t="s">
+        <v>403</v>
+      </c>
+      <c r="AF24" t="s">
         <v>404</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>405</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -9748,28 +9745,28 @@
         <v>186</v>
       </c>
       <c r="AL24" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AM24" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AN24" t="s">
-        <v>465</v>
+        <v>370</v>
       </c>
       <c r="AO24">
-        <v>0.99669176136177262</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP24">
-        <v>60.651041700835236</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
       </c>
       <c r="AS24" t="s">
+        <v>522</v>
+      </c>
+      <c r="AT24" t="s">
         <v>523</v>
-      </c>
-      <c r="AT24" t="s">
-        <v>524</v>
       </c>
       <c r="AU24" t="s">
         <v>10</v>
@@ -9784,19 +9781,19 @@
         <v>186</v>
       </c>
       <c r="AZ24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="BA24" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="BB24" t="s">
-        <v>610</v>
+        <v>353</v>
       </c>
       <c r="BC24">
-        <v>0.9205295464439136</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD24">
-        <v>1456.9583151949184</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9828,10 +9825,10 @@
         <v>264</v>
       </c>
       <c r="L25">
-        <v>2.5875928019748891</v>
+        <v>2.0672282720381219</v>
       </c>
       <c r="M25">
-        <v>0.1897509358760501</v>
+        <v>0.1897242685700597</v>
       </c>
       <c r="O25" t="s">
         <v>282</v>
@@ -9861,25 +9858,25 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="Z25" t="s">
         <v>363</v>
       </c>
       <c r="AA25">
-        <v>0.99391268208184824</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB25">
-        <v>111.60082849944791</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
       </c>
       <c r="AE25" t="s">
+        <v>405</v>
+      </c>
+      <c r="AF25" t="s">
         <v>406</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>407</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -9894,28 +9891,28 @@
         <v>186</v>
       </c>
       <c r="AL25" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AM25" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AN25" t="s">
-        <v>370</v>
+        <v>464</v>
       </c>
       <c r="AO25">
-        <v>0.93717435218793788</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP25">
-        <v>1151.8035432211395</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
       </c>
       <c r="AS25" t="s">
+        <v>524</v>
+      </c>
+      <c r="AT25" t="s">
         <v>525</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>526</v>
       </c>
       <c r="AU25" t="s">
         <v>10</v>
@@ -9930,19 +9927,19 @@
         <v>186</v>
       </c>
       <c r="AZ25" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="BA25" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="BB25" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="BC25">
-        <v>0.99895994357772033</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD25">
-        <v>19.067701075126294</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9974,10 +9971,10 @@
         <v>265</v>
       </c>
       <c r="L26">
-        <v>3.9797399643633269</v>
+        <v>5.3002505298606302</v>
       </c>
       <c r="M26">
-        <v>0.1897358019232025</v>
+        <v>0.19067081479710349</v>
       </c>
       <c r="O26" t="s">
         <v>282</v>
@@ -10007,25 +10004,25 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="Z26" t="s">
         <v>364</v>
       </c>
       <c r="AA26">
-        <v>0.99781867834130344</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB26">
-        <v>39.990897076102542</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
       </c>
       <c r="AE26" t="s">
+        <v>407</v>
+      </c>
+      <c r="AF26" t="s">
         <v>408</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>409</v>
       </c>
       <c r="AG26" t="s">
         <v>10</v>
@@ -10040,28 +10037,28 @@
         <v>186</v>
       </c>
       <c r="AL26" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AM26" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AN26" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AO26">
-        <v>0.96551955124232614</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP26">
-        <v>632.14156055735509</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
       </c>
       <c r="AS26" t="s">
+        <v>526</v>
+      </c>
+      <c r="AT26" t="s">
         <v>527</v>
-      </c>
-      <c r="AT26" t="s">
-        <v>528</v>
       </c>
       <c r="AU26" t="s">
         <v>10</v>
@@ -10076,19 +10073,19 @@
         <v>186</v>
       </c>
       <c r="AZ26" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BA26" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="BB26" t="s">
-        <v>614</v>
+        <v>356</v>
       </c>
       <c r="BC26">
-        <v>0.98822137145239475</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD26">
-        <v>215.94152337276336</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10120,10 +10117,10 @@
         <v>266</v>
       </c>
       <c r="L27">
-        <v>2.8715953269951235</v>
+        <v>3.834874392856122</v>
       </c>
       <c r="M27">
-        <v>0.18670013355518961</v>
+        <v>0.18539287912319011</v>
       </c>
       <c r="O27" t="s">
         <v>282</v>
@@ -10153,25 +10150,25 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="Z27" t="s">
         <v>365</v>
       </c>
       <c r="AA27">
-        <v>0.99897859865198069</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB27">
-        <v>18.725691380354675</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
       </c>
       <c r="AE27" t="s">
+        <v>409</v>
+      </c>
+      <c r="AF27" t="s">
         <v>410</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>411</v>
       </c>
       <c r="AG27" t="s">
         <v>10</v>
@@ -10186,28 +10183,28 @@
         <v>186</v>
       </c>
       <c r="AL27" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AM27" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN27" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AO27">
-        <v>0.99693456929731861</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP27">
-        <v>56.199562882493169</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
       </c>
       <c r="AS27" t="s">
+        <v>528</v>
+      </c>
+      <c r="AT27" t="s">
         <v>529</v>
-      </c>
-      <c r="AT27" t="s">
-        <v>530</v>
       </c>
       <c r="AU27" t="s">
         <v>10</v>
@@ -10222,19 +10219,19 @@
         <v>186</v>
       </c>
       <c r="AZ27" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="BB27" t="s">
-        <v>616</v>
+        <v>356</v>
       </c>
       <c r="BC27">
-        <v>0.99284590877035406</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD27">
-        <v>131.158339210175</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10266,10 +10263,10 @@
         <v>267</v>
       </c>
       <c r="L28">
-        <v>6.991913582308344</v>
+        <v>2.7450178137494068</v>
       </c>
       <c r="M28">
-        <v>0.1924871297641926</v>
+        <v>0.18635551573044509</v>
       </c>
       <c r="O28" t="s">
         <v>282</v>
@@ -10299,25 +10296,25 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Z28" t="s">
         <v>366</v>
       </c>
       <c r="AA28">
-        <v>0.99856748800713691</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB28">
-        <v>26.26271986915707</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
       </c>
       <c r="AE28" t="s">
+        <v>411</v>
+      </c>
+      <c r="AF28" t="s">
         <v>412</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>413</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
@@ -10332,28 +10329,28 @@
         <v>186</v>
       </c>
       <c r="AL28" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN28" t="s">
-        <v>472</v>
+        <v>353</v>
       </c>
       <c r="AO28">
-        <v>0.99804155179341392</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP28">
-        <v>35.904883787411507</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
       </c>
       <c r="AS28" t="s">
+        <v>530</v>
+      </c>
+      <c r="AT28" t="s">
         <v>531</v>
-      </c>
-      <c r="AT28" t="s">
-        <v>532</v>
       </c>
       <c r="AU28" t="s">
         <v>10</v>
@@ -10368,19 +10365,19 @@
         <v>186</v>
       </c>
       <c r="AZ28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="BB28" t="s">
-        <v>612</v>
+        <v>356</v>
       </c>
       <c r="BC28">
-        <v>0.98495036947912284</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD28">
-        <v>275.90989288274841</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10412,10 +10409,10 @@
         <v>268</v>
       </c>
       <c r="L29">
-        <v>2.9302732840741852</v>
+        <v>6.3183450599935256</v>
       </c>
       <c r="M29">
-        <v>0.1887423972415912</v>
+        <v>0.19209496103447071</v>
       </c>
       <c r="O29" t="s">
         <v>282</v>
@@ -10445,25 +10442,25 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="Z29" t="s">
         <v>367</v>
       </c>
       <c r="AA29">
-        <v>0.97905685820454003</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB29">
-        <v>383.95759958343297</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
       </c>
       <c r="AE29" t="s">
+        <v>413</v>
+      </c>
+      <c r="AF29" t="s">
         <v>414</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>415</v>
       </c>
       <c r="AG29" t="s">
         <v>10</v>
@@ -10478,28 +10475,28 @@
         <v>186</v>
       </c>
       <c r="AL29" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AN29" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AO29">
-        <v>0.99508023417818925</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP29">
-        <v>90.195706733197795</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
       </c>
       <c r="AS29" t="s">
+        <v>532</v>
+      </c>
+      <c r="AT29" t="s">
         <v>533</v>
-      </c>
-      <c r="AT29" t="s">
-        <v>534</v>
       </c>
       <c r="AU29" t="s">
         <v>10</v>
@@ -10514,19 +10511,19 @@
         <v>186</v>
       </c>
       <c r="AZ29" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="BB29" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="BC29">
-        <v>0.99536692897647694</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD29">
-        <v>84.939635431255269</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10558,10 +10555,10 @@
         <v>269</v>
       </c>
       <c r="L30">
-        <v>2.8823789766872761</v>
+        <v>0.11366418204482304</v>
       </c>
       <c r="M30">
-        <v>0.18524969233224811</v>
+        <v>0.18364651891835679</v>
       </c>
       <c r="O30" t="s">
         <v>282</v>
@@ -10591,25 +10588,25 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="Z30" t="s">
         <v>368</v>
       </c>
       <c r="AA30">
-        <v>0.99732143290864816</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB30">
-        <v>49.107063341450861</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
       </c>
       <c r="AE30" t="s">
+        <v>415</v>
+      </c>
+      <c r="AF30" t="s">
         <v>416</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>417</v>
       </c>
       <c r="AG30" t="s">
         <v>10</v>
@@ -10624,28 +10621,28 @@
         <v>186</v>
       </c>
       <c r="AL30" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AM30" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AN30" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AO30">
-        <v>0.99940622505963084</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP30">
-        <v>10.885873906767051</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
       </c>
       <c r="AS30" t="s">
+        <v>534</v>
+      </c>
+      <c r="AT30" t="s">
         <v>535</v>
-      </c>
-      <c r="AT30" t="s">
-        <v>536</v>
       </c>
       <c r="AU30" t="s">
         <v>10</v>
@@ -10660,19 +10657,19 @@
         <v>186</v>
       </c>
       <c r="AZ30" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="BB30" t="s">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="BC30">
-        <v>0.93089405249526469</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD30">
-        <v>1266.9423709201483</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10704,10 +10701,10 @@
         <v>270</v>
       </c>
       <c r="L31">
-        <v>1.0868475837211775</v>
+        <v>0.97318340167635442</v>
       </c>
       <c r="M31">
-        <v>0.18525666908653099</v>
+        <v>0.18544472860493169</v>
       </c>
       <c r="O31" t="s">
         <v>282</v>
@@ -10737,7 +10734,7 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Z31" t="s">
         <v>369</v>
@@ -10752,10 +10749,10 @@
         <v>282</v>
       </c>
       <c r="AE31" t="s">
+        <v>417</v>
+      </c>
+      <c r="AF31" t="s">
         <v>418</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>419</v>
       </c>
       <c r="AG31" t="s">
         <v>10</v>
@@ -10770,13 +10767,13 @@
         <v>186</v>
       </c>
       <c r="AL31" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AM31" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AN31" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AO31">
         <v>0.99682717865030179</v>
@@ -10788,10 +10785,10 @@
         <v>282</v>
       </c>
       <c r="AS31" t="s">
+        <v>536</v>
+      </c>
+      <c r="AT31" t="s">
         <v>537</v>
-      </c>
-      <c r="AT31" t="s">
-        <v>538</v>
       </c>
       <c r="AU31" t="s">
         <v>10</v>
@@ -10806,19 +10803,19 @@
         <v>186</v>
       </c>
       <c r="AZ31" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="BB31" t="s">
-        <v>370</v>
+        <v>614</v>
       </c>
       <c r="BC31">
-        <v>0.934538160869965</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD31">
-        <v>1200.1337173839754</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10883,25 +10880,25 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="Z32" t="s">
         <v>370</v>
       </c>
       <c r="AA32">
-        <v>0.94069903208664407</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB32">
-        <v>1087.1844117448593</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
       </c>
       <c r="AE32" t="s">
+        <v>419</v>
+      </c>
+      <c r="AF32" t="s">
         <v>420</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>421</v>
       </c>
       <c r="AG32" t="s">
         <v>10</v>
@@ -10916,28 +10913,28 @@
         <v>186</v>
       </c>
       <c r="AL32" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AM32" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AN32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AO32">
-        <v>0.99870022163576544</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP32">
-        <v>23.829270010966344</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
       </c>
       <c r="AS32" t="s">
+        <v>538</v>
+      </c>
+      <c r="AT32" t="s">
         <v>539</v>
-      </c>
-      <c r="AT32" t="s">
-        <v>540</v>
       </c>
       <c r="AU32" t="s">
         <v>10</v>
@@ -10952,19 +10949,19 @@
         <v>186</v>
       </c>
       <c r="AZ32" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="BB32" t="s">
-        <v>370</v>
+        <v>616</v>
       </c>
       <c r="BC32">
-        <v>0.94616153753972931</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD32">
-        <v>987.03847843829612</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11029,25 +11026,25 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="Z33" t="s">
         <v>371</v>
       </c>
       <c r="AA33">
-        <v>0.9972084849335241</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB33">
-        <v>51.177776218725121</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
       </c>
       <c r="AE33" t="s">
+        <v>421</v>
+      </c>
+      <c r="AF33" t="s">
         <v>422</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>423</v>
       </c>
       <c r="AG33" t="s">
         <v>10</v>
@@ -11062,28 +11059,28 @@
         <v>186</v>
       </c>
       <c r="AL33" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AM33" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AN33" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AO33">
-        <v>0.99807466477127271</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP33">
-        <v>35.297812526667357</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
       </c>
       <c r="AS33" t="s">
+        <v>540</v>
+      </c>
+      <c r="AT33" t="s">
         <v>541</v>
-      </c>
-      <c r="AT33" t="s">
-        <v>542</v>
       </c>
       <c r="AU33" t="s">
         <v>10</v>
@@ -11098,19 +11095,19 @@
         <v>186</v>
       </c>
       <c r="AZ33" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="BB33" t="s">
-        <v>370</v>
+        <v>618</v>
       </c>
       <c r="BC33">
-        <v>0.97218956380622079</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD33">
-        <v>509.85799688595205</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11175,25 +11172,25 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="Z34" t="s">
         <v>372</v>
       </c>
       <c r="AA34">
-        <v>0.9488788277802801</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB34">
-        <v>937.22149069486488</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
       </c>
       <c r="AE34" t="s">
+        <v>423</v>
+      </c>
+      <c r="AF34" t="s">
         <v>424</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>425</v>
       </c>
       <c r="AG34" t="s">
         <v>10</v>
@@ -11208,13 +11205,13 @@
         <v>186</v>
       </c>
       <c r="AL34" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AM34" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AN34" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AO34">
         <v>0.99013353407586135</v>
@@ -11226,10 +11223,10 @@
         <v>282</v>
       </c>
       <c r="AS34" t="s">
+        <v>542</v>
+      </c>
+      <c r="AT34" t="s">
         <v>543</v>
-      </c>
-      <c r="AT34" t="s">
-        <v>544</v>
       </c>
       <c r="AU34" t="s">
         <v>10</v>
@@ -11244,19 +11241,19 @@
         <v>186</v>
       </c>
       <c r="AZ34" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="BA34" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="BB34" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="BC34">
-        <v>0.9924172440074055</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD34">
-        <v>139.01719319756617</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11321,25 +11318,25 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="Z35" t="s">
         <v>373</v>
       </c>
       <c r="AA35">
-        <v>0.99854991213594346</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB35">
-        <v>26.584944174370388</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
       </c>
       <c r="AE35" t="s">
+        <v>425</v>
+      </c>
+      <c r="AF35" t="s">
         <v>426</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>427</v>
       </c>
       <c r="AG35" t="s">
         <v>10</v>
@@ -11354,13 +11351,13 @@
         <v>186</v>
       </c>
       <c r="AL35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AM35" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AN35" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AO35">
         <v>0.99869589057011365</v>
@@ -11372,10 +11369,10 @@
         <v>282</v>
       </c>
       <c r="AS35" t="s">
+        <v>544</v>
+      </c>
+      <c r="AT35" t="s">
         <v>545</v>
-      </c>
-      <c r="AT35" t="s">
-        <v>546</v>
       </c>
       <c r="AU35" t="s">
         <v>10</v>
@@ -11390,19 +11387,19 @@
         <v>186</v>
       </c>
       <c r="AZ35" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="BA35" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="BB35" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="BC35">
-        <v>0.99662747375050009</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD35">
-        <v>61.829647907498845</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11467,25 +11464,25 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="Z36" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AA36">
-        <v>0.99798824264234642</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB36">
-        <v>36.882218223648351</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
       </c>
       <c r="AE36" t="s">
+        <v>427</v>
+      </c>
+      <c r="AF36" t="s">
         <v>428</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>429</v>
       </c>
       <c r="AG36" t="s">
         <v>10</v>
@@ -11500,28 +11497,28 @@
         <v>186</v>
       </c>
       <c r="AL36" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AM36" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AN36" t="s">
-        <v>356</v>
+        <v>485</v>
       </c>
       <c r="AO36">
-        <v>0.99192535126433146</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP36">
-        <v>148.0352268205892</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
       </c>
       <c r="AS36" t="s">
+        <v>546</v>
+      </c>
+      <c r="AT36" t="s">
         <v>547</v>
-      </c>
-      <c r="AT36" t="s">
-        <v>548</v>
       </c>
       <c r="AU36" t="s">
         <v>10</v>
@@ -11536,19 +11533,19 @@
         <v>186</v>
       </c>
       <c r="AZ36" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="BA36" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="BB36" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="BC36">
-        <v>0.99637036284424008</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD36">
-        <v>66.543347855598327</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11613,25 +11610,25 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="Z37" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="AA37">
-        <v>0.9977500892185478</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB37">
-        <v>41.248364326622962</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
       </c>
       <c r="AE37" t="s">
+        <v>429</v>
+      </c>
+      <c r="AF37" t="s">
         <v>430</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>431</v>
       </c>
       <c r="AG37" t="s">
         <v>10</v>
@@ -11646,28 +11643,28 @@
         <v>186</v>
       </c>
       <c r="AL37" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM37" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AN37" t="s">
-        <v>367</v>
+        <v>487</v>
       </c>
       <c r="AO37">
-        <v>0.98092693557487454</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP37">
-        <v>349.67284779396647</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
       </c>
       <c r="AS37" t="s">
+        <v>548</v>
+      </c>
+      <c r="AT37" t="s">
         <v>549</v>
-      </c>
-      <c r="AT37" t="s">
-        <v>550</v>
       </c>
       <c r="AU37" t="s">
         <v>10</v>
@@ -11682,19 +11679,19 @@
         <v>186</v>
       </c>
       <c r="AZ37" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="BA37" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="BB37" t="s">
-        <v>370</v>
+        <v>625</v>
       </c>
       <c r="BC37">
-        <v>0.96140381292129873</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD37">
-        <v>707.59676310952364</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11759,25 +11756,25 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="Z38" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="AA38">
-        <v>0.98833720780868572</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB38">
-        <v>213.8178568407609</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
       </c>
       <c r="AE38" t="s">
+        <v>431</v>
+      </c>
+      <c r="AF38" t="s">
         <v>432</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>433</v>
       </c>
       <c r="AG38" t="s">
         <v>10</v>
@@ -11792,28 +11789,28 @@
         <v>186</v>
       </c>
       <c r="AL38" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AM38" t="s">
+        <v>488</v>
+      </c>
+      <c r="AN38" t="s">
         <v>489</v>
       </c>
-      <c r="AN38" t="s">
-        <v>490</v>
-      </c>
       <c r="AO38">
-        <v>0.99710631799330929</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP38">
-        <v>53.050836789329388</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
       </c>
       <c r="AS38" t="s">
+        <v>550</v>
+      </c>
+      <c r="AT38" t="s">
         <v>551</v>
-      </c>
-      <c r="AT38" t="s">
-        <v>552</v>
       </c>
       <c r="AU38" t="s">
         <v>10</v>
@@ -11828,19 +11825,19 @@
         <v>186</v>
       </c>
       <c r="AZ38" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="BA38" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="BB38" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="BC38">
-        <v>0.99490784156958001</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD38">
-        <v>93.356237891033686</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11908,22 +11905,22 @@
         <v>270</v>
       </c>
       <c r="Z39" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="AA39">
-        <v>0.96340341594909085</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB39">
-        <v>670.93737426666792</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD39" t="s">
         <v>282</v>
       </c>
       <c r="AE39" t="s">
+        <v>433</v>
+      </c>
+      <c r="AF39" t="s">
         <v>434</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>435</v>
       </c>
       <c r="AG39" t="s">
         <v>10</v>
@@ -11938,28 +11935,28 @@
         <v>186</v>
       </c>
       <c r="AL39" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AM39" t="s">
+        <v>490</v>
+      </c>
+      <c r="AN39" t="s">
         <v>491</v>
       </c>
-      <c r="AN39" t="s">
-        <v>492</v>
-      </c>
       <c r="AO39">
-        <v>0.99627181657233566</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP39">
-        <v>68.350029507179471</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
       </c>
       <c r="AS39" t="s">
+        <v>552</v>
+      </c>
+      <c r="AT39" t="s">
         <v>553</v>
-      </c>
-      <c r="AT39" t="s">
-        <v>554</v>
       </c>
       <c r="AU39" t="s">
         <v>10</v>
@@ -11974,19 +11971,19 @@
         <v>186</v>
       </c>
       <c r="AZ39" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BA39" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="BB39" t="s">
-        <v>360</v>
+        <v>629</v>
       </c>
       <c r="BC39">
-        <v>0.98593278553446861</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD39">
-        <v>257.89893186807615</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12051,25 +12048,25 @@
         <v>343</v>
       </c>
       <c r="Y40" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="Z40" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA40">
-        <v>0.99894650606645485</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB40">
-        <v>19.314055448326833</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD40" t="s">
         <v>282</v>
       </c>
       <c r="AE40" t="s">
+        <v>435</v>
+      </c>
+      <c r="AF40" t="s">
         <v>436</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>437</v>
       </c>
       <c r="AG40" t="s">
         <v>10</v>
@@ -12084,28 +12081,28 @@
         <v>186</v>
       </c>
       <c r="AL40" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AM40" t="s">
+        <v>492</v>
+      </c>
+      <c r="AN40" t="s">
         <v>493</v>
       </c>
-      <c r="AN40" t="s">
-        <v>494</v>
-      </c>
       <c r="AO40">
-        <v>0.99550555557680764</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP40">
-        <v>82.398147758527074</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
       </c>
       <c r="AS40" t="s">
+        <v>554</v>
+      </c>
+      <c r="AT40" t="s">
         <v>555</v>
-      </c>
-      <c r="AT40" t="s">
-        <v>556</v>
       </c>
       <c r="AU40" t="s">
         <v>10</v>
@@ -12120,19 +12117,19 @@
         <v>186</v>
       </c>
       <c r="AZ40" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BA40" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="BB40" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="BC40">
-        <v>0.99366677237144974</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD40">
-        <v>116.10917319008783</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12197,25 +12194,25 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA41">
-        <v>0.98179245618315802</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB41">
-        <v>333.80496997543548</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
       </c>
       <c r="AE41" t="s">
+        <v>437</v>
+      </c>
+      <c r="AF41" t="s">
         <v>438</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>439</v>
       </c>
       <c r="AG41" t="s">
         <v>10</v>
@@ -12230,28 +12227,28 @@
         <v>186</v>
       </c>
       <c r="AL41" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AM41" t="s">
+        <v>494</v>
+      </c>
+      <c r="AN41" t="s">
         <v>495</v>
       </c>
-      <c r="AN41" t="s">
-        <v>496</v>
-      </c>
       <c r="AO41">
-        <v>0.93896180472603763</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP41">
-        <v>1119.0335800226442</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
       </c>
       <c r="AS41" t="s">
+        <v>556</v>
+      </c>
+      <c r="AT41" t="s">
         <v>557</v>
-      </c>
-      <c r="AT41" t="s">
-        <v>558</v>
       </c>
       <c r="AU41" t="s">
         <v>10</v>
@@ -12266,19 +12263,19 @@
         <v>186</v>
       </c>
       <c r="AZ41" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="BA41" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="BB41" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="BC41">
-        <v>0.99623532634854861</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD41">
-        <v>69.01901694327529</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12286,10 +12283,10 @@
         <v>282</v>
       </c>
       <c r="AS42" t="s">
+        <v>558</v>
+      </c>
+      <c r="AT42" t="s">
         <v>559</v>
-      </c>
-      <c r="AT42" t="s">
-        <v>560</v>
       </c>
       <c r="AU42" t="s">
         <v>10</v>
@@ -12304,19 +12301,19 @@
         <v>186</v>
       </c>
       <c r="AZ42" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="BA42" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="BB42" t="s">
-        <v>468</v>
+        <v>635</v>
       </c>
       <c r="BC42">
-        <v>0.95726256957223688</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD42">
-        <v>783.51955784232393</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12324,10 +12321,10 @@
         <v>282</v>
       </c>
       <c r="AS43" t="s">
+        <v>560</v>
+      </c>
+      <c r="AT43" t="s">
         <v>561</v>
-      </c>
-      <c r="AT43" t="s">
-        <v>562</v>
       </c>
       <c r="AU43" t="s">
         <v>10</v>
@@ -12342,19 +12339,19 @@
         <v>186</v>
       </c>
       <c r="AZ43" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="BA43" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="BB43" t="s">
-        <v>367</v>
+        <v>637</v>
       </c>
       <c r="BC43">
-        <v>0.97446452706544517</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD43">
-        <v>468.15033713350488</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12362,10 +12359,10 @@
         <v>282</v>
       </c>
       <c r="AS44" t="s">
+        <v>562</v>
+      </c>
+      <c r="AT44" t="s">
         <v>563</v>
-      </c>
-      <c r="AT44" t="s">
-        <v>564</v>
       </c>
       <c r="AU44" t="s">
         <v>10</v>
@@ -12380,19 +12377,19 @@
         <v>186</v>
       </c>
       <c r="AZ44" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="BA44" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="BB44" t="s">
-        <v>370</v>
+        <v>639</v>
       </c>
       <c r="BC44">
-        <v>0.97591598065988894</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD44">
-        <v>441.54035456870389</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12400,10 +12397,10 @@
         <v>282</v>
       </c>
       <c r="AS45" t="s">
+        <v>564</v>
+      </c>
+      <c r="AT45" t="s">
         <v>565</v>
-      </c>
-      <c r="AT45" t="s">
-        <v>566</v>
       </c>
       <c r="AU45" t="s">
         <v>10</v>
@@ -12418,19 +12415,19 @@
         <v>186</v>
       </c>
       <c r="AZ45" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="BA45" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="BB45" t="s">
-        <v>642</v>
+        <v>356</v>
       </c>
       <c r="BC45">
-        <v>0.99412039195829205</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD45">
-        <v>107.79281409797902</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12438,10 +12435,10 @@
         <v>282</v>
       </c>
       <c r="AS46" t="s">
+        <v>566</v>
+      </c>
+      <c r="AT46" t="s">
         <v>567</v>
-      </c>
-      <c r="AT46" t="s">
-        <v>568</v>
       </c>
       <c r="AU46" t="s">
         <v>10</v>
@@ -12456,19 +12453,19 @@
         <v>186</v>
       </c>
       <c r="AZ46" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="BB46" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="BC46">
-        <v>0.98881218539944515</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD46">
-        <v>205.10993434350485</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12476,10 +12473,10 @@
         <v>282</v>
       </c>
       <c r="AS47" t="s">
+        <v>568</v>
+      </c>
+      <c r="AT47" t="s">
         <v>569</v>
-      </c>
-      <c r="AT47" t="s">
-        <v>570</v>
       </c>
       <c r="AU47" t="s">
         <v>10</v>
@@ -12494,19 +12491,19 @@
         <v>186</v>
       </c>
       <c r="AZ47" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="BA47" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="BB47" t="s">
-        <v>356</v>
+        <v>644</v>
       </c>
       <c r="BC47">
-        <v>0.98010989643158675</v>
+        <v>0.99017867813273497</v>
       </c>
       <c r="BD47">
-        <v>364.65189875424346</v>
+        <v>180.05756756652616</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12514,10 +12511,10 @@
         <v>282</v>
       </c>
       <c r="AS48" t="s">
+        <v>570</v>
+      </c>
+      <c r="AT48" t="s">
         <v>571</v>
-      </c>
-      <c r="AT48" t="s">
-        <v>572</v>
       </c>
       <c r="AU48" t="s">
         <v>10</v>
@@ -12532,19 +12529,19 @@
         <v>186</v>
       </c>
       <c r="AZ48" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BA48" t="s">
+        <v>645</v>
+      </c>
+      <c r="BB48" t="s">
         <v>646</v>
       </c>
-      <c r="BB48" t="s">
-        <v>647</v>
-      </c>
       <c r="BC48">
-        <v>0.99114508565756532</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD48">
-        <v>162.34009627796874</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12552,10 +12549,10 @@
         <v>282</v>
       </c>
       <c r="AS49" t="s">
+        <v>572</v>
+      </c>
+      <c r="AT49" t="s">
         <v>573</v>
-      </c>
-      <c r="AT49" t="s">
-        <v>574</v>
       </c>
       <c r="AU49" t="s">
         <v>10</v>
@@ -12570,19 +12567,19 @@
         <v>186</v>
       </c>
       <c r="AZ49" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BA49" t="s">
+        <v>647</v>
+      </c>
+      <c r="BB49" t="s">
         <v>648</v>
       </c>
-      <c r="BB49" t="s">
-        <v>649</v>
-      </c>
       <c r="BC49">
-        <v>0.99561586640696276</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD49">
-        <v>80.375782539015233</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12590,10 +12587,10 @@
         <v>282</v>
       </c>
       <c r="AS50" t="s">
+        <v>574</v>
+      </c>
+      <c r="AT50" t="s">
         <v>575</v>
-      </c>
-      <c r="AT50" t="s">
-        <v>576</v>
       </c>
       <c r="AU50" t="s">
         <v>10</v>
@@ -12608,19 +12605,19 @@
         <v>186</v>
       </c>
       <c r="AZ50" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="BA50" t="s">
+        <v>649</v>
+      </c>
+      <c r="BB50" t="s">
         <v>650</v>
       </c>
-      <c r="BB50" t="s">
-        <v>370</v>
-      </c>
       <c r="BC50">
-        <v>0.95957195194316591</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD50">
-        <v>741.18088104195795</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12628,10 +12625,10 @@
         <v>282</v>
       </c>
       <c r="AS51" t="s">
+        <v>576</v>
+      </c>
+      <c r="AT51" t="s">
         <v>577</v>
-      </c>
-      <c r="AT51" t="s">
-        <v>578</v>
       </c>
       <c r="AU51" t="s">
         <v>10</v>
@@ -12646,7 +12643,7 @@
         <v>186</v>
       </c>
       <c r="AZ51" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="BA51" t="s">
         <v>651</v>
@@ -12655,10 +12652,10 @@
         <v>652</v>
       </c>
       <c r="BC51">
-        <v>0.9973402418125219</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD51">
-        <v>48.762233437098502</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12666,10 +12663,10 @@
         <v>282</v>
       </c>
       <c r="AS52" t="s">
+        <v>578</v>
+      </c>
+      <c r="AT52" t="s">
         <v>579</v>
-      </c>
-      <c r="AT52" t="s">
-        <v>580</v>
       </c>
       <c r="AU52" t="s">
         <v>10</v>
@@ -12684,19 +12681,19 @@
         <v>186</v>
       </c>
       <c r="AZ52" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="BA52" t="s">
         <v>653</v>
       </c>
       <c r="BB52" t="s">
-        <v>590</v>
+        <v>654</v>
       </c>
       <c r="BC52">
-        <v>0.99547930517021377</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD52">
-        <v>82.879405212747869</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12704,10 +12701,10 @@
         <v>282</v>
       </c>
       <c r="AS53" t="s">
+        <v>580</v>
+      </c>
+      <c r="AT53" t="s">
         <v>581</v>
-      </c>
-      <c r="AT53" t="s">
-        <v>582</v>
       </c>
       <c r="AU53" t="s">
         <v>10</v>
@@ -12722,19 +12719,19 @@
         <v>186</v>
       </c>
       <c r="AZ53" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="BA53" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="BB53" t="s">
-        <v>655</v>
+        <v>370</v>
       </c>
       <c r="BC53">
-        <v>0.88199812838352587</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD53">
-        <v>2163.367646302027</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12742,10 +12739,10 @@
         <v>282</v>
       </c>
       <c r="AS54" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT54" t="s">
         <v>583</v>
-      </c>
-      <c r="AT54" t="s">
-        <v>584</v>
       </c>
       <c r="AU54" t="s">
         <v>10</v>
@@ -12760,19 +12757,19 @@
         <v>186</v>
       </c>
       <c r="AZ54" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="BA54" t="s">
         <v>656</v>
       </c>
       <c r="BB54" t="s">
-        <v>657</v>
+        <v>353</v>
       </c>
       <c r="BC54">
-        <v>0.99015836110796274</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD54">
-        <v>180.43004635401576</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
   </sheetData>
@@ -12781,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1985ECDF-BF1E-4332-B95C-3482EFA68CDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EC2A48-DF6B-4F64-8BA8-D2C460BD53E0}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12872,10 +12869,10 @@
         <v>182</v>
       </c>
       <c r="C11" t="s">
+        <v>657</v>
+      </c>
+      <c r="D11" t="s">
         <v>658</v>
-      </c>
-      <c r="D11" t="s">
-        <v>659</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -12890,10 +12887,10 @@
         <v>186</v>
       </c>
       <c r="J11" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12905,10 +12902,10 @@
         <v>182</v>
       </c>
       <c r="P11" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q11" t="s">
         <v>720</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>721</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -12923,10 +12920,10 @@
         <v>186</v>
       </c>
       <c r="W11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12940,10 +12937,10 @@
         <v>182</v>
       </c>
       <c r="C12" t="s">
+        <v>659</v>
+      </c>
+      <c r="D12" t="s">
         <v>660</v>
-      </c>
-      <c r="D12" t="s">
-        <v>661</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -12958,10 +12955,10 @@
         <v>186</v>
       </c>
       <c r="J12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12973,10 +12970,10 @@
         <v>182</v>
       </c>
       <c r="P12" t="s">
+        <v>721</v>
+      </c>
+      <c r="Q12" t="s">
         <v>722</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>723</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -12991,10 +12988,10 @@
         <v>186</v>
       </c>
       <c r="W12" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13008,10 +13005,10 @@
         <v>182</v>
       </c>
       <c r="C13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D13" t="s">
         <v>662</v>
-      </c>
-      <c r="D13" t="s">
-        <v>663</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -13026,10 +13023,10 @@
         <v>186</v>
       </c>
       <c r="J13" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13041,10 +13038,10 @@
         <v>182</v>
       </c>
       <c r="P13" t="s">
+        <v>723</v>
+      </c>
+      <c r="Q13" t="s">
         <v>724</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>725</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -13059,10 +13056,10 @@
         <v>186</v>
       </c>
       <c r="W13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13076,10 +13073,10 @@
         <v>182</v>
       </c>
       <c r="C14" t="s">
+        <v>663</v>
+      </c>
+      <c r="D14" t="s">
         <v>664</v>
-      </c>
-      <c r="D14" t="s">
-        <v>665</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -13094,10 +13091,10 @@
         <v>186</v>
       </c>
       <c r="J14" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13109,10 +13106,10 @@
         <v>182</v>
       </c>
       <c r="P14" t="s">
+        <v>725</v>
+      </c>
+      <c r="Q14" t="s">
         <v>726</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>727</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -13127,10 +13124,10 @@
         <v>186</v>
       </c>
       <c r="W14" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>640</v>
+        <v>599</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13144,10 +13141,10 @@
         <v>182</v>
       </c>
       <c r="C15" t="s">
+        <v>665</v>
+      </c>
+      <c r="D15" t="s">
         <v>666</v>
-      </c>
-      <c r="D15" t="s">
-        <v>667</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -13162,10 +13159,10 @@
         <v>186</v>
       </c>
       <c r="J15" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13177,10 +13174,10 @@
         <v>182</v>
       </c>
       <c r="P15" t="s">
+        <v>727</v>
+      </c>
+      <c r="Q15" t="s">
         <v>728</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>729</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -13195,10 +13192,10 @@
         <v>186</v>
       </c>
       <c r="W15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>638</v>
+        <v>584</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13212,10 +13209,10 @@
         <v>182</v>
       </c>
       <c r="C16" t="s">
+        <v>667</v>
+      </c>
+      <c r="D16" t="s">
         <v>668</v>
-      </c>
-      <c r="D16" t="s">
-        <v>669</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -13230,10 +13227,10 @@
         <v>186</v>
       </c>
       <c r="J16" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13245,10 +13242,10 @@
         <v>182</v>
       </c>
       <c r="P16" t="s">
+        <v>729</v>
+      </c>
+      <c r="Q16" t="s">
         <v>730</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>731</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -13263,10 +13260,10 @@
         <v>186</v>
       </c>
       <c r="W16" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="X16" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13280,10 +13277,10 @@
         <v>182</v>
       </c>
       <c r="C17" t="s">
+        <v>669</v>
+      </c>
+      <c r="D17" t="s">
         <v>670</v>
-      </c>
-      <c r="D17" t="s">
-        <v>671</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -13298,10 +13295,10 @@
         <v>186</v>
       </c>
       <c r="J17" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13313,10 +13310,10 @@
         <v>182</v>
       </c>
       <c r="P17" t="s">
+        <v>731</v>
+      </c>
+      <c r="Q17" t="s">
         <v>732</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>733</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -13331,10 +13328,10 @@
         <v>186</v>
       </c>
       <c r="W17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>630</v>
+        <v>598</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13348,10 +13345,10 @@
         <v>182</v>
       </c>
       <c r="C18" t="s">
+        <v>671</v>
+      </c>
+      <c r="D18" t="s">
         <v>672</v>
-      </c>
-      <c r="D18" t="s">
-        <v>673</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -13366,10 +13363,10 @@
         <v>186</v>
       </c>
       <c r="J18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13381,10 +13378,10 @@
         <v>182</v>
       </c>
       <c r="P18" t="s">
+        <v>733</v>
+      </c>
+      <c r="Q18" t="s">
         <v>734</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>735</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -13399,16 +13396,16 @@
         <v>186</v>
       </c>
       <c r="W18" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>626</v>
+        <v>594</v>
       </c>
       <c r="Y18">
-        <v>28.478249999999999</v>
+        <v>22.079249999999998</v>
       </c>
       <c r="Z18">
-        <v>0.31013048721759129</v>
+        <v>0.3223061905611202</v>
       </c>
     </row>
     <row r="19" spans="2:26">
@@ -13416,10 +13413,10 @@
         <v>182</v>
       </c>
       <c r="C19" t="s">
+        <v>673</v>
+      </c>
+      <c r="D19" t="s">
         <v>674</v>
-      </c>
-      <c r="D19" t="s">
-        <v>675</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -13434,10 +13431,10 @@
         <v>186</v>
       </c>
       <c r="J19" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13449,10 +13446,10 @@
         <v>182</v>
       </c>
       <c r="P19" t="s">
+        <v>735</v>
+      </c>
+      <c r="Q19" t="s">
         <v>736</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>737</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -13467,16 +13464,16 @@
         <v>186</v>
       </c>
       <c r="W19" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="Y19">
-        <v>22.079249999999998</v>
+        <v>29.961749999999999</v>
       </c>
       <c r="Z19">
-        <v>0.3223061905611202</v>
+        <v>0.33421489525964382</v>
       </c>
     </row>
     <row r="20" spans="2:26">
@@ -13484,10 +13481,10 @@
         <v>182</v>
       </c>
       <c r="C20" t="s">
+        <v>675</v>
+      </c>
+      <c r="D20" t="s">
         <v>676</v>
-      </c>
-      <c r="D20" t="s">
-        <v>677</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -13502,10 +13499,10 @@
         <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13517,10 +13514,10 @@
         <v>182</v>
       </c>
       <c r="P20" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q20" t="s">
         <v>738</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>739</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -13535,16 +13532,16 @@
         <v>186</v>
       </c>
       <c r="W20" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="X20" t="s">
         <v>634</v>
       </c>
       <c r="Y20">
-        <v>29.961749999999999</v>
+        <v>28.478249999999999</v>
       </c>
       <c r="Z20">
-        <v>0.33421489525964382</v>
+        <v>0.31013048721759129</v>
       </c>
     </row>
     <row r="21" spans="2:26">
@@ -13552,10 +13549,10 @@
         <v>182</v>
       </c>
       <c r="C21" t="s">
+        <v>677</v>
+      </c>
+      <c r="D21" t="s">
         <v>678</v>
-      </c>
-      <c r="D21" t="s">
-        <v>679</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -13570,10 +13567,10 @@
         <v>186</v>
       </c>
       <c r="J21" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13585,10 +13582,10 @@
         <v>182</v>
       </c>
       <c r="P21" t="s">
+        <v>739</v>
+      </c>
+      <c r="Q21" t="s">
         <v>740</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>741</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -13603,10 +13600,10 @@
         <v>186</v>
       </c>
       <c r="W21" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13620,10 +13617,10 @@
         <v>182</v>
       </c>
       <c r="C22" t="s">
+        <v>679</v>
+      </c>
+      <c r="D22" t="s">
         <v>680</v>
-      </c>
-      <c r="D22" t="s">
-        <v>681</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -13638,10 +13635,10 @@
         <v>186</v>
       </c>
       <c r="J22" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13653,10 +13650,10 @@
         <v>182</v>
       </c>
       <c r="P22" t="s">
+        <v>741</v>
+      </c>
+      <c r="Q22" t="s">
         <v>742</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>743</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -13671,10 +13668,10 @@
         <v>186</v>
       </c>
       <c r="W22" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13688,10 +13685,10 @@
         <v>182</v>
       </c>
       <c r="C23" t="s">
+        <v>681</v>
+      </c>
+      <c r="D23" t="s">
         <v>682</v>
-      </c>
-      <c r="D23" t="s">
-        <v>683</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -13706,10 +13703,10 @@
         <v>186</v>
       </c>
       <c r="J23" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13721,10 +13718,10 @@
         <v>182</v>
       </c>
       <c r="P23" t="s">
+        <v>743</v>
+      </c>
+      <c r="Q23" t="s">
         <v>744</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>745</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -13739,10 +13736,10 @@
         <v>186</v>
       </c>
       <c r="W23" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>651</v>
+        <v>604</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13756,10 +13753,10 @@
         <v>182</v>
       </c>
       <c r="C24" t="s">
+        <v>683</v>
+      </c>
+      <c r="D24" t="s">
         <v>684</v>
-      </c>
-      <c r="D24" t="s">
-        <v>685</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -13774,10 +13771,10 @@
         <v>186</v>
       </c>
       <c r="J24" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13789,10 +13786,10 @@
         <v>182</v>
       </c>
       <c r="P24" t="s">
+        <v>745</v>
+      </c>
+      <c r="Q24" t="s">
         <v>746</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>747</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -13807,10 +13804,10 @@
         <v>186</v>
       </c>
       <c r="W24" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13824,10 +13821,10 @@
         <v>182</v>
       </c>
       <c r="C25" t="s">
+        <v>685</v>
+      </c>
+      <c r="D25" t="s">
         <v>686</v>
-      </c>
-      <c r="D25" t="s">
-        <v>687</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -13842,10 +13839,10 @@
         <v>186</v>
       </c>
       <c r="J25" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13857,10 +13854,10 @@
         <v>182</v>
       </c>
       <c r="P25" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q25" t="s">
         <v>748</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>749</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -13875,16 +13872,16 @@
         <v>186</v>
       </c>
       <c r="W25" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>593</v>
+        <v>653</v>
       </c>
       <c r="Y25">
-        <v>63.731250000000003</v>
+        <v>22.785</v>
       </c>
       <c r="Z25">
-        <v>0.4483325413452795</v>
+        <v>0.35144265618738502</v>
       </c>
     </row>
     <row r="26" spans="2:26">
@@ -13892,10 +13889,10 @@
         <v>182</v>
       </c>
       <c r="C26" t="s">
+        <v>687</v>
+      </c>
+      <c r="D26" t="s">
         <v>688</v>
-      </c>
-      <c r="D26" t="s">
-        <v>689</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -13910,10 +13907,10 @@
         <v>186</v>
       </c>
       <c r="J26" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13925,10 +13922,10 @@
         <v>182</v>
       </c>
       <c r="P26" t="s">
+        <v>749</v>
+      </c>
+      <c r="Q26" t="s">
         <v>750</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>751</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -13943,16 +13940,16 @@
         <v>186</v>
       </c>
       <c r="W26" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="X26" t="s">
-        <v>603</v>
+        <v>645</v>
       </c>
       <c r="Y26">
-        <v>28.239750000000001</v>
+        <v>63.731250000000003</v>
       </c>
       <c r="Z26">
-        <v>0.39283819950969068</v>
+        <v>0.4483325413452795</v>
       </c>
     </row>
     <row r="27" spans="2:26">
@@ -13960,10 +13957,10 @@
         <v>182</v>
       </c>
       <c r="C27" t="s">
+        <v>689</v>
+      </c>
+      <c r="D27" t="s">
         <v>690</v>
-      </c>
-      <c r="D27" t="s">
-        <v>691</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -13978,10 +13975,10 @@
         <v>186</v>
       </c>
       <c r="J27" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -13993,10 +13990,10 @@
         <v>182</v>
       </c>
       <c r="P27" t="s">
+        <v>751</v>
+      </c>
+      <c r="Q27" t="s">
         <v>752</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>753</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -14011,16 +14008,16 @@
         <v>186</v>
       </c>
       <c r="W27" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="Y27">
-        <v>51.107250000000001</v>
+        <v>28.239750000000001</v>
       </c>
       <c r="Z27">
-        <v>0.43212901833706618</v>
+        <v>0.39283819950969068</v>
       </c>
     </row>
     <row r="28" spans="2:26">
@@ -14028,10 +14025,10 @@
         <v>182</v>
       </c>
       <c r="C28" t="s">
+        <v>691</v>
+      </c>
+      <c r="D28" t="s">
         <v>692</v>
-      </c>
-      <c r="D28" t="s">
-        <v>693</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -14046,10 +14043,10 @@
         <v>186</v>
       </c>
       <c r="J28" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14061,10 +14058,10 @@
         <v>182</v>
       </c>
       <c r="P28" t="s">
+        <v>753</v>
+      </c>
+      <c r="Q28" t="s">
         <v>754</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>755</v>
       </c>
       <c r="R28" t="s">
         <v>10</v>
@@ -14079,16 +14076,16 @@
         <v>186</v>
       </c>
       <c r="W28" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>589</v>
+        <v>655</v>
       </c>
       <c r="Y28">
-        <v>64.533749999999998</v>
+        <v>38.15925</v>
       </c>
       <c r="Z28">
-        <v>0.49947203939427631</v>
+        <v>0.42518909184060127</v>
       </c>
     </row>
     <row r="29" spans="2:26">
@@ -14096,10 +14093,10 @@
         <v>182</v>
       </c>
       <c r="C29" t="s">
+        <v>693</v>
+      </c>
+      <c r="D29" t="s">
         <v>694</v>
-      </c>
-      <c r="D29" t="s">
-        <v>695</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -14114,10 +14111,10 @@
         <v>186</v>
       </c>
       <c r="J29" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14129,10 +14126,10 @@
         <v>182</v>
       </c>
       <c r="P29" t="s">
+        <v>755</v>
+      </c>
+      <c r="Q29" t="s">
         <v>756</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>757</v>
       </c>
       <c r="R29" t="s">
         <v>10</v>
@@ -14147,16 +14144,16 @@
         <v>186</v>
       </c>
       <c r="W29" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>653</v>
+        <v>597</v>
       </c>
       <c r="Y29">
-        <v>38.451000000000001</v>
+        <v>3.38625</v>
       </c>
       <c r="Z29">
-        <v>0.41699608360155571</v>
+        <v>0.27397097122901398</v>
       </c>
     </row>
     <row r="30" spans="2:26">
@@ -14164,10 +14161,10 @@
         <v>182</v>
       </c>
       <c r="C30" t="s">
+        <v>695</v>
+      </c>
+      <c r="D30" t="s">
         <v>696</v>
-      </c>
-      <c r="D30" t="s">
-        <v>697</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -14182,10 +14179,10 @@
         <v>186</v>
       </c>
       <c r="J30" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14197,10 +14194,10 @@
         <v>182</v>
       </c>
       <c r="P30" t="s">
+        <v>757</v>
+      </c>
+      <c r="Q30" t="s">
         <v>758</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>759</v>
       </c>
       <c r="R30" t="s">
         <v>10</v>
@@ -14215,16 +14212,16 @@
         <v>186</v>
       </c>
       <c r="W30" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="Y30">
-        <v>54.854999999999997</v>
+        <v>30.597750000000001</v>
       </c>
       <c r="Z30">
-        <v>0.43384073815375263</v>
+        <v>0.45321604354945533</v>
       </c>
     </row>
     <row r="31" spans="2:26">
@@ -14232,10 +14229,10 @@
         <v>182</v>
       </c>
       <c r="C31" t="s">
+        <v>697</v>
+      </c>
+      <c r="D31" t="s">
         <v>698</v>
-      </c>
-      <c r="D31" t="s">
-        <v>699</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -14250,10 +14247,10 @@
         <v>186</v>
       </c>
       <c r="J31" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14265,10 +14262,10 @@
         <v>182</v>
       </c>
       <c r="P31" t="s">
+        <v>759</v>
+      </c>
+      <c r="Q31" t="s">
         <v>760</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>761</v>
       </c>
       <c r="R31" t="s">
         <v>10</v>
@@ -14283,16 +14280,16 @@
         <v>186</v>
       </c>
       <c r="W31" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="Y31">
-        <v>1.9132499999999999</v>
+        <v>98.024249999999995</v>
       </c>
       <c r="Z31">
-        <v>0.24373705543466159</v>
+        <v>0.48508660660688818</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -14300,10 +14297,10 @@
         <v>182</v>
       </c>
       <c r="C32" t="s">
+        <v>699</v>
+      </c>
+      <c r="D32" t="s">
         <v>700</v>
-      </c>
-      <c r="D32" t="s">
-        <v>701</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -14318,10 +14315,10 @@
         <v>186</v>
       </c>
       <c r="J32" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14333,10 +14330,10 @@
         <v>182</v>
       </c>
       <c r="P32" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q32" t="s">
         <v>762</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>763</v>
       </c>
       <c r="R32" t="s">
         <v>10</v>
@@ -14351,16 +14348,16 @@
         <v>186</v>
       </c>
       <c r="W32" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="Y32">
-        <v>26.042999999999999</v>
+        <v>28.459499999999998</v>
       </c>
       <c r="Z32">
-        <v>0.41233337771784651</v>
+        <v>0.46298928100882142</v>
       </c>
     </row>
     <row r="33" spans="2:26">
@@ -14368,10 +14365,10 @@
         <v>182</v>
       </c>
       <c r="C33" t="s">
+        <v>701</v>
+      </c>
+      <c r="D33" t="s">
         <v>702</v>
-      </c>
-      <c r="D33" t="s">
-        <v>703</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -14386,10 +14383,10 @@
         <v>186</v>
       </c>
       <c r="J33" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14401,10 +14398,10 @@
         <v>182</v>
       </c>
       <c r="P33" t="s">
+        <v>763</v>
+      </c>
+      <c r="Q33" t="s">
         <v>764</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>765</v>
       </c>
       <c r="R33" t="s">
         <v>10</v>
@@ -14419,16 +14416,16 @@
         <v>186</v>
       </c>
       <c r="W33" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>595</v>
+        <v>656</v>
       </c>
       <c r="Y33">
-        <v>3.38625</v>
+        <v>33.609749999999998</v>
       </c>
       <c r="Z33">
-        <v>0.27397097122901398</v>
+        <v>0.397480074831774</v>
       </c>
     </row>
     <row r="34" spans="2:26">
@@ -14436,10 +14433,10 @@
         <v>182</v>
       </c>
       <c r="C34" t="s">
+        <v>703</v>
+      </c>
+      <c r="D34" t="s">
         <v>704</v>
-      </c>
-      <c r="D34" t="s">
-        <v>705</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -14454,10 +14451,10 @@
         <v>186</v>
       </c>
       <c r="J34" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14469,10 +14466,10 @@
         <v>182</v>
       </c>
       <c r="P34" t="s">
+        <v>765</v>
+      </c>
+      <c r="Q34" t="s">
         <v>766</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>767</v>
       </c>
       <c r="R34" t="s">
         <v>10</v>
@@ -14487,16 +14484,16 @@
         <v>186</v>
       </c>
       <c r="W34" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="Y34">
-        <v>14.732250000000001</v>
+        <v>58.474499999999999</v>
       </c>
       <c r="Z34">
-        <v>0.46368351625347409</v>
+        <v>0.3742804525886429</v>
       </c>
     </row>
     <row r="35" spans="2:26">
@@ -14504,10 +14501,10 @@
         <v>182</v>
       </c>
       <c r="C35" t="s">
+        <v>705</v>
+      </c>
+      <c r="D35" t="s">
         <v>706</v>
-      </c>
-      <c r="D35" t="s">
-        <v>707</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -14522,25 +14519,25 @@
         <v>186</v>
       </c>
       <c r="J35" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="L35">
-        <v>44.894334115294185</v>
+        <v>48.700042766740395</v>
       </c>
       <c r="M35">
-        <v>0.26214900595896268</v>
+        <v>0.2724790418004075</v>
       </c>
       <c r="O35" t="s">
         <v>182</v>
       </c>
       <c r="P35" t="s">
+        <v>767</v>
+      </c>
+      <c r="Q35" t="s">
         <v>768</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>769</v>
       </c>
       <c r="R35" t="s">
         <v>10</v>
@@ -14555,16 +14552,16 @@
         <v>186</v>
       </c>
       <c r="W35" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>656</v>
+        <v>613</v>
       </c>
       <c r="Y35">
-        <v>58.474499999999999</v>
+        <v>18.711749999999999</v>
       </c>
       <c r="Z35">
-        <v>0.3742804525886429</v>
+        <v>0.2850753309410175</v>
       </c>
     </row>
     <row r="36" spans="2:26">
@@ -14572,10 +14569,10 @@
         <v>182</v>
       </c>
       <c r="C36" t="s">
+        <v>707</v>
+      </c>
+      <c r="D36" t="s">
         <v>708</v>
-      </c>
-      <c r="D36" t="s">
-        <v>709</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -14590,25 +14587,25 @@
         <v>186</v>
       </c>
       <c r="J36" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>491</v>
+        <v>443</v>
       </c>
       <c r="L36">
-        <v>14.358494358107757</v>
+        <v>10.552785706661558</v>
       </c>
       <c r="M36">
-        <v>0.48737624583080358</v>
+        <v>0.520929098878674</v>
       </c>
       <c r="O36" t="s">
         <v>182</v>
       </c>
       <c r="P36" t="s">
+        <v>769</v>
+      </c>
+      <c r="Q36" t="s">
         <v>770</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>771</v>
       </c>
       <c r="R36" t="s">
         <v>10</v>
@@ -14623,16 +14620,16 @@
         <v>186</v>
       </c>
       <c r="W36" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>648</v>
+        <v>590</v>
       </c>
       <c r="Y36">
-        <v>18.711749999999999</v>
+        <v>29.186250000000001</v>
       </c>
       <c r="Z36">
-        <v>0.2850753309410175</v>
+        <v>0.35239758613659811</v>
       </c>
     </row>
     <row r="37" spans="2:26">
@@ -14640,10 +14637,10 @@
         <v>182</v>
       </c>
       <c r="C37" t="s">
+        <v>709</v>
+      </c>
+      <c r="D37" t="s">
         <v>710</v>
-      </c>
-      <c r="D37" t="s">
-        <v>711</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -14658,10 +14655,10 @@
         <v>186</v>
       </c>
       <c r="J37" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14673,10 +14670,10 @@
         <v>182</v>
       </c>
       <c r="P37" t="s">
+        <v>771</v>
+      </c>
+      <c r="Q37" t="s">
         <v>772</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>773</v>
       </c>
       <c r="R37" t="s">
         <v>10</v>
@@ -14691,16 +14688,16 @@
         <v>186</v>
       </c>
       <c r="W37" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="Y37">
-        <v>29.186250000000001</v>
+        <v>14.49</v>
       </c>
       <c r="Z37">
-        <v>0.35239758613659811</v>
+        <v>0.4104874743436856</v>
       </c>
     </row>
     <row r="38" spans="2:26">
@@ -14708,10 +14705,10 @@
         <v>182</v>
       </c>
       <c r="C38" t="s">
+        <v>711</v>
+      </c>
+      <c r="D38" t="s">
         <v>712</v>
-      </c>
-      <c r="D38" t="s">
-        <v>713</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -14726,10 +14723,10 @@
         <v>186</v>
       </c>
       <c r="J38" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>487</v>
+        <v>445</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14741,10 +14738,10 @@
         <v>182</v>
       </c>
       <c r="P38" t="s">
+        <v>773</v>
+      </c>
+      <c r="Q38" t="s">
         <v>774</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>775</v>
       </c>
       <c r="R38" t="s">
         <v>10</v>
@@ -14759,16 +14756,16 @@
         <v>186</v>
       </c>
       <c r="W38" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>646</v>
+        <v>592</v>
       </c>
       <c r="Y38">
-        <v>14.49</v>
+        <v>64.437749999999994</v>
       </c>
       <c r="Z38">
-        <v>0.4104874743436856</v>
+        <v>0.4224374651715968</v>
       </c>
     </row>
     <row r="39" spans="2:26">
@@ -14776,10 +14773,10 @@
         <v>182</v>
       </c>
       <c r="C39" t="s">
+        <v>713</v>
+      </c>
+      <c r="D39" t="s">
         <v>714</v>
-      </c>
-      <c r="D39" t="s">
-        <v>715</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -14794,10 +14791,10 @@
         <v>186</v>
       </c>
       <c r="J39" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14809,10 +14806,10 @@
         <v>182</v>
       </c>
       <c r="P39" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q39" t="s">
         <v>776</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>777</v>
       </c>
       <c r="R39" t="s">
         <v>10</v>
@@ -14827,16 +14824,16 @@
         <v>186</v>
       </c>
       <c r="W39" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>607</v>
+        <v>647</v>
       </c>
       <c r="Y39">
-        <v>64.437749999999994</v>
+        <v>59.085000000000001</v>
       </c>
       <c r="Z39">
-        <v>0.4224374651715968</v>
+        <v>0.3909895628623698</v>
       </c>
     </row>
     <row r="40" spans="2:26">
@@ -14844,10 +14841,10 @@
         <v>182</v>
       </c>
       <c r="C40" t="s">
+        <v>715</v>
+      </c>
+      <c r="D40" t="s">
         <v>716</v>
-      </c>
-      <c r="D40" t="s">
-        <v>717</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -14862,10 +14859,10 @@
         <v>186</v>
       </c>
       <c r="J40" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14877,10 +14874,10 @@
         <v>182</v>
       </c>
       <c r="P40" t="s">
+        <v>777</v>
+      </c>
+      <c r="Q40" t="s">
         <v>778</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>779</v>
       </c>
       <c r="R40" t="s">
         <v>10</v>
@@ -14895,16 +14892,16 @@
         <v>186</v>
       </c>
       <c r="W40" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="Y40">
-        <v>59.085000000000001</v>
+        <v>37.460250000000002</v>
       </c>
       <c r="Z40">
-        <v>0.3909895628623698</v>
+        <v>0.4156656148053956</v>
       </c>
     </row>
     <row r="41" spans="2:26">
@@ -14912,10 +14909,10 @@
         <v>182</v>
       </c>
       <c r="C41" t="s">
+        <v>717</v>
+      </c>
+      <c r="D41" t="s">
         <v>718</v>
-      </c>
-      <c r="D41" t="s">
-        <v>719</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -14930,10 +14927,10 @@
         <v>186</v>
       </c>
       <c r="J41" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>488</v>
+        <v>446</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14945,10 +14942,10 @@
         <v>182</v>
       </c>
       <c r="P41" t="s">
+        <v>779</v>
+      </c>
+      <c r="Q41" t="s">
         <v>780</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>781</v>
       </c>
       <c r="R41" t="s">
         <v>10</v>
@@ -14963,16 +14960,16 @@
         <v>186</v>
       </c>
       <c r="W41" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="X41" t="s">
-        <v>585</v>
+        <v>641</v>
       </c>
       <c r="Y41">
-        <v>37.460250000000002</v>
+        <v>27.642749999999999</v>
       </c>
       <c r="Z41">
-        <v>0.4156656148053956</v>
+        <v>0.36206437671723612</v>
       </c>
     </row>
     <row r="42" spans="2:26">
@@ -14980,10 +14977,10 @@
         <v>182</v>
       </c>
       <c r="P42" t="s">
+        <v>781</v>
+      </c>
+      <c r="Q42" t="s">
         <v>782</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>783</v>
       </c>
       <c r="R42" t="s">
         <v>10</v>
@@ -14998,16 +14995,16 @@
         <v>186</v>
       </c>
       <c r="W42" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="Y42">
-        <v>27.642749999999999</v>
+        <v>62.597250000000003</v>
       </c>
       <c r="Z42">
-        <v>0.36206437671723612</v>
+        <v>0.36639621425278329</v>
       </c>
     </row>
     <row r="43" spans="2:26">
@@ -15015,10 +15012,10 @@
         <v>182</v>
       </c>
       <c r="P43" t="s">
+        <v>783</v>
+      </c>
+      <c r="Q43" t="s">
         <v>784</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>785</v>
       </c>
       <c r="R43" t="s">
         <v>10</v>
@@ -15033,16 +15030,16 @@
         <v>186</v>
       </c>
       <c r="W43" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>641</v>
+        <v>585</v>
       </c>
       <c r="Y43">
-        <v>62.597250000000003</v>
+        <v>17.07525</v>
       </c>
       <c r="Z43">
-        <v>0.36639621425278329</v>
+        <v>0.366335622458484</v>
       </c>
     </row>
     <row r="44" spans="2:26">
@@ -15050,10 +15047,10 @@
         <v>182</v>
       </c>
       <c r="P44" t="s">
+        <v>785</v>
+      </c>
+      <c r="Q44" t="s">
         <v>786</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>787</v>
       </c>
       <c r="R44" t="s">
         <v>10</v>
@@ -15068,16 +15065,16 @@
         <v>186</v>
       </c>
       <c r="W44" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="Y44">
-        <v>17.07525</v>
+        <v>0.42149999999999999</v>
       </c>
       <c r="Z44">
-        <v>0.366335622458484</v>
+        <v>0.28906735909449488</v>
       </c>
     </row>
     <row r="45" spans="2:26">
@@ -15085,10 +15082,10 @@
         <v>182</v>
       </c>
       <c r="P45" t="s">
+        <v>787</v>
+      </c>
+      <c r="Q45" t="s">
         <v>788</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>789</v>
       </c>
       <c r="R45" t="s">
         <v>10</v>
@@ -15103,16 +15100,16 @@
         <v>186</v>
       </c>
       <c r="W45" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>654</v>
+        <v>623</v>
       </c>
       <c r="Y45">
-        <v>0.42149999999999999</v>
+        <v>5.7389999999999999</v>
       </c>
       <c r="Z45">
-        <v>0.28906735909449488</v>
+        <v>0.33165266509529728</v>
       </c>
     </row>
     <row r="46" spans="2:26">
@@ -15120,10 +15117,10 @@
         <v>182</v>
       </c>
       <c r="P46" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q46" t="s">
         <v>790</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>791</v>
       </c>
       <c r="R46" t="s">
         <v>10</v>
@@ -15138,16 +15135,16 @@
         <v>186</v>
       </c>
       <c r="W46" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="Y46">
-        <v>5.7389999999999999</v>
+        <v>1.81725</v>
       </c>
       <c r="Z46">
-        <v>0.33165266509529728</v>
+        <v>0.3242980885897736</v>
       </c>
     </row>
     <row r="47" spans="2:26">
@@ -15155,10 +15152,10 @@
         <v>182</v>
       </c>
       <c r="P47" t="s">
+        <v>791</v>
+      </c>
+      <c r="Q47" t="s">
         <v>792</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>793</v>
       </c>
       <c r="R47" t="s">
         <v>10</v>
@@ -15173,16 +15170,16 @@
         <v>186</v>
       </c>
       <c r="W47" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="Y47">
-        <v>1.81725</v>
+        <v>15.998250000000001</v>
       </c>
       <c r="Z47">
-        <v>0.3242980885897736</v>
+        <v>0.54144035774355337</v>
       </c>
     </row>
     <row r="48" spans="2:26">
@@ -15190,10 +15187,10 @@
         <v>182</v>
       </c>
       <c r="P48" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q48" t="s">
         <v>794</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>795</v>
       </c>
       <c r="R48" t="s">
         <v>10</v>
@@ -15208,16 +15205,16 @@
         <v>186</v>
       </c>
       <c r="W48" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="Y48">
-        <v>10.709250000000001</v>
+        <v>6.5272500000000004</v>
       </c>
       <c r="Z48">
-        <v>0.50948065857827751</v>
+        <v>0.49660100952715858</v>
       </c>
     </row>
     <row r="49" spans="15:26">
@@ -15225,10 +15222,10 @@
         <v>182</v>
       </c>
       <c r="P49" t="s">
+        <v>795</v>
+      </c>
+      <c r="Q49" t="s">
         <v>796</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>797</v>
       </c>
       <c r="R49" t="s">
         <v>10</v>
@@ -15243,16 +15240,16 @@
         <v>186</v>
       </c>
       <c r="W49" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="X49" t="s">
-        <v>587</v>
+        <v>643</v>
       </c>
       <c r="Y49">
-        <v>16.497</v>
+        <v>42.144750000000002</v>
       </c>
       <c r="Z49">
-        <v>0.45133214213550138</v>
+        <v>0.52506501598903088</v>
       </c>
     </row>
     <row r="50" spans="15:26">
@@ -15260,10 +15257,10 @@
         <v>182</v>
       </c>
       <c r="P50" t="s">
+        <v>797</v>
+      </c>
+      <c r="Q50" t="s">
         <v>798</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>799</v>
       </c>
       <c r="R50" t="s">
         <v>10</v>
@@ -15278,16 +15275,16 @@
         <v>186</v>
       </c>
       <c r="W50" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>643</v>
+        <v>586</v>
       </c>
       <c r="Y50">
-        <v>53.960999999999999</v>
+        <v>16.497</v>
       </c>
       <c r="Z50">
-        <v>0.52956978618689865</v>
+        <v>0.45133214213550138</v>
       </c>
     </row>
     <row r="51" spans="15:26">
@@ -15295,10 +15292,10 @@
         <v>182</v>
       </c>
       <c r="P51" t="s">
+        <v>799</v>
+      </c>
+      <c r="Q51" t="s">
         <v>800</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>801</v>
       </c>
       <c r="R51" t="s">
         <v>10</v>
@@ -15313,10 +15310,10 @@
         <v>186</v>
       </c>
       <c r="W51" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15330,10 +15327,10 @@
         <v>182</v>
       </c>
       <c r="P52" t="s">
+        <v>801</v>
+      </c>
+      <c r="Q52" t="s">
         <v>802</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>803</v>
       </c>
       <c r="R52" t="s">
         <v>10</v>
@@ -15348,10 +15345,10 @@
         <v>186</v>
       </c>
       <c r="W52" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>591</v>
+        <v>624</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15365,10 +15362,10 @@
         <v>182</v>
       </c>
       <c r="P53" t="s">
+        <v>803</v>
+      </c>
+      <c r="Q53" t="s">
         <v>804</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>805</v>
       </c>
       <c r="R53" t="s">
         <v>10</v>
@@ -15383,10 +15380,10 @@
         <v>186</v>
       </c>
       <c r="W53" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15400,10 +15397,10 @@
         <v>182</v>
       </c>
       <c r="P54" t="s">
+        <v>805</v>
+      </c>
+      <c r="Q54" t="s">
         <v>806</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>807</v>
       </c>
       <c r="R54" t="s">
         <v>10</v>
@@ -15418,10 +15415,10 @@
         <v>186</v>
       </c>
       <c r="W54" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>636</v>
+        <v>651</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15436,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC304CC-AC97-4142-A10B-A3202EF87864}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C78ACE-F1AB-4BE3-9C46-9E0EBD4A5397}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15494,7 +15491,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -15518,7 +15515,7 @@
         <v>182</v>
       </c>
       <c r="K11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -15530,12 +15527,12 @@
         <v>286</v>
       </c>
       <c r="P11" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -15553,13 +15550,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="J12" t="s">
         <v>182</v>
       </c>
       <c r="K12" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -15571,12 +15568,12 @@
         <v>286</v>
       </c>
       <c r="P12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -15594,13 +15591,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J13" t="s">
         <v>182</v>
       </c>
       <c r="K13" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -15612,12 +15609,12 @@
         <v>286</v>
       </c>
       <c r="P13" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -15635,13 +15632,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="J14" t="s">
         <v>182</v>
       </c>
       <c r="K14" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -15653,12 +15650,12 @@
         <v>286</v>
       </c>
       <c r="P14" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -15676,13 +15673,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J15" t="s">
         <v>182</v>
       </c>
       <c r="K15" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -15694,12 +15691,12 @@
         <v>286</v>
       </c>
       <c r="P15" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -15723,7 +15720,7 @@
         <v>182</v>
       </c>
       <c r="K16" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -15735,12 +15732,12 @@
         <v>286</v>
       </c>
       <c r="P16" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -15758,13 +15755,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="J17" t="s">
         <v>182</v>
       </c>
       <c r="K17" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -15776,12 +15773,12 @@
         <v>286</v>
       </c>
       <c r="P17" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -15799,13 +15796,13 @@
         <v>2250</v>
       </c>
       <c r="H18" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J18" t="s">
         <v>182</v>
       </c>
       <c r="K18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -15817,12 +15814,12 @@
         <v>286</v>
       </c>
       <c r="P18" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -15840,13 +15837,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="J19" t="s">
         <v>182</v>
       </c>
       <c r="K19" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -15858,12 +15855,12 @@
         <v>286</v>
       </c>
       <c r="P19" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -15881,13 +15878,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J20" t="s">
         <v>182</v>
       </c>
       <c r="K20" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -15899,12 +15896,12 @@
         <v>286</v>
       </c>
       <c r="P20" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -15928,7 +15925,7 @@
         <v>182</v>
       </c>
       <c r="K21" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -15940,12 +15937,12 @@
         <v>286</v>
       </c>
       <c r="P21" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -15963,13 +15960,13 @@
         <v>1100</v>
       </c>
       <c r="H22" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J22" t="s">
         <v>182</v>
       </c>
       <c r="K22" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -15981,12 +15978,12 @@
         <v>286</v>
       </c>
       <c r="P22" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -16004,13 +16001,13 @@
         <v>30</v>
       </c>
       <c r="H23" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="J23" t="s">
         <v>182</v>
       </c>
       <c r="K23" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -16022,12 +16019,12 @@
         <v>286</v>
       </c>
       <c r="P23" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -16051,7 +16048,7 @@
         <v>182</v>
       </c>
       <c r="K24" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -16063,12 +16060,12 @@
         <v>286</v>
       </c>
       <c r="P24" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -16086,13 +16083,13 @@
         <v>2500</v>
       </c>
       <c r="H25" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J25" t="s">
         <v>182</v>
       </c>
       <c r="K25" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -16104,12 +16101,12 @@
         <v>286</v>
       </c>
       <c r="P25" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -16127,13 +16124,13 @@
         <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="J26" t="s">
         <v>182</v>
       </c>
       <c r="K26" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -16145,12 +16142,12 @@
         <v>286</v>
       </c>
       <c r="P26" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -16174,7 +16171,7 @@
         <v>182</v>
       </c>
       <c r="K27" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -16186,12 +16183,12 @@
         <v>286</v>
       </c>
       <c r="P27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -16209,12 +16206,12 @@
         <v>4750</v>
       </c>
       <c r="H28" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -16232,12 +16229,12 @@
         <v>140</v>
       </c>
       <c r="H29" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -16260,7 +16257,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -16278,12 +16275,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -16301,12 +16298,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -16329,7 +16326,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -16347,12 +16344,12 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -16370,12 +16367,12 @@
         <v>2400</v>
       </c>
       <c r="H35" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -16393,12 +16390,12 @@
         <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -16416,12 +16413,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -16444,7 +16441,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -16462,12 +16459,12 @@
         <v>2700</v>
       </c>
       <c r="H39" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -16485,12 +16482,12 @@
         <v>95</v>
       </c>
       <c r="H40" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -16513,7 +16510,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -16531,12 +16528,12 @@
         <v>5500</v>
       </c>
       <c r="H42" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -16554,12 +16551,12 @@
         <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -16582,7 +16579,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -16600,12 +16597,12 @@
         <v>4000</v>
       </c>
       <c r="H45" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -16623,12 +16620,12 @@
         <v>225</v>
       </c>
       <c r="H46" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -16651,7 +16648,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -16669,12 +16666,12 @@
         <v>5500</v>
       </c>
       <c r="H48" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -16692,12 +16689,12 @@
         <v>165</v>
       </c>
       <c r="H49" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -16720,7 +16717,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -16738,12 +16735,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -16761,12 +16758,12 @@
         <v>940</v>
       </c>
       <c r="H52" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -16784,12 +16781,12 @@
         <v>24</v>
       </c>
       <c r="H53" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -16807,12 +16804,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -16835,7 +16832,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -16853,12 +16850,12 @@
         <v>2100</v>
       </c>
       <c r="H56" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -16876,12 +16873,12 @@
         <v>55</v>
       </c>
       <c r="H57" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -16904,7 +16901,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -16922,12 +16919,12 @@
         <v>2400</v>
       </c>
       <c r="H59" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -16945,12 +16942,12 @@
         <v>70</v>
       </c>
       <c r="H60" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -16973,7 +16970,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -16991,12 +16988,12 @@
         <v>2600</v>
       </c>
       <c r="H62" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -17014,15 +17011,15 @@
         <v>80</v>
       </c>
       <c r="H63" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
+        <v>826</v>
+      </c>
+      <c r="C64" t="s">
         <v>827</v>
-      </c>
-      <c r="C64" t="s">
-        <v>828</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -17042,10 +17039,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
+        <v>826</v>
+      </c>
+      <c r="C65" t="s">
         <v>827</v>
-      </c>
-      <c r="C65" t="s">
-        <v>828</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -17060,15 +17057,15 @@
         <v>0.46</v>
       </c>
       <c r="H65" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
+        <v>826</v>
+      </c>
+      <c r="C66" t="s">
         <v>827</v>
-      </c>
-      <c r="C66" t="s">
-        <v>828</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -17083,15 +17080,15 @@
         <v>2760</v>
       </c>
       <c r="H66" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
+        <v>826</v>
+      </c>
+      <c r="C67" t="s">
         <v>827</v>
-      </c>
-      <c r="C67" t="s">
-        <v>828</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -17106,15 +17103,15 @@
         <v>85</v>
       </c>
       <c r="H67" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
+        <v>826</v>
+      </c>
+      <c r="C68" t="s">
         <v>827</v>
-      </c>
-      <c r="C68" t="s">
-        <v>828</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -17129,15 +17126,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C69" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -17157,10 +17154,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C70" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -17175,15 +17172,15 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H70" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C71" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -17198,15 +17195,15 @@
         <v>2140</v>
       </c>
       <c r="H71" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C72" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -17221,15 +17218,15 @@
         <v>56</v>
       </c>
       <c r="H72" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C73" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -17244,7 +17241,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -17253,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C424ADC-4497-4AD9-8D05-4F3B262F4465}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C58D07B2-C206-4ADA-8DFE-7A743EA0D1E9}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17288,10 +17285,10 @@
         <v>165</v>
       </c>
       <c r="K3" t="s">
+        <v>850</v>
+      </c>
+      <c r="L3" t="s">
         <v>851</v>
-      </c>
-      <c r="L3" t="s">
-        <v>852</v>
       </c>
       <c r="M3" t="s">
         <v>166</v>
@@ -17299,13 +17296,13 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" t="s">
+        <v>830</v>
+      </c>
+      <c r="C4" t="s">
         <v>831</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>832</v>
-      </c>
-      <c r="D4" t="s">
-        <v>833</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -17314,10 +17311,10 @@
         <v>282</v>
       </c>
       <c r="I4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J4" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -17331,13 +17328,13 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -17346,10 +17343,10 @@
         <v>282</v>
       </c>
       <c r="I5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="J5" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
@@ -17363,13 +17360,13 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
+        <v>834</v>
+      </c>
+      <c r="C6" t="s">
         <v>835</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>836</v>
-      </c>
-      <c r="D6" t="s">
-        <v>837</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -17378,10 +17375,10 @@
         <v>282</v>
       </c>
       <c r="I6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="J6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -17395,13 +17392,13 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C7" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D7" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -17410,10 +17407,10 @@
         <v>282</v>
       </c>
       <c r="I7" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="J7" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -17427,13 +17424,13 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" t="s">
+        <v>838</v>
+      </c>
+      <c r="C8" t="s">
         <v>839</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>840</v>
-      </c>
-      <c r="D8" t="s">
-        <v>841</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -17442,10 +17439,10 @@
         <v>282</v>
       </c>
       <c r="I8" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="J8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -17459,13 +17456,13 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C9" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D9" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -17474,10 +17471,10 @@
         <v>282</v>
       </c>
       <c r="I9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="J9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -17491,13 +17488,13 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
+        <v>842</v>
+      </c>
+      <c r="C10" t="s">
         <v>843</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>844</v>
-      </c>
-      <c r="D10" t="s">
-        <v>845</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -17506,10 +17503,10 @@
         <v>282</v>
       </c>
       <c r="I10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="J10" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -17523,13 +17520,13 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C11" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D11" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -17538,10 +17535,10 @@
         <v>282</v>
       </c>
       <c r="I11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="J11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K11" t="s">
         <v>21</v>
@@ -17555,13 +17552,13 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
+        <v>846</v>
+      </c>
+      <c r="C12" t="s">
         <v>847</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>848</v>
-      </c>
-      <c r="D12" t="s">
-        <v>849</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -17570,10 +17567,10 @@
         <v>282</v>
       </c>
       <c r="I12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="J12" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -17587,13 +17584,13 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -17602,10 +17599,10 @@
         <v>282</v>
       </c>
       <c r="I13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="J13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33597F6A-7DB4-43D3-A75E-0B796240D426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F36AD2A4-5C9D-402C-9B21-38FE4B7FDD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,16 +980,130 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_028</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_solelc_spv_018</t>
@@ -1010,12 +1124,6 @@
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_012</t>
   </si>
   <si>
@@ -1028,78 +1136,6 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_010</t>
   </si>
   <si>
@@ -1118,42 +1154,6 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_021</t>
   </si>
   <si>
@@ -1178,9 +1178,63 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
     <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
   </si>
   <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
     <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
   </si>
   <si>
@@ -1190,94 +1244,82 @@
     <t>e_JP6-275</t>
   </si>
   <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
     <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
   </si>
   <si>
     <t>e_w216956620-500,e_w216953915-500</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
     <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
   </si>
   <si>
     <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
   </si>
   <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
     <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
   </si>
   <si>
     <t>e_w179863079-275,e_JP6-275</t>
   </si>
   <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_008</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wonelc_won_028</t>
@@ -1292,6 +1334,18 @@
     <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_004</t>
   </si>
   <si>
@@ -1310,12 +1364,66 @@
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_016</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_017</t>
   </si>
   <si>
@@ -1334,118 +1442,40 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_015</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
   </si>
   <si>
     <t>elc_won_008</t>
@@ -1454,16 +1484,28 @@
     <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
   </si>
   <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
     <t>elc_won_028</t>
@@ -1472,6 +1514,18 @@
     <t>elc_won_031</t>
   </si>
   <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
     <t>elc_won_004</t>
   </si>
   <si>
@@ -1487,12 +1541,60 @@
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
   </si>
   <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
     <t>elc_won_016</t>
   </si>
   <si>
     <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
   </si>
   <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
     <t>elc_won_017</t>
   </si>
   <si>
@@ -1511,112 +1613,262 @@
     <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
     <t>elc_won_015</t>
   </si>
   <si>
     <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wofelc_wof_005</t>
@@ -1631,475 +1883,223 @@
     <t>connecting wind offshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
   </si>
   <si>
     <t>elc_wof_005</t>
   </si>
   <si>
     <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E3DCEE-918C-4564-A09E-998D4F26F72E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7435C97D-E728-4F2F-880A-1A458C6B9EBC}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7814,16 +7814,16 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.99798824264234642</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB11">
-        <v>36.882218223648351</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
@@ -7856,10 +7856,10 @@
         <v>440</v>
       </c>
       <c r="AO11">
-        <v>0.99869874972548245</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP11">
-        <v>23.856255032822389</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
@@ -7889,13 +7889,13 @@
         <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>449</v>
+        <v>585</v>
       </c>
       <c r="BC11">
-        <v>0.95726256957223688</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD11">
-        <v>783.51955784232393</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7960,16 +7960,16 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.99825665520226836</v>
+        <v>0.99809166649408687</v>
       </c>
       <c r="AB12">
-        <v>31.96132129174655</v>
+        <v>34.986114275074357</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
@@ -8002,10 +8002,10 @@
         <v>442</v>
       </c>
       <c r="AO12">
-        <v>0.99863922747017897</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP12">
-        <v>24.947496380053089</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8032,16 +8032,16 @@
         <v>498</v>
       </c>
       <c r="BA12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="BB12" t="s">
-        <v>491</v>
+        <v>587</v>
       </c>
       <c r="BC12">
-        <v>0.9437657388784082</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD12">
-        <v>1030.9614538958492</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8106,16 +8106,16 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.99894650606645485</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB13">
-        <v>19.314055448326833</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
@@ -8148,10 +8148,10 @@
         <v>444</v>
       </c>
       <c r="AO13">
-        <v>0.99582230548799566</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP13">
-        <v>76.591066053413869</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8178,16 +8178,16 @@
         <v>500</v>
       </c>
       <c r="BA13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="BB13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="BC13">
-        <v>0.99681267676383467</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD13">
-        <v>58.434259329697142</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8252,16 +8252,16 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.98179245618315802</v>
+        <v>0.99621285878087551</v>
       </c>
       <c r="AB14">
-        <v>333.80496997543548</v>
+        <v>69.43092235061502</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
@@ -8291,13 +8291,13 @@
         <v>445</v>
       </c>
       <c r="AN14" t="s">
-        <v>376</v>
+        <v>446</v>
       </c>
       <c r="AO14">
-        <v>0.99192535126433146</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP14">
-        <v>148.0352268205892</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
@@ -8324,16 +8324,16 @@
         <v>502</v>
       </c>
       <c r="BA14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="BB14" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="BC14">
-        <v>0.99602290686668338</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD14">
-        <v>72.91337411080552</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8398,16 +8398,16 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.99116451092312863</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB15">
-        <v>161.98396640930775</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
@@ -8434,16 +8434,16 @@
         <v>385</v>
       </c>
       <c r="AM15" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN15" t="s">
-        <v>370</v>
+        <v>448</v>
       </c>
       <c r="AO15">
-        <v>0.98092693557487454</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP15">
-        <v>349.67284779396647</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
@@ -8470,16 +8470,16 @@
         <v>504</v>
       </c>
       <c r="BA15" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="BB15" t="s">
-        <v>591</v>
+        <v>366</v>
       </c>
       <c r="BC15">
-        <v>0.99637036284424008</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD15">
-        <v>66.543347855598327</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8544,16 +8544,16 @@
         <v>295</v>
       </c>
       <c r="Y16" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="Z16" t="s">
         <v>354</v>
       </c>
       <c r="AA16">
-        <v>0.99852430677621173</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB16">
-        <v>27.054375769451152</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD16" t="s">
         <v>282</v>
@@ -8580,16 +8580,16 @@
         <v>387</v>
       </c>
       <c r="AM16" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AN16" t="s">
-        <v>356</v>
+        <v>450</v>
       </c>
       <c r="AO16">
-        <v>0.93717435218793788</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP16">
-        <v>1151.8035432211395</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8616,16 +8616,16 @@
         <v>506</v>
       </c>
       <c r="BA16" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="BB16" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="BC16">
-        <v>0.99234935324205875</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD16">
-        <v>140.26185722892211</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.99838604658336239</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB17">
-        <v>29.589145971689483</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8726,16 +8726,16 @@
         <v>389</v>
       </c>
       <c r="AM17" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AN17" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AO17">
-        <v>0.96551955124232614</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP17">
-        <v>632.14156055735509</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="BB17" t="s">
-        <v>355</v>
+        <v>596</v>
       </c>
       <c r="BC17">
-        <v>0.99536692897647694</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD17">
-        <v>84.939635431255269</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8836,16 +8836,16 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.94069903208664407</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB18">
-        <v>1087.1844117448593</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
@@ -8872,16 +8872,16 @@
         <v>391</v>
       </c>
       <c r="AM18" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AN18" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AO18">
-        <v>0.99693456929731861</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP18">
-        <v>56.199562882493169</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="BB18" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="BC18">
-        <v>0.88199812838352587</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD18">
-        <v>2163.367646302027</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.99756610784588629</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB19">
-        <v>44.621356158751233</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9018,16 +9018,16 @@
         <v>393</v>
       </c>
       <c r="AM19" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AN19" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AO19">
-        <v>0.99750949182367343</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP19">
-        <v>45.659316565986806</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9054,16 +9054,16 @@
         <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="BB19" t="s">
-        <v>352</v>
+        <v>600</v>
       </c>
       <c r="BC19">
-        <v>0.97902641975794957</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD19">
-        <v>384.51563777092457</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.9972084849335241</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB20">
-        <v>51.177776218725121</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9164,16 +9164,16 @@
         <v>395</v>
       </c>
       <c r="AM20" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AN20" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AO20">
-        <v>0.99804155179341392</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP20">
-        <v>35.904883787411507</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9200,16 +9200,16 @@
         <v>514</v>
       </c>
       <c r="BA20" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="BB20" t="s">
-        <v>356</v>
+        <v>602</v>
       </c>
       <c r="BC20">
-        <v>0.96140381292129873</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD20">
-        <v>707.59676310952364</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="Z21" t="s">
         <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.99809166649408687</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB21">
-        <v>34.986114275074357</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9310,16 +9310,16 @@
         <v>397</v>
       </c>
       <c r="AM21" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AN21" t="s">
-        <v>457</v>
+        <v>376</v>
       </c>
       <c r="AO21">
-        <v>0.99508023417818925</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP21">
-        <v>90.195706733197795</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9346,16 +9346,16 @@
         <v>516</v>
       </c>
       <c r="BA21" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="BB21" t="s">
-        <v>356</v>
+        <v>604</v>
       </c>
       <c r="BC21">
-        <v>0.97591598065988894</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD21">
-        <v>441.54035456870389</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Z22" t="s">
         <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.99850557699173803</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB22">
-        <v>27.397755151469518</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9456,16 +9456,16 @@
         <v>399</v>
       </c>
       <c r="AM22" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN22" t="s">
-        <v>459</v>
+        <v>366</v>
       </c>
       <c r="AO22">
-        <v>0.99940622505963084</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP22">
-        <v>10.885873906767051</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9492,16 +9492,16 @@
         <v>518</v>
       </c>
       <c r="BA22" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="BB22" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="BC22">
-        <v>0.99412039195829205</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD22">
-        <v>107.79281409797902</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="Z23" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AA23">
-        <v>0.99621285878087551</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB23">
-        <v>69.43092235061502</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9602,16 +9602,16 @@
         <v>401</v>
       </c>
       <c r="AM23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO23">
-        <v>0.99827635377245738</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP23">
-        <v>31.600180838280902</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9638,16 +9638,16 @@
         <v>520</v>
       </c>
       <c r="BA23" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="BB23" t="s">
-        <v>491</v>
+        <v>608</v>
       </c>
       <c r="BC23">
-        <v>0.98292548292671178</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD23">
-        <v>313.03281301028323</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="Z24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AA24">
-        <v>0.9975431479552237</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB24">
-        <v>45.042287487565297</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN24" t="s">
-        <v>370</v>
+        <v>464</v>
       </c>
       <c r="AO24">
-        <v>0.98949004263841422</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP24">
-        <v>192.68255162907312</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9784,16 +9784,16 @@
         <v>522</v>
       </c>
       <c r="BA24" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="BB24" t="s">
-        <v>353</v>
+        <v>610</v>
       </c>
       <c r="BC24">
-        <v>0.98355967005268352</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD24">
-        <v>301.40604903413595</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="Z25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AA25">
-        <v>0.99636728996375623</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB25">
-        <v>66.599683997802714</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AN25" t="s">
-        <v>464</v>
+        <v>357</v>
       </c>
       <c r="AO25">
-        <v>0.99811838305018963</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP25">
-        <v>34.496310746523356</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="BB25" t="s">
-        <v>605</v>
+        <v>357</v>
       </c>
       <c r="BC25">
-        <v>0.9973402418125219</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD25">
-        <v>48.762233437098502</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10004,16 +10004,16 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA26">
-        <v>0.99628076912917996</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB26">
-        <v>68.185899298368355</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
@@ -10040,16 +10040,16 @@
         <v>407</v>
       </c>
       <c r="AM26" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN26" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO26">
-        <v>0.9985928182686985</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP26">
-        <v>25.798331740528162</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10076,16 +10076,16 @@
         <v>526</v>
       </c>
       <c r="BA26" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="BB26" t="s">
-        <v>356</v>
+        <v>613</v>
       </c>
       <c r="BC26">
-        <v>0.934538160869965</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD26">
-        <v>1200.1337173839754</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10150,16 +10150,16 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="Z27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AA27">
-        <v>0.9981032549815434</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB27">
-        <v>34.773658671704098</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
@@ -10186,16 +10186,16 @@
         <v>409</v>
       </c>
       <c r="AM27" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN27" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO27">
-        <v>0.99769811225811866</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP27">
-        <v>42.201275267825203</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="BB27" t="s">
-        <v>356</v>
+        <v>615</v>
       </c>
       <c r="BC27">
-        <v>0.94616153753972931</v>
+        <v>0.99017867813273497</v>
       </c>
       <c r="BD27">
-        <v>987.03847843829612</v>
+        <v>180.05756756652616</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10296,16 +10296,16 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA28">
-        <v>0.99900168239190124</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB28">
-        <v>18.302489481810518</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
@@ -10332,16 +10332,16 @@
         <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN28" t="s">
-        <v>353</v>
+        <v>471</v>
       </c>
       <c r="AO28">
-        <v>0.98814178187791379</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP28">
-        <v>217.40066557158059</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="BB28" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="BC28">
-        <v>0.97218956380622079</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD28">
-        <v>509.85799688595205</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="Z29" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA29">
-        <v>0.9488788277802801</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB29">
-        <v>937.22149069486488</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10478,10 +10478,10 @@
         <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN29" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO29">
         <v>0.99762356494824644</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="BB29" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="BC29">
-        <v>0.9924172440074055</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD29">
-        <v>139.01719319756617</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Z30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA30">
-        <v>0.9977500892185478</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB30">
-        <v>41.248364326622962</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10624,10 +10624,10 @@
         <v>415</v>
       </c>
       <c r="AM30" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AN30" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AO30">
         <v>0.99669176136177262</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="BB30" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="BC30">
-        <v>0.99114508565756532</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD30">
-        <v>162.34009627796874</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Z31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA31">
-        <v>0.9982812149336332</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB31">
-        <v>31.51105955005805</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10770,16 +10770,16 @@
         <v>417</v>
       </c>
       <c r="AM31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AN31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AO31">
-        <v>0.99682717865030179</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP31">
-        <v>58.168391411134159</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="BB31" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="BC31">
-        <v>0.99561586640696276</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD31">
-        <v>80.375782539015233</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="Z32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AA32">
-        <v>0.98833720780868572</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB32">
-        <v>213.8178568407609</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10916,16 +10916,16 @@
         <v>419</v>
       </c>
       <c r="AM32" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AN32" t="s">
-        <v>477</v>
+        <v>366</v>
       </c>
       <c r="AO32">
-        <v>0.99841760060377538</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP32">
-        <v>29.010655597451841</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10952,16 +10952,16 @@
         <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="BB32" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="BC32">
-        <v>0.99253849155603513</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD32">
-        <v>136.79432147269009</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="Z33" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA33">
-        <v>0.99391268208184824</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB33">
-        <v>111.60082849944791</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11062,16 +11062,16 @@
         <v>421</v>
       </c>
       <c r="AM33" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN33" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO33">
-        <v>0.99781438034778358</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP33">
-        <v>40.069693623967019</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11098,16 +11098,16 @@
         <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="BB33" t="s">
-        <v>618</v>
+        <v>357</v>
       </c>
       <c r="BC33">
-        <v>0.973232135644435</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD33">
-        <v>490.74417985202501</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Z34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AA34">
-        <v>0.99871218762601011</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB34">
-        <v>23.609893523147914</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11208,16 +11208,16 @@
         <v>423</v>
       </c>
       <c r="AM34" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN34" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO34">
-        <v>0.99013353407586135</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP34">
-        <v>180.88520860920943</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11244,16 +11244,16 @@
         <v>542</v>
       </c>
       <c r="BA34" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="BB34" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="BC34">
-        <v>0.98779966071713954</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD34">
-        <v>223.67288685244134</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="Z35" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA35">
-        <v>0.99856748800713691</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB35">
-        <v>26.26271986915707</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11354,16 +11354,16 @@
         <v>425</v>
       </c>
       <c r="AM35" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN35" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO35">
-        <v>0.99869589057011365</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP35">
-        <v>23.908672881248773</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="BB35" t="s">
-        <v>622</v>
+        <v>444</v>
       </c>
       <c r="BC35">
-        <v>0.98841501119699848</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD35">
-        <v>212.39146138836088</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11464,16 +11464,16 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z36" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AA36">
-        <v>0.97905685820454003</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB36">
-        <v>383.95759958343297</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
@@ -11500,16 +11500,16 @@
         <v>427</v>
       </c>
       <c r="AM36" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN36" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO36">
-        <v>0.99686124252542985</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP36">
-        <v>57.543887033786262</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11536,16 +11536,16 @@
         <v>546</v>
       </c>
       <c r="BA36" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="BB36" t="s">
-        <v>618</v>
+        <v>359</v>
       </c>
       <c r="BC36">
-        <v>0.93089405249526469</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD36">
-        <v>1266.9423709201483</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11610,16 +11610,16 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="Z37" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="AA37">
-        <v>0.97633688849282452</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB37">
-        <v>433.82371096488447</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
@@ -11646,16 +11646,16 @@
         <v>429</v>
       </c>
       <c r="AM37" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN37" t="s">
-        <v>487</v>
+        <v>359</v>
       </c>
       <c r="AO37">
-        <v>0.99710631799330929</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP37">
-        <v>53.050836789329388</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11682,16 +11682,16 @@
         <v>548</v>
       </c>
       <c r="BA37" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="BB37" t="s">
-        <v>625</v>
+        <v>370</v>
       </c>
       <c r="BC37">
-        <v>0.99302778580016682</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD37">
-        <v>127.82392699694152</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11756,16 +11756,16 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="Z38" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="AA38">
-        <v>0.99726055556014181</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB38">
-        <v>50.223148064066145</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
@@ -11798,10 +11798,10 @@
         <v>489</v>
       </c>
       <c r="AO38">
-        <v>0.99550555557680764</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP38">
-        <v>82.398147758527074</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11828,16 +11828,16 @@
         <v>550</v>
       </c>
       <c r="BA38" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="BB38" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="BC38">
-        <v>0.99366677237144974</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD38">
-        <v>116.10917319008783</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11905,7 +11905,7 @@
         <v>270</v>
       </c>
       <c r="Z39" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA39">
         <v>0.96189283472138964</v>
@@ -11944,10 +11944,10 @@
         <v>491</v>
       </c>
       <c r="AO39">
-        <v>0.93896180472603763</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP39">
-        <v>1119.0335800226442</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11974,16 +11974,16 @@
         <v>552</v>
       </c>
       <c r="BA39" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="BB39" t="s">
-        <v>629</v>
+        <v>357</v>
       </c>
       <c r="BC39">
-        <v>0.9205295464439136</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD39">
-        <v>1456.9583151949184</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12090,10 +12090,10 @@
         <v>493</v>
       </c>
       <c r="AO40">
-        <v>0.99870022163576544</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP40">
-        <v>23.829270010966344</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="BB40" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="BC40">
-        <v>0.99519319222421976</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD40">
-        <v>88.124809222638589</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12236,10 +12236,10 @@
         <v>495</v>
       </c>
       <c r="AO41">
-        <v>0.99807466477127271</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP41">
-        <v>35.297812526667357</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12266,16 +12266,16 @@
         <v>556</v>
       </c>
       <c r="BA41" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="BB41" t="s">
-        <v>633</v>
+        <v>372</v>
       </c>
       <c r="BC41">
-        <v>0.98822137145239475</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD41">
-        <v>215.94152337276336</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12304,16 +12304,16 @@
         <v>558</v>
       </c>
       <c r="BA42" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="BB42" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="BC42">
-        <v>0.99662747375050009</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD42">
-        <v>61.829647907498845</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12342,16 +12342,16 @@
         <v>560</v>
       </c>
       <c r="BA43" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="BB43" t="s">
-        <v>637</v>
+        <v>359</v>
       </c>
       <c r="BC43">
-        <v>0.99284590877035406</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD43">
-        <v>131.158339210175</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12380,16 +12380,16 @@
         <v>562</v>
       </c>
       <c r="BA44" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="BB44" t="s">
-        <v>639</v>
+        <v>357</v>
       </c>
       <c r="BC44">
-        <v>0.97803702976044449</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD44">
-        <v>402.65445439185123</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12418,16 +12418,16 @@
         <v>564</v>
       </c>
       <c r="BA45" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB45" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="BC45">
-        <v>0.95957195194316591</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD45">
-        <v>741.18088104195795</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12456,16 +12456,16 @@
         <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="BB46" t="s">
-        <v>642</v>
+        <v>357</v>
       </c>
       <c r="BC46">
-        <v>0.99603667376986049</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD46">
-        <v>72.660980885890424</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12500,10 +12500,10 @@
         <v>644</v>
       </c>
       <c r="BC47">
-        <v>0.99017867813273497</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD47">
-        <v>180.05756756652616</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12538,10 +12538,10 @@
         <v>646</v>
       </c>
       <c r="BC48">
-        <v>0.99504061303190972</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD48">
-        <v>90.922094414988095</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12576,10 +12576,10 @@
         <v>648</v>
       </c>
       <c r="BC49">
-        <v>0.99490784156958001</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD49">
-        <v>93.356237891033686</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12614,10 +12614,10 @@
         <v>650</v>
       </c>
       <c r="BC50">
-        <v>0.99015836110796274</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD50">
-        <v>180.43004635401576</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12652,10 +12652,10 @@
         <v>652</v>
       </c>
       <c r="BC51">
-        <v>0.99623532634854861</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD51">
-        <v>69.01901694327529</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12690,10 +12690,10 @@
         <v>654</v>
       </c>
       <c r="BC52">
-        <v>0.9966173923071765</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD52">
-        <v>62.014474368430825</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12725,13 +12725,13 @@
         <v>655</v>
       </c>
       <c r="BB53" t="s">
-        <v>370</v>
+        <v>467</v>
       </c>
       <c r="BC53">
-        <v>0.98180592470173533</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD53">
-        <v>333.55804713485287</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12763,13 +12763,13 @@
         <v>656</v>
       </c>
       <c r="BB54" t="s">
-        <v>353</v>
+        <v>444</v>
       </c>
       <c r="BC54">
-        <v>0.98235584693125277</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD54">
-        <v>323.47613959369914</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EC2A48-DF6B-4F64-8BA8-D2C460BD53E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05E0B7D-888D-4E63-BC18-E33F9A764257}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>606</v>
+        <v>640</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>607</v>
+        <v>641</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>608</v>
+        <v>642</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13162,7 +13162,7 @@
         <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>584</v>
+        <v>655</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13263,7 +13263,7 @@
         <v>729</v>
       </c>
       <c r="X16" t="s">
-        <v>640</v>
+        <v>611</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>486</v>
+        <v>439</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13331,7 +13331,7 @@
         <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>598</v>
+        <v>633</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13399,7 +13399,7 @@
         <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>594</v>
+        <v>636</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13467,7 +13467,7 @@
         <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>634</v>
+        <v>605</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>492</v>
+        <v>455</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>632</v>
+        <v>603</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>615</v>
+        <v>593</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>653</v>
+        <v>590</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13910,7 +13910,7 @@
         <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13943,7 +13943,7 @@
         <v>749</v>
       </c>
       <c r="X26" t="s">
-        <v>645</v>
+        <v>616</v>
       </c>
       <c r="Y26">
         <v>63.731250000000003</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14011,7 +14011,7 @@
         <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="Y27">
         <v>28.239750000000001</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>655</v>
+        <v>592</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14147,7 +14147,7 @@
         <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="Y29">
         <v>3.38625</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>638</v>
+        <v>609</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>603</v>
+        <v>629</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>649</v>
+        <v>586</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>613</v>
+        <v>647</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>488</v>
+        <v>441</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>611</v>
+        <v>645</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14759,7 +14759,7 @@
         <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>592</v>
+        <v>634</v>
       </c>
       <c r="Y38">
         <v>64.437749999999994</v>
@@ -14794,7 +14794,7 @@
         <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>647</v>
+        <v>584</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14963,7 +14963,7 @@
         <v>779</v>
       </c>
       <c r="X41" t="s">
-        <v>641</v>
+        <v>612</v>
       </c>
       <c r="Y41">
         <v>27.642749999999999</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>585</v>
+        <v>656</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15068,7 +15068,7 @@
         <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>595</v>
+        <v>637</v>
       </c>
       <c r="Y44">
         <v>0.42149999999999999</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15138,7 +15138,7 @@
         <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>628</v>
+        <v>651</v>
       </c>
       <c r="Y46">
         <v>1.81725</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>602</v>
+        <v>628</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>617</v>
+        <v>595</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15243,7 +15243,7 @@
         <v>795</v>
       </c>
       <c r="X49" t="s">
-        <v>643</v>
+        <v>614</v>
       </c>
       <c r="Y49">
         <v>42.144750000000002</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>636</v>
+        <v>607</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>651</v>
+        <v>588</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C78ACE-F1AB-4BE3-9C46-9E0EBD4A5397}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC73FD5-C733-48CB-967D-49F8EF5CB3FB}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C58D07B2-C206-4ADA-8DFE-7A743EA0D1E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9076CAE5-2016-4E48-81C6-DB8D7A193F34}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F36AD2A4-5C9D-402C-9B21-38FE4B7FDD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1D9B58F-52DA-4E30-BC4A-B198EEE508A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,46 +980,88 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_solelc_spv_029</t>
@@ -1028,16 +1070,100 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_031</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_solelc_spv_028</t>
@@ -1046,220 +1172,232 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
     <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
   </si>
   <si>
-    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
   </si>
   <si>
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
   </si>
   <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
     <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
   </si>
   <si>
     <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
   </si>
   <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
     <t>distr_wonelc_won_007</t>
@@ -1280,58 +1418,22 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_wonelc_won_001</t>
@@ -1346,106 +1448,130 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
   </si>
   <si>
     <t>elc_won_007</t>
@@ -1466,52 +1592,19 @@
     <t>e_JP219-500,e_JP132-500</t>
   </si>
   <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
   </si>
   <si>
     <t>elc_won_001</t>
@@ -1526,97 +1619,76 @@
     <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wofelc_wof_029</t>
@@ -1661,226 +1733,205 @@
     <t>connecting wind offshore to buses in cluster 38</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_026</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
   </si>
   <si>
     <t>elc_wof_029</t>
@@ -1922,184 +1973,133 @@
     <t>e_JP219-500</t>
   </si>
   <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
     <t>elc_wof_026</t>
   </si>
   <si>
     <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7435C97D-E728-4F2F-880A-1A458C6B9EBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E52397-0F56-41E1-912C-05D6225FA055}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7814,16 +7814,16 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.9488788277802801</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB11">
-        <v>937.22149069486488</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
@@ -7856,10 +7856,10 @@
         <v>440</v>
       </c>
       <c r="AO11">
-        <v>0.99710631799330929</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP11">
-        <v>53.050836789329388</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
@@ -7889,13 +7889,13 @@
         <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>585</v>
+        <v>358</v>
       </c>
       <c r="BC11">
-        <v>0.99490784156958001</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD11">
-        <v>93.356237891033686</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8002,10 +8002,10 @@
         <v>442</v>
       </c>
       <c r="AO12">
-        <v>0.99550555557680764</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP12">
-        <v>82.398147758527074</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8032,16 +8032,16 @@
         <v>498</v>
       </c>
       <c r="BA12" t="s">
+        <v>585</v>
+      </c>
+      <c r="BB12" t="s">
         <v>586</v>
       </c>
-      <c r="BB12" t="s">
-        <v>587</v>
-      </c>
       <c r="BC12">
-        <v>0.99015836110796274</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD12">
-        <v>180.43004635401576</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8148,10 +8148,10 @@
         <v>444</v>
       </c>
       <c r="AO13">
-        <v>0.93896180472603763</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP13">
-        <v>1119.0335800226442</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8178,16 +8178,16 @@
         <v>500</v>
       </c>
       <c r="BA13" t="s">
+        <v>587</v>
+      </c>
+      <c r="BB13" t="s">
         <v>588</v>
       </c>
-      <c r="BB13" t="s">
-        <v>589</v>
-      </c>
       <c r="BC13">
-        <v>0.99623532634854861</v>
+        <v>0.99017867813273497</v>
       </c>
       <c r="BD13">
-        <v>69.01901694327529</v>
+        <v>180.05756756652616</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8294,10 +8294,10 @@
         <v>446</v>
       </c>
       <c r="AO14">
-        <v>0.99863922747017897</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP14">
-        <v>24.947496380053089</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
@@ -8324,16 +8324,16 @@
         <v>502</v>
       </c>
       <c r="BA14" t="s">
+        <v>589</v>
+      </c>
+      <c r="BB14" t="s">
         <v>590</v>
       </c>
-      <c r="BB14" t="s">
-        <v>591</v>
-      </c>
       <c r="BC14">
-        <v>0.9966173923071765</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD14">
-        <v>62.014474368430825</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8440,10 +8440,10 @@
         <v>448</v>
       </c>
       <c r="AO15">
-        <v>0.99582230548799566</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP15">
-        <v>76.591066053413869</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
@@ -8470,16 +8470,16 @@
         <v>504</v>
       </c>
       <c r="BA15" t="s">
+        <v>591</v>
+      </c>
+      <c r="BB15" t="s">
         <v>592</v>
       </c>
-      <c r="BB15" t="s">
-        <v>366</v>
-      </c>
       <c r="BC15">
-        <v>0.98180592470173533</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD15">
-        <v>333.55804713485287</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8586,10 +8586,10 @@
         <v>450</v>
       </c>
       <c r="AO16">
-        <v>0.99869874972548245</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP16">
-        <v>23.856255032822389</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8619,13 +8619,13 @@
         <v>593</v>
       </c>
       <c r="BB16" t="s">
-        <v>594</v>
+        <v>358</v>
       </c>
       <c r="BC16">
-        <v>0.99253849155603513</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD16">
-        <v>136.79432147269009</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.99628076912917996</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB17">
-        <v>68.185899298368355</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8732,10 +8732,10 @@
         <v>452</v>
       </c>
       <c r="AO17">
-        <v>0.99841760060377538</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP17">
-        <v>29.010655597451841</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
+        <v>594</v>
+      </c>
+      <c r="BB17" t="s">
         <v>595</v>
       </c>
-      <c r="BB17" t="s">
-        <v>596</v>
-      </c>
       <c r="BC17">
-        <v>0.973232135644435</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD17">
-        <v>490.74417985202501</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8836,16 +8836,16 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.9981032549815434</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB18">
-        <v>34.773658671704098</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
@@ -8878,10 +8878,10 @@
         <v>454</v>
       </c>
       <c r="AO18">
-        <v>0.99781438034778358</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP18">
-        <v>40.069693623967019</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="BB18" t="s">
-        <v>598</v>
+        <v>486</v>
       </c>
       <c r="BC18">
-        <v>0.99637036284424008</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD18">
-        <v>66.543347855598327</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.97633688849282452</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB19">
-        <v>433.82371096488447</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9024,10 +9024,10 @@
         <v>456</v>
       </c>
       <c r="AO19">
-        <v>0.99870022163576544</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP19">
-        <v>23.829270010966344</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9054,16 +9054,16 @@
         <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="BB19" t="s">
-        <v>600</v>
+        <v>349</v>
       </c>
       <c r="BC19">
-        <v>0.99681267676383467</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD19">
-        <v>58.434259329697142</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.99798824264234642</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB20">
-        <v>36.882218223648351</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9167,13 +9167,13 @@
         <v>457</v>
       </c>
       <c r="AN20" t="s">
-        <v>458</v>
+        <v>360</v>
       </c>
       <c r="AO20">
-        <v>0.99807466477127271</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP20">
-        <v>35.297812526667357</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9200,16 +9200,16 @@
         <v>514</v>
       </c>
       <c r="BA20" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="BB20" t="s">
-        <v>602</v>
+        <v>461</v>
       </c>
       <c r="BC20">
-        <v>0.99602290686668338</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD20">
-        <v>72.91337411080552</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="Z21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA21">
-        <v>0.99116451092312863</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB21">
-        <v>161.98396640930775</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9310,16 +9310,16 @@
         <v>397</v>
       </c>
       <c r="AM21" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AN21" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="AO21">
-        <v>0.99192535126433146</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP21">
-        <v>148.0352268205892</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9346,16 +9346,16 @@
         <v>516</v>
       </c>
       <c r="BA21" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="BB21" t="s">
-        <v>604</v>
+        <v>486</v>
       </c>
       <c r="BC21">
-        <v>0.98822137145239475</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD21">
-        <v>215.94152337276336</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="Z22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA22">
-        <v>0.99900168239190124</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB22">
-        <v>18.302489481810518</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9456,16 +9456,16 @@
         <v>399</v>
       </c>
       <c r="AM22" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AN22" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="AO22">
-        <v>0.98092693557487454</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP22">
-        <v>349.67284779396647</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9492,16 +9492,16 @@
         <v>518</v>
       </c>
       <c r="BA22" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="BB22" t="s">
-        <v>606</v>
+        <v>358</v>
       </c>
       <c r="BC22">
-        <v>0.99662747375050009</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD22">
-        <v>61.829647907498845</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="Z23" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AA23">
-        <v>0.94069903208664407</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB23">
-        <v>1087.1844117448593</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9602,16 +9602,16 @@
         <v>401</v>
       </c>
       <c r="AM23" t="s">
+        <v>460</v>
+      </c>
+      <c r="AN23" t="s">
         <v>461</v>
       </c>
-      <c r="AN23" t="s">
-        <v>462</v>
-      </c>
       <c r="AO23">
-        <v>0.99013353407586135</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP23">
-        <v>180.88520860920943</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9638,16 +9638,16 @@
         <v>520</v>
       </c>
       <c r="BA23" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="BB23" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="BC23">
-        <v>0.99284590877035406</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD23">
-        <v>131.158339210175</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="Z24" t="s">
         <v>361</v>
       </c>
       <c r="AA24">
-        <v>0.99756610784588629</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB24">
-        <v>44.621356158751233</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
+        <v>462</v>
+      </c>
+      <c r="AN24" t="s">
         <v>463</v>
       </c>
-      <c r="AN24" t="s">
-        <v>464</v>
-      </c>
       <c r="AO24">
-        <v>0.99869589057011365</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP24">
-        <v>23.908672881248773</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9784,16 +9784,16 @@
         <v>522</v>
       </c>
       <c r="BA24" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="BB24" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="BC24">
-        <v>0.97803702976044449</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD24">
-        <v>402.65445439185123</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="Z25" t="s">
         <v>362</v>
       </c>
       <c r="AA25">
-        <v>0.9972084849335241</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB25">
-        <v>51.177776218725121</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
+        <v>464</v>
+      </c>
+      <c r="AN25" t="s">
         <v>465</v>
       </c>
-      <c r="AN25" t="s">
-        <v>357</v>
-      </c>
       <c r="AO25">
-        <v>0.93717435218793788</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP25">
-        <v>1151.8035432211395</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="BB25" t="s">
-        <v>357</v>
+        <v>606</v>
       </c>
       <c r="BC25">
-        <v>0.95957195194316591</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD25">
-        <v>741.18088104195795</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10004,16 +10004,16 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="Z26" t="s">
         <v>363</v>
       </c>
       <c r="AA26">
-        <v>0.99391268208184824</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB26">
-        <v>111.60082849944791</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
@@ -10046,10 +10046,10 @@
         <v>467</v>
       </c>
       <c r="AO26">
-        <v>0.96551955124232614</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP26">
-        <v>632.14156055735509</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10076,16 +10076,16 @@
         <v>526</v>
       </c>
       <c r="BA26" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="BB26" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="BC26">
-        <v>0.99603667376986049</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD26">
-        <v>72.660980885890424</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10150,16 +10150,16 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Z27" t="s">
         <v>364</v>
       </c>
       <c r="AA27">
-        <v>0.99871218762601011</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB27">
-        <v>23.609893523147914</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
@@ -10192,10 +10192,10 @@
         <v>469</v>
       </c>
       <c r="AO27">
-        <v>0.99693456929731861</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP27">
-        <v>56.199562882493169</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="BB27" t="s">
-        <v>615</v>
+        <v>369</v>
       </c>
       <c r="BC27">
-        <v>0.99017867813273497</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD27">
-        <v>180.05756756652616</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10296,16 +10296,16 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z28" t="s">
         <v>365</v>
       </c>
       <c r="AA28">
-        <v>0.99856748800713691</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB28">
-        <v>26.26271986915707</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
@@ -10338,10 +10338,10 @@
         <v>471</v>
       </c>
       <c r="AO28">
-        <v>0.99682717865030179</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP28">
-        <v>58.168391411134159</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="BB28" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="BC28">
-        <v>0.99504061303190972</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD28">
-        <v>90.922094414988095</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z29" t="s">
         <v>366</v>
       </c>
       <c r="AA29">
-        <v>0.97905685820454003</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB29">
-        <v>383.95759958343297</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10484,10 +10484,10 @@
         <v>473</v>
       </c>
       <c r="AO29">
-        <v>0.99762356494824644</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP29">
-        <v>43.567975948815601</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="BB29" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="BC29">
-        <v>0.98779966071713954</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD29">
-        <v>223.67288685244134</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="Z30" t="s">
         <v>367</v>
       </c>
       <c r="AA30">
-        <v>0.99726055556014181</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB30">
-        <v>50.223148064066145</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10630,10 +10630,10 @@
         <v>475</v>
       </c>
       <c r="AO30">
-        <v>0.99669176136177262</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP30">
-        <v>60.651041700835236</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="BB30" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="BC30">
-        <v>0.98841501119699848</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD30">
-        <v>212.39146138836088</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="Z31" t="s">
         <v>368</v>
       </c>
       <c r="AA31">
-        <v>0.99825665520226836</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB31">
-        <v>31.96132129174655</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10773,13 +10773,13 @@
         <v>476</v>
       </c>
       <c r="AN31" t="s">
-        <v>477</v>
+        <v>349</v>
       </c>
       <c r="AO31">
-        <v>0.99827635377245738</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP31">
-        <v>31.600180838280902</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="BB31" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="BC31">
-        <v>0.93089405249526469</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD31">
-        <v>1266.9423709201483</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="Z32" t="s">
         <v>369</v>
       </c>
       <c r="AA32">
-        <v>0.99894650606645485</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB32">
-        <v>19.314055448326833</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10916,16 +10916,16 @@
         <v>419</v>
       </c>
       <c r="AM32" t="s">
+        <v>477</v>
+      </c>
+      <c r="AN32" t="s">
         <v>478</v>
       </c>
-      <c r="AN32" t="s">
-        <v>366</v>
-      </c>
       <c r="AO32">
-        <v>0.98949004263841422</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP32">
-        <v>192.68255162907312</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10952,16 +10952,16 @@
         <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="BB32" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="BC32">
-        <v>0.99302778580016682</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD32">
-        <v>127.82392699694152</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="Z33" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="AA33">
-        <v>0.98179245618315802</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB33">
-        <v>333.80496997543548</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11068,10 +11068,10 @@
         <v>480</v>
       </c>
       <c r="AO33">
-        <v>0.99750949182367343</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP33">
-        <v>45.659316565986806</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11098,16 +11098,16 @@
         <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="BB33" t="s">
-        <v>357</v>
+        <v>621</v>
       </c>
       <c r="BC33">
-        <v>0.97591598065988894</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD33">
-        <v>441.54035456870389</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Z34" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA34">
-        <v>0.99852430677621173</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB34">
-        <v>27.054375769451152</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11214,10 +11214,10 @@
         <v>482</v>
       </c>
       <c r="AO34">
-        <v>0.99811838305018963</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP34">
-        <v>34.496310746523356</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11244,16 +11244,16 @@
         <v>542</v>
       </c>
       <c r="BA34" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="BB34" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="BC34">
-        <v>0.99412039195829205</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD34">
-        <v>107.79281409797902</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="Z35" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AA35">
-        <v>0.99838604658336239</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB35">
-        <v>29.589145971689483</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11360,10 +11360,10 @@
         <v>484</v>
       </c>
       <c r="AO35">
-        <v>0.9985928182686985</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP35">
-        <v>25.798331740528162</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="BB35" t="s">
-        <v>444</v>
+        <v>625</v>
       </c>
       <c r="BC35">
-        <v>0.98292548292671178</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD35">
-        <v>313.03281301028323</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11464,16 +11464,16 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="Z36" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA36">
-        <v>0.9977500892185478</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB36">
-        <v>41.248364326622962</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
@@ -11506,10 +11506,10 @@
         <v>486</v>
       </c>
       <c r="AO36">
-        <v>0.99769811225811866</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP36">
-        <v>42.201275267825203</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11536,16 +11536,16 @@
         <v>546</v>
       </c>
       <c r="BA36" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="BB36" t="s">
-        <v>359</v>
+        <v>627</v>
       </c>
       <c r="BC36">
-        <v>0.98355967005268352</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD36">
-        <v>301.40604903413595</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11610,16 +11610,16 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Z37" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA37">
-        <v>0.9982812149336332</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB37">
-        <v>31.51105955005805</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
@@ -11649,13 +11649,13 @@
         <v>487</v>
       </c>
       <c r="AN37" t="s">
-        <v>359</v>
+        <v>488</v>
       </c>
       <c r="AO37">
-        <v>0.98814178187791379</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP37">
-        <v>217.40066557158059</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11682,16 +11682,16 @@
         <v>548</v>
       </c>
       <c r="BA37" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="BB37" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="BC37">
-        <v>0.97902641975794957</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD37">
-        <v>384.51563777092457</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11756,16 +11756,16 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Z38" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="AA38">
-        <v>0.98833720780868572</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB38">
-        <v>213.8178568407609</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
@@ -11792,16 +11792,16 @@
         <v>431</v>
       </c>
       <c r="AM38" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN38" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO38">
-        <v>0.99804155179341392</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP38">
-        <v>35.904883787411507</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11828,16 +11828,16 @@
         <v>550</v>
       </c>
       <c r="BA38" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="BB38" t="s">
-        <v>632</v>
+        <v>366</v>
       </c>
       <c r="BC38">
-        <v>0.9973402418125219</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD38">
-        <v>48.762233437098502</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11902,16 +11902,16 @@
         <v>341</v>
       </c>
       <c r="Y39" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Z39" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="AA39">
-        <v>0.96189283472138964</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB39">
-        <v>698.63136344118936</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD39" t="s">
         <v>282</v>
@@ -11938,16 +11938,16 @@
         <v>433</v>
       </c>
       <c r="AM39" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN39" t="s">
-        <v>491</v>
+        <v>369</v>
       </c>
       <c r="AO39">
-        <v>0.99508023417818925</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP39">
-        <v>90.195706733197795</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11974,16 +11974,16 @@
         <v>552</v>
       </c>
       <c r="BA39" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="BB39" t="s">
-        <v>357</v>
+        <v>631</v>
       </c>
       <c r="BC39">
-        <v>0.96140381292129873</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD39">
-        <v>707.59676310952364</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12048,16 +12048,16 @@
         <v>343</v>
       </c>
       <c r="Y40" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Z40" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AA40">
-        <v>0.99410594174368461</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB40">
-        <v>108.05773469911641</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD40" t="s">
         <v>282</v>
@@ -12090,10 +12090,10 @@
         <v>493</v>
       </c>
       <c r="AO40">
-        <v>0.99940622505963084</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP40">
-        <v>10.885873906767051</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="BB40" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="BC40">
-        <v>0.99234935324205875</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD40">
-        <v>140.26185722892211</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="Z41" t="s">
         <v>376</v>
       </c>
       <c r="AA41">
-        <v>0.98968917222400854</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB41">
-        <v>189.03184255984442</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
@@ -12236,10 +12236,10 @@
         <v>495</v>
       </c>
       <c r="AO41">
-        <v>0.99686124252542985</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP41">
-        <v>57.543887033786262</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12266,16 +12266,16 @@
         <v>556</v>
       </c>
       <c r="BA41" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="BB41" t="s">
-        <v>372</v>
+        <v>613</v>
       </c>
       <c r="BC41">
-        <v>0.99536692897647694</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD41">
-        <v>84.939635431255269</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12304,16 +12304,16 @@
         <v>558</v>
       </c>
       <c r="BA42" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="BB42" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="BC42">
-        <v>0.88199812838352587</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD42">
-        <v>2163.367646302027</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12342,16 +12342,16 @@
         <v>560</v>
       </c>
       <c r="BA43" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="BB43" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="BC43">
-        <v>0.98235584693125277</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD43">
-        <v>323.47613959369914</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12380,16 +12380,16 @@
         <v>562</v>
       </c>
       <c r="BA44" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="BB44" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="BC44">
-        <v>0.934538160869965</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD44">
-        <v>1200.1337173839754</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12418,16 +12418,16 @@
         <v>564</v>
       </c>
       <c r="BA45" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="BB45" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="BC45">
-        <v>0.94616153753972931</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD45">
-        <v>987.03847843829612</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12456,16 +12456,16 @@
         <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="BB46" t="s">
-        <v>357</v>
+        <v>641</v>
       </c>
       <c r="BC46">
-        <v>0.97218956380622079</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD46">
-        <v>509.85799688595205</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12494,16 +12494,16 @@
         <v>568</v>
       </c>
       <c r="BA47" t="s">
+        <v>642</v>
+      </c>
+      <c r="BB47" t="s">
         <v>643</v>
       </c>
-      <c r="BB47" t="s">
-        <v>644</v>
-      </c>
       <c r="BC47">
-        <v>0.9924172440074055</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD47">
-        <v>139.01719319756617</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12532,16 +12532,16 @@
         <v>570</v>
       </c>
       <c r="BA48" t="s">
+        <v>644</v>
+      </c>
+      <c r="BB48" t="s">
         <v>645</v>
       </c>
-      <c r="BB48" t="s">
-        <v>646</v>
-      </c>
       <c r="BC48">
-        <v>0.99114508565756532</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD48">
-        <v>162.34009627796874</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12570,16 +12570,16 @@
         <v>572</v>
       </c>
       <c r="BA49" t="s">
+        <v>646</v>
+      </c>
+      <c r="BB49" t="s">
         <v>647</v>
       </c>
-      <c r="BB49" t="s">
-        <v>648</v>
-      </c>
       <c r="BC49">
-        <v>0.99561586640696276</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD49">
-        <v>80.375782539015233</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12608,16 +12608,16 @@
         <v>574</v>
       </c>
       <c r="BA50" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="BB50" t="s">
-        <v>650</v>
+        <v>357</v>
       </c>
       <c r="BC50">
-        <v>0.99366677237144974</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD50">
-        <v>116.10917319008783</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12646,16 +12646,16 @@
         <v>576</v>
       </c>
       <c r="BA51" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="BB51" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="BC51">
-        <v>0.9205295464439136</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD51">
-        <v>1456.9583151949184</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12684,16 +12684,16 @@
         <v>578</v>
       </c>
       <c r="BA52" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="BB52" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="BC52">
-        <v>0.99519319222421976</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD52">
-        <v>88.124809222638589</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12722,16 +12722,16 @@
         <v>580</v>
       </c>
       <c r="BA53" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="BB53" t="s">
-        <v>467</v>
+        <v>654</v>
       </c>
       <c r="BC53">
-        <v>0.95726256957223688</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD53">
-        <v>783.51955784232393</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12760,16 +12760,16 @@
         <v>582</v>
       </c>
       <c r="BA54" t="s">
+        <v>655</v>
+      </c>
+      <c r="BB54" t="s">
         <v>656</v>
       </c>
-      <c r="BB54" t="s">
-        <v>444</v>
-      </c>
       <c r="BC54">
-        <v>0.9437657388784082</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD54">
-        <v>1030.9614538958492</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05E0B7D-888D-4E63-BC18-E33F9A764257}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1EC915-2B59-4872-9822-EFF25B5846A7}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>443</v>
+        <v>485</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>625</v>
+        <v>593</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13162,7 +13162,7 @@
         <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>655</v>
+        <v>598</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13263,7 +13263,7 @@
         <v>729</v>
       </c>
       <c r="X16" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13331,7 +13331,7 @@
         <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>633</v>
+        <v>600</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13399,7 +13399,7 @@
         <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13467,7 +13467,7 @@
         <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>649</v>
+        <v>614</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>631</v>
+        <v>591</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13910,7 +13910,7 @@
         <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13943,7 +13943,7 @@
         <v>749</v>
       </c>
       <c r="X26" t="s">
-        <v>616</v>
+        <v>589</v>
       </c>
       <c r="Y26">
         <v>63.731250000000003</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14011,7 +14011,7 @@
         <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="Y27">
         <v>28.239750000000001</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>472</v>
+        <v>441</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14147,7 +14147,7 @@
         <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Y29">
         <v>3.38625</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>490</v>
+        <v>451</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>629</v>
+        <v>597</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>597</v>
+        <v>655</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14759,7 +14759,7 @@
         <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="Y38">
         <v>64.437749999999994</v>
@@ -14794,7 +14794,7 @@
         <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14963,7 +14963,7 @@
         <v>779</v>
       </c>
       <c r="X41" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="Y41">
         <v>27.642749999999999</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>626</v>
+        <v>594</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>656</v>
+        <v>599</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15068,7 +15068,7 @@
         <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="Y44">
         <v>0.42149999999999999</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15138,7 +15138,7 @@
         <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>651</v>
+        <v>616</v>
       </c>
       <c r="Y46">
         <v>1.81725</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>628</v>
+        <v>596</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15243,7 +15243,7 @@
         <v>795</v>
       </c>
       <c r="X49" t="s">
-        <v>614</v>
+        <v>587</v>
       </c>
       <c r="Y49">
         <v>42.144750000000002</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>599</v>
+        <v>651</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>601</v>
+        <v>653</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC73FD5-C733-48CB-967D-49F8EF5CB3FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B5337C-083A-469B-AFC8-F4DE06E304D4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9076CAE5-2016-4E48-81C6-DB8D7A193F34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE530C1-9D2E-4E26-BCA5-41635F015C52}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1D9B58F-52DA-4E30-BC4A-B198EEE508A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DEDDE7F-0F1F-438F-9FFE-95F121E786DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,72 +980,180 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_021</t>
   </si>
   <si>
@@ -1064,202 +1172,232 @@
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
     <t>e_w179863079-275</t>
   </si>
   <si>
-    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
     <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
   </si>
   <si>
     <t>e_w179863079-275,e_JP6-275</t>
   </si>
   <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_wonelc_won_024</t>
@@ -1268,6 +1406,18 @@
     <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_019</t>
   </si>
   <si>
@@ -1280,34 +1430,16 @@
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
     <t>distr_wonelc_won_008</t>
@@ -1316,136 +1448,127 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
   </si>
   <si>
     <t>elc_won_024</t>
@@ -1454,6 +1577,18 @@
     <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
   </si>
   <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
     <t>elc_won_019</t>
   </si>
   <si>
@@ -1466,34 +1601,16 @@
     <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
   </si>
   <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
   </si>
   <si>
     <t>elc_won_008</t>
@@ -1502,121 +1619,16 @@
     <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
   </si>
   <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
   </si>
   <si>
     <t>distr_wofelc_wof_006</t>
@@ -1643,34 +1655,130 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_013</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_wofelc_wof_005</t>
@@ -1685,10 +1793,40 @@
     <t>connecting wind offshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wofelc_wof_029</t>
@@ -1721,72 +1859,6 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_030</t>
   </si>
   <si>
@@ -1811,76 +1883,16 @@
     <t>connecting wind offshore to buses in cluster 42</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
   </si>
   <si>
     <t>elc_wof_006</t>
@@ -1904,25 +1916,106 @@
     <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
   </si>
   <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
     <t>elc_wof_013</t>
   </si>
   <si>
     <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
   </si>
   <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
   </si>
   <si>
     <t>elc_wof_005</t>
@@ -1931,7 +2024,34 @@
     <t>elc_wof_033</t>
   </si>
   <si>
-    <t>elc_wof_007</t>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
   </si>
   <si>
     <t>elc_wof_029</t>
@@ -1961,66 +2081,6 @@
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
     <t>elc_wof_030</t>
   </si>
   <si>
@@ -2040,66 +2100,6 @@
   </si>
   <si>
     <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E52397-0F56-41E1-912C-05D6225FA055}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4FE38B-3769-4395-ABDF-F524AC2B626F}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7814,16 +7814,16 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.99116451092312863</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB11">
-        <v>161.98396640930775</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
@@ -7853,13 +7853,13 @@
         <v>439</v>
       </c>
       <c r="AN11" t="s">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="AO11">
-        <v>0.99682717865030179</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP11">
-        <v>58.168391411134159</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
@@ -7889,13 +7889,13 @@
         <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>358</v>
+        <v>585</v>
       </c>
       <c r="BC11">
-        <v>0.95957195194316591</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD11">
-        <v>741.18088104195795</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7960,16 +7960,16 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.99809166649408687</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB12">
-        <v>34.986114275074357</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
@@ -7996,16 +7996,16 @@
         <v>379</v>
       </c>
       <c r="AM12" t="s">
+        <v>440</v>
+      </c>
+      <c r="AN12" t="s">
         <v>441</v>
       </c>
-      <c r="AN12" t="s">
-        <v>442</v>
-      </c>
       <c r="AO12">
-        <v>0.99762356494824644</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP12">
-        <v>43.567975948815601</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8032,16 +8032,16 @@
         <v>498</v>
       </c>
       <c r="BA12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="BB12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="BC12">
-        <v>0.99603667376986049</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD12">
-        <v>72.660980885890424</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8106,16 +8106,16 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.99850557699173803</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB13">
-        <v>27.397755151469518</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
@@ -8142,16 +8142,16 @@
         <v>381</v>
       </c>
       <c r="AM13" t="s">
+        <v>442</v>
+      </c>
+      <c r="AN13" t="s">
         <v>443</v>
       </c>
-      <c r="AN13" t="s">
-        <v>444</v>
-      </c>
       <c r="AO13">
-        <v>0.99669176136177262</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP13">
-        <v>60.651041700835236</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8178,16 +8178,16 @@
         <v>500</v>
       </c>
       <c r="BA13" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="BB13" t="s">
-        <v>588</v>
+        <v>353</v>
       </c>
       <c r="BC13">
-        <v>0.99017867813273497</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD13">
-        <v>180.05756756652616</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8252,16 +8252,16 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.99621285878087551</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB14">
-        <v>69.43092235061502</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
@@ -8288,16 +8288,16 @@
         <v>383</v>
       </c>
       <c r="AM14" t="s">
+        <v>444</v>
+      </c>
+      <c r="AN14" t="s">
         <v>445</v>
       </c>
-      <c r="AN14" t="s">
-        <v>446</v>
-      </c>
       <c r="AO14">
-        <v>0.99841760060377538</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP14">
-        <v>29.010655597451841</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
@@ -8330,10 +8330,10 @@
         <v>590</v>
       </c>
       <c r="BC14">
-        <v>0.99504061303190972</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD14">
-        <v>90.922094414988095</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8398,16 +8398,16 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.9975431479552237</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB15">
-        <v>45.042287487565297</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
@@ -8434,16 +8434,16 @@
         <v>385</v>
       </c>
       <c r="AM15" t="s">
+        <v>446</v>
+      </c>
+      <c r="AN15" t="s">
         <v>447</v>
       </c>
-      <c r="AN15" t="s">
-        <v>448</v>
-      </c>
       <c r="AO15">
-        <v>0.99781438034778358</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP15">
-        <v>40.069693623967019</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
@@ -8476,10 +8476,10 @@
         <v>592</v>
       </c>
       <c r="BC15">
-        <v>0.9973402418125219</v>
+        <v>0.99017867813273497</v>
       </c>
       <c r="BD15">
-        <v>48.762233437098502</v>
+        <v>180.05756756652616</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8544,16 +8544,16 @@
         <v>295</v>
       </c>
       <c r="Y16" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="Z16" t="s">
         <v>354</v>
       </c>
       <c r="AA16">
-        <v>0.99636728996375623</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB16">
-        <v>66.599683997802714</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD16" t="s">
         <v>282</v>
@@ -8580,16 +8580,16 @@
         <v>387</v>
       </c>
       <c r="AM16" t="s">
+        <v>448</v>
+      </c>
+      <c r="AN16" t="s">
         <v>449</v>
       </c>
-      <c r="AN16" t="s">
-        <v>450</v>
-      </c>
       <c r="AO16">
-        <v>0.99804155179341392</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP16">
-        <v>35.904883787411507</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8619,13 +8619,13 @@
         <v>593</v>
       </c>
       <c r="BB16" t="s">
-        <v>358</v>
+        <v>594</v>
       </c>
       <c r="BC16">
-        <v>0.97591598065988894</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD16">
-        <v>441.54035456870389</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.9488788277802801</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB17">
-        <v>937.22149069486488</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8726,16 +8726,16 @@
         <v>389</v>
       </c>
       <c r="AM17" t="s">
+        <v>450</v>
+      </c>
+      <c r="AN17" t="s">
         <v>451</v>
       </c>
-      <c r="AN17" t="s">
-        <v>452</v>
-      </c>
       <c r="AO17">
-        <v>0.99508023417818925</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP17">
-        <v>90.195706733197795</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="BB17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="BC17">
-        <v>0.99412039195829205</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD17">
-        <v>107.79281409797902</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8836,16 +8836,16 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.99852430677621173</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB18">
-        <v>27.054375769451152</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
@@ -8872,16 +8872,16 @@
         <v>391</v>
       </c>
       <c r="AM18" t="s">
+        <v>452</v>
+      </c>
+      <c r="AN18" t="s">
         <v>453</v>
       </c>
-      <c r="AN18" t="s">
-        <v>454</v>
-      </c>
       <c r="AO18">
-        <v>0.99940622505963084</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP18">
-        <v>10.885873906767051</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="BB18" t="s">
-        <v>486</v>
+        <v>598</v>
       </c>
       <c r="BC18">
-        <v>0.98292548292671178</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD18">
-        <v>313.03281301028323</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.99838604658336239</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB19">
-        <v>29.589145971689483</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9018,16 +9018,16 @@
         <v>393</v>
       </c>
       <c r="AM19" t="s">
+        <v>454</v>
+      </c>
+      <c r="AN19" t="s">
         <v>455</v>
       </c>
-      <c r="AN19" t="s">
-        <v>456</v>
-      </c>
       <c r="AO19">
-        <v>0.99869874972548245</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP19">
-        <v>23.856255032822389</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9054,16 +9054,16 @@
         <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="BB19" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="BC19">
-        <v>0.98355967005268352</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD19">
-        <v>301.40604903413595</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.97633688849282452</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB20">
-        <v>433.82371096488447</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9164,16 +9164,16 @@
         <v>395</v>
       </c>
       <c r="AM20" t="s">
+        <v>456</v>
+      </c>
+      <c r="AN20" t="s">
         <v>457</v>
       </c>
-      <c r="AN20" t="s">
-        <v>360</v>
-      </c>
       <c r="AO20">
-        <v>0.99192535126433146</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP20">
-        <v>148.0352268205892</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9200,16 +9200,16 @@
         <v>514</v>
       </c>
       <c r="BA20" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="BB20" t="s">
-        <v>461</v>
+        <v>353</v>
       </c>
       <c r="BC20">
-        <v>0.95726256957223688</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD20">
-        <v>783.51955784232393</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Z21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.96189283472138964</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB21">
-        <v>698.63136344118936</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9313,13 +9313,13 @@
         <v>458</v>
       </c>
       <c r="AN21" t="s">
-        <v>369</v>
+        <v>459</v>
       </c>
       <c r="AO21">
-        <v>0.98092693557487454</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP21">
-        <v>349.67284779396647</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9346,16 +9346,16 @@
         <v>516</v>
       </c>
       <c r="BA21" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="BB21" t="s">
-        <v>486</v>
+        <v>602</v>
       </c>
       <c r="BC21">
-        <v>0.9437657388784082</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD21">
-        <v>1030.9614538958492</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Z22" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.99410594174368461</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB22">
-        <v>108.05773469911641</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9456,16 +9456,16 @@
         <v>399</v>
       </c>
       <c r="AM22" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN22" t="s">
-        <v>358</v>
+        <v>461</v>
       </c>
       <c r="AO22">
-        <v>0.93717435218793788</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP22">
-        <v>1151.8035432211395</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9492,16 +9492,16 @@
         <v>518</v>
       </c>
       <c r="BA22" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="BB22" t="s">
-        <v>358</v>
+        <v>449</v>
       </c>
       <c r="BC22">
-        <v>0.96140381292129873</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD22">
-        <v>707.59676310952364</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="Z23" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA23">
-        <v>0.98968917222400854</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB23">
-        <v>189.03184255984442</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9602,16 +9602,16 @@
         <v>401</v>
       </c>
       <c r="AM23" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AN23" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO23">
-        <v>0.96551955124232614</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP23">
-        <v>632.14156055735509</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9638,16 +9638,16 @@
         <v>520</v>
       </c>
       <c r="BA23" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="BB23" t="s">
-        <v>602</v>
+        <v>374</v>
       </c>
       <c r="BC23">
-        <v>0.99490784156958001</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD23">
-        <v>93.356237891033686</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="Z24" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="AA24">
-        <v>0.99628076912917996</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB24">
-        <v>68.185899298368355</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN24" t="s">
-        <v>463</v>
+        <v>374</v>
       </c>
       <c r="AO24">
-        <v>0.99693456929731861</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP24">
-        <v>56.199562882493169</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9784,16 +9784,16 @@
         <v>522</v>
       </c>
       <c r="BA24" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="BB24" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="BC24">
-        <v>0.99015836110796274</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD24">
-        <v>180.43004635401576</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="Z25" t="s">
         <v>362</v>
       </c>
       <c r="AA25">
-        <v>0.99726055556014181</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB25">
-        <v>50.223148064066145</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN25" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO25">
-        <v>0.99686124252542985</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP25">
-        <v>57.543887033786262</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="BB25" t="s">
-        <v>606</v>
+        <v>350</v>
       </c>
       <c r="BC25">
-        <v>0.99623532634854861</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD25">
-        <v>69.01901694327529</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10004,16 +10004,16 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="Z26" t="s">
         <v>363</v>
       </c>
       <c r="AA26">
-        <v>0.9981032549815434</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB26">
-        <v>34.773658671704098</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
@@ -10040,16 +10040,16 @@
         <v>407</v>
       </c>
       <c r="AM26" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN26" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO26">
-        <v>0.99870022163576544</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP26">
-        <v>23.829270010966344</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10076,16 +10076,16 @@
         <v>526</v>
       </c>
       <c r="BA26" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="BB26" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="BC26">
-        <v>0.9966173923071765</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD26">
-        <v>62.014474368430825</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10150,16 +10150,16 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s">
         <v>364</v>
       </c>
       <c r="AA27">
-        <v>0.99825665520226836</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB27">
-        <v>31.96132129174655</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
@@ -10186,16 +10186,16 @@
         <v>409</v>
       </c>
       <c r="AM27" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN27" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO27">
-        <v>0.99807466477127271</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP27">
-        <v>35.297812526667357</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="BB27" t="s">
-        <v>369</v>
+        <v>611</v>
       </c>
       <c r="BC27">
-        <v>0.98180592470173533</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD27">
-        <v>333.55804713485287</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10296,16 +10296,16 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Z28" t="s">
         <v>365</v>
       </c>
       <c r="AA28">
-        <v>0.99894650606645485</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB28">
-        <v>19.314055448326833</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
@@ -10332,16 +10332,16 @@
         <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO28">
-        <v>0.99811838305018963</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP28">
-        <v>34.496310746523356</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="BB28" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="BC28">
-        <v>0.99253849155603513</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD28">
-        <v>136.79432147269009</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="Z29" t="s">
         <v>366</v>
       </c>
       <c r="AA29">
-        <v>0.98179245618315802</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB29">
-        <v>333.80496997543548</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10478,16 +10478,16 @@
         <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN29" t="s">
-        <v>473</v>
+        <v>376</v>
       </c>
       <c r="AO29">
-        <v>0.9985928182686985</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP29">
-        <v>25.798331740528162</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="BB29" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="BC29">
-        <v>0.973232135644435</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD29">
-        <v>490.74417985202501</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="Z30" t="s">
         <v>367</v>
       </c>
       <c r="AA30">
-        <v>0.9977500892185478</v>
+        <v>0.99809166649408687</v>
       </c>
       <c r="AB30">
-        <v>41.248364326622962</v>
+        <v>34.986114275074357</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10627,13 +10627,13 @@
         <v>474</v>
       </c>
       <c r="AN30" t="s">
-        <v>475</v>
+        <v>360</v>
       </c>
       <c r="AO30">
-        <v>0.99769811225811866</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP30">
-        <v>42.201275267825203</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="BB30" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="BC30">
-        <v>0.99366677237144974</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD30">
-        <v>116.10917319008783</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Z31" t="s">
         <v>368</v>
       </c>
       <c r="AA31">
-        <v>0.9982812149336332</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB31">
-        <v>31.51105955005805</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10770,16 +10770,16 @@
         <v>417</v>
       </c>
       <c r="AM31" t="s">
+        <v>475</v>
+      </c>
+      <c r="AN31" t="s">
         <v>476</v>
       </c>
-      <c r="AN31" t="s">
-        <v>349</v>
-      </c>
       <c r="AO31">
-        <v>0.98814178187791379</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP31">
-        <v>217.40066557158059</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="BB31" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="BC31">
-        <v>0.9205295464439136</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD31">
-        <v>1456.9583151949184</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="Z32" t="s">
         <v>369</v>
       </c>
       <c r="AA32">
-        <v>0.98833720780868572</v>
+        <v>0.99621285878087551</v>
       </c>
       <c r="AB32">
-        <v>213.8178568407609</v>
+        <v>69.43092235061502</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10922,10 +10922,10 @@
         <v>478</v>
       </c>
       <c r="AO32">
-        <v>0.99863922747017897</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP32">
-        <v>24.947496380053089</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10952,16 +10952,16 @@
         <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="BB32" t="s">
-        <v>619</v>
+        <v>353</v>
       </c>
       <c r="BC32">
-        <v>0.99519319222421976</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD32">
-        <v>88.124809222638589</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="Z33" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="AA33">
-        <v>0.94069903208664407</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB33">
-        <v>1087.1844117448593</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11065,13 +11065,13 @@
         <v>479</v>
       </c>
       <c r="AN33" t="s">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="AO33">
-        <v>0.99582230548799566</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP33">
-        <v>76.591066053413869</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11098,16 +11098,16 @@
         <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="BB33" t="s">
-        <v>621</v>
+        <v>353</v>
       </c>
       <c r="BC33">
-        <v>0.98822137145239475</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD33">
-        <v>215.94152337276336</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="Z34" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA34">
-        <v>0.99756610784588629</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB34">
-        <v>44.621356158751233</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11208,16 +11208,16 @@
         <v>423</v>
       </c>
       <c r="AM34" t="s">
+        <v>480</v>
+      </c>
+      <c r="AN34" t="s">
         <v>481</v>
       </c>
-      <c r="AN34" t="s">
-        <v>482</v>
-      </c>
       <c r="AO34">
-        <v>0.99710631799330929</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP34">
-        <v>53.050836789329388</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11247,13 +11247,13 @@
         <v>622</v>
       </c>
       <c r="BB34" t="s">
-        <v>623</v>
+        <v>353</v>
       </c>
       <c r="BC34">
-        <v>0.99662747375050009</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD34">
-        <v>61.829647907498845</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="Z35" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA35">
-        <v>0.9972084849335241</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB35">
-        <v>51.177776218725121</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11354,16 +11354,16 @@
         <v>425</v>
       </c>
       <c r="AM35" t="s">
+        <v>482</v>
+      </c>
+      <c r="AN35" t="s">
         <v>483</v>
       </c>
-      <c r="AN35" t="s">
-        <v>484</v>
-      </c>
       <c r="AO35">
-        <v>0.99550555557680764</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP35">
-        <v>82.398147758527074</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
+        <v>623</v>
+      </c>
+      <c r="BB35" t="s">
         <v>624</v>
       </c>
-      <c r="BB35" t="s">
-        <v>625</v>
-      </c>
       <c r="BC35">
-        <v>0.99284590877035406</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD35">
-        <v>131.158339210175</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11464,16 +11464,16 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="Z36" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA36">
-        <v>0.99900168239190124</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB36">
-        <v>18.302489481810518</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
@@ -11500,16 +11500,16 @@
         <v>427</v>
       </c>
       <c r="AM36" t="s">
+        <v>484</v>
+      </c>
+      <c r="AN36" t="s">
         <v>485</v>
       </c>
-      <c r="AN36" t="s">
-        <v>486</v>
-      </c>
       <c r="AO36">
-        <v>0.93896180472603763</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP36">
-        <v>1119.0335800226442</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11536,16 +11536,16 @@
         <v>546</v>
       </c>
       <c r="BA36" t="s">
+        <v>625</v>
+      </c>
+      <c r="BB36" t="s">
         <v>626</v>
       </c>
-      <c r="BB36" t="s">
-        <v>627</v>
-      </c>
       <c r="BC36">
-        <v>0.97803702976044449</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD36">
-        <v>402.65445439185123</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11610,16 +11610,16 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Z37" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="AA37">
-        <v>0.99391268208184824</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB37">
-        <v>111.60082849944791</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
@@ -11646,16 +11646,16 @@
         <v>429</v>
       </c>
       <c r="AM37" t="s">
+        <v>486</v>
+      </c>
+      <c r="AN37" t="s">
         <v>487</v>
       </c>
-      <c r="AN37" t="s">
-        <v>488</v>
-      </c>
       <c r="AO37">
-        <v>0.99750949182367343</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP37">
-        <v>45.659316565986806</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11682,16 +11682,16 @@
         <v>548</v>
       </c>
       <c r="BA37" t="s">
+        <v>627</v>
+      </c>
+      <c r="BB37" t="s">
         <v>628</v>
       </c>
-      <c r="BB37" t="s">
-        <v>349</v>
-      </c>
       <c r="BC37">
-        <v>0.98235584693125277</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD37">
-        <v>323.47613959369914</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11756,16 +11756,16 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="Z38" t="s">
         <v>374</v>
       </c>
       <c r="AA38">
-        <v>0.99871218762601011</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB38">
-        <v>23.609893523147914</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
@@ -11792,16 +11792,16 @@
         <v>431</v>
       </c>
       <c r="AM38" t="s">
+        <v>488</v>
+      </c>
+      <c r="AN38" t="s">
         <v>489</v>
       </c>
-      <c r="AN38" t="s">
-        <v>490</v>
-      </c>
       <c r="AO38">
-        <v>0.99827635377245738</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP38">
-        <v>31.600180838280902</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11831,13 +11831,13 @@
         <v>629</v>
       </c>
       <c r="BB38" t="s">
-        <v>366</v>
+        <v>441</v>
       </c>
       <c r="BC38">
-        <v>0.97902641975794957</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD38">
-        <v>384.51563777092457</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11902,16 +11902,16 @@
         <v>341</v>
       </c>
       <c r="Y39" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="Z39" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="AA39">
-        <v>0.99856748800713691</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB39">
-        <v>26.26271986915707</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD39" t="s">
         <v>282</v>
@@ -11938,16 +11938,16 @@
         <v>433</v>
       </c>
       <c r="AM39" t="s">
+        <v>490</v>
+      </c>
+      <c r="AN39" t="s">
         <v>491</v>
       </c>
-      <c r="AN39" t="s">
-        <v>369</v>
-      </c>
       <c r="AO39">
-        <v>0.98949004263841422</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP39">
-        <v>192.68255162907312</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11977,13 +11977,13 @@
         <v>630</v>
       </c>
       <c r="BB39" t="s">
-        <v>631</v>
+        <v>449</v>
       </c>
       <c r="BC39">
-        <v>0.98779966071713954</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD39">
-        <v>223.67288685244134</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12048,16 +12048,16 @@
         <v>343</v>
       </c>
       <c r="Y40" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="Z40" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="AA40">
-        <v>0.97905685820454003</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB40">
-        <v>383.95759958343297</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD40" t="s">
         <v>282</v>
@@ -12090,10 +12090,10 @@
         <v>493</v>
       </c>
       <c r="AO40">
-        <v>0.99013353407586135</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP40">
-        <v>180.88520860920943</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
+        <v>631</v>
+      </c>
+      <c r="BB40" t="s">
         <v>632</v>
       </c>
-      <c r="BB40" t="s">
-        <v>633</v>
-      </c>
       <c r="BC40">
-        <v>0.98841501119699848</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD40">
-        <v>212.39146138836088</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="Z41" t="s">
         <v>376</v>
       </c>
       <c r="AA41">
-        <v>0.99798824264234642</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB41">
-        <v>36.882218223648351</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
@@ -12236,10 +12236,10 @@
         <v>495</v>
       </c>
       <c r="AO41">
-        <v>0.99869589057011365</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP41">
-        <v>23.908672881248773</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12266,16 +12266,16 @@
         <v>556</v>
       </c>
       <c r="BA41" t="s">
+        <v>633</v>
+      </c>
+      <c r="BB41" t="s">
         <v>634</v>
       </c>
-      <c r="BB41" t="s">
-        <v>613</v>
-      </c>
       <c r="BC41">
-        <v>0.93089405249526469</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD41">
-        <v>1266.9423709201483</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12310,10 +12310,10 @@
         <v>636</v>
       </c>
       <c r="BC42">
-        <v>0.99302778580016682</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD42">
-        <v>127.82392699694152</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12345,13 +12345,13 @@
         <v>637</v>
       </c>
       <c r="BB43" t="s">
-        <v>358</v>
+        <v>638</v>
       </c>
       <c r="BC43">
-        <v>0.934538160869965</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD43">
-        <v>1200.1337173839754</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12380,16 +12380,16 @@
         <v>562</v>
       </c>
       <c r="BA44" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="BB44" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="BC44">
-        <v>0.94616153753972931</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD44">
-        <v>987.03847843829612</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12418,16 +12418,16 @@
         <v>564</v>
       </c>
       <c r="BA45" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="BB45" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="BC45">
-        <v>0.97218956380622079</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD45">
-        <v>509.85799688595205</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12456,16 +12456,16 @@
         <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB46" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="BC46">
-        <v>0.9924172440074055</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD46">
-        <v>139.01719319756617</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12494,16 +12494,16 @@
         <v>568</v>
       </c>
       <c r="BA47" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BB47" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="BC47">
-        <v>0.99114508565756532</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD47">
-        <v>162.34009627796874</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12532,16 +12532,16 @@
         <v>570</v>
       </c>
       <c r="BA48" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="BB48" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="BC48">
-        <v>0.99561586640696276</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD48">
-        <v>80.375782539015233</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12570,16 +12570,16 @@
         <v>572</v>
       </c>
       <c r="BA49" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="BB49" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BC49">
-        <v>0.99234935324205875</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD49">
-        <v>140.26185722892211</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12608,16 +12608,16 @@
         <v>574</v>
       </c>
       <c r="BA50" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="BB50" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="BC50">
-        <v>0.99536692897647694</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD50">
-        <v>84.939635431255269</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12646,16 +12646,16 @@
         <v>576</v>
       </c>
       <c r="BA51" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="BB51" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="BC51">
-        <v>0.88199812838352587</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD51">
-        <v>2163.367646302027</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12684,16 +12684,16 @@
         <v>578</v>
       </c>
       <c r="BA52" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="BB52" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="BC52">
-        <v>0.99681267676383467</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD52">
-        <v>58.434259329697142</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12722,16 +12722,16 @@
         <v>580</v>
       </c>
       <c r="BA53" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="BB53" t="s">
-        <v>654</v>
+        <v>598</v>
       </c>
       <c r="BC53">
-        <v>0.99602290686668338</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD53">
-        <v>72.91337411080552</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12766,10 +12766,10 @@
         <v>656</v>
       </c>
       <c r="BC54">
-        <v>0.99637036284424008</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD54">
-        <v>66.543347855598327</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1EC915-2B59-4872-9822-EFF25B5846A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF2B0D4-7FCE-41A5-9BDF-634FE71E8AAB}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13162,7 +13162,7 @@
         <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13263,7 +13263,7 @@
         <v>729</v>
       </c>
       <c r="X16" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13331,7 +13331,7 @@
         <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13399,7 +13399,7 @@
         <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>648</v>
+        <v>607</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>607</v>
+        <v>647</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13910,7 +13910,7 @@
         <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>487</v>
+        <v>450</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13943,7 +13943,7 @@
         <v>749</v>
       </c>
       <c r="X26" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="Y26">
         <v>63.731250000000003</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>609</v>
+        <v>649</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14147,7 +14147,7 @@
         <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="Y29">
         <v>3.38625</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>603</v>
+        <v>643</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>655</v>
+        <v>612</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14759,7 +14759,7 @@
         <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>646</v>
+        <v>605</v>
       </c>
       <c r="Y38">
         <v>64.437749999999994</v>
@@ -14794,7 +14794,7 @@
         <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>601</v>
+        <v>641</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14963,7 +14963,7 @@
         <v>779</v>
       </c>
       <c r="X41" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="Y41">
         <v>27.642749999999999</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15068,7 +15068,7 @@
         <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>649</v>
+        <v>608</v>
       </c>
       <c r="Y44">
         <v>0.42149999999999999</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>612</v>
+        <v>597</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15243,7 +15243,7 @@
         <v>795</v>
       </c>
       <c r="X49" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="Y49">
         <v>42.144750000000002</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>651</v>
+        <v>584</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>653</v>
+        <v>586</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>605</v>
+        <v>645</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B5337C-083A-469B-AFC8-F4DE06E304D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4F0FB0-F65C-4F28-B822-90F8BFFF0DD7}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE530C1-9D2E-4E26-BCA5-41635F015C52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2133D946-8218-4F6D-9F6F-27071B45715F}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DEDDE7F-0F1F-438F-9FFE-95F121E786DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4560B97-0F08-44BB-AB45-E56CE64751D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,28 +980,190 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_015</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_solelc_spv_028</t>
@@ -1010,256 +1172,106 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
     <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
   </si>
   <si>
     <t>e_w216956620-500,e_w216953915-500</t>
   </si>
   <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
   </si>
   <si>
     <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wonelc_won_004</t>
@@ -1280,6 +1292,132 @@
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_007</t>
   </si>
   <si>
@@ -1298,126 +1436,6 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_019</t>
   </si>
   <si>
@@ -1430,22 +1448,16 @@
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
     <t>elc_won_004</t>
@@ -1463,6 +1475,120 @@
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
   </si>
   <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
+  </si>
+  <si>
     <t>elc_won_007</t>
   </si>
   <si>
@@ -1481,114 +1607,6 @@
     <t>e_JP219-500,e_JP132-500</t>
   </si>
   <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
     <t>elc_won_019</t>
   </si>
   <si>
@@ -1601,22 +1619,58 @@
     <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
   </si>
   <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wofelc_wof_040</t>
@@ -1631,28 +1685,190 @@
     <t>connecting wind offshore to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_014</t>
@@ -1667,220 +1883,49 @@
     <t>connecting wind offshore to buses in cluster 38</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
   </si>
   <si>
     <t>elc_wof_040</t>
@@ -1895,25 +1940,157 @@
     <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
   </si>
   <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
   </si>
   <si>
     <t>elc_wof_014</t>
@@ -1923,183 +2100,6 @@
   </si>
   <si>
     <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4FE38B-3769-4395-ABDF-F524AC2B626F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3178471-0D50-444B-A0AE-66925D398DB0}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7814,16 +7814,16 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.99852430677621173</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB11">
-        <v>27.054375769451152</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
@@ -7853,13 +7853,13 @@
         <v>439</v>
       </c>
       <c r="AN11" t="s">
-        <v>353</v>
+        <v>440</v>
       </c>
       <c r="AO11">
-        <v>0.93717435218793788</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP11">
-        <v>1151.8035432211395</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
@@ -7892,10 +7892,10 @@
         <v>585</v>
       </c>
       <c r="BC11">
-        <v>0.99681267676383467</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD11">
-        <v>58.434259329697142</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7960,16 +7960,16 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.99838604658336239</v>
+        <v>0.99809166649408687</v>
       </c>
       <c r="AB12">
-        <v>29.589145971689483</v>
+        <v>34.986114275074357</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
@@ -7996,16 +7996,16 @@
         <v>379</v>
       </c>
       <c r="AM12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO12">
-        <v>0.96551955124232614</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP12">
-        <v>632.14156055735509</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8038,10 +8038,10 @@
         <v>587</v>
       </c>
       <c r="BC12">
-        <v>0.99602290686668338</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD12">
-        <v>72.91337411080552</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8106,16 +8106,16 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.9981032549815434</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB13">
-        <v>34.773658671704098</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
@@ -8142,16 +8142,16 @@
         <v>381</v>
       </c>
       <c r="AM13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN13" t="s">
-        <v>443</v>
+        <v>363</v>
       </c>
       <c r="AO13">
-        <v>0.99693456929731861</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP13">
-        <v>56.199562882493169</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8181,13 +8181,13 @@
         <v>588</v>
       </c>
       <c r="BB13" t="s">
-        <v>353</v>
+        <v>589</v>
       </c>
       <c r="BC13">
-        <v>0.95957195194316591</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD13">
-        <v>741.18088104195795</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8252,16 +8252,16 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.99798824264234642</v>
+        <v>0.99621285878087551</v>
       </c>
       <c r="AB14">
-        <v>36.882218223648351</v>
+        <v>69.43092235061502</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
@@ -8294,10 +8294,10 @@
         <v>445</v>
       </c>
       <c r="AO14">
-        <v>0.99710631799330929</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP14">
-        <v>53.050836789329388</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
@@ -8324,16 +8324,16 @@
         <v>502</v>
       </c>
       <c r="BA14" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="BB14" t="s">
-        <v>590</v>
+        <v>375</v>
       </c>
       <c r="BC14">
-        <v>0.99603667376986049</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD14">
-        <v>72.660980885890424</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8398,16 +8398,16 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.94069903208664407</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB15">
-        <v>1087.1844117448593</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
@@ -8440,10 +8440,10 @@
         <v>447</v>
       </c>
       <c r="AO15">
-        <v>0.99550555557680764</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP15">
-        <v>82.398147758527074</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
@@ -8473,13 +8473,13 @@
         <v>591</v>
       </c>
       <c r="BB15" t="s">
-        <v>592</v>
+        <v>363</v>
       </c>
       <c r="BC15">
-        <v>0.99017867813273497</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD15">
-        <v>180.05756756652616</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8544,16 +8544,16 @@
         <v>295</v>
       </c>
       <c r="Y16" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="Z16" t="s">
         <v>354</v>
       </c>
       <c r="AA16">
-        <v>0.99756610784588629</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB16">
-        <v>44.621356158751233</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD16" t="s">
         <v>282</v>
@@ -8586,10 +8586,10 @@
         <v>449</v>
       </c>
       <c r="AO16">
-        <v>0.93896180472603763</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP16">
-        <v>1119.0335800226442</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8616,16 +8616,16 @@
         <v>506</v>
       </c>
       <c r="BA16" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="BB16" t="s">
-        <v>594</v>
+        <v>363</v>
       </c>
       <c r="BC16">
-        <v>0.99504061303190972</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD16">
-        <v>90.922094414988095</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.9972084849335241</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB17">
-        <v>51.177776218725121</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8732,10 +8732,10 @@
         <v>451</v>
       </c>
       <c r="AO17">
-        <v>0.99750949182367343</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP17">
-        <v>45.659316565986806</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="BB17" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="BC17">
-        <v>0.99253849155603513</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD17">
-        <v>136.79432147269009</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8875,13 +8875,13 @@
         <v>452</v>
       </c>
       <c r="AN18" t="s">
-        <v>453</v>
+        <v>369</v>
       </c>
       <c r="AO18">
-        <v>0.99804155179341392</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP18">
-        <v>35.904883787411507</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="BB18" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="BC18">
-        <v>0.973232135644435</v>
+        <v>0.99017867813273497</v>
       </c>
       <c r="BD18">
-        <v>490.74417985202501</v>
+        <v>180.05756756652616</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.99391268208184824</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB19">
-        <v>111.60082849944791</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9018,16 +9018,16 @@
         <v>393</v>
       </c>
       <c r="AM19" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN19" t="s">
         <v>454</v>
       </c>
-      <c r="AN19" t="s">
-        <v>455</v>
-      </c>
       <c r="AO19">
-        <v>0.99508023417818925</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP19">
-        <v>90.195706733197795</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9054,16 +9054,16 @@
         <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="BB19" t="s">
-        <v>353</v>
+        <v>598</v>
       </c>
       <c r="BC19">
-        <v>0.96140381292129873</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD19">
-        <v>707.59676310952364</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.99871218762601011</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB20">
-        <v>23.609893523147914</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9164,16 +9164,16 @@
         <v>395</v>
       </c>
       <c r="AM20" t="s">
+        <v>455</v>
+      </c>
+      <c r="AN20" t="s">
         <v>456</v>
       </c>
-      <c r="AN20" t="s">
-        <v>457</v>
-      </c>
       <c r="AO20">
-        <v>0.99940622505963084</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP20">
-        <v>10.885873906767051</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9200,16 +9200,16 @@
         <v>514</v>
       </c>
       <c r="BA20" t="s">
+        <v>599</v>
+      </c>
+      <c r="BB20" t="s">
         <v>600</v>
       </c>
-      <c r="BB20" t="s">
-        <v>353</v>
-      </c>
       <c r="BC20">
-        <v>0.97591598065988894</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD20">
-        <v>441.54035456870389</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="Z21" t="s">
         <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.99856748800713691</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB21">
-        <v>26.26271986915707</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9310,16 +9310,16 @@
         <v>397</v>
       </c>
       <c r="AM21" t="s">
+        <v>457</v>
+      </c>
+      <c r="AN21" t="s">
         <v>458</v>
       </c>
-      <c r="AN21" t="s">
-        <v>459</v>
-      </c>
       <c r="AO21">
-        <v>0.99811838305018963</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP21">
-        <v>34.496310746523356</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9352,10 +9352,10 @@
         <v>602</v>
       </c>
       <c r="BC21">
-        <v>0.99412039195829205</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD21">
-        <v>107.79281409797902</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z22" t="s">
         <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.97905685820454003</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB22">
-        <v>383.95759958343297</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9456,16 +9456,16 @@
         <v>399</v>
       </c>
       <c r="AM22" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AN22" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="AO22">
-        <v>0.9985928182686985</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP22">
-        <v>25.798331740528162</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9495,13 +9495,13 @@
         <v>603</v>
       </c>
       <c r="BB22" t="s">
-        <v>449</v>
+        <v>604</v>
       </c>
       <c r="BC22">
-        <v>0.98292548292671178</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD22">
-        <v>313.03281301028323</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s">
         <v>361</v>
       </c>
       <c r="AA23">
-        <v>0.99726055556014181</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB23">
-        <v>50.223148064066145</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9602,16 +9602,16 @@
         <v>401</v>
       </c>
       <c r="AM23" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AN23" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AO23">
-        <v>0.99769811225811866</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP23">
-        <v>42.201275267825203</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9638,16 +9638,16 @@
         <v>520</v>
       </c>
       <c r="BA23" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="BB23" t="s">
-        <v>374</v>
+        <v>606</v>
       </c>
       <c r="BC23">
-        <v>0.98355967005268352</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD23">
-        <v>301.40604903413595</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AA24">
-        <v>0.97633688849282452</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB24">
-        <v>433.82371096488447</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AN24" t="s">
-        <v>374</v>
+        <v>463</v>
       </c>
       <c r="AO24">
-        <v>0.98814178187791379</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP24">
-        <v>217.40066557158059</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9784,16 +9784,16 @@
         <v>522</v>
       </c>
       <c r="BA24" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="BB24" t="s">
-        <v>606</v>
+        <v>362</v>
       </c>
       <c r="BC24">
-        <v>0.99234935324205875</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD24">
-        <v>140.26185722892211</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Z25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA25">
-        <v>0.99825665520226836</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB25">
-        <v>31.96132129174655</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
+        <v>464</v>
+      </c>
+      <c r="AN25" t="s">
         <v>465</v>
       </c>
-      <c r="AN25" t="s">
-        <v>466</v>
-      </c>
       <c r="AO25">
-        <v>0.99870022163576544</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP25">
-        <v>23.829270010966344</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="BB25" t="s">
-        <v>350</v>
+        <v>609</v>
       </c>
       <c r="BC25">
-        <v>0.99536692897647694</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD25">
-        <v>84.939635431255269</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10004,16 +10004,16 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="Z26" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA26">
-        <v>0.99894650606645485</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB26">
-        <v>19.314055448326833</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
@@ -10040,16 +10040,16 @@
         <v>407</v>
       </c>
       <c r="AM26" t="s">
+        <v>466</v>
+      </c>
+      <c r="AN26" t="s">
         <v>467</v>
       </c>
-      <c r="AN26" t="s">
-        <v>468</v>
-      </c>
       <c r="AO26">
-        <v>0.99807466477127271</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP26">
-        <v>35.297812526667357</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10076,16 +10076,16 @@
         <v>526</v>
       </c>
       <c r="BA26" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="BB26" t="s">
-        <v>609</v>
+        <v>359</v>
       </c>
       <c r="BC26">
-        <v>0.88199812838352587</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD26">
-        <v>2163.367646302027</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10150,16 +10150,16 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA27">
-        <v>0.98179245618315802</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB27">
-        <v>333.80496997543548</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
@@ -10186,16 +10186,16 @@
         <v>409</v>
       </c>
       <c r="AM27" t="s">
+        <v>468</v>
+      </c>
+      <c r="AN27" t="s">
         <v>469</v>
       </c>
-      <c r="AN27" t="s">
-        <v>470</v>
-      </c>
       <c r="AO27">
-        <v>0.99841760060377538</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP27">
-        <v>29.010655597451841</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="BB27" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="BC27">
-        <v>0.9973402418125219</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD27">
-        <v>48.762233437098502</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10296,16 +10296,16 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA28">
-        <v>0.99900168239190124</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB28">
-        <v>18.302489481810518</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
@@ -10332,16 +10332,16 @@
         <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AN28" t="s">
-        <v>472</v>
+        <v>365</v>
       </c>
       <c r="AO28">
-        <v>0.99781438034778358</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP28">
-        <v>40.069693623967019</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="BB28" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="BC28">
-        <v>0.99637036284424008</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD28">
-        <v>66.543347855598327</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="Z29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA29">
-        <v>0.9488788277802801</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB29">
-        <v>937.22149069486488</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10478,16 +10478,16 @@
         <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AN29" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="AO29">
-        <v>0.99192535126433146</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP29">
-        <v>148.0352268205892</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="BB29" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="BC29">
-        <v>0.99366677237144974</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD29">
-        <v>116.10917319008783</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA30">
-        <v>0.99809166649408687</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB30">
-        <v>34.986114275074357</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10624,16 +10624,16 @@
         <v>415</v>
       </c>
       <c r="AM30" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AN30" t="s">
-        <v>360</v>
+        <v>473</v>
       </c>
       <c r="AO30">
-        <v>0.98092693557487454</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP30">
-        <v>349.67284779396647</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="BB30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="BC30">
-        <v>0.9205295464439136</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD30">
-        <v>1456.9583151949184</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="Z31" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA31">
-        <v>0.99850557699173803</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB31">
-        <v>27.397755151469518</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10770,16 +10770,16 @@
         <v>417</v>
       </c>
       <c r="AM31" t="s">
+        <v>474</v>
+      </c>
+      <c r="AN31" t="s">
         <v>475</v>
       </c>
-      <c r="AN31" t="s">
-        <v>476</v>
-      </c>
       <c r="AO31">
-        <v>0.99686124252542985</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP31">
-        <v>57.543887033786262</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="BB31" t="s">
-        <v>619</v>
+        <v>445</v>
       </c>
       <c r="BC31">
-        <v>0.99519319222421976</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD31">
-        <v>88.124809222638589</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="Z32" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AA32">
-        <v>0.99621285878087551</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB32">
-        <v>69.43092235061502</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10916,16 +10916,16 @@
         <v>419</v>
       </c>
       <c r="AM32" t="s">
+        <v>476</v>
+      </c>
+      <c r="AN32" t="s">
         <v>477</v>
       </c>
-      <c r="AN32" t="s">
-        <v>478</v>
-      </c>
       <c r="AO32">
-        <v>0.99827635377245738</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP32">
-        <v>31.600180838280902</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10955,13 +10955,13 @@
         <v>620</v>
       </c>
       <c r="BB32" t="s">
-        <v>353</v>
+        <v>491</v>
       </c>
       <c r="BC32">
-        <v>0.934538160869965</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD32">
-        <v>1200.1337173839754</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="Z33" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="AA33">
-        <v>0.9975431479552237</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB33">
-        <v>45.042287487565297</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11062,16 +11062,16 @@
         <v>421</v>
       </c>
       <c r="AM33" t="s">
+        <v>478</v>
+      </c>
+      <c r="AN33" t="s">
         <v>479</v>
       </c>
-      <c r="AN33" t="s">
-        <v>360</v>
-      </c>
       <c r="AO33">
-        <v>0.98949004263841422</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP33">
-        <v>192.68255162907312</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11101,13 +11101,13 @@
         <v>621</v>
       </c>
       <c r="BB33" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="BC33">
-        <v>0.94616153753972931</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD33">
-        <v>987.03847843829612</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="Z34" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA34">
-        <v>0.99636728996375623</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB34">
-        <v>66.599683997802714</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11214,10 +11214,10 @@
         <v>481</v>
       </c>
       <c r="AO34">
-        <v>0.99682717865030179</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP34">
-        <v>58.168391411134159</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11247,13 +11247,13 @@
         <v>622</v>
       </c>
       <c r="BB34" t="s">
-        <v>353</v>
+        <v>623</v>
       </c>
       <c r="BC34">
-        <v>0.97218956380622079</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD34">
-        <v>509.85799688595205</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="Z35" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AA35">
-        <v>0.9977500892185478</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB35">
-        <v>41.248364326622962</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11360,10 +11360,10 @@
         <v>483</v>
       </c>
       <c r="AO35">
-        <v>0.99013353407586135</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP35">
-        <v>180.88520860920943</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="BB35" t="s">
-        <v>624</v>
+        <v>491</v>
       </c>
       <c r="BC35">
-        <v>0.9924172440074055</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD35">
-        <v>139.01719319756617</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11464,16 +11464,16 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Z36" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA36">
-        <v>0.9982812149336332</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB36">
-        <v>31.51105955005805</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
@@ -11506,10 +11506,10 @@
         <v>485</v>
       </c>
       <c r="AO36">
-        <v>0.99869589057011365</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP36">
-        <v>23.908672881248773</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11539,13 +11539,13 @@
         <v>625</v>
       </c>
       <c r="BB36" t="s">
-        <v>626</v>
+        <v>375</v>
       </c>
       <c r="BC36">
-        <v>0.99114508565756532</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD36">
-        <v>162.34009627796874</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11610,16 +11610,16 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Z37" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="AA37">
-        <v>0.98833720780868572</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB37">
-        <v>213.8178568407609</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
@@ -11652,10 +11652,10 @@
         <v>487</v>
       </c>
       <c r="AO37">
-        <v>0.99762356494824644</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP37">
-        <v>43.567975948815601</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11682,16 +11682,16 @@
         <v>548</v>
       </c>
       <c r="BA37" t="s">
+        <v>626</v>
+      </c>
+      <c r="BB37" t="s">
         <v>627</v>
       </c>
-      <c r="BB37" t="s">
-        <v>628</v>
-      </c>
       <c r="BC37">
-        <v>0.99561586640696276</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD37">
-        <v>80.375782539015233</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11756,16 +11756,16 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="Z38" t="s">
         <v>374</v>
       </c>
       <c r="AA38">
-        <v>0.99116451092312863</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB38">
-        <v>161.98396640930775</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
@@ -11798,10 +11798,10 @@
         <v>489</v>
       </c>
       <c r="AO38">
-        <v>0.99669176136177262</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP38">
-        <v>60.651041700835236</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11828,16 +11828,16 @@
         <v>550</v>
       </c>
       <c r="BA38" t="s">
+        <v>628</v>
+      </c>
+      <c r="BB38" t="s">
         <v>629</v>
       </c>
-      <c r="BB38" t="s">
-        <v>441</v>
-      </c>
       <c r="BC38">
-        <v>0.95726256957223688</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD38">
-        <v>783.51955784232393</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11902,16 +11902,16 @@
         <v>341</v>
       </c>
       <c r="Y39" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="Z39" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="AA39">
-        <v>0.96189283472138964</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB39">
-        <v>698.63136344118936</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD39" t="s">
         <v>282</v>
@@ -11944,10 +11944,10 @@
         <v>491</v>
       </c>
       <c r="AO39">
-        <v>0.99863922747017897</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP39">
-        <v>24.947496380053089</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11977,13 +11977,13 @@
         <v>630</v>
       </c>
       <c r="BB39" t="s">
-        <v>449</v>
+        <v>631</v>
       </c>
       <c r="BC39">
-        <v>0.9437657388784082</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD39">
-        <v>1030.9614538958492</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12048,16 +12048,16 @@
         <v>343</v>
       </c>
       <c r="Y40" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Z40" t="s">
         <v>375</v>
       </c>
       <c r="AA40">
-        <v>0.99410594174368461</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB40">
-        <v>108.05773469911641</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD40" t="s">
         <v>282</v>
@@ -12090,10 +12090,10 @@
         <v>493</v>
       </c>
       <c r="AO40">
-        <v>0.99582230548799566</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP40">
-        <v>76.591066053413869</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="BB40" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="BC40">
-        <v>0.98822137145239475</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD40">
-        <v>215.94152337276336</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="Z41" t="s">
         <v>376</v>
       </c>
       <c r="AA41">
-        <v>0.98968917222400854</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB41">
-        <v>189.03184255984442</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
@@ -12236,10 +12236,10 @@
         <v>495</v>
       </c>
       <c r="AO41">
-        <v>0.99869874972548245</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP41">
-        <v>23.856255032822389</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12266,16 +12266,16 @@
         <v>556</v>
       </c>
       <c r="BA41" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="BB41" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="BC41">
-        <v>0.99662747375050009</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD41">
-        <v>61.829647907498845</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12304,16 +12304,16 @@
         <v>558</v>
       </c>
       <c r="BA42" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="BB42" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="BC42">
-        <v>0.99284590877035406</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD42">
-        <v>131.158339210175</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12342,16 +12342,16 @@
         <v>560</v>
       </c>
       <c r="BA43" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="BB43" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="BC43">
-        <v>0.97803702976044449</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD43">
-        <v>402.65445439185123</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12380,16 +12380,16 @@
         <v>562</v>
       </c>
       <c r="BA44" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="BB44" t="s">
-        <v>374</v>
+        <v>641</v>
       </c>
       <c r="BC44">
-        <v>0.98235584693125277</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD44">
-        <v>323.47613959369914</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12418,16 +12418,16 @@
         <v>564</v>
       </c>
       <c r="BA45" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="BB45" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="BC45">
-        <v>0.97902641975794957</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD45">
-        <v>384.51563777092457</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12456,16 +12456,16 @@
         <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="BB46" t="s">
-        <v>642</v>
+        <v>363</v>
       </c>
       <c r="BC46">
-        <v>0.99490784156958001</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD46">
-        <v>93.356237891033686</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12494,16 +12494,16 @@
         <v>568</v>
       </c>
       <c r="BA47" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="BB47" t="s">
-        <v>644</v>
+        <v>363</v>
       </c>
       <c r="BC47">
-        <v>0.99015836110796274</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD47">
-        <v>180.43004635401576</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12535,13 +12535,13 @@
         <v>645</v>
       </c>
       <c r="BB48" t="s">
-        <v>646</v>
+        <v>363</v>
       </c>
       <c r="BC48">
-        <v>0.99623532634854861</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD48">
-        <v>69.01901694327529</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12570,16 +12570,16 @@
         <v>572</v>
       </c>
       <c r="BA49" t="s">
+        <v>646</v>
+      </c>
+      <c r="BB49" t="s">
         <v>647</v>
       </c>
-      <c r="BB49" t="s">
-        <v>648</v>
-      </c>
       <c r="BC49">
-        <v>0.9966173923071765</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD49">
-        <v>62.014474368430825</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12608,16 +12608,16 @@
         <v>574</v>
       </c>
       <c r="BA50" t="s">
+        <v>648</v>
+      </c>
+      <c r="BB50" t="s">
         <v>649</v>
       </c>
-      <c r="BB50" t="s">
-        <v>360</v>
-      </c>
       <c r="BC50">
-        <v>0.98180592470173533</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD50">
-        <v>333.55804713485287</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12652,10 +12652,10 @@
         <v>651</v>
       </c>
       <c r="BC51">
-        <v>0.98779966071713954</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD51">
-        <v>223.67288685244134</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12690,10 +12690,10 @@
         <v>653</v>
       </c>
       <c r="BC52">
-        <v>0.98841501119699848</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD52">
-        <v>212.39146138836088</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12725,13 +12725,13 @@
         <v>654</v>
       </c>
       <c r="BB53" t="s">
-        <v>598</v>
+        <v>655</v>
       </c>
       <c r="BC53">
-        <v>0.93089405249526469</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD53">
-        <v>1266.9423709201483</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12760,16 +12760,16 @@
         <v>582</v>
       </c>
       <c r="BA54" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="BB54" t="s">
-        <v>656</v>
+        <v>631</v>
       </c>
       <c r="BC54">
-        <v>0.99302778580016682</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD54">
-        <v>127.82392699694152</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF2B0D4-7FCE-41A5-9BDF-634FE71E8AAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75A2C2BC-BA53-4D8E-8187-90FE9980A9B6}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>622</v>
+        <v>645</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13162,7 +13162,7 @@
         <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13263,7 +13263,7 @@
         <v>729</v>
       </c>
       <c r="X16" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13331,7 +13331,7 @@
         <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13467,7 +13467,7 @@
         <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>614</v>
+        <v>584</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>610</v>
+        <v>652</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>595</v>
+        <v>654</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13910,7 +13910,7 @@
         <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13943,7 +13943,7 @@
         <v>749</v>
       </c>
       <c r="X26" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="Y26">
         <v>63.731250000000003</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14011,7 +14011,7 @@
         <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="Y27">
         <v>28.239750000000001</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14147,7 +14147,7 @@
         <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="Y29">
         <v>3.38625</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>637</v>
+        <v>617</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>639</v>
+        <v>590</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>446</v>
+        <v>488</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14794,7 +14794,7 @@
         <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>650</v>
+        <v>626</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14963,7 +14963,7 @@
         <v>779</v>
       </c>
       <c r="X41" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="Y41">
         <v>27.642749999999999</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>654</v>
+        <v>630</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15138,7 +15138,7 @@
         <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>616</v>
+        <v>586</v>
       </c>
       <c r="Y46">
         <v>1.81725</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>597</v>
+        <v>656</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15243,7 +15243,7 @@
         <v>795</v>
       </c>
       <c r="X49" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="Y49">
         <v>42.144750000000002</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>655</v>
+        <v>632</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4F0FB0-F65C-4F28-B822-90F8BFFF0DD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68572CA-9647-4F84-87D3-09908E8C57AC}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2133D946-8218-4F6D-9F6F-27071B45715F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5158136A-2E1B-48CD-ADA6-EDFCEA2FD80D}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{902AD0E4-530C-487D-AFA3-1595F09C500A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6AED4B1-09F8-46D6-9711-2E62A8CE5011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,18 +980,48 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_013</t>
   </si>
   <si>
@@ -1004,16 +1034,136 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_028</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_solelc_spv_020</t>
@@ -1022,162 +1172,27 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
     <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
   </si>
   <si>
@@ -1187,27 +1202,42 @@
     <t>e_JP7-275,e_JP6-275</t>
   </si>
   <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
     <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
   </si>
   <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
     <t>e_JP306-500,e_w215451416-500</t>
   </si>
   <si>
@@ -1217,33 +1247,6 @@
     <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
   </si>
   <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
     <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
   </si>
   <si>
@@ -1259,7 +1262,106 @@
     <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_wonelc_won_017</t>
@@ -1280,6 +1382,42 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_007</t>
   </si>
   <si>
@@ -1310,142 +1448,94 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
   </si>
   <si>
     <t>elc_won_017</t>
@@ -1466,6 +1556,39 @@
     <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
   </si>
   <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
     <t>elc_won_007</t>
   </si>
   <si>
@@ -1496,127 +1619,94 @@
     <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_030</t>
@@ -1673,6 +1763,66 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_014</t>
   </si>
   <si>
@@ -1685,112 +1835,28 @@
     <t>connecting wind offshore to buses in cluster 38</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
   </si>
   <si>
     <t>distr_wofelc_wof_004</t>
@@ -1817,70 +1883,82 @@
     <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
   </si>
   <si>
     <t>elc_wof_030</t>
@@ -1934,6 +2012,54 @@
     <t>elc_wof_018</t>
   </si>
   <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
     <t>elc_wof_014</t>
   </si>
   <si>
@@ -1943,97 +2069,22 @@
     <t>elc_wof_038</t>
   </si>
   <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
   </si>
   <si>
     <t>elc_wof_004</t>
@@ -2049,57 +2100,6 @@
   </si>
   <si>
     <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64C833B-9147-4694-B330-B4E9DC7BF840}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2000C03E-B24F-4054-B7A4-62BA2DB591F9}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7814,16 +7814,16 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.9977500892185478</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB11">
-        <v>41.248364326622962</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
@@ -7856,10 +7856,10 @@
         <v>440</v>
       </c>
       <c r="AO11">
-        <v>0.99804155179341392</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP11">
-        <v>35.904883787411507</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
@@ -7889,13 +7889,13 @@
         <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>585</v>
+        <v>358</v>
       </c>
       <c r="BC11">
-        <v>0.98779966071713954</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD11">
-        <v>223.67288685244134</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7960,16 +7960,16 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.9982812149336332</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB12">
-        <v>31.51105955005805</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
@@ -8002,10 +8002,10 @@
         <v>442</v>
       </c>
       <c r="AO12">
-        <v>0.99508023417818925</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP12">
-        <v>90.195706733197795</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8032,16 +8032,16 @@
         <v>498</v>
       </c>
       <c r="BA12" t="s">
+        <v>585</v>
+      </c>
+      <c r="BB12" t="s">
         <v>586</v>
       </c>
-      <c r="BB12" t="s">
-        <v>587</v>
-      </c>
       <c r="BC12">
-        <v>0.98841501119699848</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD12">
-        <v>212.39146138836088</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8106,16 +8106,16 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.98833720780868572</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB13">
-        <v>213.8178568407609</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
@@ -8148,10 +8148,10 @@
         <v>444</v>
       </c>
       <c r="AO13">
-        <v>0.99940622505963084</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP13">
-        <v>10.885873906767051</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8178,16 +8178,16 @@
         <v>500</v>
       </c>
       <c r="BA13" t="s">
+        <v>587</v>
+      </c>
+      <c r="BB13" t="s">
         <v>588</v>
       </c>
-      <c r="BB13" t="s">
-        <v>589</v>
-      </c>
       <c r="BC13">
-        <v>0.93089405249526469</v>
+        <v>0.99017867813273497</v>
       </c>
       <c r="BD13">
-        <v>1266.9423709201483</v>
+        <v>180.05756756652616</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8252,16 +8252,16 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.99798824264234642</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB14">
-        <v>36.882218223648351</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
@@ -8294,10 +8294,10 @@
         <v>446</v>
       </c>
       <c r="AO14">
-        <v>0.99710631799330929</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP14">
-        <v>53.050836789329388</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
@@ -8324,16 +8324,16 @@
         <v>502</v>
       </c>
       <c r="BA14" t="s">
+        <v>589</v>
+      </c>
+      <c r="BB14" t="s">
         <v>590</v>
       </c>
-      <c r="BB14" t="s">
-        <v>591</v>
-      </c>
       <c r="BC14">
-        <v>0.99302778580016682</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD14">
-        <v>127.82392699694152</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8398,16 +8398,16 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.99900168239190124</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB15">
-        <v>18.302489481810518</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
@@ -8437,13 +8437,13 @@
         <v>447</v>
       </c>
       <c r="AN15" t="s">
-        <v>448</v>
+        <v>356</v>
       </c>
       <c r="AO15">
-        <v>0.99550555557680764</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP15">
-        <v>82.398147758527074</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
@@ -8470,16 +8470,16 @@
         <v>504</v>
       </c>
       <c r="BA15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="BB15" t="s">
-        <v>593</v>
+        <v>452</v>
       </c>
       <c r="BC15">
-        <v>0.99490784156958001</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD15">
-        <v>93.356237891033686</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8544,16 +8544,16 @@
         <v>295</v>
       </c>
       <c r="Y16" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="Z16" t="s">
         <v>354</v>
       </c>
       <c r="AA16">
-        <v>0.97633688849282452</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB16">
-        <v>433.82371096488447</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD16" t="s">
         <v>282</v>
@@ -8580,16 +8580,16 @@
         <v>387</v>
       </c>
       <c r="AM16" t="s">
+        <v>448</v>
+      </c>
+      <c r="AN16" t="s">
         <v>449</v>
       </c>
-      <c r="AN16" t="s">
-        <v>450</v>
-      </c>
       <c r="AO16">
-        <v>0.93896180472603763</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP16">
-        <v>1119.0335800226442</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8616,16 +8616,16 @@
         <v>506</v>
       </c>
       <c r="BA16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="BB16" t="s">
-        <v>595</v>
+        <v>491</v>
       </c>
       <c r="BC16">
-        <v>0.99015836110796274</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD16">
-        <v>180.43004635401576</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.9981032549815434</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB17">
-        <v>34.773658671704098</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8726,16 +8726,16 @@
         <v>389</v>
       </c>
       <c r="AM17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AN17" t="s">
-        <v>452</v>
+        <v>358</v>
       </c>
       <c r="AO17">
-        <v>0.99013353407586135</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP17">
-        <v>180.88520860920943</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="BB17" t="s">
-        <v>597</v>
+        <v>357</v>
       </c>
       <c r="BC17">
-        <v>0.99623532634854861</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD17">
-        <v>69.01901694327529</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8836,16 +8836,16 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.99852430677621173</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB18">
-        <v>27.054375769451152</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
@@ -8872,16 +8872,16 @@
         <v>391</v>
       </c>
       <c r="AM18" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AN18" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AO18">
-        <v>0.99869589057011365</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP18">
-        <v>23.908672881248773</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="BB18" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="BC18">
-        <v>0.9966173923071765</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD18">
-        <v>62.014474368430825</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.99838604658336239</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB19">
-        <v>29.589145971689483</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9018,16 +9018,16 @@
         <v>393</v>
       </c>
       <c r="AM19" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AO19">
-        <v>0.99827635377245738</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP19">
-        <v>31.600180838280902</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9054,16 +9054,16 @@
         <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="BB19" t="s">
-        <v>351</v>
+        <v>597</v>
       </c>
       <c r="BC19">
-        <v>0.98180592470173533</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD19">
-        <v>333.55804713485287</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.99628076912917996</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB20">
-        <v>68.185899298368355</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9164,16 +9164,16 @@
         <v>395</v>
       </c>
       <c r="AM20" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AN20" t="s">
-        <v>351</v>
+        <v>456</v>
       </c>
       <c r="AO20">
-        <v>0.98949004263841422</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP20">
-        <v>192.68255162907312</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9200,16 +9200,16 @@
         <v>514</v>
       </c>
       <c r="BA20" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="BB20" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="BC20">
-        <v>0.99253849155603513</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD20">
-        <v>136.79432147269009</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="Z21" t="s">
         <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.99391268208184824</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB21">
-        <v>111.60082849944791</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9310,16 +9310,16 @@
         <v>397</v>
       </c>
       <c r="AM21" t="s">
+        <v>457</v>
+      </c>
+      <c r="AN21" t="s">
         <v>458</v>
       </c>
-      <c r="AN21" t="s">
-        <v>459</v>
-      </c>
       <c r="AO21">
-        <v>0.99682717865030179</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP21">
-        <v>58.168391411134159</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9346,16 +9346,16 @@
         <v>516</v>
       </c>
       <c r="BA21" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="BB21" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="BC21">
-        <v>0.973232135644435</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD21">
-        <v>490.74417985202501</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="Z22" t="s">
         <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.99871218762601011</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB22">
-        <v>23.609893523147914</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9456,16 +9456,16 @@
         <v>399</v>
       </c>
       <c r="AM22" t="s">
+        <v>459</v>
+      </c>
+      <c r="AN22" t="s">
         <v>460</v>
       </c>
-      <c r="AN22" t="s">
-        <v>461</v>
-      </c>
       <c r="AO22">
-        <v>0.99762356494824644</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP22">
-        <v>43.567975948815601</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9492,16 +9492,16 @@
         <v>518</v>
       </c>
       <c r="BA22" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="BB22" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="BC22">
-        <v>0.99681267676383467</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD22">
-        <v>58.434259329697142</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s">
         <v>361</v>
       </c>
       <c r="AA23">
-        <v>0.99856748800713691</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB23">
-        <v>26.26271986915707</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9602,16 +9602,16 @@
         <v>401</v>
       </c>
       <c r="AM23" t="s">
+        <v>461</v>
+      </c>
+      <c r="AN23" t="s">
         <v>462</v>
       </c>
-      <c r="AN23" t="s">
-        <v>463</v>
-      </c>
       <c r="AO23">
-        <v>0.99669176136177262</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP23">
-        <v>60.651041700835236</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9638,16 +9638,16 @@
         <v>520</v>
       </c>
       <c r="BA23" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="BB23" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="BC23">
-        <v>0.99602290686668338</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD23">
-        <v>72.91337411080552</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AA24">
-        <v>0.97905685820454003</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB24">
-        <v>383.95759958343297</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
+        <v>463</v>
+      </c>
+      <c r="AN24" t="s">
         <v>464</v>
       </c>
-      <c r="AN24" t="s">
-        <v>465</v>
-      </c>
       <c r="AO24">
-        <v>0.99863922747017897</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP24">
-        <v>24.947496380053089</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9784,16 +9784,16 @@
         <v>522</v>
       </c>
       <c r="BA24" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="BB24" t="s">
-        <v>354</v>
+        <v>607</v>
       </c>
       <c r="BC24">
-        <v>0.934538160869965</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD24">
-        <v>1200.1337173839754</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="Z25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA25">
-        <v>0.99116451092312863</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB25">
-        <v>161.98396640930775</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
+        <v>465</v>
+      </c>
+      <c r="AN25" t="s">
         <v>466</v>
       </c>
-      <c r="AN25" t="s">
-        <v>467</v>
-      </c>
       <c r="AO25">
-        <v>0.99582230548799566</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP25">
-        <v>76.591066053413869</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
+        <v>608</v>
+      </c>
+      <c r="BB25" t="s">
         <v>609</v>
       </c>
-      <c r="BB25" t="s">
-        <v>354</v>
-      </c>
       <c r="BC25">
-        <v>0.94616153753972931</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD25">
-        <v>987.03847843829612</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10007,7 +10007,7 @@
         <v>271</v>
       </c>
       <c r="Z26" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AA26">
         <v>0.94069903208664407</v>
@@ -10040,16 +10040,16 @@
         <v>407</v>
       </c>
       <c r="AM26" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AN26" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AO26">
-        <v>0.93717435218793788</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP26">
-        <v>1151.8035432211395</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10079,13 +10079,13 @@
         <v>610</v>
       </c>
       <c r="BB26" t="s">
-        <v>354</v>
+        <v>611</v>
       </c>
       <c r="BC26">
-        <v>0.97218956380622079</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD26">
-        <v>509.85799688595205</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10153,7 +10153,7 @@
         <v>265</v>
       </c>
       <c r="Z27" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA27">
         <v>0.99756610784588629</v>
@@ -10186,16 +10186,16 @@
         <v>409</v>
       </c>
       <c r="AM27" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AN27" t="s">
-        <v>470</v>
+        <v>356</v>
       </c>
       <c r="AO27">
-        <v>0.96551955124232614</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP27">
-        <v>632.14156055735509</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="BB27" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="BC27">
-        <v>0.9924172440074055</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD27">
-        <v>139.01719319756617</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10299,7 +10299,7 @@
         <v>276</v>
       </c>
       <c r="Z28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA28">
         <v>0.9972084849335241</v>
@@ -10332,16 +10332,16 @@
         <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN28" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AO28">
-        <v>0.99693456929731861</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP28">
-        <v>56.199562882493169</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="BB28" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="BC28">
-        <v>0.99114508565756532</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD28">
-        <v>162.34009627796874</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="Z29" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="AA29">
-        <v>0.96189283472138964</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB29">
-        <v>698.63136344118936</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10478,16 +10478,16 @@
         <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AN29" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AO29">
-        <v>0.99750949182367343</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP29">
-        <v>45.659316565986806</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="BB29" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="BC29">
-        <v>0.99561586640696276</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD29">
-        <v>80.375782539015233</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="Z30" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AA30">
-        <v>0.99410594174368461</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB30">
-        <v>108.05773469911641</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10624,16 +10624,16 @@
         <v>415</v>
       </c>
       <c r="AM30" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AN30" t="s">
-        <v>366</v>
+        <v>474</v>
       </c>
       <c r="AO30">
-        <v>0.99192535126433146</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP30">
-        <v>148.0352268205892</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="BB30" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="BC30">
-        <v>0.99637036284424008</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD30">
-        <v>66.543347855598327</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="Z31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AA31">
-        <v>0.98968917222400854</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB31">
-        <v>189.03184255984442</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10770,16 +10770,16 @@
         <v>417</v>
       </c>
       <c r="AM31" t="s">
+        <v>475</v>
+      </c>
+      <c r="AN31" t="s">
         <v>476</v>
       </c>
-      <c r="AN31" t="s">
-        <v>351</v>
-      </c>
       <c r="AO31">
-        <v>0.98092693557487454</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP31">
-        <v>349.67284779396647</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="BB31" t="s">
-        <v>369</v>
+        <v>621</v>
       </c>
       <c r="BC31">
-        <v>0.97902641975794957</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD31">
-        <v>384.51563777092457</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="Z32" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AA32">
-        <v>0.99825665520226836</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB32">
-        <v>31.96132129174655</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10922,10 +10922,10 @@
         <v>478</v>
       </c>
       <c r="AO32">
-        <v>0.99811838305018963</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP32">
-        <v>34.496310746523356</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10952,16 +10952,16 @@
         <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="BB32" t="s">
-        <v>362</v>
+        <v>623</v>
       </c>
       <c r="BC32">
-        <v>0.98235584693125277</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD32">
-        <v>323.47613959369914</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="Z33" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AA33">
-        <v>0.99894650606645485</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB33">
-        <v>19.314055448326833</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11068,10 +11068,10 @@
         <v>480</v>
       </c>
       <c r="AO33">
-        <v>0.9985928182686985</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP33">
-        <v>25.798331740528162</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11098,16 +11098,16 @@
         <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="BB33" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="BC33">
-        <v>0.99366677237144974</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD33">
-        <v>116.10917319008783</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="Z34" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AA34">
-        <v>0.98179245618315802</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB34">
-        <v>333.80496997543548</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11214,10 +11214,10 @@
         <v>482</v>
       </c>
       <c r="AO34">
-        <v>0.99769811225811866</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP34">
-        <v>42.201275267825203</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11244,16 +11244,16 @@
         <v>542</v>
       </c>
       <c r="BA34" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="BB34" t="s">
-        <v>624</v>
+        <v>356</v>
       </c>
       <c r="BC34">
-        <v>0.9205295464439136</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD34">
-        <v>1456.9583151949184</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="Z35" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="AA35">
-        <v>0.99726055556014181</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB35">
-        <v>50.223148064066145</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11357,13 +11357,13 @@
         <v>483</v>
       </c>
       <c r="AN35" t="s">
-        <v>362</v>
+        <v>484</v>
       </c>
       <c r="AO35">
-        <v>0.98814178187791379</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP35">
-        <v>217.40066557158059</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="BB35" t="s">
-        <v>626</v>
+        <v>353</v>
       </c>
       <c r="BC35">
-        <v>0.99519319222421976</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD35">
-        <v>88.124809222638589</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11467,7 +11467,7 @@
         <v>266</v>
       </c>
       <c r="Z36" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA36">
         <v>0.99809166649408687</v>
@@ -11500,16 +11500,16 @@
         <v>427</v>
       </c>
       <c r="AM36" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN36" t="s">
-        <v>485</v>
+        <v>357</v>
       </c>
       <c r="AO36">
-        <v>0.99841760060377538</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP36">
-        <v>29.010655597451841</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11536,16 +11536,16 @@
         <v>546</v>
       </c>
       <c r="BA36" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="BB36" t="s">
-        <v>628</v>
+        <v>358</v>
       </c>
       <c r="BC36">
-        <v>0.98822137145239475</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD36">
-        <v>215.94152337276336</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11613,7 +11613,7 @@
         <v>268</v>
       </c>
       <c r="Z37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA37">
         <v>0.99850557699173803</v>
@@ -11652,10 +11652,10 @@
         <v>487</v>
       </c>
       <c r="AO37">
-        <v>0.99781438034778358</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP37">
-        <v>40.069693623967019</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11685,13 +11685,13 @@
         <v>629</v>
       </c>
       <c r="BB37" t="s">
-        <v>630</v>
+        <v>358</v>
       </c>
       <c r="BC37">
-        <v>0.99662747375050009</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD37">
-        <v>61.829647907498845</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11759,7 +11759,7 @@
         <v>279</v>
       </c>
       <c r="Z38" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA38">
         <v>0.99621285878087551</v>
@@ -11798,10 +11798,10 @@
         <v>489</v>
       </c>
       <c r="AO38">
-        <v>0.99869874972548245</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP38">
-        <v>23.856255032822389</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11828,16 +11828,16 @@
         <v>550</v>
       </c>
       <c r="BA38" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BB38" t="s">
-        <v>632</v>
+        <v>358</v>
       </c>
       <c r="BC38">
-        <v>0.99284590877035406</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD38">
-        <v>131.158339210175</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11905,7 +11905,7 @@
         <v>253</v>
       </c>
       <c r="Z39" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA39">
         <v>0.9975431479552237</v>
@@ -11944,10 +11944,10 @@
         <v>491</v>
       </c>
       <c r="AO39">
-        <v>0.99870022163576544</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP39">
-        <v>23.829270010966344</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11974,16 +11974,16 @@
         <v>552</v>
       </c>
       <c r="BA39" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="BB39" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="BC39">
-        <v>0.97803702976044449</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD39">
-        <v>402.65445439185123</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12051,7 +12051,7 @@
         <v>252</v>
       </c>
       <c r="Z40" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA40">
         <v>0.99636728996375623</v>
@@ -12090,10 +12090,10 @@
         <v>493</v>
       </c>
       <c r="AO40">
-        <v>0.99807466477127271</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP40">
-        <v>35.297812526667357</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="BB40" t="s">
-        <v>354</v>
+        <v>634</v>
       </c>
       <c r="BC40">
-        <v>0.97591598065988894</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD40">
-        <v>441.54035456870389</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Z41" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="AA41">
-        <v>0.9488788277802801</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB41">
-        <v>937.22149069486488</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
@@ -12236,10 +12236,10 @@
         <v>495</v>
       </c>
       <c r="AO41">
-        <v>0.99686124252542985</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP41">
-        <v>57.543887033786262</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12266,16 +12266,16 @@
         <v>556</v>
       </c>
       <c r="BA41" t="s">
+        <v>635</v>
+      </c>
+      <c r="BB41" t="s">
         <v>636</v>
       </c>
-      <c r="BB41" t="s">
-        <v>637</v>
-      </c>
       <c r="BC41">
-        <v>0.99412039195829205</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD41">
-        <v>107.79281409797902</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12304,16 +12304,16 @@
         <v>558</v>
       </c>
       <c r="BA42" t="s">
+        <v>637</v>
+      </c>
+      <c r="BB42" t="s">
         <v>638</v>
       </c>
-      <c r="BB42" t="s">
-        <v>450</v>
-      </c>
       <c r="BC42">
-        <v>0.98292548292671178</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD42">
-        <v>313.03281301028323</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12345,13 +12345,13 @@
         <v>639</v>
       </c>
       <c r="BB43" t="s">
-        <v>362</v>
+        <v>640</v>
       </c>
       <c r="BC43">
-        <v>0.98355967005268352</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD43">
-        <v>301.40604903413595</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12380,16 +12380,16 @@
         <v>562</v>
       </c>
       <c r="BA44" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB44" t="s">
-        <v>470</v>
+        <v>642</v>
       </c>
       <c r="BC44">
-        <v>0.95726256957223688</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD44">
-        <v>783.51955784232393</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12418,16 +12418,16 @@
         <v>564</v>
       </c>
       <c r="BA45" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="BB45" t="s">
-        <v>450</v>
+        <v>644</v>
       </c>
       <c r="BC45">
-        <v>0.9437657388784082</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD45">
-        <v>1030.9614538958492</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12456,16 +12456,16 @@
         <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="BB46" t="s">
-        <v>643</v>
+        <v>615</v>
       </c>
       <c r="BC46">
-        <v>0.99234935324205875</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD46">
-        <v>140.26185722892211</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12494,16 +12494,16 @@
         <v>568</v>
       </c>
       <c r="BA47" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="BB47" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="BC47">
-        <v>0.99536692897647694</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD47">
-        <v>84.939635431255269</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12532,16 +12532,16 @@
         <v>570</v>
       </c>
       <c r="BA48" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="BB48" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="BC48">
-        <v>0.88199812838352587</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD48">
-        <v>2163.367646302027</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12570,16 +12570,16 @@
         <v>572</v>
       </c>
       <c r="BA49" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="BB49" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="BC49">
-        <v>0.95957195194316591</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD49">
-        <v>741.18088104195795</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12608,16 +12608,16 @@
         <v>574</v>
       </c>
       <c r="BA50" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="BB50" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="BC50">
-        <v>0.99603667376986049</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD50">
-        <v>72.660980885890424</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12646,16 +12646,16 @@
         <v>576</v>
       </c>
       <c r="BA51" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="BB51" t="s">
-        <v>651</v>
+        <v>358</v>
       </c>
       <c r="BC51">
-        <v>0.99017867813273497</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD51">
-        <v>180.05756756652616</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12684,16 +12684,16 @@
         <v>578</v>
       </c>
       <c r="BA52" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="BB52" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="BC52">
-        <v>0.99504061303190972</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD52">
-        <v>90.922094414988095</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12722,16 +12722,16 @@
         <v>580</v>
       </c>
       <c r="BA53" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="BB53" t="s">
-        <v>354</v>
+        <v>491</v>
       </c>
       <c r="BC53">
-        <v>0.96140381292129873</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD53">
-        <v>707.59676310952364</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12760,16 +12760,16 @@
         <v>582</v>
       </c>
       <c r="BA54" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="BB54" t="s">
-        <v>656</v>
+        <v>357</v>
       </c>
       <c r="BC54">
-        <v>0.9973402418125219</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD54">
-        <v>48.762233437098502</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207E4535-82ED-4659-8388-C7BA6AE31F45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866CF6B4-E67A-42AB-8CCB-3A263AD136B7}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13162,7 +13162,7 @@
         <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>640</v>
+        <v>591</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13263,7 +13263,7 @@
         <v>729</v>
       </c>
       <c r="X16" t="s">
-        <v>647</v>
+        <v>584</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>445</v>
+        <v>486</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13331,7 +13331,7 @@
         <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>488</v>
+        <v>439</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13399,7 +13399,7 @@
         <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13467,7 +13467,7 @@
         <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>621</v>
+        <v>594</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>490</v>
+        <v>441</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>627</v>
+        <v>600</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>655</v>
+        <v>608</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>601</v>
+        <v>643</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>598</v>
+        <v>624</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13910,7 +13910,7 @@
         <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13943,7 +13943,7 @@
         <v>749</v>
       </c>
       <c r="X26" t="s">
-        <v>652</v>
+        <v>589</v>
       </c>
       <c r="Y26">
         <v>63.731250000000003</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14011,7 +14011,7 @@
         <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>625</v>
+        <v>598</v>
       </c>
       <c r="Y27">
         <v>28.239750000000001</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14147,7 +14147,7 @@
         <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="Y29">
         <v>3.38625</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>492</v>
+        <v>443</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>639</v>
+        <v>656</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>594</v>
+        <v>620</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14759,7 +14759,7 @@
         <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="Y38">
         <v>64.437749999999994</v>
@@ -14794,7 +14794,7 @@
         <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14963,7 +14963,7 @@
         <v>779</v>
       </c>
       <c r="X41" t="s">
-        <v>648</v>
+        <v>585</v>
       </c>
       <c r="Y41">
         <v>27.642749999999999</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>641</v>
+        <v>592</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15068,7 +15068,7 @@
         <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="Y44">
         <v>0.42149999999999999</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15138,7 +15138,7 @@
         <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>623</v>
+        <v>596</v>
       </c>
       <c r="Y46">
         <v>1.81725</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>603</v>
+        <v>645</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15243,7 +15243,7 @@
         <v>795</v>
       </c>
       <c r="X49" t="s">
-        <v>650</v>
+        <v>587</v>
       </c>
       <c r="Y49">
         <v>42.144750000000002</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>604</v>
+        <v>639</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>590</v>
+        <v>616</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>606</v>
+        <v>641</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{515B97F4-93F8-4D1F-B441-7ADFCEE47876}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2248F8CD-5DBC-42A1-8ECA-F21F7AB09C14}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6991837F-DF85-41D7-BDFA-FB1BD00AAC32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6681D872-B8E6-48A6-859A-D104D10C64E0}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6AED4B1-09F8-46D6-9711-2E62A8CE5011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{902D4F7D-7A65-49F0-B248-B889911BE6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -992,46 +992,154 @@
     <t>daynite</t>
   </si>
   <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_024</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
     <t>distr_solelc_spv_005</t>
@@ -1058,120 +1166,12 @@
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1181,85 +1181,169 @@
     <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
   </si>
   <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
     <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
   </si>
   <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
+    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
   </si>
   <si>
     <t>e_w179863079-275</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
     <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
   </si>
   <si>
     <t>e_w179863079-275,e_JP6-275</t>
   </si>
   <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
     <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
   </si>
   <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wonelc_won_008</t>
@@ -1268,6 +1352,66 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_011</t>
   </si>
   <si>
@@ -1280,52 +1424,16 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_wonelc_won_016</t>
@@ -1340,112 +1448,79 @@
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
   </si>
   <si>
     <t>elc_won_008</t>
@@ -1454,6 +1529,66 @@
     <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
   </si>
   <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
     <t>elc_won_011</t>
   </si>
   <si>
@@ -1466,46 +1601,10 @@
     <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
   </si>
   <si>
     <t>elc_won_016</t>
@@ -1520,105 +1619,6 @@
     <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
   </si>
   <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
@@ -1643,6 +1643,132 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_005</t>
   </si>
   <si>
@@ -1655,28 +1781,82 @@
     <t>connecting wind offshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wofelc_wof_011</t>
@@ -1703,186 +1883,6 @@
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
@@ -1904,31 +1904,178 @@
     <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
   </si>
   <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
     <t>elc_wof_005</t>
   </si>
   <si>
     <t>elc_wof_033</t>
   </si>
   <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
   </si>
   <si>
     <t>elc_wof_011</t>
@@ -1953,153 +2100,6 @@
   </si>
   <si>
     <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2000C03E-B24F-4054-B7A4-62BA2DB591F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80742817-EA7D-4E41-9BCD-FDDA1F6BAD7C}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7856,10 +7856,10 @@
         <v>440</v>
       </c>
       <c r="AO11">
-        <v>0.99869874972548245</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP11">
-        <v>23.856255032822389</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
@@ -7889,7 +7889,7 @@
         <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="BC11">
         <v>0.95957195194316591</v>
@@ -7960,16 +7960,16 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.99900168239190124</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB12">
-        <v>18.302489481810518</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
@@ -8002,10 +8002,10 @@
         <v>442</v>
       </c>
       <c r="AO12">
-        <v>0.99870022163576544</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP12">
-        <v>23.829270010966344</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8106,16 +8106,16 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.99825665520226836</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB13">
-        <v>31.96132129174655</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
@@ -8148,10 +8148,10 @@
         <v>444</v>
       </c>
       <c r="AO13">
-        <v>0.99807466477127271</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP13">
-        <v>35.297812526667357</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8252,16 +8252,16 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.99894650606645485</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB14">
-        <v>19.314055448326833</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
@@ -8398,16 +8398,16 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.98179245618315802</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB15">
-        <v>333.80496997543548</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
@@ -8437,7 +8437,7 @@
         <v>447</v>
       </c>
       <c r="AN15" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AO15">
         <v>0.98949004263841422</v>
@@ -8473,13 +8473,13 @@
         <v>591</v>
       </c>
       <c r="BB15" t="s">
-        <v>452</v>
+        <v>592</v>
       </c>
       <c r="BC15">
-        <v>0.95726256957223688</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD15">
-        <v>783.51955784232393</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8544,16 +8544,16 @@
         <v>295</v>
       </c>
       <c r="Y16" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="Z16" t="s">
         <v>354</v>
       </c>
       <c r="AA16">
-        <v>0.9977500892185478</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB16">
-        <v>41.248364326622962</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD16" t="s">
         <v>282</v>
@@ -8583,13 +8583,13 @@
         <v>448</v>
       </c>
       <c r="AN16" t="s">
-        <v>449</v>
+        <v>370</v>
       </c>
       <c r="AO16">
-        <v>0.99682717865030179</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP16">
-        <v>58.168391411134159</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8616,16 +8616,16 @@
         <v>506</v>
       </c>
       <c r="BA16" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="BB16" t="s">
-        <v>491</v>
+        <v>594</v>
       </c>
       <c r="BC16">
-        <v>0.9437657388784082</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD16">
-        <v>1030.9614538958492</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.9982812149336332</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB17">
-        <v>31.51105955005805</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8726,16 +8726,16 @@
         <v>389</v>
       </c>
       <c r="AM17" t="s">
+        <v>449</v>
+      </c>
+      <c r="AN17" t="s">
         <v>450</v>
       </c>
-      <c r="AN17" t="s">
-        <v>358</v>
-      </c>
       <c r="AO17">
-        <v>0.93717435218793788</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP17">
-        <v>1151.8035432211395</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="BB17" t="s">
-        <v>357</v>
+        <v>596</v>
       </c>
       <c r="BC17">
-        <v>0.98235584693125277</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD17">
-        <v>323.47613959369914</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8836,16 +8836,16 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.98833720780868572</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB18">
-        <v>213.8178568407609</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
@@ -8878,10 +8878,10 @@
         <v>452</v>
       </c>
       <c r="AO18">
-        <v>0.96551955124232614</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP18">
-        <v>632.14156055735509</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="BB18" t="s">
-        <v>595</v>
+        <v>370</v>
       </c>
       <c r="BC18">
-        <v>0.99366677237144974</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD18">
-        <v>116.10917319008783</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.99116451092312863</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB19">
-        <v>161.98396640930775</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9024,10 +9024,10 @@
         <v>454</v>
       </c>
       <c r="AO19">
-        <v>0.99693456929731861</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP19">
-        <v>56.199562882493169</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9054,16 +9054,16 @@
         <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="BB19" t="s">
-        <v>597</v>
+        <v>370</v>
       </c>
       <c r="BC19">
-        <v>0.9205295464439136</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD19">
-        <v>1456.9583151949184</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.96189283472138964</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB20">
-        <v>698.63136344118936</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9170,10 +9170,10 @@
         <v>456</v>
       </c>
       <c r="AO20">
-        <v>0.99762356494824644</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP20">
-        <v>43.567975948815601</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9200,16 +9200,16 @@
         <v>514</v>
       </c>
       <c r="BA20" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="BB20" t="s">
-        <v>599</v>
+        <v>370</v>
       </c>
       <c r="BC20">
-        <v>0.99519319222421976</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD20">
-        <v>88.124809222638589</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="Z21" t="s">
         <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.99410594174368461</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB21">
-        <v>108.05773469911641</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9316,10 +9316,10 @@
         <v>458</v>
       </c>
       <c r="AO21">
-        <v>0.99669176136177262</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP21">
-        <v>60.651041700835236</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9352,10 +9352,10 @@
         <v>601</v>
       </c>
       <c r="BC21">
-        <v>0.98822137145239475</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD21">
-        <v>215.94152337276336</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="Z22" t="s">
         <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.98968917222400854</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB22">
-        <v>189.03184255984442</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9459,13 +9459,13 @@
         <v>459</v>
       </c>
       <c r="AN22" t="s">
-        <v>460</v>
+        <v>373</v>
       </c>
       <c r="AO22">
-        <v>0.99750949182367343</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP22">
-        <v>45.659316565986806</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9498,10 +9498,10 @@
         <v>603</v>
       </c>
       <c r="BC22">
-        <v>0.99662747375050009</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD22">
-        <v>61.829647907498845</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="Z23" t="s">
         <v>361</v>
       </c>
       <c r="AA23">
-        <v>0.99852430677621173</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB23">
-        <v>27.054375769451152</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9602,16 +9602,16 @@
         <v>401</v>
       </c>
       <c r="AM23" t="s">
+        <v>460</v>
+      </c>
+      <c r="AN23" t="s">
         <v>461</v>
       </c>
-      <c r="AN23" t="s">
-        <v>462</v>
-      </c>
       <c r="AO23">
-        <v>0.99686124252542985</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP23">
-        <v>57.543887033786262</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9644,10 +9644,10 @@
         <v>605</v>
       </c>
       <c r="BC23">
-        <v>0.99284590877035406</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD23">
-        <v>131.158339210175</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z24" t="s">
         <v>362</v>
       </c>
       <c r="AA24">
-        <v>0.99838604658336239</v>
+        <v>0.99809166649408687</v>
       </c>
       <c r="AB24">
-        <v>29.589145971689483</v>
+        <v>34.986114275074357</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
+        <v>462</v>
+      </c>
+      <c r="AN24" t="s">
         <v>463</v>
       </c>
-      <c r="AN24" t="s">
-        <v>464</v>
-      </c>
       <c r="AO24">
-        <v>0.99841760060377538</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP24">
-        <v>29.010655597451841</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9787,13 +9787,13 @@
         <v>606</v>
       </c>
       <c r="BB24" t="s">
-        <v>607</v>
+        <v>373</v>
       </c>
       <c r="BC24">
-        <v>0.97803702976044449</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD24">
-        <v>402.65445439185123</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="Z25" t="s">
         <v>363</v>
       </c>
       <c r="AA25">
-        <v>0.99726055556014181</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB25">
-        <v>50.223148064066145</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
+        <v>464</v>
+      </c>
+      <c r="AN25" t="s">
         <v>465</v>
       </c>
-      <c r="AN25" t="s">
-        <v>466</v>
-      </c>
       <c r="AO25">
-        <v>0.99781438034778358</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP25">
-        <v>40.069693623967019</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
+        <v>607</v>
+      </c>
+      <c r="BB25" t="s">
         <v>608</v>
       </c>
-      <c r="BB25" t="s">
-        <v>609</v>
-      </c>
       <c r="BC25">
-        <v>0.9973402418125219</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD25">
-        <v>48.762233437098502</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10004,16 +10004,16 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="Z26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AA26">
-        <v>0.94069903208664407</v>
+        <v>0.99621285878087551</v>
       </c>
       <c r="AB26">
-        <v>1087.1844117448593</v>
+        <v>69.43092235061502</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
@@ -10040,16 +10040,16 @@
         <v>407</v>
       </c>
       <c r="AM26" t="s">
+        <v>466</v>
+      </c>
+      <c r="AN26" t="s">
         <v>467</v>
       </c>
-      <c r="AN26" t="s">
-        <v>360</v>
-      </c>
       <c r="AO26">
-        <v>0.99192535126433146</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP26">
-        <v>148.0352268205892</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10076,16 +10076,16 @@
         <v>526</v>
       </c>
       <c r="BA26" t="s">
+        <v>609</v>
+      </c>
+      <c r="BB26" t="s">
         <v>610</v>
       </c>
-      <c r="BB26" t="s">
-        <v>611</v>
-      </c>
       <c r="BC26">
-        <v>0.98779966071713954</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD26">
-        <v>223.67288685244134</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10150,16 +10150,16 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="Z27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA27">
-        <v>0.99756610784588629</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB27">
-        <v>44.621356158751233</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
@@ -10189,13 +10189,13 @@
         <v>468</v>
       </c>
       <c r="AN27" t="s">
-        <v>356</v>
+        <v>469</v>
       </c>
       <c r="AO27">
-        <v>0.98092693557487454</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP27">
-        <v>349.67284779396647</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
+        <v>611</v>
+      </c>
+      <c r="BB27" t="s">
         <v>612</v>
       </c>
-      <c r="BB27" t="s">
-        <v>613</v>
-      </c>
       <c r="BC27">
-        <v>0.98841501119699848</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD27">
-        <v>212.39146138836088</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10296,16 +10296,16 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="Z28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA28">
-        <v>0.9972084849335241</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB28">
-        <v>51.177776218725121</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
@@ -10332,16 +10332,16 @@
         <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO28">
-        <v>0.99804155179341392</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP28">
-        <v>35.904883787411507</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="BB28" t="s">
-        <v>615</v>
+        <v>352</v>
       </c>
       <c r="BC28">
-        <v>0.93089405249526469</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD28">
-        <v>1266.9423709201483</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="Z29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA29">
-        <v>0.99628076912917996</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB29">
-        <v>68.185899298368355</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10478,16 +10478,16 @@
         <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO29">
-        <v>0.99508023417818925</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP29">
-        <v>90.195706733197795</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="BB29" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="BC29">
-        <v>0.99302778580016682</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD29">
-        <v>127.82392699694152</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="Z30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA30">
-        <v>0.9981032549815434</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB30">
-        <v>34.773658671704098</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10624,16 +10624,16 @@
         <v>415</v>
       </c>
       <c r="AM30" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN30" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO30">
-        <v>0.99940622505963084</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP30">
-        <v>10.885873906767051</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="BB30" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="BC30">
-        <v>0.99490784156958001</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD30">
-        <v>93.356237891033686</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Z31" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA31">
-        <v>0.99798824264234642</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB31">
-        <v>36.882218223648351</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10770,16 +10770,16 @@
         <v>417</v>
       </c>
       <c r="AM31" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN31" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO31">
-        <v>0.99863922747017897</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP31">
-        <v>24.947496380053089</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="BB31" t="s">
-        <v>621</v>
+        <v>370</v>
       </c>
       <c r="BC31">
-        <v>0.99015836110796274</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD31">
-        <v>180.43004635401576</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Z32" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="AA32">
-        <v>0.99391268208184824</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB32">
-        <v>111.60082849944791</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10916,16 +10916,16 @@
         <v>419</v>
       </c>
       <c r="AM32" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN32" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO32">
-        <v>0.99582230548799566</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP32">
-        <v>76.591066053413869</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10952,16 +10952,16 @@
         <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="BB32" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="BC32">
-        <v>0.99623532634854861</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD32">
-        <v>69.01901694327529</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Z33" t="s">
         <v>370</v>
       </c>
       <c r="AA33">
-        <v>0.99871218762601011</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB33">
-        <v>23.609893523147914</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11062,16 +11062,16 @@
         <v>421</v>
       </c>
       <c r="AM33" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN33" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO33">
-        <v>0.99811838305018963</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP33">
-        <v>34.496310746523356</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11098,16 +11098,16 @@
         <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="BB33" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="BC33">
-        <v>0.9966173923071765</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD33">
-        <v>62.014474368430825</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Z34" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA34">
-        <v>0.99856748800713691</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB34">
-        <v>26.26271986915707</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11208,16 +11208,16 @@
         <v>423</v>
       </c>
       <c r="AM34" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN34" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO34">
-        <v>0.9985928182686985</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP34">
-        <v>25.798331740528162</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11244,16 +11244,16 @@
         <v>542</v>
       </c>
       <c r="BA34" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="BB34" t="s">
-        <v>356</v>
+        <v>610</v>
       </c>
       <c r="BC34">
-        <v>0.98180592470173533</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD34">
-        <v>333.55804713485287</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Z35" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="AA35">
-        <v>0.97905685820454003</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB35">
-        <v>383.95759958343297</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11354,16 +11354,16 @@
         <v>425</v>
       </c>
       <c r="AM35" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN35" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO35">
-        <v>0.99769811225811866</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP35">
-        <v>42.201275267825203</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="BB35" t="s">
-        <v>353</v>
+        <v>625</v>
       </c>
       <c r="BC35">
-        <v>0.97902641975794957</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD35">
-        <v>384.51563777092457</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11464,16 +11464,16 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="Z36" t="s">
         <v>372</v>
       </c>
       <c r="AA36">
-        <v>0.99809166649408687</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB36">
-        <v>34.986114275074357</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
@@ -11500,16 +11500,16 @@
         <v>427</v>
       </c>
       <c r="AM36" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN36" t="s">
-        <v>357</v>
+        <v>487</v>
       </c>
       <c r="AO36">
-        <v>0.98814178187791379</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP36">
-        <v>217.40066557158059</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11536,16 +11536,16 @@
         <v>546</v>
       </c>
       <c r="BA36" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="BB36" t="s">
-        <v>358</v>
+        <v>450</v>
       </c>
       <c r="BC36">
-        <v>0.934538160869965</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD36">
-        <v>1200.1337173839754</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11610,16 +11610,16 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="Z37" t="s">
         <v>373</v>
       </c>
       <c r="AA37">
-        <v>0.99850557699173803</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB37">
-        <v>27.397755151469518</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
@@ -11646,16 +11646,16 @@
         <v>429</v>
       </c>
       <c r="AM37" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AN37" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AO37">
-        <v>0.99710631799330929</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP37">
-        <v>53.050836789329388</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11682,16 +11682,16 @@
         <v>548</v>
       </c>
       <c r="BA37" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="BB37" t="s">
-        <v>358</v>
+        <v>477</v>
       </c>
       <c r="BC37">
-        <v>0.94616153753972931</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD37">
-        <v>987.03847843829612</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11756,16 +11756,16 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="Z38" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AA38">
-        <v>0.99621285878087551</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB38">
-        <v>69.43092235061502</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
@@ -11792,16 +11792,16 @@
         <v>431</v>
       </c>
       <c r="AM38" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AN38" t="s">
-        <v>489</v>
+        <v>375</v>
       </c>
       <c r="AO38">
-        <v>0.99550555557680764</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP38">
-        <v>82.398147758527074</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11828,16 +11828,16 @@
         <v>550</v>
       </c>
       <c r="BA38" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="BB38" t="s">
-        <v>358</v>
+        <v>629</v>
       </c>
       <c r="BC38">
-        <v>0.97218956380622079</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD38">
-        <v>509.85799688595205</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11902,16 +11902,16 @@
         <v>341</v>
       </c>
       <c r="Y39" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Z39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AA39">
-        <v>0.9975431479552237</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB39">
-        <v>45.042287487565297</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD39" t="s">
         <v>282</v>
@@ -11938,16 +11938,16 @@
         <v>433</v>
       </c>
       <c r="AM39" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN39" t="s">
-        <v>491</v>
+        <v>359</v>
       </c>
       <c r="AO39">
-        <v>0.93896180472603763</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP39">
-        <v>1119.0335800226442</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11974,16 +11974,16 @@
         <v>552</v>
       </c>
       <c r="BA39" t="s">
+        <v>630</v>
+      </c>
+      <c r="BB39" t="s">
         <v>631</v>
       </c>
-      <c r="BB39" t="s">
-        <v>632</v>
-      </c>
       <c r="BC39">
-        <v>0.9924172440074055</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD39">
-        <v>139.01719319756617</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12048,16 +12048,16 @@
         <v>343</v>
       </c>
       <c r="Y40" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Z40" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA40">
-        <v>0.99636728996375623</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB40">
-        <v>66.599683997802714</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD40" t="s">
         <v>282</v>
@@ -12090,10 +12090,10 @@
         <v>493</v>
       </c>
       <c r="AO40">
-        <v>0.99013353407586135</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP40">
-        <v>180.88520860920943</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
+        <v>632</v>
+      </c>
+      <c r="BB40" t="s">
         <v>633</v>
       </c>
-      <c r="BB40" t="s">
-        <v>634</v>
-      </c>
       <c r="BC40">
-        <v>0.99114508565756532</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD40">
-        <v>162.34009627796874</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="Z41" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="AA41">
-        <v>0.97633688849282452</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB41">
-        <v>433.82371096488447</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
@@ -12236,10 +12236,10 @@
         <v>495</v>
       </c>
       <c r="AO41">
-        <v>0.99869589057011365</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP41">
-        <v>23.908672881248773</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12266,16 +12266,16 @@
         <v>556</v>
       </c>
       <c r="BA41" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="BB41" t="s">
-        <v>636</v>
+        <v>355</v>
       </c>
       <c r="BC41">
-        <v>0.99561586640696276</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD41">
-        <v>80.375782539015233</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12304,16 +12304,16 @@
         <v>558</v>
       </c>
       <c r="BA42" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="BB42" t="s">
-        <v>638</v>
+        <v>370</v>
       </c>
       <c r="BC42">
-        <v>0.99637036284424008</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD42">
-        <v>66.543347855598327</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12342,16 +12342,16 @@
         <v>560</v>
       </c>
       <c r="BA43" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="BB43" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="BC43">
-        <v>0.99681267676383467</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD43">
-        <v>58.434259329697142</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12380,16 +12380,16 @@
         <v>562</v>
       </c>
       <c r="BA44" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="BB44" t="s">
-        <v>642</v>
+        <v>477</v>
       </c>
       <c r="BC44">
-        <v>0.99602290686668338</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD44">
-        <v>72.91337411080552</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12418,16 +12418,16 @@
         <v>564</v>
       </c>
       <c r="BA45" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="BB45" t="s">
-        <v>644</v>
+        <v>373</v>
       </c>
       <c r="BC45">
-        <v>0.99253849155603513</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD45">
-        <v>136.79432147269009</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12456,16 +12456,16 @@
         <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="BB46" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="BC46">
-        <v>0.973232135644435</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD46">
-        <v>490.74417985202501</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12494,16 +12494,16 @@
         <v>568</v>
       </c>
       <c r="BA47" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="BB47" t="s">
-        <v>358</v>
+        <v>643</v>
       </c>
       <c r="BC47">
-        <v>0.96140381292129873</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD47">
-        <v>707.59676310952364</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12532,16 +12532,16 @@
         <v>570</v>
       </c>
       <c r="BA48" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="BB48" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="BC48">
-        <v>0.99234935324205875</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD48">
-        <v>140.26185722892211</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12570,16 +12570,16 @@
         <v>572</v>
       </c>
       <c r="BA49" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="BB49" t="s">
-        <v>362</v>
+        <v>647</v>
       </c>
       <c r="BC49">
-        <v>0.99536692897647694</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD49">
-        <v>84.939635431255269</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12608,16 +12608,16 @@
         <v>574</v>
       </c>
       <c r="BA50" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="BB50" t="s">
-        <v>651</v>
+        <v>359</v>
       </c>
       <c r="BC50">
-        <v>0.88199812838352587</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD50">
-        <v>2163.367646302027</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12646,16 +12646,16 @@
         <v>576</v>
       </c>
       <c r="BA51" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="BB51" t="s">
-        <v>358</v>
+        <v>650</v>
       </c>
       <c r="BC51">
-        <v>0.97591598065988894</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD51">
-        <v>441.54035456870389</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12684,16 +12684,16 @@
         <v>578</v>
       </c>
       <c r="BA52" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="BB52" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="BC52">
-        <v>0.99412039195829205</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD52">
-        <v>107.79281409797902</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12722,16 +12722,16 @@
         <v>580</v>
       </c>
       <c r="BA53" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="BB53" t="s">
-        <v>491</v>
+        <v>654</v>
       </c>
       <c r="BC53">
-        <v>0.98292548292671178</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD53">
-        <v>313.03281301028323</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12760,16 +12760,16 @@
         <v>582</v>
       </c>
       <c r="BA54" t="s">
+        <v>655</v>
+      </c>
+      <c r="BB54" t="s">
         <v>656</v>
       </c>
-      <c r="BB54" t="s">
-        <v>357</v>
-      </c>
       <c r="BC54">
-        <v>0.98355967005268352</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD54">
-        <v>301.40604903413595</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866CF6B4-E67A-42AB-8CCB-3A263AD136B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2F19EE-D574-4DE9-9948-E90715C2D559}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>628</v>
+        <v>597</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>629</v>
+        <v>598</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>630</v>
+        <v>599</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13331,7 +13331,7 @@
         <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>646</v>
+        <v>618</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13399,7 +13399,7 @@
         <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>649</v>
+        <v>613</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13467,7 +13467,7 @@
         <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>602</v>
+        <v>651</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>600</v>
+        <v>649</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>631</v>
+        <v>600</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>643</v>
+        <v>607</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>624</v>
+        <v>646</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13910,7 +13910,7 @@
         <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14011,7 +14011,7 @@
         <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="Y27">
         <v>28.239750000000001</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14147,7 +14147,7 @@
         <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="Y29">
         <v>3.38625</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>606</v>
+        <v>655</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>635</v>
+        <v>604</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>633</v>
+        <v>602</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14759,7 +14759,7 @@
         <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>647</v>
+        <v>611</v>
       </c>
       <c r="Y38">
         <v>64.437749999999994</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>592</v>
+        <v>627</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15068,7 +15068,7 @@
         <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>650</v>
+        <v>614</v>
       </c>
       <c r="Y44">
         <v>0.42149999999999999</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15138,7 +15138,7 @@
         <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="Y46">
         <v>1.81725</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>645</v>
+        <v>609</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2248F8CD-5DBC-42A1-8ECA-F21F7AB09C14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F1CF02-53C7-4D1D-9AE8-5B56644DE359}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6681D872-B8E6-48A6-859A-D104D10C64E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056D0D94-189F-4F8D-87C3-E5DA8F32FB4E}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{902D4F7D-7A65-49F0-B248-B889911BE6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6EA56F0-93F2-46B4-9812-A182A5BF936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,16 +980,148 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_solelc_spv_029</t>
@@ -998,102 +1130,6 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_011</t>
   </si>
   <si>
@@ -1118,12 +1154,6 @@
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_022</t>
   </si>
   <si>
@@ -1142,96 +1172,81 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
     <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
   </si>
   <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
   </si>
   <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
     <t>e_JP306-500,e_w215451416-500</t>
   </si>
   <si>
@@ -1241,25 +1256,154 @@
     <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
     <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
   </si>
   <si>
     <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
   </si>
   <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
     <t>distr_wonelc_won_017</t>
@@ -1280,78 +1424,6 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_019</t>
   </si>
   <si>
@@ -1364,66 +1436,6 @@
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_028</t>
   </si>
   <si>
@@ -1436,16 +1448,139 @@
     <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
   </si>
   <si>
     <t>elc_won_017</t>
@@ -1466,69 +1601,6 @@
     <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
-  </si>
-  <si>
     <t>elc_won_019</t>
   </si>
   <si>
@@ -1541,84 +1613,12 @@
     <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
   </si>
   <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
     <t>elc_won_028</t>
   </si>
   <si>
     <t>elc_won_031</t>
   </si>
   <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
@@ -1643,6 +1643,90 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_009</t>
   </si>
   <si>
@@ -1661,6 +1745,42 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
@@ -1703,34 +1823,28 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wofelc_wof_013</t>
@@ -1739,12 +1853,6 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_030</t>
   </si>
   <si>
@@ -1769,120 +1877,12 @@
     <t>connecting wind offshore to buses in cluster 42</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_019</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
@@ -1904,6 +1904,69 @@
     <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
   </si>
   <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
     <t>elc_wof_009</t>
   </si>
   <si>
@@ -1922,6 +1985,39 @@
     <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
   </si>
   <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
@@ -1952,31 +2048,28 @@
     <t>elc_wof_023</t>
   </si>
   <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
     <t>elc_wof_013</t>
@@ -1985,9 +2078,6 @@
     <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
   </si>
   <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
     <t>elc_wof_030</t>
   </si>
   <si>
@@ -2009,97 +2099,7 @@
     <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
   </si>
   <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
     <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80742817-EA7D-4E41-9BCD-FDDA1F6BAD7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B8F5486-181F-4901-842E-93F26D75B0E2}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7814,16 +7814,16 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.9488788277802801</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB11">
-        <v>937.22149069486488</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
@@ -7856,10 +7856,10 @@
         <v>440</v>
       </c>
       <c r="AO11">
-        <v>0.99804155179341392</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP11">
-        <v>35.904883787411507</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
@@ -7889,7 +7889,7 @@
         <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="BC11">
         <v>0.95957195194316591</v>
@@ -7960,16 +7960,16 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.99628076912917996</v>
+        <v>0.99809166649408687</v>
       </c>
       <c r="AB12">
-        <v>68.185899298368355</v>
+        <v>34.986114275074357</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
@@ -7999,13 +7999,13 @@
         <v>441</v>
       </c>
       <c r="AN12" t="s">
-        <v>442</v>
+        <v>364</v>
       </c>
       <c r="AO12">
-        <v>0.99508023417818925</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP12">
-        <v>90.195706733197795</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8106,16 +8106,16 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.99852430677621173</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB13">
-        <v>27.054375769451152</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
@@ -8142,16 +8142,16 @@
         <v>381</v>
       </c>
       <c r="AM13" t="s">
+        <v>442</v>
+      </c>
+      <c r="AN13" t="s">
         <v>443</v>
       </c>
-      <c r="AN13" t="s">
-        <v>444</v>
-      </c>
       <c r="AO13">
-        <v>0.99940622505963084</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP13">
-        <v>10.885873906767051</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8252,16 +8252,16 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.99838604658336239</v>
+        <v>0.99621285878087551</v>
       </c>
       <c r="AB14">
-        <v>29.589145971689483</v>
+        <v>69.43092235061502</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
@@ -8288,16 +8288,16 @@
         <v>383</v>
       </c>
       <c r="AM14" t="s">
+        <v>444</v>
+      </c>
+      <c r="AN14" t="s">
         <v>445</v>
       </c>
-      <c r="AN14" t="s">
-        <v>446</v>
-      </c>
       <c r="AO14">
-        <v>0.99827635377245738</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP14">
-        <v>31.600180838280902</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
@@ -8398,16 +8398,16 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.99825665520226836</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB15">
-        <v>31.96132129174655</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
@@ -8434,16 +8434,16 @@
         <v>385</v>
       </c>
       <c r="AM15" t="s">
+        <v>446</v>
+      </c>
+      <c r="AN15" t="s">
         <v>447</v>
       </c>
-      <c r="AN15" t="s">
-        <v>359</v>
-      </c>
       <c r="AO15">
-        <v>0.98949004263841422</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP15">
-        <v>192.68255162907312</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
@@ -8476,10 +8476,10 @@
         <v>592</v>
       </c>
       <c r="BC15">
-        <v>0.99366677237144974</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD15">
-        <v>116.10917319008783</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8544,16 +8544,16 @@
         <v>295</v>
       </c>
       <c r="Y16" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="Z16" t="s">
         <v>354</v>
       </c>
       <c r="AA16">
-        <v>0.99894650606645485</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB16">
-        <v>19.314055448326833</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD16" t="s">
         <v>282</v>
@@ -8583,13 +8583,13 @@
         <v>448</v>
       </c>
       <c r="AN16" t="s">
-        <v>370</v>
+        <v>449</v>
       </c>
       <c r="AO16">
-        <v>0.93717435218793788</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP16">
-        <v>1151.8035432211395</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8619,13 +8619,13 @@
         <v>593</v>
       </c>
       <c r="BB16" t="s">
-        <v>594</v>
+        <v>367</v>
       </c>
       <c r="BC16">
-        <v>0.9205295464439136</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD16">
-        <v>1456.9583151949184</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.98179245618315802</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB17">
-        <v>333.80496997543548</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8726,16 +8726,16 @@
         <v>389</v>
       </c>
       <c r="AM17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO17">
-        <v>0.96551955124232614</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP17">
-        <v>632.14156055735509</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
+        <v>594</v>
+      </c>
+      <c r="BB17" t="s">
         <v>595</v>
       </c>
-      <c r="BB17" t="s">
-        <v>596</v>
-      </c>
       <c r="BC17">
-        <v>0.99519319222421976</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD17">
-        <v>88.124809222638589</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8836,16 +8836,16 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.9981032549815434</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB18">
-        <v>34.773658671704098</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
@@ -8872,16 +8872,16 @@
         <v>391</v>
       </c>
       <c r="AM18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO18">
-        <v>0.99693456929731861</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP18">
-        <v>56.199562882493169</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
+        <v>596</v>
+      </c>
+      <c r="BB18" t="s">
         <v>597</v>
       </c>
-      <c r="BB18" t="s">
-        <v>370</v>
-      </c>
       <c r="BC18">
-        <v>0.934538160869965</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD18">
-        <v>1200.1337173839754</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.9977500892185478</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB19">
-        <v>41.248364326622962</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9018,16 +9018,16 @@
         <v>393</v>
       </c>
       <c r="AM19" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN19" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO19">
-        <v>0.99811838305018963</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP19">
-        <v>34.496310746523356</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9057,13 +9057,13 @@
         <v>598</v>
       </c>
       <c r="BB19" t="s">
-        <v>370</v>
+        <v>599</v>
       </c>
       <c r="BC19">
-        <v>0.94616153753972931</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD19">
-        <v>987.03847843829612</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.9982812149336332</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB20">
-        <v>31.51105955005805</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9164,16 +9164,16 @@
         <v>395</v>
       </c>
       <c r="AM20" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN20" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO20">
-        <v>0.9985928182686985</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP20">
-        <v>25.798331740528162</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9200,16 +9200,16 @@
         <v>514</v>
       </c>
       <c r="BA20" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="BB20" t="s">
-        <v>370</v>
+        <v>601</v>
       </c>
       <c r="BC20">
-        <v>0.97218956380622079</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD20">
-        <v>509.85799688595205</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="Z21" t="s">
         <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.98833720780868572</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB21">
-        <v>213.8178568407609</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9310,16 +9310,16 @@
         <v>397</v>
       </c>
       <c r="AM21" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN21" t="s">
-        <v>458</v>
+        <v>360</v>
       </c>
       <c r="AO21">
-        <v>0.99769811225811866</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP21">
-        <v>42.201275267825203</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9346,16 +9346,16 @@
         <v>516</v>
       </c>
       <c r="BA21" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="BB21" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="BC21">
-        <v>0.9924172440074055</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD21">
-        <v>139.01719319756617</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="Z22" t="s">
         <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.99900168239190124</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB22">
-        <v>18.302489481810518</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9459,13 +9459,13 @@
         <v>459</v>
       </c>
       <c r="AN22" t="s">
-        <v>373</v>
+        <v>460</v>
       </c>
       <c r="AO22">
-        <v>0.98814178187791379</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP22">
-        <v>217.40066557158059</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9492,16 +9492,16 @@
         <v>518</v>
       </c>
       <c r="BA22" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="BB22" t="s">
-        <v>603</v>
+        <v>364</v>
       </c>
       <c r="BC22">
-        <v>0.99114508565756532</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD22">
-        <v>162.34009627796874</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="Z23" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AA23">
-        <v>0.99798824264234642</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB23">
-        <v>36.882218223648351</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9602,16 +9602,16 @@
         <v>401</v>
       </c>
       <c r="AM23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO23">
-        <v>0.99841760060377538</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP23">
-        <v>29.010655597451841</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9638,16 +9638,16 @@
         <v>520</v>
       </c>
       <c r="BA23" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="BB23" t="s">
-        <v>605</v>
+        <v>355</v>
       </c>
       <c r="BC23">
-        <v>0.99561586640696276</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD23">
-        <v>80.375782539015233</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Z24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AA24">
-        <v>0.99809166649408687</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB24">
-        <v>34.986114275074357</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN24" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO24">
-        <v>0.99781438034778358</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP24">
-        <v>40.069693623967019</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9787,13 +9787,13 @@
         <v>606</v>
       </c>
       <c r="BB24" t="s">
-        <v>373</v>
+        <v>607</v>
       </c>
       <c r="BC24">
-        <v>0.98235584693125277</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD24">
-        <v>323.47613959369914</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="Z25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AA25">
-        <v>0.99850557699173803</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB25">
-        <v>27.397755151469518</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN25" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO25">
-        <v>0.99869874972548245</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP25">
-        <v>23.856255032822389</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="BB25" t="s">
-        <v>608</v>
+        <v>464</v>
       </c>
       <c r="BC25">
-        <v>0.99253849155603513</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD25">
-        <v>136.79432147269009</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10004,16 +10004,16 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="Z26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA26">
-        <v>0.99621285878087551</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB26">
-        <v>69.43092235061502</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
@@ -10040,16 +10040,16 @@
         <v>407</v>
       </c>
       <c r="AM26" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN26" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO26">
-        <v>0.99762356494824644</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP26">
-        <v>43.567975948815601</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10079,13 +10079,13 @@
         <v>609</v>
       </c>
       <c r="BB26" t="s">
-        <v>610</v>
+        <v>360</v>
       </c>
       <c r="BC26">
-        <v>0.973232135644435</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD26">
-        <v>490.74417985202501</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10150,16 +10150,16 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Z27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AA27">
-        <v>0.9975431479552237</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB27">
-        <v>45.042287487565297</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
@@ -10186,16 +10186,16 @@
         <v>409</v>
       </c>
       <c r="AM27" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN27" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO27">
-        <v>0.99669176136177262</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP27">
-        <v>60.651041700835236</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="BB27" t="s">
-        <v>612</v>
+        <v>477</v>
       </c>
       <c r="BC27">
-        <v>0.99234935324205875</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD27">
-        <v>140.26185722892211</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10296,16 +10296,16 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="Z28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA28">
-        <v>0.99636728996375623</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB28">
-        <v>66.599683997802714</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
@@ -10332,16 +10332,16 @@
         <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO28">
-        <v>0.99682717865030179</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP28">
-        <v>58.168391411134159</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="BB28" t="s">
-        <v>352</v>
+        <v>464</v>
       </c>
       <c r="BC28">
-        <v>0.99536692897647694</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD28">
-        <v>84.939635431255269</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z29" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA29">
-        <v>0.99391268208184824</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB29">
-        <v>111.60082849944791</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10478,16 +10478,16 @@
         <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO29">
-        <v>0.99710631799330929</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP29">
-        <v>53.050836789329388</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="BB29" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="BC29">
-        <v>0.88199812838352587</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD29">
-        <v>2163.367646302027</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA30">
-        <v>0.99871218762601011</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB30">
-        <v>23.609893523147914</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10624,16 +10624,16 @@
         <v>415</v>
       </c>
       <c r="AM30" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN30" t="s">
-        <v>475</v>
+        <v>355</v>
       </c>
       <c r="AO30">
-        <v>0.99550555557680764</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP30">
-        <v>82.398147758527074</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="BB30" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="BC30">
-        <v>0.9973402418125219</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD30">
-        <v>48.762233437098502</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="Z31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA31">
-        <v>0.99856748800713691</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB31">
-        <v>26.26271986915707</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10776,10 +10776,10 @@
         <v>477</v>
       </c>
       <c r="AO31">
-        <v>0.93896180472603763</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP31">
-        <v>1119.0335800226442</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="BB31" t="s">
-        <v>370</v>
+        <v>617</v>
       </c>
       <c r="BC31">
-        <v>0.96140381292129873</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD31">
-        <v>707.59676310952364</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Z32" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="AA32">
-        <v>0.97905685820454003</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB32">
-        <v>383.95759958343297</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10922,10 +10922,10 @@
         <v>479</v>
       </c>
       <c r="AO32">
-        <v>0.99863922747017897</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP32">
-        <v>24.947496380053089</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10952,16 +10952,16 @@
         <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="BB32" t="s">
-        <v>620</v>
+        <v>355</v>
       </c>
       <c r="BC32">
-        <v>0.98779966071713954</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD32">
-        <v>223.67288685244134</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="Z33" t="s">
         <v>370</v>
       </c>
       <c r="AA33">
-        <v>0.97633688849282452</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB33">
-        <v>433.82371096488447</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11068,10 +11068,10 @@
         <v>481</v>
       </c>
       <c r="AO33">
-        <v>0.99582230548799566</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP33">
-        <v>76.591066053413869</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11098,16 +11098,16 @@
         <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="BB33" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="BC33">
-        <v>0.98841501119699848</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD33">
-        <v>212.39146138836088</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="Z34" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA34">
-        <v>0.94069903208664407</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB34">
-        <v>1087.1844117448593</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11214,10 +11214,10 @@
         <v>483</v>
       </c>
       <c r="AO34">
-        <v>0.99013353407586135</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP34">
-        <v>180.88520860920943</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11244,16 +11244,16 @@
         <v>542</v>
       </c>
       <c r="BA34" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="BB34" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="BC34">
-        <v>0.93089405249526469</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD34">
-        <v>1266.9423709201483</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="Z35" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA35">
-        <v>0.99756610784588629</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB35">
-        <v>44.621356158751233</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11360,10 +11360,10 @@
         <v>485</v>
       </c>
       <c r="AO35">
-        <v>0.99869589057011365</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP35">
-        <v>23.908672881248773</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
+        <v>623</v>
+      </c>
+      <c r="BB35" t="s">
         <v>624</v>
       </c>
-      <c r="BB35" t="s">
-        <v>625</v>
-      </c>
       <c r="BC35">
-        <v>0.99302778580016682</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD35">
-        <v>127.82392699694152</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11464,16 +11464,16 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="Z36" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA36">
-        <v>0.9972084849335241</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB36">
-        <v>51.177776218725121</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
@@ -11506,10 +11506,10 @@
         <v>487</v>
       </c>
       <c r="AO36">
-        <v>0.99870022163576544</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP36">
-        <v>23.829270010966344</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11536,16 +11536,16 @@
         <v>546</v>
       </c>
       <c r="BA36" t="s">
+        <v>625</v>
+      </c>
+      <c r="BB36" t="s">
         <v>626</v>
       </c>
-      <c r="BB36" t="s">
-        <v>450</v>
-      </c>
       <c r="BC36">
-        <v>0.95726256957223688</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD36">
-        <v>783.51955784232393</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11610,16 +11610,16 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="Z37" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA37">
-        <v>0.99116451092312863</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB37">
-        <v>161.98396640930775</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
@@ -11652,10 +11652,10 @@
         <v>489</v>
       </c>
       <c r="AO37">
-        <v>0.99807466477127271</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP37">
-        <v>35.297812526667357</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11685,13 +11685,13 @@
         <v>627</v>
       </c>
       <c r="BB37" t="s">
-        <v>477</v>
+        <v>628</v>
       </c>
       <c r="BC37">
-        <v>0.9437657388784082</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD37">
-        <v>1030.9614538958492</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11756,16 +11756,16 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="Z38" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AA38">
-        <v>0.96189283472138964</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB38">
-        <v>698.63136344118936</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
@@ -11795,13 +11795,13 @@
         <v>490</v>
       </c>
       <c r="AN38" t="s">
-        <v>375</v>
+        <v>491</v>
       </c>
       <c r="AO38">
-        <v>0.99192535126433146</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP38">
-        <v>148.0352268205892</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11828,16 +11828,16 @@
         <v>550</v>
       </c>
       <c r="BA38" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="BB38" t="s">
-        <v>629</v>
+        <v>355</v>
       </c>
       <c r="BC38">
-        <v>0.99681267676383467</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD38">
-        <v>58.434259329697142</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11902,16 +11902,16 @@
         <v>341</v>
       </c>
       <c r="Y39" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="Z39" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="AA39">
-        <v>0.99410594174368461</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB39">
-        <v>108.05773469911641</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD39" t="s">
         <v>282</v>
@@ -11938,16 +11938,16 @@
         <v>433</v>
       </c>
       <c r="AM39" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN39" t="s">
-        <v>359</v>
+        <v>493</v>
       </c>
       <c r="AO39">
-        <v>0.98092693557487454</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP39">
-        <v>349.67284779396647</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11977,13 +11977,13 @@
         <v>630</v>
       </c>
       <c r="BB39" t="s">
-        <v>631</v>
+        <v>355</v>
       </c>
       <c r="BC39">
-        <v>0.99602290686668338</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD39">
-        <v>72.91337411080552</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12048,16 +12048,16 @@
         <v>343</v>
       </c>
       <c r="Y40" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="Z40" t="s">
         <v>375</v>
       </c>
       <c r="AA40">
-        <v>0.98968917222400854</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB40">
-        <v>189.03184255984442</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD40" t="s">
         <v>282</v>
@@ -12084,16 +12084,16 @@
         <v>435</v>
       </c>
       <c r="AM40" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN40" t="s">
-        <v>493</v>
+        <v>357</v>
       </c>
       <c r="AO40">
-        <v>0.99750949182367343</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP40">
-        <v>45.659316565986806</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="BB40" t="s">
-        <v>633</v>
+        <v>355</v>
       </c>
       <c r="BC40">
-        <v>0.99637036284424008</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD40">
-        <v>66.543347855598327</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="Z41" t="s">
         <v>376</v>
       </c>
       <c r="AA41">
-        <v>0.99726055556014181</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB41">
-        <v>50.223148064066145</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
@@ -12230,16 +12230,16 @@
         <v>437</v>
       </c>
       <c r="AM41" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN41" t="s">
-        <v>495</v>
+        <v>364</v>
       </c>
       <c r="AO41">
-        <v>0.99686124252542985</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP41">
-        <v>57.543887033786262</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12266,16 +12266,16 @@
         <v>556</v>
       </c>
       <c r="BA41" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="BB41" t="s">
-        <v>355</v>
+        <v>633</v>
       </c>
       <c r="BC41">
-        <v>0.97902641975794957</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD41">
-        <v>384.51563777092457</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12304,16 +12304,16 @@
         <v>558</v>
       </c>
       <c r="BA42" t="s">
+        <v>634</v>
+      </c>
+      <c r="BB42" t="s">
         <v>635</v>
       </c>
-      <c r="BB42" t="s">
-        <v>370</v>
-      </c>
       <c r="BC42">
-        <v>0.97591598065988894</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD42">
-        <v>441.54035456870389</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12348,10 +12348,10 @@
         <v>637</v>
       </c>
       <c r="BC43">
-        <v>0.99412039195829205</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD43">
-        <v>107.79281409797902</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12383,13 +12383,13 @@
         <v>638</v>
       </c>
       <c r="BB44" t="s">
-        <v>477</v>
+        <v>360</v>
       </c>
       <c r="BC44">
-        <v>0.98292548292671178</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD44">
-        <v>313.03281301028323</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12421,13 +12421,13 @@
         <v>639</v>
       </c>
       <c r="BB45" t="s">
-        <v>373</v>
+        <v>640</v>
       </c>
       <c r="BC45">
-        <v>0.98355967005268352</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD45">
-        <v>301.40604903413595</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12456,16 +12456,16 @@
         <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB46" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="BC46">
-        <v>0.99490784156958001</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD46">
-        <v>93.356237891033686</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12494,16 +12494,16 @@
         <v>568</v>
       </c>
       <c r="BA47" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BB47" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="BC47">
-        <v>0.99015836110796274</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD47">
-        <v>180.43004635401576</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12532,16 +12532,16 @@
         <v>570</v>
       </c>
       <c r="BA48" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="BB48" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="BC48">
-        <v>0.99623532634854861</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD48">
-        <v>69.01901694327529</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12570,16 +12570,16 @@
         <v>572</v>
       </c>
       <c r="BA49" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="BB49" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BC49">
-        <v>0.9966173923071765</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD49">
-        <v>62.014474368430825</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12608,16 +12608,16 @@
         <v>574</v>
       </c>
       <c r="BA50" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="BB50" t="s">
-        <v>359</v>
+        <v>650</v>
       </c>
       <c r="BC50">
-        <v>0.98180592470173533</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD50">
-        <v>333.55804713485287</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12646,16 +12646,16 @@
         <v>576</v>
       </c>
       <c r="BA51" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="BB51" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="BC51">
-        <v>0.98822137145239475</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD51">
-        <v>215.94152337276336</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12684,16 +12684,16 @@
         <v>578</v>
       </c>
       <c r="BA52" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="BB52" t="s">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="BC52">
-        <v>0.99662747375050009</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD52">
-        <v>61.829647907498845</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12722,16 +12722,16 @@
         <v>580</v>
       </c>
       <c r="BA53" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="BB53" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="BC53">
-        <v>0.99284590877035406</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD53">
-        <v>131.158339210175</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12760,16 +12760,16 @@
         <v>582</v>
       </c>
       <c r="BA54" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="BB54" t="s">
-        <v>656</v>
+        <v>370</v>
       </c>
       <c r="BC54">
-        <v>0.97803702976044449</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD54">
-        <v>402.65445439185123</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2F19EE-D574-4DE9-9948-E90715C2D559}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7540F7D5-AA42-403C-B891-82C2A92F52B4}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>598</v>
+        <v>630</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>599</v>
+        <v>631</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>635</v>
+        <v>605</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13162,7 +13162,7 @@
         <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13399,7 +13399,7 @@
         <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13467,7 +13467,7 @@
         <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>484</v>
+        <v>450</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>646</v>
+        <v>602</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13910,7 +13910,7 @@
         <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>439</v>
+        <v>484</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14011,7 +14011,7 @@
         <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="Y27">
         <v>28.239750000000001</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>648</v>
+        <v>604</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14147,7 +14147,7 @@
         <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="Y29">
         <v>3.38625</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>621</v>
+        <v>651</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>639</v>
+        <v>609</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>642</v>
+        <v>598</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>604</v>
+        <v>636</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14759,7 +14759,7 @@
         <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="Y38">
         <v>64.437749999999994</v>
@@ -14794,7 +14794,7 @@
         <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>640</v>
+        <v>596</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15068,7 +15068,7 @@
         <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>614</v>
+        <v>594</v>
       </c>
       <c r="Y44">
         <v>0.42149999999999999</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15138,7 +15138,7 @@
         <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="Y46">
         <v>1.81725</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>638</v>
+        <v>608</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>624</v>
+        <v>654</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>644</v>
+        <v>600</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F1CF02-53C7-4D1D-9AE8-5B56644DE359}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673870E0-C3DD-4CDE-AE60-0F54D7E07E4D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056D0D94-189F-4F8D-87C3-E5DA8F32FB4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ABA1162-FE85-4AAA-B40C-D6DFAFDB4FCE}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6EA56F0-93F2-46B4-9812-A182A5BF936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE1952DB-203B-43DC-86BB-1BAB2D1986BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,46 +980,178 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_028</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_solelc_spv_021</t>
@@ -1040,226 +1172,112 @@
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
     <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
   </si>
   <si>
-    <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
   </si>
   <si>
     <t>e_JP306-500</t>
   </si>
   <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
     <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
   </si>
   <si>
     <t>e_w179863079-275,e_JP6-275</t>
   </si>
   <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wonelc_won_005</t>
@@ -1274,22 +1292,64 @@
     <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_024</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_001</t>
@@ -1328,6 +1388,36 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_007</t>
   </si>
   <si>
@@ -1346,24 +1436,6 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_006</t>
   </si>
   <si>
@@ -1376,76 +1448,22 @@
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
     <t>elc_won_005</t>
@@ -1457,22 +1475,55 @@
     <t>elc_won_029</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
     <t>elc_won_024</t>
   </si>
   <si>
     <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
   </si>
   <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
   </si>
   <si>
     <t>elc_won_001</t>
@@ -1508,6 +1559,36 @@
     <t>elc_won_030</t>
   </si>
   <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
     <t>elc_won_007</t>
   </si>
   <si>
@@ -1526,24 +1607,6 @@
     <t>e_JP219-500,e_JP132-500</t>
   </si>
   <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
     <t>elc_won_006</t>
   </si>
   <si>
@@ -1556,67 +1619,190 @@
     <t>e_w459476442-500,e_w150065045-500</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wofelc_wof_006</t>
@@ -1643,120 +1829,6 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_040</t>
   </si>
   <si>
@@ -1769,18 +1841,6 @@
     <t>connecting wind offshore to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
@@ -1817,72 +1877,168 @@
     <t>connecting wind offshore to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_019</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
@@ -1904,96 +2060,6 @@
     <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
   </si>
   <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
     <t>elc_wof_040</t>
   </si>
   <si>
@@ -2006,18 +2072,6 @@
     <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
   </si>
   <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
@@ -2043,60 +2097,6 @@
   </si>
   <si>
     <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
   </si>
   <si>
     <t>elc_wof_019</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B8F5486-181F-4901-842E-93F26D75B0E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E4E3E15-0AC2-497E-B931-838D1CC6289F}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7814,16 +7814,16 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.99798824264234642</v>
+        <v>0.99809166649408687</v>
       </c>
       <c r="AB11">
-        <v>36.882218223648351</v>
+        <v>34.986114275074357</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
@@ -7856,10 +7856,10 @@
         <v>440</v>
       </c>
       <c r="AO11">
-        <v>0.99827635377245738</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP11">
-        <v>31.600180838280902</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR11" t="s">
         <v>282</v>
@@ -7889,13 +7889,13 @@
         <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="BC11">
-        <v>0.95957195194316591</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD11">
-        <v>741.18088104195795</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7960,16 +7960,16 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.99809166649408687</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB12">
-        <v>34.986114275074357</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
@@ -7999,13 +7999,13 @@
         <v>441</v>
       </c>
       <c r="AN12" t="s">
-        <v>364</v>
+        <v>442</v>
       </c>
       <c r="AO12">
-        <v>0.98949004263841422</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP12">
-        <v>192.68255162907312</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8038,10 +8038,10 @@
         <v>586</v>
       </c>
       <c r="BC12">
-        <v>0.99603667376986049</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD12">
-        <v>72.660980885890424</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8106,16 +8106,16 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.99850557699173803</v>
+        <v>0.99621285878087551</v>
       </c>
       <c r="AB13">
-        <v>27.397755151469518</v>
+        <v>69.43092235061502</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
@@ -8142,16 +8142,16 @@
         <v>381</v>
       </c>
       <c r="AM13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO13">
-        <v>0.99682717865030179</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP13">
-        <v>58.168391411134159</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8184,10 +8184,10 @@
         <v>588</v>
       </c>
       <c r="BC13">
-        <v>0.99017867813273497</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD13">
-        <v>180.05756756652616</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8252,16 +8252,16 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.99621285878087551</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB14">
-        <v>69.43092235061502</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
@@ -8288,16 +8288,16 @@
         <v>383</v>
       </c>
       <c r="AM14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO14">
-        <v>0.99750949182367343</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP14">
-        <v>45.659316565986806</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
@@ -8330,10 +8330,10 @@
         <v>590</v>
       </c>
       <c r="BC14">
-        <v>0.99504061303190972</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD14">
-        <v>90.922094414988095</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8398,16 +8398,16 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.9975431479552237</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB15">
-        <v>45.042287487565297</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
@@ -8434,16 +8434,16 @@
         <v>385</v>
       </c>
       <c r="AM15" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN15" t="s">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AO15">
-        <v>0.99869874972548245</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP15">
-        <v>23.856255032822389</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
@@ -8476,10 +8476,10 @@
         <v>592</v>
       </c>
       <c r="BC15">
-        <v>0.99234935324205875</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD15">
-        <v>140.26185722892211</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8544,16 +8544,16 @@
         <v>295</v>
       </c>
       <c r="Y16" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="Z16" t="s">
         <v>354</v>
       </c>
       <c r="AA16">
-        <v>0.99636728996375623</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB16">
-        <v>66.599683997802714</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD16" t="s">
         <v>282</v>
@@ -8583,13 +8583,13 @@
         <v>448</v>
       </c>
       <c r="AN16" t="s">
-        <v>449</v>
+        <v>365</v>
       </c>
       <c r="AO16">
-        <v>0.99013353407586135</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP16">
-        <v>180.88520860920943</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8619,13 +8619,13 @@
         <v>593</v>
       </c>
       <c r="BB16" t="s">
-        <v>367</v>
+        <v>594</v>
       </c>
       <c r="BC16">
-        <v>0.99536692897647694</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD16">
-        <v>84.939635431255269</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.96189283472138964</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB17">
-        <v>698.63136344118936</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8726,16 +8726,16 @@
         <v>389</v>
       </c>
       <c r="AM17" t="s">
+        <v>449</v>
+      </c>
+      <c r="AN17" t="s">
         <v>450</v>
       </c>
-      <c r="AN17" t="s">
-        <v>451</v>
-      </c>
       <c r="AO17">
-        <v>0.99869589057011365</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP17">
-        <v>23.908672881248773</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="BB17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="BC17">
-        <v>0.88199812838352587</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD17">
-        <v>2163.367646302027</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8836,16 +8836,16 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.99410594174368461</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB18">
-        <v>108.05773469911641</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
@@ -8872,16 +8872,16 @@
         <v>391</v>
       </c>
       <c r="AM18" t="s">
+        <v>451</v>
+      </c>
+      <c r="AN18" t="s">
         <v>452</v>
       </c>
-      <c r="AN18" t="s">
-        <v>453</v>
-      </c>
       <c r="AO18">
-        <v>0.99811838305018963</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP18">
-        <v>34.496310746523356</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="BB18" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="BC18">
-        <v>0.99490784156958001</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD18">
-        <v>93.356237891033686</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.98968917222400854</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB19">
-        <v>189.03184255984442</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9018,16 +9018,16 @@
         <v>393</v>
       </c>
       <c r="AM19" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN19" t="s">
         <v>454</v>
       </c>
-      <c r="AN19" t="s">
-        <v>455</v>
-      </c>
       <c r="AO19">
-        <v>0.9985928182686985</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP19">
-        <v>25.798331740528162</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9054,16 +9054,16 @@
         <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="BB19" t="s">
-        <v>599</v>
+        <v>450</v>
       </c>
       <c r="BC19">
-        <v>0.99015836110796274</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD19">
-        <v>180.43004635401576</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.9981032549815434</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB20">
-        <v>34.773658671704098</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9164,16 +9164,16 @@
         <v>395</v>
       </c>
       <c r="AM20" t="s">
+        <v>455</v>
+      </c>
+      <c r="AN20" t="s">
         <v>456</v>
       </c>
-      <c r="AN20" t="s">
-        <v>457</v>
-      </c>
       <c r="AO20">
-        <v>0.99769811225811866</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP20">
-        <v>42.201275267825203</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9203,13 +9203,13 @@
         <v>600</v>
       </c>
       <c r="BB20" t="s">
-        <v>601</v>
+        <v>491</v>
       </c>
       <c r="BC20">
-        <v>0.99623532634854861</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD20">
-        <v>69.01901694327529</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Z21" t="s">
         <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.99726055556014181</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB21">
-        <v>50.223148064066145</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9310,16 +9310,16 @@
         <v>397</v>
       </c>
       <c r="AM21" t="s">
+        <v>457</v>
+      </c>
+      <c r="AN21" t="s">
         <v>458</v>
       </c>
-      <c r="AN21" t="s">
-        <v>360</v>
-      </c>
       <c r="AO21">
-        <v>0.98814178187791379</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP21">
-        <v>217.40066557158059</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9346,16 +9346,16 @@
         <v>516</v>
       </c>
       <c r="BA21" t="s">
+        <v>601</v>
+      </c>
+      <c r="BB21" t="s">
         <v>602</v>
       </c>
-      <c r="BB21" t="s">
-        <v>603</v>
-      </c>
       <c r="BC21">
-        <v>0.9966173923071765</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD21">
-        <v>62.014474368430825</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Z22" t="s">
         <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.99116451092312863</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB22">
-        <v>161.98396640930775</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9462,10 +9462,10 @@
         <v>460</v>
       </c>
       <c r="AO22">
-        <v>0.99710631799330929</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP22">
-        <v>53.050836789329388</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9492,16 +9492,16 @@
         <v>518</v>
       </c>
       <c r="BA22" t="s">
+        <v>603</v>
+      </c>
+      <c r="BB22" t="s">
         <v>604</v>
       </c>
-      <c r="BB22" t="s">
-        <v>364</v>
-      </c>
       <c r="BC22">
-        <v>0.98180592470173533</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD22">
-        <v>333.55804713485287</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="Z23" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AA23">
-        <v>0.97633688849282452</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB23">
-        <v>433.82371096488447</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9605,13 +9605,13 @@
         <v>461</v>
       </c>
       <c r="AN23" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="AO23">
-        <v>0.99550555557680764</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP23">
-        <v>82.398147758527074</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9641,13 +9641,13 @@
         <v>605</v>
       </c>
       <c r="BB23" t="s">
-        <v>355</v>
+        <v>606</v>
       </c>
       <c r="BC23">
-        <v>0.97591598065988894</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD23">
-        <v>441.54035456870389</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Z24" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA24">
-        <v>0.9488788277802801</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB24">
-        <v>937.22149069486488</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN24" t="s">
-        <v>464</v>
+        <v>360</v>
       </c>
       <c r="AO24">
-        <v>0.93896180472603763</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP24">
-        <v>1119.0335800226442</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9784,16 +9784,16 @@
         <v>522</v>
       </c>
       <c r="BA24" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="BB24" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="BC24">
-        <v>0.99412039195829205</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD24">
-        <v>107.79281409797902</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="Z25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA25">
-        <v>0.9977500892185478</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB25">
-        <v>41.248364326622962</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AN25" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AO25">
-        <v>0.99870022163576544</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP25">
-        <v>23.829270010966344</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="BB25" t="s">
-        <v>464</v>
+        <v>610</v>
       </c>
       <c r="BC25">
-        <v>0.98292548292671178</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD25">
-        <v>313.03281301028323</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10004,16 +10004,16 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="Z26" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA26">
-        <v>0.9982812149336332</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB26">
-        <v>31.51105955005805</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
@@ -10040,16 +10040,16 @@
         <v>407</v>
       </c>
       <c r="AM26" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AN26" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AO26">
-        <v>0.99807466477127271</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP26">
-        <v>35.297812526667357</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10076,16 +10076,16 @@
         <v>526</v>
       </c>
       <c r="BA26" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="BB26" t="s">
-        <v>360</v>
+        <v>612</v>
       </c>
       <c r="BC26">
-        <v>0.98355967005268352</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD26">
-        <v>301.40604903413595</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10150,16 +10150,16 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="Z27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA27">
-        <v>0.98833720780868572</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB27">
-        <v>213.8178568407609</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
@@ -10186,16 +10186,16 @@
         <v>409</v>
       </c>
       <c r="AM27" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN27" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AO27">
-        <v>0.99686124252542985</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP27">
-        <v>57.543887033786262</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="BB27" t="s">
-        <v>477</v>
+        <v>614</v>
       </c>
       <c r="BC27">
-        <v>0.95726256957223688</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD27">
-        <v>783.51955784232393</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10296,16 +10296,16 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Z28" t="s">
         <v>365</v>
       </c>
       <c r="AA28">
-        <v>0.99900168239190124</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB28">
-        <v>18.302489481810518</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
@@ -10332,16 +10332,16 @@
         <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN28" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AO28">
-        <v>0.99841760060377538</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP28">
-        <v>29.010655597451841</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="BB28" t="s">
-        <v>464</v>
+        <v>596</v>
       </c>
       <c r="BC28">
-        <v>0.9437657388784082</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD28">
-        <v>1030.9614538958492</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Z29" t="s">
         <v>366</v>
       </c>
       <c r="AA29">
-        <v>0.99852430677621173</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB29">
-        <v>27.054375769451152</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10478,16 +10478,16 @@
         <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AN29" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AO29">
-        <v>0.99781438034778358</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP29">
-        <v>40.069693623967019</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="BB29" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="BC29">
-        <v>0.99366677237144974</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD29">
-        <v>116.10917319008783</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="Z30" t="s">
         <v>367</v>
       </c>
       <c r="AA30">
-        <v>0.99838604658336239</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB30">
-        <v>29.589145971689483</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10624,16 +10624,16 @@
         <v>415</v>
       </c>
       <c r="AM30" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AN30" t="s">
-        <v>355</v>
+        <v>474</v>
       </c>
       <c r="AO30">
-        <v>0.93717435218793788</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP30">
-        <v>1151.8035432211395</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="BB30" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="BC30">
-        <v>0.9205295464439136</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD30">
-        <v>1456.9583151949184</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Z31" t="s">
         <v>368</v>
       </c>
       <c r="AA31">
-        <v>0.99825665520226836</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB31">
-        <v>31.96132129174655</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10770,16 +10770,16 @@
         <v>417</v>
       </c>
       <c r="AM31" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AN31" t="s">
-        <v>477</v>
+        <v>361</v>
       </c>
       <c r="AO31">
-        <v>0.96551955124232614</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP31">
-        <v>632.14156055735509</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="BB31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="BC31">
-        <v>0.99519319222421976</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD31">
-        <v>88.124809222638589</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="Z32" t="s">
         <v>369</v>
       </c>
       <c r="AA32">
-        <v>0.99894650606645485</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB32">
-        <v>19.314055448326833</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10916,16 +10916,16 @@
         <v>419</v>
       </c>
       <c r="AM32" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AN32" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AO32">
-        <v>0.99693456929731861</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP32">
-        <v>56.199562882493169</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10952,16 +10952,16 @@
         <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="BB32" t="s">
-        <v>355</v>
+        <v>623</v>
       </c>
       <c r="BC32">
-        <v>0.96140381292129873</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD32">
-        <v>707.59676310952364</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="Z33" t="s">
         <v>370</v>
       </c>
       <c r="AA33">
-        <v>0.98179245618315802</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB33">
-        <v>333.80496997543548</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11062,16 +11062,16 @@
         <v>421</v>
       </c>
       <c r="AM33" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AN33" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AO33">
-        <v>0.99863922747017897</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP33">
-        <v>24.947496380053089</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11098,16 +11098,16 @@
         <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="BB33" t="s">
-        <v>620</v>
+        <v>360</v>
       </c>
       <c r="BC33">
-        <v>0.99637036284424008</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD33">
-        <v>66.543347855598327</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="Z34" t="s">
         <v>371</v>
       </c>
       <c r="AA34">
-        <v>0.99628076912917996</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB34">
-        <v>68.185899298368355</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11208,16 +11208,16 @@
         <v>423</v>
       </c>
       <c r="AM34" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AN34" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AO34">
-        <v>0.99582230548799566</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP34">
-        <v>76.591066053413869</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11244,16 +11244,16 @@
         <v>542</v>
       </c>
       <c r="BA34" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="BB34" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="BC34">
-        <v>0.99681267676383467</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD34">
-        <v>58.434259329697142</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Z35" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="AA35">
-        <v>0.99391268208184824</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB35">
-        <v>111.60082849944791</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11354,16 +11354,16 @@
         <v>425</v>
       </c>
       <c r="AM35" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AN35" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AO35">
-        <v>0.99804155179341392</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP35">
-        <v>35.904883787411507</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="BB35" t="s">
-        <v>624</v>
+        <v>355</v>
       </c>
       <c r="BC35">
-        <v>0.99602290686668338</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD35">
-        <v>72.91337411080552</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11464,16 +11464,16 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Z36" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA36">
-        <v>0.99871218762601011</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB36">
-        <v>23.609893523147914</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
@@ -11500,16 +11500,16 @@
         <v>427</v>
       </c>
       <c r="AM36" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AN36" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AO36">
-        <v>0.99508023417818925</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP36">
-        <v>90.195706733197795</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11536,16 +11536,16 @@
         <v>546</v>
       </c>
       <c r="BA36" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="BB36" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="BC36">
-        <v>0.99253849155603513</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD36">
-        <v>136.79432147269009</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11610,16 +11610,16 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z37" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA37">
-        <v>0.99856748800713691</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB37">
-        <v>26.26271986915707</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
@@ -11646,16 +11646,16 @@
         <v>429</v>
       </c>
       <c r="AM37" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AN37" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AO37">
-        <v>0.99940622505963084</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP37">
-        <v>10.885873906767051</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11682,16 +11682,16 @@
         <v>548</v>
       </c>
       <c r="BA37" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="BB37" t="s">
-        <v>628</v>
+        <v>365</v>
       </c>
       <c r="BC37">
-        <v>0.973232135644435</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD37">
-        <v>490.74417985202501</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11756,16 +11756,16 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z38" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="AA38">
-        <v>0.97905685820454003</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB38">
-        <v>383.95759958343297</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
@@ -11792,16 +11792,16 @@
         <v>431</v>
       </c>
       <c r="AM38" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AN38" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AO38">
-        <v>0.99762356494824644</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP38">
-        <v>43.567975948815601</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11828,16 +11828,16 @@
         <v>550</v>
       </c>
       <c r="BA38" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="BB38" t="s">
-        <v>355</v>
+        <v>632</v>
       </c>
       <c r="BC38">
-        <v>0.934538160869965</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD38">
-        <v>1200.1337173839754</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11902,16 +11902,16 @@
         <v>341</v>
       </c>
       <c r="Y39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Z39" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="AA39">
-        <v>0.94069903208664407</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB39">
-        <v>1087.1844117448593</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD39" t="s">
         <v>282</v>
@@ -11938,16 +11938,16 @@
         <v>433</v>
       </c>
       <c r="AM39" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AN39" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AO39">
-        <v>0.99669176136177262</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP39">
-        <v>60.651041700835236</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11974,16 +11974,16 @@
         <v>552</v>
       </c>
       <c r="BA39" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="BB39" t="s">
-        <v>355</v>
+        <v>491</v>
       </c>
       <c r="BC39">
-        <v>0.94616153753972931</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD39">
-        <v>987.03847843829612</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12048,16 +12048,16 @@
         <v>343</v>
       </c>
       <c r="Y40" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="Z40" t="s">
         <v>375</v>
       </c>
       <c r="AA40">
-        <v>0.99756610784588629</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB40">
-        <v>44.621356158751233</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD40" t="s">
         <v>282</v>
@@ -12084,16 +12084,16 @@
         <v>435</v>
       </c>
       <c r="AM40" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AN40" t="s">
-        <v>357</v>
+        <v>493</v>
       </c>
       <c r="AO40">
-        <v>0.99192535126433146</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP40">
-        <v>148.0352268205892</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="BB40" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="BC40">
-        <v>0.97218956380622079</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD40">
-        <v>509.85799688595205</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="Z41" t="s">
         <v>376</v>
       </c>
       <c r="AA41">
-        <v>0.9972084849335241</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB41">
-        <v>51.177776218725121</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
@@ -12230,16 +12230,16 @@
         <v>437</v>
       </c>
       <c r="AM41" t="s">
+        <v>494</v>
+      </c>
+      <c r="AN41" t="s">
         <v>495</v>
       </c>
-      <c r="AN41" t="s">
-        <v>364</v>
-      </c>
       <c r="AO41">
-        <v>0.98092693557487454</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP41">
-        <v>349.67284779396647</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12266,16 +12266,16 @@
         <v>556</v>
       </c>
       <c r="BA41" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="BB41" t="s">
-        <v>633</v>
+        <v>365</v>
       </c>
       <c r="BC41">
-        <v>0.9924172440074055</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD41">
-        <v>139.01719319756617</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12304,16 +12304,16 @@
         <v>558</v>
       </c>
       <c r="BA42" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="BB42" t="s">
-        <v>635</v>
+        <v>365</v>
       </c>
       <c r="BC42">
-        <v>0.99114508565756532</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD42">
-        <v>162.34009627796874</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12342,16 +12342,16 @@
         <v>560</v>
       </c>
       <c r="BA43" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="BB43" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="BC43">
-        <v>0.99561586640696276</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD43">
-        <v>80.375782539015233</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12380,16 +12380,16 @@
         <v>562</v>
       </c>
       <c r="BA44" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="BB44" t="s">
-        <v>360</v>
+        <v>640</v>
       </c>
       <c r="BC44">
-        <v>0.98235584693125277</v>
+        <v>0.99017867813273497</v>
       </c>
       <c r="BD44">
-        <v>323.47613959369914</v>
+        <v>180.05756756652616</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12418,16 +12418,16 @@
         <v>564</v>
       </c>
       <c r="BA45" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="BB45" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="BC45">
-        <v>0.98822137145239475</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD45">
-        <v>215.94152337276336</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12456,16 +12456,16 @@
         <v>566</v>
       </c>
       <c r="BA46" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="BB46" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="BC46">
-        <v>0.99662747375050009</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD46">
-        <v>61.829647907498845</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12494,16 +12494,16 @@
         <v>568</v>
       </c>
       <c r="BA47" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="BB47" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="BC47">
-        <v>0.99284590877035406</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD47">
-        <v>131.158339210175</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12532,16 +12532,16 @@
         <v>570</v>
       </c>
       <c r="BA48" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="BB48" t="s">
-        <v>646</v>
+        <v>365</v>
       </c>
       <c r="BC48">
-        <v>0.97803702976044449</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD48">
-        <v>402.65445439185123</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12570,16 +12570,16 @@
         <v>572</v>
       </c>
       <c r="BA49" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BB49" t="s">
-        <v>648</v>
+        <v>365</v>
       </c>
       <c r="BC49">
-        <v>0.9973402418125219</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD49">
-        <v>48.762233437098502</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12611,13 +12611,13 @@
         <v>649</v>
       </c>
       <c r="BB50" t="s">
-        <v>650</v>
+        <v>365</v>
       </c>
       <c r="BC50">
-        <v>0.98779966071713954</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD50">
-        <v>223.67288685244134</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12646,16 +12646,16 @@
         <v>576</v>
       </c>
       <c r="BA51" t="s">
+        <v>650</v>
+      </c>
+      <c r="BB51" t="s">
         <v>651</v>
       </c>
-      <c r="BB51" t="s">
-        <v>652</v>
-      </c>
       <c r="BC51">
-        <v>0.98841501119699848</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD51">
-        <v>212.39146138836088</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12684,16 +12684,16 @@
         <v>578</v>
       </c>
       <c r="BA52" t="s">
+        <v>652</v>
+      </c>
+      <c r="BB52" t="s">
         <v>653</v>
       </c>
-      <c r="BB52" t="s">
-        <v>628</v>
-      </c>
       <c r="BC52">
-        <v>0.93089405249526469</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD52">
-        <v>1266.9423709201483</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12728,10 +12728,10 @@
         <v>655</v>
       </c>
       <c r="BC53">
-        <v>0.99302778580016682</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD53">
-        <v>127.82392699694152</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12763,7 +12763,7 @@
         <v>656</v>
       </c>
       <c r="BB54" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="BC54">
         <v>0.97902641975794957</v>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7540F7D5-AA42-403C-B891-82C2A92F52B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE8CFE2-D75A-4433-83CE-3C70783162B0}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>631</v>
+        <v>649</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13162,7 +13162,7 @@
         <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13263,7 +13263,7 @@
         <v>729</v>
       </c>
       <c r="X16" t="s">
-        <v>584</v>
+        <v>636</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13331,7 +13331,7 @@
         <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13399,7 +13399,7 @@
         <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>593</v>
+        <v>627</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13467,7 +13467,7 @@
         <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>641</v>
+        <v>607</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>639</v>
+        <v>605</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>647</v>
+        <v>601</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13910,7 +13910,7 @@
         <v>687</v>
       </c>
       <c r="K26" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13943,7 +13943,7 @@
         <v>749</v>
       </c>
       <c r="X26" t="s">
-        <v>589</v>
+        <v>641</v>
       </c>
       <c r="Y26">
         <v>63.731250000000003</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14011,7 +14011,7 @@
         <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>616</v>
+        <v>589</v>
       </c>
       <c r="Y27">
         <v>28.239750000000001</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>645</v>
+        <v>611</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>651</v>
+        <v>593</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>638</v>
+        <v>584</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14759,7 +14759,7 @@
         <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>591</v>
+        <v>625</v>
       </c>
       <c r="Y38">
         <v>64.437749999999994</v>
@@ -14794,7 +14794,7 @@
         <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>649</v>
+        <v>591</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14963,7 +14963,7 @@
         <v>779</v>
       </c>
       <c r="X41" t="s">
-        <v>585</v>
+        <v>637</v>
       </c>
       <c r="Y41">
         <v>27.642749999999999</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15068,7 +15068,7 @@
         <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>594</v>
+        <v>628</v>
       </c>
       <c r="Y44">
         <v>0.42149999999999999</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>653</v>
+        <v>595</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15138,7 +15138,7 @@
         <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>614</v>
+        <v>587</v>
       </c>
       <c r="Y46">
         <v>1.81725</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15243,7 +15243,7 @@
         <v>795</v>
       </c>
       <c r="X49" t="s">
-        <v>587</v>
+        <v>639</v>
       </c>
       <c r="Y49">
         <v>42.144750000000002</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>643</v>
+        <v>609</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>654</v>
+        <v>597</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>623</v>
+        <v>645</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673870E0-C3DD-4CDE-AE60-0F54D7E07E4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F0D8E0-2AD4-4A21-B284-8385F71DED6D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ABA1162-FE85-4AAA-B40C-D6DFAFDB4FCE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E086378-3C0A-4B9E-8930-E879D90B9CB7}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE1952DB-203B-43DC-86BB-1BAB2D1986BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD3AA309-1693-488C-9488-C9BDC3FE5294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,18 +980,24 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_017</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_019</t>
   </si>
   <si>
@@ -1016,6 +1022,18 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_012</t>
   </si>
   <si>
@@ -1028,6 +1046,84 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_024</t>
   </si>
   <si>
@@ -1040,22 +1136,22 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_solelc_spv_005</t>
@@ -1064,18 +1160,6 @@
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_029</t>
   </si>
   <si>
@@ -1088,96 +1172,15 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
     <t>e_w317416612-500,e_JP117-500,e_w242103481-500,e_w317511904-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
   </si>
   <si>
@@ -1193,81 +1196,174 @@
     <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
+    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
     <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
   </si>
   <si>
     <t>e_w216956620-500,e_w216953915-500</t>
   </si>
   <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
     <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
   </si>
   <si>
     <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
   </si>
   <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
   </si>
   <si>
     <t>e_w179863079-275</t>
   </si>
   <si>
-    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_016</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_011</t>
   </si>
   <si>
@@ -1280,6 +1376,30 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_005</t>
   </si>
   <si>
@@ -1292,34 +1412,28 @@
     <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_wonelc_won_013</t>
@@ -1334,126 +1448,102 @@
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
     <t>elc_won_016</t>
   </si>
   <si>
     <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
   </si>
   <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
     <t>elc_won_011</t>
   </si>
   <si>
@@ -1466,6 +1556,30 @@
     <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
     <t>elc_won_005</t>
   </si>
   <si>
@@ -1475,31 +1589,22 @@
     <t>elc_won_029</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
   </si>
   <si>
     <t>elc_won_013</t>
@@ -1514,109 +1619,196 @@
     <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_JP7-275</t>
   </si>
   <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275,e_w179863079-275,e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
   </si>
   <si>
     <t>distr_wofelc_wof_023</t>
@@ -1625,58 +1817,34 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wofelc_wof_013</t>
@@ -1691,90 +1859,6 @@
     <t>connecting wind offshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
@@ -1799,139 +1883,196 @@
     <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
   </si>
   <si>
     <t>elc_wof_023</t>
   </si>
   <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
   </si>
   <si>
     <t>elc_wof_013</t>
@@ -1946,81 +2087,6 @@
     <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
   </si>
   <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
     <t>elc_wof_004</t>
   </si>
   <si>
@@ -2034,72 +2100,6 @@
   </si>
   <si>
     <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7576,7 +7576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E4E3E15-0AC2-497E-B931-838D1CC6289F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41F1079A-819C-449A-881A-F425B9250FAA}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7814,16 +7814,16 @@
         <v>283</v>
       </c>
       <c r="Y11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Z11" t="s">
         <v>349</v>
       </c>
       <c r="AA11">
-        <v>0.99809166649408687</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB11">
-        <v>34.986114275074357</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD11" t="s">
         <v>282</v>
@@ -7889,13 +7889,13 @@
         <v>584</v>
       </c>
       <c r="BB11" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="BC11">
-        <v>0.98235584693125277</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD11">
-        <v>323.47613959369914</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7960,16 +7960,16 @@
         <v>287</v>
       </c>
       <c r="Y12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Z12" t="s">
         <v>350</v>
       </c>
       <c r="AA12">
-        <v>0.99850557699173803</v>
+        <v>0.99809166649408687</v>
       </c>
       <c r="AB12">
-        <v>27.397755151469518</v>
+        <v>34.986114275074357</v>
       </c>
       <c r="AD12" t="s">
         <v>282</v>
@@ -8002,10 +8002,10 @@
         <v>442</v>
       </c>
       <c r="AO12">
-        <v>0.99870022163576544</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP12">
-        <v>23.829270010966344</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR12" t="s">
         <v>282</v>
@@ -8038,10 +8038,10 @@
         <v>586</v>
       </c>
       <c r="BC12">
-        <v>0.99366677237144974</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD12">
-        <v>116.10917319008783</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8106,16 +8106,16 @@
         <v>289</v>
       </c>
       <c r="Y13" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="Z13" t="s">
         <v>351</v>
       </c>
       <c r="AA13">
-        <v>0.99621285878087551</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB13">
-        <v>69.43092235061502</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD13" t="s">
         <v>282</v>
@@ -8148,10 +8148,10 @@
         <v>444</v>
       </c>
       <c r="AO13">
-        <v>0.99807466477127271</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP13">
-        <v>35.297812526667357</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR13" t="s">
         <v>282</v>
@@ -8184,10 +8184,10 @@
         <v>588</v>
       </c>
       <c r="BC13">
-        <v>0.9205295464439136</v>
+        <v>0.973232135644435</v>
       </c>
       <c r="BD13">
-        <v>1456.9583151949184</v>
+        <v>490.74417985202501</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8252,16 +8252,16 @@
         <v>291</v>
       </c>
       <c r="Y14" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="Z14" t="s">
         <v>352</v>
       </c>
       <c r="AA14">
-        <v>0.9975431479552237</v>
+        <v>0.99621285878087551</v>
       </c>
       <c r="AB14">
-        <v>45.042287487565297</v>
+        <v>69.43092235061502</v>
       </c>
       <c r="AD14" t="s">
         <v>282</v>
@@ -8294,10 +8294,10 @@
         <v>446</v>
       </c>
       <c r="AO14">
-        <v>0.99827635377245738</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP14">
-        <v>31.600180838280902</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR14" t="s">
         <v>282</v>
@@ -8327,13 +8327,13 @@
         <v>589</v>
       </c>
       <c r="BB14" t="s">
-        <v>590</v>
+        <v>468</v>
       </c>
       <c r="BC14">
-        <v>0.99519319222421976</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD14">
-        <v>88.124809222638589</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8398,16 +8398,16 @@
         <v>293</v>
       </c>
       <c r="Y15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z15" t="s">
         <v>353</v>
       </c>
       <c r="AA15">
-        <v>0.99636728996375623</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB15">
-        <v>66.599683997802714</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD15" t="s">
         <v>282</v>
@@ -8437,13 +8437,13 @@
         <v>447</v>
       </c>
       <c r="AN15" t="s">
-        <v>360</v>
+        <v>448</v>
       </c>
       <c r="AO15">
-        <v>0.98949004263841422</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP15">
-        <v>192.68255162907312</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR15" t="s">
         <v>282</v>
@@ -8470,16 +8470,16 @@
         <v>504</v>
       </c>
       <c r="BA15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="BB15" t="s">
-        <v>592</v>
+        <v>450</v>
       </c>
       <c r="BC15">
-        <v>0.98779966071713954</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD15">
-        <v>223.67288685244134</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8544,16 +8544,16 @@
         <v>295</v>
       </c>
       <c r="Y16" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="Z16" t="s">
         <v>354</v>
       </c>
       <c r="AA16">
-        <v>0.99852430677621173</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB16">
-        <v>27.054375769451152</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD16" t="s">
         <v>282</v>
@@ -8580,16 +8580,16 @@
         <v>387</v>
       </c>
       <c r="AM16" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN16" t="s">
-        <v>365</v>
+        <v>450</v>
       </c>
       <c r="AO16">
-        <v>0.93717435218793788</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP16">
-        <v>1151.8035432211395</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR16" t="s">
         <v>282</v>
@@ -8616,16 +8616,16 @@
         <v>506</v>
       </c>
       <c r="BA16" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="BB16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="BC16">
-        <v>0.98841501119699848</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD16">
-        <v>212.39146138836088</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8690,16 +8690,16 @@
         <v>297</v>
       </c>
       <c r="Y17" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="Z17" t="s">
         <v>355</v>
       </c>
       <c r="AA17">
-        <v>0.99838604658336239</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB17">
-        <v>29.589145971689483</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD17" t="s">
         <v>282</v>
@@ -8726,16 +8726,16 @@
         <v>389</v>
       </c>
       <c r="AM17" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AN17" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AO17">
-        <v>0.96551955124232614</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP17">
-        <v>632.14156055735509</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR17" t="s">
         <v>282</v>
@@ -8762,16 +8762,16 @@
         <v>508</v>
       </c>
       <c r="BA17" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="BB17" t="s">
-        <v>596</v>
+        <v>358</v>
       </c>
       <c r="BC17">
-        <v>0.93089405249526469</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD17">
-        <v>1266.9423709201483</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8836,16 +8836,16 @@
         <v>299</v>
       </c>
       <c r="Y18" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="Z18" t="s">
         <v>356</v>
       </c>
       <c r="AA18">
-        <v>0.99900168239190124</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB18">
-        <v>18.302489481810518</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD18" t="s">
         <v>282</v>
@@ -8872,16 +8872,16 @@
         <v>391</v>
       </c>
       <c r="AM18" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AN18" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO18">
-        <v>0.99693456929731861</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP18">
-        <v>56.199562882493169</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR18" t="s">
         <v>282</v>
@@ -8908,16 +8908,16 @@
         <v>510</v>
       </c>
       <c r="BA18" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="BB18" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="BC18">
-        <v>0.99302778580016682</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD18">
-        <v>127.82392699694152</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8982,16 +8982,16 @@
         <v>301</v>
       </c>
       <c r="Y19" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="Z19" t="s">
         <v>357</v>
       </c>
       <c r="AA19">
-        <v>0.99726055556014181</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB19">
-        <v>50.223148064066145</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD19" t="s">
         <v>282</v>
@@ -9018,16 +9018,16 @@
         <v>393</v>
       </c>
       <c r="AM19" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN19" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO19">
-        <v>0.99869874972548245</v>
+        <v>0.99769811225811866</v>
       </c>
       <c r="AP19">
-        <v>23.856255032822389</v>
+        <v>42.201275267825203</v>
       </c>
       <c r="AR19" t="s">
         <v>282</v>
@@ -9054,16 +9054,16 @@
         <v>512</v>
       </c>
       <c r="BA19" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="BB19" t="s">
-        <v>450</v>
+        <v>597</v>
       </c>
       <c r="BC19">
-        <v>0.95726256957223688</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD19">
-        <v>783.51955784232393</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9128,16 +9128,16 @@
         <v>303</v>
       </c>
       <c r="Y20" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Z20" t="s">
         <v>358</v>
       </c>
       <c r="AA20">
-        <v>0.9977500892185478</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB20">
-        <v>41.248364326622962</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD20" t="s">
         <v>282</v>
@@ -9164,16 +9164,16 @@
         <v>395</v>
       </c>
       <c r="AM20" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AN20" t="s">
-        <v>456</v>
+        <v>375</v>
       </c>
       <c r="AO20">
-        <v>0.99682717865030179</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP20">
-        <v>58.168391411134159</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR20" t="s">
         <v>282</v>
@@ -9200,16 +9200,16 @@
         <v>514</v>
       </c>
       <c r="BA20" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="BB20" t="s">
-        <v>491</v>
+        <v>599</v>
       </c>
       <c r="BC20">
-        <v>0.9437657388784082</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD20">
-        <v>1030.9614538958492</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9274,16 +9274,16 @@
         <v>305</v>
       </c>
       <c r="Y21" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Z21" t="s">
         <v>359</v>
       </c>
       <c r="AA21">
-        <v>0.9982812149336332</v>
+        <v>0.99825665520226836</v>
       </c>
       <c r="AB21">
-        <v>31.51105955005805</v>
+        <v>31.96132129174655</v>
       </c>
       <c r="AD21" t="s">
         <v>282</v>
@@ -9310,16 +9310,16 @@
         <v>397</v>
       </c>
       <c r="AM21" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN21" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO21">
-        <v>0.99863922747017897</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP21">
-        <v>24.947496380053089</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR21" t="s">
         <v>282</v>
@@ -9346,16 +9346,16 @@
         <v>516</v>
       </c>
       <c r="BA21" t="s">
+        <v>600</v>
+      </c>
+      <c r="BB21" t="s">
         <v>601</v>
       </c>
-      <c r="BB21" t="s">
-        <v>602</v>
-      </c>
       <c r="BC21">
-        <v>0.9973402418125219</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD21">
-        <v>48.762233437098502</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9420,16 +9420,16 @@
         <v>307</v>
       </c>
       <c r="Y22" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="Z22" t="s">
         <v>360</v>
       </c>
       <c r="AA22">
-        <v>0.98833720780868572</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB22">
-        <v>213.8178568407609</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD22" t="s">
         <v>282</v>
@@ -9456,16 +9456,16 @@
         <v>399</v>
       </c>
       <c r="AM22" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN22" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO22">
-        <v>0.99582230548799566</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP22">
-        <v>76.591066053413869</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR22" t="s">
         <v>282</v>
@@ -9492,16 +9492,16 @@
         <v>518</v>
       </c>
       <c r="BA22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="BB22" t="s">
-        <v>604</v>
+        <v>368</v>
       </c>
       <c r="BC22">
-        <v>0.99637036284424008</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD22">
-        <v>66.543347855598327</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9566,16 +9566,16 @@
         <v>309</v>
       </c>
       <c r="Y23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z23" t="s">
         <v>361</v>
       </c>
       <c r="AA23">
-        <v>0.99116451092312863</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB23">
-        <v>161.98396640930775</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD23" t="s">
         <v>282</v>
@@ -9602,16 +9602,16 @@
         <v>401</v>
       </c>
       <c r="AM23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN23" t="s">
-        <v>376</v>
+        <v>463</v>
       </c>
       <c r="AO23">
-        <v>0.99192535126433146</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP23">
-        <v>148.0352268205892</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR23" t="s">
         <v>282</v>
@@ -9638,16 +9638,16 @@
         <v>520</v>
       </c>
       <c r="BA23" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="BB23" t="s">
-        <v>606</v>
+        <v>368</v>
       </c>
       <c r="BC23">
-        <v>0.98822137145239475</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD23">
-        <v>215.94152337276336</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9712,16 +9712,16 @@
         <v>311</v>
       </c>
       <c r="Y24" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="Z24" t="s">
         <v>362</v>
       </c>
       <c r="AA24">
-        <v>0.99798824264234642</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB24">
-        <v>36.882218223648351</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD24" t="s">
         <v>282</v>
@@ -9748,16 +9748,16 @@
         <v>403</v>
       </c>
       <c r="AM24" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN24" t="s">
-        <v>360</v>
+        <v>465</v>
       </c>
       <c r="AO24">
-        <v>0.98092693557487454</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP24">
-        <v>349.67284779396647</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR24" t="s">
         <v>282</v>
@@ -9784,16 +9784,16 @@
         <v>522</v>
       </c>
       <c r="BA24" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="BB24" t="s">
-        <v>608</v>
+        <v>368</v>
       </c>
       <c r="BC24">
-        <v>0.99662747375050009</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD24">
-        <v>61.829647907498845</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9858,16 +9858,16 @@
         <v>313</v>
       </c>
       <c r="Y25" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="Z25" t="s">
         <v>363</v>
       </c>
       <c r="AA25">
-        <v>0.9981032549815434</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB25">
-        <v>34.773658671704098</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD25" t="s">
         <v>282</v>
@@ -9894,16 +9894,16 @@
         <v>405</v>
       </c>
       <c r="AM25" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AN25" t="s">
-        <v>464</v>
+        <v>368</v>
       </c>
       <c r="AO25">
-        <v>0.99686124252542985</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP25">
-        <v>57.543887033786262</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR25" t="s">
         <v>282</v>
@@ -9930,16 +9930,16 @@
         <v>524</v>
       </c>
       <c r="BA25" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="BB25" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="BC25">
-        <v>0.99284590877035406</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD25">
-        <v>131.158339210175</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10004,16 +10004,16 @@
         <v>315</v>
       </c>
       <c r="Y26" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="Z26" t="s">
         <v>364</v>
       </c>
       <c r="AA26">
-        <v>0.99628076912917996</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB26">
-        <v>68.185899298368355</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD26" t="s">
         <v>282</v>
@@ -10040,16 +10040,16 @@
         <v>407</v>
       </c>
       <c r="AM26" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN26" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO26">
-        <v>0.99013353407586135</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP26">
-        <v>180.88520860920943</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR26" t="s">
         <v>282</v>
@@ -10076,16 +10076,16 @@
         <v>526</v>
       </c>
       <c r="BA26" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="BB26" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="BC26">
-        <v>0.97803702976044449</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD26">
-        <v>402.65445439185123</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10150,16 +10150,16 @@
         <v>317</v>
       </c>
       <c r="Y27" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s">
         <v>365</v>
       </c>
       <c r="AA27">
-        <v>0.97633688849282452</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB27">
-        <v>433.82371096488447</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD27" t="s">
         <v>282</v>
@@ -10186,16 +10186,16 @@
         <v>409</v>
       </c>
       <c r="AM27" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN27" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO27">
-        <v>0.99869589057011365</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP27">
-        <v>23.908672881248773</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR27" t="s">
         <v>282</v>
@@ -10222,16 +10222,16 @@
         <v>528</v>
       </c>
       <c r="BA27" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="BB27" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="BC27">
-        <v>0.99253849155603513</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD27">
-        <v>136.79432147269009</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10296,16 +10296,16 @@
         <v>319</v>
       </c>
       <c r="Y28" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="Z28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA28">
-        <v>0.94069903208664407</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB28">
-        <v>1087.1844117448593</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD28" t="s">
         <v>282</v>
@@ -10332,16 +10332,16 @@
         <v>411</v>
       </c>
       <c r="AM28" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN28" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO28">
-        <v>0.99811838305018963</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP28">
-        <v>34.496310746523356</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR28" t="s">
         <v>282</v>
@@ -10368,16 +10368,16 @@
         <v>530</v>
       </c>
       <c r="BA28" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="BB28" t="s">
-        <v>596</v>
+        <v>361</v>
       </c>
       <c r="BC28">
-        <v>0.973232135644435</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD28">
-        <v>490.74417985202501</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10442,16 +10442,16 @@
         <v>321</v>
       </c>
       <c r="Y29" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="Z29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA29">
-        <v>0.99756610784588629</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB29">
-        <v>44.621356158751233</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD29" t="s">
         <v>282</v>
@@ -10478,16 +10478,16 @@
         <v>413</v>
       </c>
       <c r="AM29" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AN29" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AO29">
-        <v>0.9985928182686985</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP29">
-        <v>25.798331740528162</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR29" t="s">
         <v>282</v>
@@ -10514,16 +10514,16 @@
         <v>532</v>
       </c>
       <c r="BA29" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="BB29" t="s">
-        <v>617</v>
+        <v>368</v>
       </c>
       <c r="BC29">
-        <v>0.99490784156958001</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD29">
-        <v>93.356237891033686</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10588,16 +10588,16 @@
         <v>323</v>
       </c>
       <c r="Y30" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="Z30" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AA30">
-        <v>0.9972084849335241</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB30">
-        <v>51.177776218725121</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD30" t="s">
         <v>282</v>
@@ -10624,16 +10624,16 @@
         <v>415</v>
       </c>
       <c r="AM30" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN30" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO30">
-        <v>0.99769811225811866</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP30">
-        <v>42.201275267825203</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR30" t="s">
         <v>282</v>
@@ -10660,16 +10660,16 @@
         <v>534</v>
       </c>
       <c r="BA30" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="BB30" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="BC30">
-        <v>0.99015836110796274</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD30">
-        <v>180.43004635401576</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10734,16 +10734,16 @@
         <v>325</v>
       </c>
       <c r="Y31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Z31" t="s">
         <v>368</v>
       </c>
       <c r="AA31">
-        <v>0.9488788277802801</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB31">
-        <v>937.22149069486488</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD31" t="s">
         <v>282</v>
@@ -10770,16 +10770,16 @@
         <v>417</v>
       </c>
       <c r="AM31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN31" t="s">
-        <v>361</v>
+        <v>478</v>
       </c>
       <c r="AO31">
-        <v>0.98814178187791379</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP31">
-        <v>217.40066557158059</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR31" t="s">
         <v>282</v>
@@ -10806,16 +10806,16 @@
         <v>536</v>
       </c>
       <c r="BA31" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="BB31" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="BC31">
-        <v>0.99623532634854861</v>
+        <v>0.99017867813273497</v>
       </c>
       <c r="BD31">
-        <v>69.01901694327529</v>
+        <v>180.05756756652616</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10880,16 +10880,16 @@
         <v>327</v>
       </c>
       <c r="Y32" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Z32" t="s">
         <v>369</v>
       </c>
       <c r="AA32">
-        <v>0.99391268208184824</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB32">
-        <v>111.60082849944791</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD32" t="s">
         <v>282</v>
@@ -10916,16 +10916,16 @@
         <v>419</v>
       </c>
       <c r="AM32" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AN32" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AO32">
-        <v>0.99762356494824644</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP32">
-        <v>43.567975948815601</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR32" t="s">
         <v>282</v>
@@ -10952,16 +10952,16 @@
         <v>538</v>
       </c>
       <c r="BA32" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="BB32" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="BC32">
-        <v>0.9966173923071765</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD32">
-        <v>62.014474368430825</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11026,16 +11026,16 @@
         <v>329</v>
       </c>
       <c r="Y33" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="Z33" t="s">
         <v>370</v>
       </c>
       <c r="AA33">
-        <v>0.99871218762601011</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB33">
-        <v>23.609893523147914</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD33" t="s">
         <v>282</v>
@@ -11062,16 +11062,16 @@
         <v>421</v>
       </c>
       <c r="AM33" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AN33" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AO33">
-        <v>0.99669176136177262</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP33">
-        <v>60.651041700835236</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR33" t="s">
         <v>282</v>
@@ -11098,16 +11098,16 @@
         <v>540</v>
       </c>
       <c r="BA33" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="BB33" t="s">
-        <v>360</v>
+        <v>620</v>
       </c>
       <c r="BC33">
-        <v>0.98180592470173533</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD33">
-        <v>333.55804713485287</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11172,16 +11172,16 @@
         <v>331</v>
       </c>
       <c r="Y34" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Z34" t="s">
         <v>371</v>
       </c>
       <c r="AA34">
-        <v>0.99856748800713691</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB34">
-        <v>26.26271986915707</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD34" t="s">
         <v>282</v>
@@ -11208,16 +11208,16 @@
         <v>423</v>
       </c>
       <c r="AM34" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AN34" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AO34">
-        <v>0.99804155179341392</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP34">
-        <v>35.904883787411507</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR34" t="s">
         <v>282</v>
@@ -11244,16 +11244,16 @@
         <v>542</v>
       </c>
       <c r="BA34" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="BB34" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="BC34">
-        <v>0.99234935324205875</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD34">
-        <v>140.26185722892211</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11318,16 +11318,16 @@
         <v>333</v>
       </c>
       <c r="Y35" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z35" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="AA35">
-        <v>0.97905685820454003</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB35">
-        <v>383.95759958343297</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD35" t="s">
         <v>282</v>
@@ -11354,16 +11354,16 @@
         <v>425</v>
       </c>
       <c r="AM35" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AN35" t="s">
-        <v>483</v>
+        <v>365</v>
       </c>
       <c r="AO35">
-        <v>0.99508023417818925</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP35">
-        <v>90.195706733197795</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR35" t="s">
         <v>282</v>
@@ -11390,16 +11390,16 @@
         <v>544</v>
       </c>
       <c r="BA35" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="BB35" t="s">
-        <v>355</v>
+        <v>624</v>
       </c>
       <c r="BC35">
-        <v>0.99536692897647694</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD35">
-        <v>84.939635431255269</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11464,16 +11464,16 @@
         <v>335</v>
       </c>
       <c r="Y36" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Z36" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AA36">
-        <v>0.99825665520226836</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB36">
-        <v>31.96132129174655</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD36" t="s">
         <v>282</v>
@@ -11500,16 +11500,16 @@
         <v>427</v>
       </c>
       <c r="AM36" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AN36" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AO36">
-        <v>0.99940622505963084</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP36">
-        <v>10.885873906767051</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR36" t="s">
         <v>282</v>
@@ -11536,16 +11536,16 @@
         <v>546</v>
       </c>
       <c r="BA36" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="BB36" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="BC36">
-        <v>0.88199812838352587</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD36">
-        <v>2163.367646302027</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11610,16 +11610,16 @@
         <v>337</v>
       </c>
       <c r="Y37" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="Z37" t="s">
         <v>373</v>
       </c>
       <c r="AA37">
-        <v>0.99894650606645485</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB37">
-        <v>19.314055448326833</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD37" t="s">
         <v>282</v>
@@ -11646,16 +11646,16 @@
         <v>429</v>
       </c>
       <c r="AM37" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AN37" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AO37">
-        <v>0.99710631799330929</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP37">
-        <v>53.050836789329388</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR37" t="s">
         <v>282</v>
@@ -11682,16 +11682,16 @@
         <v>548</v>
       </c>
       <c r="BA37" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="BB37" t="s">
-        <v>365</v>
+        <v>628</v>
       </c>
       <c r="BC37">
-        <v>0.97591598065988894</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD37">
-        <v>441.54035456870389</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11756,16 +11756,16 @@
         <v>339</v>
       </c>
       <c r="Y38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z38" t="s">
         <v>374</v>
       </c>
       <c r="AA38">
-        <v>0.98179245618315802</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB38">
-        <v>333.80496997543548</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD38" t="s">
         <v>282</v>
@@ -11792,16 +11792,16 @@
         <v>431</v>
       </c>
       <c r="AM38" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AN38" t="s">
-        <v>489</v>
+        <v>374</v>
       </c>
       <c r="AO38">
-        <v>0.99550555557680764</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP38">
-        <v>82.398147758527074</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR38" t="s">
         <v>282</v>
@@ -11828,16 +11828,16 @@
         <v>550</v>
       </c>
       <c r="BA38" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="BB38" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="BC38">
-        <v>0.99412039195829205</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD38">
-        <v>107.79281409797902</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11902,16 +11902,16 @@
         <v>341</v>
       </c>
       <c r="Y39" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="Z39" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AA39">
-        <v>0.96189283472138964</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB39">
-        <v>698.63136344118936</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD39" t="s">
         <v>282</v>
@@ -11938,16 +11938,16 @@
         <v>433</v>
       </c>
       <c r="AM39" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN39" t="s">
-        <v>491</v>
+        <v>365</v>
       </c>
       <c r="AO39">
-        <v>0.93896180472603763</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP39">
-        <v>1119.0335800226442</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR39" t="s">
         <v>282</v>
@@ -11974,16 +11974,16 @@
         <v>552</v>
       </c>
       <c r="BA39" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="BB39" t="s">
-        <v>491</v>
+        <v>632</v>
       </c>
       <c r="BC39">
-        <v>0.98292548292671178</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD39">
-        <v>313.03281301028323</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12048,16 +12048,16 @@
         <v>343</v>
       </c>
       <c r="Y40" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="Z40" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA40">
-        <v>0.99410594174368461</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB40">
-        <v>108.05773469911641</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD40" t="s">
         <v>282</v>
@@ -12090,10 +12090,10 @@
         <v>493</v>
       </c>
       <c r="AO40">
-        <v>0.99841760060377538</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP40">
-        <v>29.010655597451841</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR40" t="s">
         <v>282</v>
@@ -12120,16 +12120,16 @@
         <v>554</v>
       </c>
       <c r="BA40" t="s">
+        <v>633</v>
+      </c>
+      <c r="BB40" t="s">
         <v>634</v>
       </c>
-      <c r="BB40" t="s">
-        <v>361</v>
-      </c>
       <c r="BC40">
-        <v>0.98355967005268352</v>
+        <v>0.98841501119699848</v>
       </c>
       <c r="BD40">
-        <v>301.40604903413595</v>
+        <v>212.39146138836088</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>345</v>
       </c>
       <c r="Y41" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="Z41" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="AA41">
-        <v>0.98968917222400854</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB41">
-        <v>189.03184255984442</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD41" t="s">
         <v>282</v>
@@ -12236,10 +12236,10 @@
         <v>495</v>
       </c>
       <c r="AO41">
-        <v>0.99781438034778358</v>
+        <v>0.99582230548799566</v>
       </c>
       <c r="AP41">
-        <v>40.069693623967019</v>
+        <v>76.591066053413869</v>
       </c>
       <c r="AR41" t="s">
         <v>282</v>
@@ -12269,13 +12269,13 @@
         <v>635</v>
       </c>
       <c r="BB41" t="s">
-        <v>365</v>
+        <v>588</v>
       </c>
       <c r="BC41">
-        <v>0.96140381292129873</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD41">
-        <v>707.59676310952364</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12307,13 +12307,13 @@
         <v>636</v>
       </c>
       <c r="BB42" t="s">
-        <v>365</v>
+        <v>637</v>
       </c>
       <c r="BC42">
-        <v>0.95957195194316591</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD42">
-        <v>741.18088104195795</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12342,16 +12342,16 @@
         <v>560</v>
       </c>
       <c r="BA43" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="BB43" t="s">
-        <v>638</v>
+        <v>375</v>
       </c>
       <c r="BC43">
-        <v>0.99603667376986049</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD43">
-        <v>72.660980885890424</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12386,10 +12386,10 @@
         <v>640</v>
       </c>
       <c r="BC44">
-        <v>0.99017867813273497</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD44">
-        <v>180.05756756652616</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12424,10 +12424,10 @@
         <v>642</v>
       </c>
       <c r="BC45">
-        <v>0.99504061303190972</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD45">
-        <v>90.922094414988095</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12462,10 +12462,10 @@
         <v>644</v>
       </c>
       <c r="BC46">
-        <v>0.99681267676383467</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD46">
-        <v>58.434259329697142</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12500,10 +12500,10 @@
         <v>646</v>
       </c>
       <c r="BC47">
-        <v>0.99602290686668338</v>
+        <v>0.9966173923071765</v>
       </c>
       <c r="BD47">
-        <v>72.91337411080552</v>
+        <v>62.014474368430825</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12538,10 +12538,10 @@
         <v>365</v>
       </c>
       <c r="BC48">
-        <v>0.934538160869965</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD48">
-        <v>1200.1337173839754</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12573,13 +12573,13 @@
         <v>648</v>
       </c>
       <c r="BB49" t="s">
-        <v>365</v>
+        <v>649</v>
       </c>
       <c r="BC49">
-        <v>0.94616153753972931</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD49">
-        <v>987.03847843829612</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12608,16 +12608,16 @@
         <v>574</v>
       </c>
       <c r="BA50" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="BB50" t="s">
-        <v>365</v>
+        <v>651</v>
       </c>
       <c r="BC50">
-        <v>0.97218956380622079</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD50">
-        <v>509.85799688595205</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12646,16 +12646,16 @@
         <v>576</v>
       </c>
       <c r="BA51" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="BB51" t="s">
-        <v>651</v>
+        <v>368</v>
       </c>
       <c r="BC51">
-        <v>0.9924172440074055</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD51">
-        <v>139.01719319756617</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12684,16 +12684,16 @@
         <v>578</v>
       </c>
       <c r="BA52" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="BB52" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="BC52">
-        <v>0.99114508565756532</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD52">
-        <v>162.34009627796874</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12722,16 +12722,16 @@
         <v>580</v>
       </c>
       <c r="BA53" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="BB53" t="s">
-        <v>655</v>
+        <v>450</v>
       </c>
       <c r="BC53">
-        <v>0.99561586640696276</v>
+        <v>0.98292548292671178</v>
       </c>
       <c r="BD53">
-        <v>80.375782539015233</v>
+        <v>313.03281301028323</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12763,13 +12763,13 @@
         <v>656</v>
       </c>
       <c r="BB54" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="BC54">
-        <v>0.97902641975794957</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD54">
-        <v>384.51563777092457</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +12778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE8CFE2-D75A-4433-83CE-3C70783162B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA08BFE-E934-4B9C-A6EB-0CE98AF32616}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12890,7 +12890,7 @@
         <v>657</v>
       </c>
       <c r="K11" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12923,7 +12923,7 @@
         <v>719</v>
       </c>
       <c r="X11" t="s">
-        <v>647</v>
+        <v>602</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12958,7 +12958,7 @@
         <v>659</v>
       </c>
       <c r="K12" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12991,7 +12991,7 @@
         <v>721</v>
       </c>
       <c r="X12" t="s">
-        <v>648</v>
+        <v>603</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -13026,7 +13026,7 @@
         <v>661</v>
       </c>
       <c r="K13" t="s">
-        <v>490</v>
+        <v>449</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -13059,7 +13059,7 @@
         <v>723</v>
       </c>
       <c r="X13" t="s">
-        <v>649</v>
+        <v>604</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -13094,7 +13094,7 @@
         <v>663</v>
       </c>
       <c r="K14" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -13127,7 +13127,7 @@
         <v>725</v>
       </c>
       <c r="X14" t="s">
-        <v>630</v>
+        <v>652</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -13162,7 +13162,7 @@
         <v>665</v>
       </c>
       <c r="K15" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13195,7 +13195,7 @@
         <v>727</v>
       </c>
       <c r="X15" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13230,7 +13230,7 @@
         <v>667</v>
       </c>
       <c r="K16" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13263,7 +13263,7 @@
         <v>729</v>
       </c>
       <c r="X16" t="s">
-        <v>636</v>
+        <v>612</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13298,7 +13298,7 @@
         <v>669</v>
       </c>
       <c r="K17" t="s">
-        <v>486</v>
+        <v>445</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13331,7 +13331,7 @@
         <v>731</v>
       </c>
       <c r="X17" t="s">
-        <v>635</v>
+        <v>584</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13366,7 +13366,7 @@
         <v>671</v>
       </c>
       <c r="K18" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13399,7 +13399,7 @@
         <v>733</v>
       </c>
       <c r="X18" t="s">
-        <v>627</v>
+        <v>593</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13434,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="K19" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13467,7 +13467,7 @@
         <v>735</v>
       </c>
       <c r="X19" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13502,7 +13502,7 @@
         <v>675</v>
       </c>
       <c r="K20" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13535,7 +13535,7 @@
         <v>737</v>
       </c>
       <c r="X20" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13570,7 +13570,7 @@
         <v>677</v>
       </c>
       <c r="K21" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13603,7 +13603,7 @@
         <v>739</v>
       </c>
       <c r="X21" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13638,7 +13638,7 @@
         <v>679</v>
       </c>
       <c r="K22" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13671,7 +13671,7 @@
         <v>741</v>
       </c>
       <c r="X22" t="s">
-        <v>650</v>
+        <v>605</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13706,7 +13706,7 @@
         <v>681</v>
       </c>
       <c r="K23" t="s">
-        <v>457</v>
+        <v>492</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13739,7 +13739,7 @@
         <v>743</v>
       </c>
       <c r="X23" t="s">
-        <v>601</v>
+        <v>648</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13774,7 +13774,7 @@
         <v>683</v>
       </c>
       <c r="K24" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13807,7 +13807,7 @@
         <v>745</v>
       </c>
       <c r="X24" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13842,7 +13842,7 @@
         <v>685</v>
       </c>
       <c r="K25" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13875,7 +13875,7 @@
         <v>747</v>
       </c>
       <c r="X25" t="s">
-        <v>622</v>
+        <v>645</v>
       </c>
       <c r="Y25">
         <v>22.785</v>
@@ -13943,7 +13943,7 @@
         <v>749</v>
       </c>
       <c r="X26" t="s">
-        <v>641</v>
+        <v>617</v>
       </c>
       <c r="Y26">
         <v>63.731250000000003</v>
@@ -13978,7 +13978,7 @@
         <v>689</v>
       </c>
       <c r="K27" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -14011,7 +14011,7 @@
         <v>751</v>
       </c>
       <c r="X27" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="Y27">
         <v>28.239750000000001</v>
@@ -14046,7 +14046,7 @@
         <v>691</v>
       </c>
       <c r="K28" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -14079,7 +14079,7 @@
         <v>753</v>
       </c>
       <c r="X28" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="Y28">
         <v>38.15925</v>
@@ -14114,7 +14114,7 @@
         <v>693</v>
       </c>
       <c r="K29" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -14147,7 +14147,7 @@
         <v>755</v>
       </c>
       <c r="X29" t="s">
-        <v>656</v>
+        <v>611</v>
       </c>
       <c r="Y29">
         <v>3.38625</v>
@@ -14182,7 +14182,7 @@
         <v>695</v>
       </c>
       <c r="K30" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14215,7 +14215,7 @@
         <v>757</v>
       </c>
       <c r="X30" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="Y30">
         <v>30.597750000000001</v>
@@ -14250,7 +14250,7 @@
         <v>697</v>
       </c>
       <c r="K31" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14283,7 +14283,7 @@
         <v>759</v>
       </c>
       <c r="X31" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="Y31">
         <v>98.024249999999995</v>
@@ -14318,7 +14318,7 @@
         <v>699</v>
       </c>
       <c r="K32" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14351,7 +14351,7 @@
         <v>761</v>
       </c>
       <c r="X32" t="s">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="Y32">
         <v>28.459499999999998</v>
@@ -14386,7 +14386,7 @@
         <v>701</v>
       </c>
       <c r="K33" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14419,7 +14419,7 @@
         <v>763</v>
       </c>
       <c r="X33" t="s">
-        <v>584</v>
+        <v>638</v>
       </c>
       <c r="Y33">
         <v>33.609749999999998</v>
@@ -14454,7 +14454,7 @@
         <v>703</v>
       </c>
       <c r="K34" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14487,7 +14487,7 @@
         <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="Y34">
         <v>58.474499999999999</v>
@@ -14522,7 +14522,7 @@
         <v>705</v>
       </c>
       <c r="K35" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="L35">
         <v>48.700042766740395</v>
@@ -14555,7 +14555,7 @@
         <v>767</v>
       </c>
       <c r="X35" t="s">
-        <v>654</v>
+        <v>609</v>
       </c>
       <c r="Y35">
         <v>18.711749999999999</v>
@@ -14590,7 +14590,7 @@
         <v>707</v>
       </c>
       <c r="K36" t="s">
-        <v>459</v>
+        <v>494</v>
       </c>
       <c r="L36">
         <v>10.552785706661558</v>
@@ -14623,7 +14623,7 @@
         <v>769</v>
       </c>
       <c r="X36" t="s">
-        <v>603</v>
+        <v>650</v>
       </c>
       <c r="Y36">
         <v>29.186250000000001</v>
@@ -14658,7 +14658,7 @@
         <v>709</v>
       </c>
       <c r="K37" t="s">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14691,7 +14691,7 @@
         <v>771</v>
       </c>
       <c r="X37" t="s">
-        <v>652</v>
+        <v>607</v>
       </c>
       <c r="Y37">
         <v>14.49</v>
@@ -14726,7 +14726,7 @@
         <v>711</v>
       </c>
       <c r="K38" t="s">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14759,7 +14759,7 @@
         <v>773</v>
       </c>
       <c r="X38" t="s">
-        <v>625</v>
+        <v>591</v>
       </c>
       <c r="Y38">
         <v>64.437749999999994</v>
@@ -14794,7 +14794,7 @@
         <v>713</v>
       </c>
       <c r="K39" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14827,7 +14827,7 @@
         <v>775</v>
       </c>
       <c r="X39" t="s">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="Y39">
         <v>59.085000000000001</v>
@@ -14862,7 +14862,7 @@
         <v>715</v>
       </c>
       <c r="K40" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14895,7 +14895,7 @@
         <v>777</v>
       </c>
       <c r="X40" t="s">
-        <v>591</v>
+        <v>631</v>
       </c>
       <c r="Y40">
         <v>37.460250000000002</v>
@@ -14930,7 +14930,7 @@
         <v>717</v>
       </c>
       <c r="K41" t="s">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14963,7 +14963,7 @@
         <v>779</v>
       </c>
       <c r="X41" t="s">
-        <v>637</v>
+        <v>613</v>
       </c>
       <c r="Y41">
         <v>27.642749999999999</v>
@@ -14998,7 +14998,7 @@
         <v>781</v>
       </c>
       <c r="X42" t="s">
-        <v>631</v>
+        <v>653</v>
       </c>
       <c r="Y42">
         <v>62.597250000000003</v>
@@ -15033,7 +15033,7 @@
         <v>783</v>
       </c>
       <c r="X43" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="Y43">
         <v>17.07525</v>
@@ -15068,7 +15068,7 @@
         <v>785</v>
       </c>
       <c r="X44" t="s">
-        <v>628</v>
+        <v>594</v>
       </c>
       <c r="Y44">
         <v>0.42149999999999999</v>
@@ -15103,7 +15103,7 @@
         <v>787</v>
       </c>
       <c r="X45" t="s">
-        <v>595</v>
+        <v>635</v>
       </c>
       <c r="Y45">
         <v>5.7389999999999999</v>
@@ -15138,7 +15138,7 @@
         <v>789</v>
       </c>
       <c r="X46" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="Y46">
         <v>1.81725</v>
@@ -15173,7 +15173,7 @@
         <v>791</v>
       </c>
       <c r="X47" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="Y47">
         <v>15.998250000000001</v>
@@ -15208,7 +15208,7 @@
         <v>793</v>
       </c>
       <c r="X48" t="s">
-        <v>615</v>
+        <v>587</v>
       </c>
       <c r="Y48">
         <v>6.5272500000000004</v>
@@ -15243,7 +15243,7 @@
         <v>795</v>
       </c>
       <c r="X49" t="s">
-        <v>639</v>
+        <v>615</v>
       </c>
       <c r="Y49">
         <v>42.144750000000002</v>
@@ -15278,7 +15278,7 @@
         <v>797</v>
       </c>
       <c r="X50" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="Y50">
         <v>16.497</v>
@@ -15313,7 +15313,7 @@
         <v>799</v>
       </c>
       <c r="X51" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15348,7 +15348,7 @@
         <v>801</v>
       </c>
       <c r="X52" t="s">
-        <v>597</v>
+        <v>636</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15383,7 +15383,7 @@
         <v>803</v>
       </c>
       <c r="X53" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15418,7 +15418,7 @@
         <v>805</v>
       </c>
       <c r="X54" t="s">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15433,7 +15433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F0D8E0-2AD4-4A21-B284-8385F71DED6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A46A0-17C6-45DB-AF7A-7919A5629F50}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17250,7 +17250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E086378-3C0A-4B9E-8930-E879D90B9CB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5FF9D79-F0B2-42B1-B584-71B0B8C86B8E}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F1CA846-C053-4A5C-A93A-C87BBBC0AA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE3A635C-44BA-4F9C-B96E-F31F442CFBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,42 +949,186 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_012</t>
   </si>
   <si>
@@ -997,241 +1141,223 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
     <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
   </si>
   <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
     <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
   </si>
   <si>
     <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
   </si>
   <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_008</t>
@@ -1240,6 +1366,24 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_009</t>
   </si>
   <si>
@@ -1264,22 +1408,10 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wonelc_won_013</t>
@@ -1288,136 +1420,121 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
   </si>
   <si>
     <t>elc_won_008</t>
@@ -1426,6 +1543,21 @@
     <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
     <t>elc_won_009</t>
   </si>
   <si>
@@ -1447,19 +1579,10 @@
     <t>elc_won_030</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
   </si>
   <si>
     <t>elc_won_013</t>
@@ -1468,127 +1591,34 @@
     <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
   </si>
   <si>
     <t>distr_wofelc_wof_042</t>
@@ -1609,6 +1639,48 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_013</t>
   </si>
   <si>
@@ -1633,6 +1705,132 @@
     <t>connecting wind offshore to buses in cluster 35</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_032</t>
   </si>
   <si>
@@ -1657,202 +1855,31 @@
     <t>connecting wind offshore to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
   </si>
   <si>
     <t>elc_wof_042</t>
@@ -1867,7 +1894,40 @@
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
   </si>
   <si>
     <t>elc_wof_013</t>
@@ -1891,6 +1951,111 @@
     <t>e_JP132-500,e_w105298089-500</t>
   </si>
   <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
     <t>elc_wof_032</t>
   </si>
   <si>
@@ -1900,9 +2065,6 @@
     <t>elc_wof_038</t>
   </si>
   <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
     <t>elc_wof_034</t>
   </si>
   <si>
@@ -1910,168 +2072,6 @@
   </si>
   <si>
     <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7396,7 +7396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D2AFED4-5211-4904-A24F-45C1450CF37E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43C71B8-EBCF-4EDA-89B6-F3E9ECF971CC}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7634,16 +7634,16 @@
         <v>273</v>
       </c>
       <c r="Y11" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="Z11" t="s">
         <v>339</v>
       </c>
       <c r="AA11">
-        <v>0.99856748800713691</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB11">
-        <v>26.26271986915707</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD11" t="s">
         <v>272</v>
@@ -7676,10 +7676,10 @@
         <v>431</v>
       </c>
       <c r="AO11">
-        <v>0.99869874972548245</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP11">
-        <v>23.856255032822389</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR11" t="s">
         <v>272</v>
@@ -7709,13 +7709,13 @@
         <v>575</v>
       </c>
       <c r="BB11" t="s">
-        <v>576</v>
+        <v>352</v>
       </c>
       <c r="BC11">
-        <v>0.99302778580016682</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD11">
-        <v>127.82392699694152</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7780,16 +7780,16 @@
         <v>277</v>
       </c>
       <c r="Y12" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="Z12" t="s">
         <v>340</v>
       </c>
       <c r="AA12">
-        <v>0.9981032549815434</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB12">
-        <v>34.773658671704098</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD12" t="s">
         <v>272</v>
@@ -7819,13 +7819,13 @@
         <v>432</v>
       </c>
       <c r="AN12" t="s">
-        <v>433</v>
+        <v>340</v>
       </c>
       <c r="AO12">
-        <v>0.99811838305018963</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP12">
-        <v>34.496310746523356</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR12" t="s">
         <v>272</v>
@@ -7852,16 +7852,16 @@
         <v>489</v>
       </c>
       <c r="BA12" t="s">
+        <v>576</v>
+      </c>
+      <c r="BB12" t="s">
         <v>577</v>
       </c>
-      <c r="BB12" t="s">
-        <v>351</v>
-      </c>
       <c r="BC12">
-        <v>0.98180592470173533</v>
+        <v>0.98627205860840139</v>
       </c>
       <c r="BD12">
-        <v>333.55804713485287</v>
+        <v>251.67892551264018</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7926,16 +7926,16 @@
         <v>279</v>
       </c>
       <c r="Y13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Z13" t="s">
         <v>341</v>
       </c>
       <c r="AA13">
-        <v>0.99894650606645485</v>
+        <v>0.99592928381702117</v>
       </c>
       <c r="AB13">
-        <v>19.314055448326833</v>
+        <v>74.629796687944193</v>
       </c>
       <c r="AD13" t="s">
         <v>272</v>
@@ -7962,16 +7962,16 @@
         <v>372</v>
       </c>
       <c r="AM13" t="s">
+        <v>433</v>
+      </c>
+      <c r="AN13" t="s">
         <v>434</v>
       </c>
-      <c r="AN13" t="s">
-        <v>435</v>
-      </c>
       <c r="AO13">
-        <v>0.9985928182686985</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP13">
-        <v>25.798331740528162</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR13" t="s">
         <v>272</v>
@@ -8004,10 +8004,10 @@
         <v>579</v>
       </c>
       <c r="BC13">
-        <v>0.99547930517021377</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD13">
-        <v>82.879405212747869</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8072,16 +8072,16 @@
         <v>281</v>
       </c>
       <c r="Y14" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="Z14" t="s">
         <v>342</v>
       </c>
       <c r="AA14">
-        <v>0.99756610784588629</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB14">
-        <v>44.621356158751233</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD14" t="s">
         <v>272</v>
@@ -8108,16 +8108,16 @@
         <v>374</v>
       </c>
       <c r="AM14" t="s">
+        <v>435</v>
+      </c>
+      <c r="AN14" t="s">
         <v>436</v>
       </c>
-      <c r="AN14" t="s">
-        <v>437</v>
-      </c>
       <c r="AO14">
-        <v>0.99771335854027388</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP14">
-        <v>41.921760094978509</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR14" t="s">
         <v>272</v>
@@ -8150,10 +8150,10 @@
         <v>581</v>
       </c>
       <c r="BC14">
-        <v>0.9973402418125219</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD14">
-        <v>48.762233437098502</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8218,16 +8218,16 @@
         <v>283</v>
       </c>
       <c r="Y15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z15" t="s">
         <v>343</v>
       </c>
       <c r="AA15">
-        <v>0.99636728996375623</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB15">
-        <v>66.599683997802714</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD15" t="s">
         <v>272</v>
@@ -8254,16 +8254,16 @@
         <v>376</v>
       </c>
       <c r="AM15" t="s">
+        <v>437</v>
+      </c>
+      <c r="AN15" t="s">
         <v>438</v>
       </c>
-      <c r="AN15" t="s">
-        <v>354</v>
-      </c>
       <c r="AO15">
-        <v>0.98814178187791379</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP15">
-        <v>217.40066557158059</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR15" t="s">
         <v>272</v>
@@ -8296,10 +8296,10 @@
         <v>583</v>
       </c>
       <c r="BC15">
-        <v>0.99519319222421976</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD15">
-        <v>88.124809222638589</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8364,16 +8364,16 @@
         <v>285</v>
       </c>
       <c r="Y16" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Z16" t="s">
         <v>344</v>
       </c>
       <c r="AA16">
-        <v>0.99850557699173803</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB16">
-        <v>27.397755151469518</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD16" t="s">
         <v>272</v>
@@ -8403,13 +8403,13 @@
         <v>439</v>
       </c>
       <c r="AN16" t="s">
-        <v>348</v>
+        <v>440</v>
       </c>
       <c r="AO16">
-        <v>0.93717435218793788</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP16">
-        <v>1151.8035432211395</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR16" t="s">
         <v>272</v>
@@ -8439,13 +8439,13 @@
         <v>584</v>
       </c>
       <c r="BB16" t="s">
-        <v>354</v>
+        <v>585</v>
       </c>
       <c r="BC16">
-        <v>0.98605307635189521</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD16">
-        <v>255.693600215255</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8510,16 +8510,16 @@
         <v>287</v>
       </c>
       <c r="Y17" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="Z17" t="s">
         <v>345</v>
       </c>
       <c r="AA17">
-        <v>0.99866775225229476</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB17">
-        <v>24.424542041262942</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD17" t="s">
         <v>272</v>
@@ -8546,16 +8546,16 @@
         <v>380</v>
       </c>
       <c r="AM17" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO17">
-        <v>0.96551955124232614</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP17">
-        <v>632.14156055735509</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR17" t="s">
         <v>272</v>
@@ -8582,16 +8582,16 @@
         <v>499</v>
       </c>
       <c r="BA17" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="BB17" t="s">
-        <v>586</v>
+        <v>340</v>
       </c>
       <c r="BC17">
-        <v>0.88199812838352587</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD17">
-        <v>2163.367646302027</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8656,16 +8656,16 @@
         <v>289</v>
       </c>
       <c r="Y18" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Z18" t="s">
         <v>346</v>
       </c>
       <c r="AA18">
-        <v>0.9982812149336332</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB18">
-        <v>31.51105955005805</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD18" t="s">
         <v>272</v>
@@ -8692,16 +8692,16 @@
         <v>382</v>
       </c>
       <c r="AM18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN18" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO18">
-        <v>0.99693456929731861</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP18">
-        <v>56.199562882493169</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR18" t="s">
         <v>272</v>
@@ -8731,13 +8731,13 @@
         <v>587</v>
       </c>
       <c r="BB18" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="BC18">
-        <v>0.99603667376986049</v>
+        <v>0.99547930517021377</v>
       </c>
       <c r="BD18">
-        <v>72.660980885890424</v>
+        <v>82.879405212747869</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8802,16 +8802,16 @@
         <v>291</v>
       </c>
       <c r="Y19" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="Z19" t="s">
         <v>347</v>
       </c>
       <c r="AA19">
-        <v>0.99782703065964284</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB19">
-        <v>39.837771239882208</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD19" t="s">
         <v>272</v>
@@ -8838,16 +8838,16 @@
         <v>384</v>
       </c>
       <c r="AM19" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN19" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO19">
-        <v>0.99863922747017897</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP19">
-        <v>24.947496380053089</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR19" t="s">
         <v>272</v>
@@ -8874,16 +8874,16 @@
         <v>503</v>
       </c>
       <c r="BA19" t="s">
+        <v>588</v>
+      </c>
+      <c r="BB19" t="s">
         <v>589</v>
       </c>
-      <c r="BB19" t="s">
-        <v>590</v>
-      </c>
       <c r="BC19">
-        <v>0.97589985979527272</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD19">
-        <v>441.83590375333313</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8948,16 +8948,16 @@
         <v>293</v>
       </c>
       <c r="Y20" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="Z20" t="s">
         <v>348</v>
       </c>
       <c r="AA20">
-        <v>0.96340341594909085</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB20">
-        <v>670.93737426666792</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD20" t="s">
         <v>272</v>
@@ -8984,16 +8984,16 @@
         <v>386</v>
       </c>
       <c r="AM20" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN20" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO20">
-        <v>0.99827635377245738</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP20">
-        <v>31.600180838280902</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR20" t="s">
         <v>272</v>
@@ -9020,16 +9020,16 @@
         <v>505</v>
       </c>
       <c r="BA20" t="s">
+        <v>590</v>
+      </c>
+      <c r="BB20" t="s">
         <v>591</v>
       </c>
-      <c r="BB20" t="s">
-        <v>466</v>
-      </c>
       <c r="BC20">
-        <v>0.9437657388784082</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD20">
-        <v>1030.9614538958492</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9094,16 +9094,16 @@
         <v>295</v>
       </c>
       <c r="Y21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Z21" t="s">
         <v>349</v>
       </c>
       <c r="AA21">
-        <v>0.99838604658336239</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB21">
-        <v>29.589145971689483</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD21" t="s">
         <v>272</v>
@@ -9130,16 +9130,16 @@
         <v>388</v>
       </c>
       <c r="AM21" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN21" t="s">
-        <v>351</v>
+        <v>450</v>
       </c>
       <c r="AO21">
-        <v>0.98949004263841422</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP21">
-        <v>192.68255162907312</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR21" t="s">
         <v>272</v>
@@ -9172,10 +9172,10 @@
         <v>593</v>
       </c>
       <c r="BC21">
-        <v>0.99602290686668338</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD21">
-        <v>72.91337411080552</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9240,16 +9240,16 @@
         <v>297</v>
       </c>
       <c r="Y22" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="Z22" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AA22">
-        <v>0.94069903208664407</v>
+        <v>0.99788758639511588</v>
       </c>
       <c r="AB22">
-        <v>1087.1844117448593</v>
+        <v>38.727582756208619</v>
       </c>
       <c r="AD22" t="s">
         <v>272</v>
@@ -9276,16 +9276,16 @@
         <v>390</v>
       </c>
       <c r="AM22" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AN22" t="s">
-        <v>450</v>
+        <v>343</v>
       </c>
       <c r="AO22">
-        <v>0.99682717865030179</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP22">
-        <v>58.168391411134159</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR22" t="s">
         <v>272</v>
@@ -9318,10 +9318,10 @@
         <v>595</v>
       </c>
       <c r="BC22">
-        <v>0.99114508565756532</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD22">
-        <v>162.34009627796874</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9386,16 +9386,16 @@
         <v>299</v>
       </c>
       <c r="Y23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA23">
-        <v>0.99900168239190124</v>
+        <v>0.99841742239430997</v>
       </c>
       <c r="AB23">
-        <v>18.302489481810518</v>
+        <v>29.013922770983669</v>
       </c>
       <c r="AD23" t="s">
         <v>272</v>
@@ -9422,16 +9422,16 @@
         <v>392</v>
       </c>
       <c r="AM23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN23" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="AO23">
-        <v>0.99192535126433146</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP23">
-        <v>148.0352268205892</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR23" t="s">
         <v>272</v>
@@ -9461,13 +9461,13 @@
         <v>596</v>
       </c>
       <c r="BB23" t="s">
-        <v>597</v>
+        <v>473</v>
       </c>
       <c r="BC23">
-        <v>0.99561586640696276</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD23">
-        <v>80.375782539015233</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9532,16 +9532,16 @@
         <v>301</v>
       </c>
       <c r="Y24" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="Z24" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA24">
-        <v>0.98833720780868572</v>
+        <v>0.96340341594909085</v>
       </c>
       <c r="AB24">
-        <v>213.8178568407609</v>
+        <v>670.93737426666792</v>
       </c>
       <c r="AD24" t="s">
         <v>272</v>
@@ -9568,16 +9568,16 @@
         <v>394</v>
       </c>
       <c r="AM24" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN24" t="s">
-        <v>351</v>
+        <v>454</v>
       </c>
       <c r="AO24">
-        <v>0.98092693557487454</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP24">
-        <v>349.67284779396647</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR24" t="s">
         <v>272</v>
@@ -9604,16 +9604,16 @@
         <v>513</v>
       </c>
       <c r="BA24" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="BB24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="BC24">
-        <v>0.98235584693125277</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD24">
-        <v>323.47613959369914</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9678,16 +9678,16 @@
         <v>303</v>
       </c>
       <c r="Y25" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="Z25" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA25">
-        <v>0.99864010607905451</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB25">
-        <v>24.931388550667378</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD25" t="s">
         <v>272</v>
@@ -9714,16 +9714,16 @@
         <v>396</v>
       </c>
       <c r="AM25" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN25" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO25">
-        <v>0.99804155179341392</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP25">
-        <v>35.904883787411507</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR25" t="s">
         <v>272</v>
@@ -9750,16 +9750,16 @@
         <v>515</v>
       </c>
       <c r="BA25" t="s">
+        <v>598</v>
+      </c>
+      <c r="BB25" t="s">
         <v>599</v>
       </c>
-      <c r="BB25" t="s">
-        <v>349</v>
-      </c>
       <c r="BC25">
-        <v>0.99536692897647694</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD25">
-        <v>84.939635431255269</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9824,16 +9824,16 @@
         <v>305</v>
       </c>
       <c r="Y26" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="Z26" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA26">
-        <v>0.99706930328635524</v>
+        <v>0.99809153006866247</v>
       </c>
       <c r="AB26">
-        <v>53.729439750153354</v>
+        <v>34.98861540785537</v>
       </c>
       <c r="AD26" t="s">
         <v>272</v>
@@ -9860,16 +9860,16 @@
         <v>398</v>
       </c>
       <c r="AM26" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AN26" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AO26">
-        <v>0.99508023417818925</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP26">
-        <v>90.195706733197795</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR26" t="s">
         <v>272</v>
@@ -9899,13 +9899,13 @@
         <v>600</v>
       </c>
       <c r="BB26" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="BC26">
-        <v>0.93089405249526469</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD26">
-        <v>1266.9423709201483</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9970,16 +9970,16 @@
         <v>307</v>
       </c>
       <c r="Y27" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="Z27" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA27">
-        <v>0.99116451092312863</v>
+        <v>0.99323944641370343</v>
       </c>
       <c r="AB27">
-        <v>161.98396640930775</v>
+        <v>123.94348241543759</v>
       </c>
       <c r="AD27" t="s">
         <v>272</v>
@@ -10006,16 +10006,16 @@
         <v>400</v>
       </c>
       <c r="AM27" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AN27" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AO27">
-        <v>0.99940622505963084</v>
+        <v>0.99627181657233566</v>
       </c>
       <c r="AP27">
-        <v>10.885873906767051</v>
+        <v>68.350029507179471</v>
       </c>
       <c r="AR27" t="s">
         <v>272</v>
@@ -10042,16 +10042,16 @@
         <v>519</v>
       </c>
       <c r="BA27" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="BB27" t="s">
-        <v>348</v>
+        <v>603</v>
       </c>
       <c r="BC27">
-        <v>0.95957195194316591</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD27">
-        <v>741.18088104195795</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10116,16 +10116,16 @@
         <v>309</v>
       </c>
       <c r="Y28" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="Z28" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA28">
-        <v>0.9977500892185478</v>
+        <v>0.99864010607905451</v>
       </c>
       <c r="AB28">
-        <v>41.248364326622962</v>
+        <v>24.931388550667378</v>
       </c>
       <c r="AD28" t="s">
         <v>272</v>
@@ -10152,16 +10152,16 @@
         <v>402</v>
       </c>
       <c r="AM28" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN28" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO28">
-        <v>0.99710631799330929</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP28">
-        <v>53.050836789329388</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR28" t="s">
         <v>272</v>
@@ -10188,16 +10188,16 @@
         <v>521</v>
       </c>
       <c r="BA28" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="BB28" t="s">
-        <v>579</v>
+        <v>358</v>
       </c>
       <c r="BC28">
-        <v>0.98627205860840139</v>
+        <v>0.98605307635189521</v>
       </c>
       <c r="BD28">
-        <v>251.67892551264018</v>
+        <v>255.693600215255</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10262,16 +10262,16 @@
         <v>311</v>
       </c>
       <c r="Y29" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Z29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA29">
-        <v>0.99788758639511588</v>
+        <v>0.99706930328635524</v>
       </c>
       <c r="AB29">
-        <v>38.727582756208619</v>
+        <v>53.729439750153354</v>
       </c>
       <c r="AD29" t="s">
         <v>272</v>
@@ -10298,16 +10298,16 @@
         <v>404</v>
       </c>
       <c r="AM29" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN29" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO29">
-        <v>0.99627181657233566</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP29">
-        <v>68.350029507179471</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR29" t="s">
         <v>272</v>
@@ -10334,16 +10334,16 @@
         <v>523</v>
       </c>
       <c r="BA29" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="BB29" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="BC29">
-        <v>0.99504061303190972</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD29">
-        <v>90.922094414988095</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10408,16 +10408,16 @@
         <v>313</v>
       </c>
       <c r="Y30" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Z30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA30">
-        <v>0.99841742239430997</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB30">
-        <v>29.013922770983669</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD30" t="s">
         <v>272</v>
@@ -10444,16 +10444,16 @@
         <v>406</v>
       </c>
       <c r="AM30" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AN30" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AO30">
-        <v>0.99550555557680764</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP30">
-        <v>82.398147758527074</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR30" t="s">
         <v>272</v>
@@ -10480,16 +10480,16 @@
         <v>525</v>
       </c>
       <c r="BA30" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="BB30" t="s">
-        <v>606</v>
+        <v>352</v>
       </c>
       <c r="BC30">
-        <v>0.98822137145239475</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD30">
-        <v>215.94152337276336</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10557,7 +10557,7 @@
         <v>242</v>
       </c>
       <c r="Z31" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA31">
         <v>0.9488788277802801</v>
@@ -10590,16 +10590,16 @@
         <v>408</v>
       </c>
       <c r="AM31" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO31">
-        <v>0.93896180472603763</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP31">
-        <v>1119.0335800226442</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR31" t="s">
         <v>272</v>
@@ -10626,16 +10626,16 @@
         <v>527</v>
       </c>
       <c r="BA31" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="BB31" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="BC31">
-        <v>0.99284590877035406</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD31">
-        <v>131.158339210175</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10700,16 +10700,16 @@
         <v>317</v>
       </c>
       <c r="Y32" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="Z32" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AA32">
-        <v>0.97905685820454003</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB32">
-        <v>383.95759958343297</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD32" t="s">
         <v>272</v>
@@ -10736,16 +10736,16 @@
         <v>410</v>
       </c>
       <c r="AM32" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN32" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO32">
-        <v>0.99841760060377538</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP32">
-        <v>29.010655597451841</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR32" t="s">
         <v>272</v>
@@ -10772,16 +10772,16 @@
         <v>529</v>
       </c>
       <c r="BA32" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="BB32" t="s">
-        <v>610</v>
+        <v>346</v>
       </c>
       <c r="BC32">
-        <v>0.99366677237144974</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD32">
-        <v>116.10917319008783</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10846,16 +10846,16 @@
         <v>319</v>
       </c>
       <c r="Y33" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="Z33" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA33">
-        <v>0.99852430677621173</v>
+        <v>0.99782703065964284</v>
       </c>
       <c r="AB33">
-        <v>27.054375769451152</v>
+        <v>39.837771239882208</v>
       </c>
       <c r="AD33" t="s">
         <v>272</v>
@@ -10882,16 +10882,16 @@
         <v>412</v>
       </c>
       <c r="AM33" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN33" t="s">
-        <v>470</v>
+        <v>352</v>
       </c>
       <c r="AO33">
-        <v>0.99781438034778358</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP33">
-        <v>40.069693623967019</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR33" t="s">
         <v>272</v>
@@ -10924,10 +10924,10 @@
         <v>612</v>
       </c>
       <c r="BC33">
-        <v>0.99623532634854861</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD33">
-        <v>69.01901694327529</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -10992,16 +10992,16 @@
         <v>321</v>
       </c>
       <c r="Y34" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="Z34" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA34">
-        <v>0.9975431479552237</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB34">
-        <v>45.042287487565297</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD34" t="s">
         <v>272</v>
@@ -11028,16 +11028,16 @@
         <v>414</v>
       </c>
       <c r="AM34" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN34" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO34">
-        <v>0.99762356494824644</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP34">
-        <v>43.567975948815601</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR34" t="s">
         <v>272</v>
@@ -11070,10 +11070,10 @@
         <v>614</v>
       </c>
       <c r="BC34">
-        <v>0.99895994357772033</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD34">
-        <v>19.067701075126294</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11138,16 +11138,16 @@
         <v>323</v>
       </c>
       <c r="Y35" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Z35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AA35">
-        <v>0.98179245618315802</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB35">
-        <v>333.80496997543548</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD35" t="s">
         <v>272</v>
@@ -11174,16 +11174,16 @@
         <v>416</v>
       </c>
       <c r="AM35" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN35" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO35">
-        <v>0.99669176136177262</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP35">
-        <v>60.651041700835236</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR35" t="s">
         <v>272</v>
@@ -11213,13 +11213,13 @@
         <v>615</v>
       </c>
       <c r="BB35" t="s">
-        <v>348</v>
+        <v>616</v>
       </c>
       <c r="BC35">
-        <v>0.96140381292129873</v>
+        <v>0.99895994357772033</v>
       </c>
       <c r="BD35">
-        <v>707.59676310952364</v>
+        <v>19.067701075126294</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11284,16 +11284,16 @@
         <v>325</v>
       </c>
       <c r="Y36" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="Z36" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="AA36">
-        <v>0.99592928381702117</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB36">
-        <v>74.629796687944193</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD36" t="s">
         <v>272</v>
@@ -11320,16 +11320,16 @@
         <v>418</v>
       </c>
       <c r="AM36" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN36" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO36">
-        <v>0.99750949182367343</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP36">
-        <v>45.659316565986806</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR36" t="s">
         <v>272</v>
@@ -11356,16 +11356,16 @@
         <v>537</v>
       </c>
       <c r="BA36" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="BB36" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="BC36">
-        <v>0.99490784156958001</v>
+        <v>0.99220908762204307</v>
       </c>
       <c r="BD36">
-        <v>93.356237891033686</v>
+        <v>142.83339359587785</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11430,16 +11430,16 @@
         <v>327</v>
       </c>
       <c r="Y37" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="Z37" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA37">
-        <v>0.99726055556014181</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB37">
-        <v>50.223148064066145</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD37" t="s">
         <v>272</v>
@@ -11466,16 +11466,16 @@
         <v>420</v>
       </c>
       <c r="AM37" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN37" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO37">
-        <v>0.99013353407586135</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP37">
-        <v>180.88520860920943</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR37" t="s">
         <v>272</v>
@@ -11502,16 +11502,16 @@
         <v>539</v>
       </c>
       <c r="BA37" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="BB37" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="BC37">
-        <v>0.97902641975794957</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD37">
-        <v>384.51563777092457</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11576,16 +11576,16 @@
         <v>329</v>
       </c>
       <c r="Y38" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Z38" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="AA38">
-        <v>0.98968917222400854</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB38">
-        <v>189.03184255984442</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD38" t="s">
         <v>272</v>
@@ -11612,16 +11612,16 @@
         <v>422</v>
       </c>
       <c r="AM38" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN38" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO38">
-        <v>0.99869589057011365</v>
+        <v>0.99771335854027388</v>
       </c>
       <c r="AP38">
-        <v>23.908672881248773</v>
+        <v>41.921760094978509</v>
       </c>
       <c r="AR38" t="s">
         <v>272</v>
@@ -11648,16 +11648,16 @@
         <v>541</v>
       </c>
       <c r="BA38" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="BB38" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="BC38">
-        <v>0.99015836110796274</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD38">
-        <v>180.43004635401576</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11722,16 +11722,16 @@
         <v>331</v>
       </c>
       <c r="Y39" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="Z39" t="s">
         <v>365</v>
       </c>
       <c r="AA39">
-        <v>0.99809153006866247</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB39">
-        <v>34.98861540785537</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD39" t="s">
         <v>272</v>
@@ -11758,16 +11758,16 @@
         <v>424</v>
       </c>
       <c r="AM39" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN39" t="s">
-        <v>482</v>
+        <v>358</v>
       </c>
       <c r="AO39">
-        <v>0.99686124252542985</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP39">
-        <v>57.543887033786262</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR39" t="s">
         <v>272</v>
@@ -11794,16 +11794,16 @@
         <v>543</v>
       </c>
       <c r="BA39" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="BB39" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="BC39">
-        <v>0.97803702976044449</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD39">
-        <v>402.65445439185123</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11868,16 +11868,16 @@
         <v>333</v>
       </c>
       <c r="Y40" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="Z40" t="s">
         <v>366</v>
       </c>
       <c r="AA40">
-        <v>0.99323944641370343</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB40">
-        <v>123.94348241543759</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD40" t="s">
         <v>272</v>
@@ -11910,10 +11910,10 @@
         <v>484</v>
       </c>
       <c r="AO40">
-        <v>0.99870022163576544</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP40">
-        <v>23.829270010966344</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR40" t="s">
         <v>272</v>
@@ -11940,16 +11940,16 @@
         <v>545</v>
       </c>
       <c r="BA40" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="BB40" t="s">
-        <v>624</v>
+        <v>352</v>
       </c>
       <c r="BC40">
-        <v>0.99234935324205875</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD40">
-        <v>140.26185722892211</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12014,16 +12014,16 @@
         <v>335</v>
       </c>
       <c r="Y41" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Z41" t="s">
         <v>367</v>
       </c>
       <c r="AA41">
-        <v>0.99391268208184824</v>
+        <v>0.99866775225229476</v>
       </c>
       <c r="AB41">
-        <v>111.60082849944791</v>
+        <v>24.424542041262942</v>
       </c>
       <c r="AD41" t="s">
         <v>272</v>
@@ -12056,10 +12056,10 @@
         <v>486</v>
       </c>
       <c r="AO41">
-        <v>0.99807466477127271</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP41">
-        <v>35.297812526667357</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR41" t="s">
         <v>272</v>
@@ -12089,13 +12089,13 @@
         <v>625</v>
       </c>
       <c r="BB41" t="s">
-        <v>626</v>
+        <v>352</v>
       </c>
       <c r="BC41">
-        <v>0.9205295464439136</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD41">
-        <v>1456.9583151949184</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12124,16 +12124,16 @@
         <v>549</v>
       </c>
       <c r="BA42" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="BB42" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="BC42">
-        <v>0.934538160869965</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD42">
-        <v>1200.1337173839754</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12162,16 +12162,16 @@
         <v>551</v>
       </c>
       <c r="BA43" t="s">
+        <v>627</v>
+      </c>
+      <c r="BB43" t="s">
         <v>628</v>
       </c>
-      <c r="BB43" t="s">
-        <v>348</v>
-      </c>
       <c r="BC43">
-        <v>0.94616153753972931</v>
+        <v>0.99272888574049079</v>
       </c>
       <c r="BD43">
-        <v>987.03847843829612</v>
+        <v>133.30376142433548</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12203,13 +12203,13 @@
         <v>629</v>
       </c>
       <c r="BB44" t="s">
-        <v>348</v>
+        <v>630</v>
       </c>
       <c r="BC44">
-        <v>0.97218956380622079</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD44">
-        <v>509.85799688595205</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12238,16 +12238,16 @@
         <v>555</v>
       </c>
       <c r="BA45" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="BB45" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="BC45">
-        <v>0.99272888574049079</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD45">
-        <v>133.30376142433548</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12276,16 +12276,16 @@
         <v>557</v>
       </c>
       <c r="BA46" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="BB46" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="BC46">
-        <v>0.99662747375050009</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD46">
-        <v>61.829647907498845</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12314,16 +12314,16 @@
         <v>559</v>
       </c>
       <c r="BA47" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="BB47" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="BC47">
-        <v>0.99637036284424008</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD47">
-        <v>66.543347855598327</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12352,16 +12352,16 @@
         <v>561</v>
       </c>
       <c r="BA48" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="BB48" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="BC48">
-        <v>0.98779966071713954</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD48">
-        <v>223.67288685244134</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12390,16 +12390,16 @@
         <v>563</v>
       </c>
       <c r="BA49" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="BB49" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="BC49">
-        <v>0.99681267676383467</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD49">
-        <v>58.434259329697142</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12428,16 +12428,16 @@
         <v>565</v>
       </c>
       <c r="BA50" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB50" t="s">
-        <v>441</v>
+        <v>358</v>
       </c>
       <c r="BC50">
-        <v>0.95726256957223688</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD50">
-        <v>783.51955784232393</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12466,16 +12466,16 @@
         <v>567</v>
       </c>
       <c r="BA51" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="BB51" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BC51">
-        <v>0.99220908762204307</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD51">
-        <v>142.83339359587785</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12504,16 +12504,16 @@
         <v>569</v>
       </c>
       <c r="BA52" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="BB52" t="s">
-        <v>348</v>
+        <v>599</v>
       </c>
       <c r="BC52">
-        <v>0.97591598065988894</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD52">
-        <v>441.54035456870389</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12542,16 +12542,16 @@
         <v>571</v>
       </c>
       <c r="BA53" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="BB53" t="s">
-        <v>645</v>
+        <v>464</v>
       </c>
       <c r="BC53">
-        <v>0.99412039195829205</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD53">
-        <v>107.79281409797902</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12586,10 +12586,10 @@
         <v>647</v>
       </c>
       <c r="BC54">
-        <v>0.98881218539944515</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD54">
-        <v>205.10993434350485</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
   </sheetData>
@@ -12598,7 +12598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD2A8B4-11E8-4B82-8CD1-4B82514121B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EBE32DF-24D2-424B-AEA1-59E91761AEBC}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12710,7 +12710,7 @@
         <v>648</v>
       </c>
       <c r="K11" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12743,7 +12743,7 @@
         <v>710</v>
       </c>
       <c r="X11" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12778,7 +12778,7 @@
         <v>650</v>
       </c>
       <c r="K12" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12811,7 +12811,7 @@
         <v>712</v>
       </c>
       <c r="X12" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12846,7 +12846,7 @@
         <v>652</v>
       </c>
       <c r="K13" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -12879,7 +12879,7 @@
         <v>714</v>
       </c>
       <c r="X13" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12914,7 +12914,7 @@
         <v>654</v>
       </c>
       <c r="K14" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -12947,7 +12947,7 @@
         <v>716</v>
       </c>
       <c r="X14" t="s">
-        <v>643</v>
+        <v>619</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12982,7 +12982,7 @@
         <v>656</v>
       </c>
       <c r="K15" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13015,7 +13015,7 @@
         <v>718</v>
       </c>
       <c r="X15" t="s">
-        <v>640</v>
+        <v>596</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13050,7 +13050,7 @@
         <v>658</v>
       </c>
       <c r="K16" t="s">
-        <v>467</v>
+        <v>433</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13083,7 +13083,7 @@
         <v>720</v>
       </c>
       <c r="X16" t="s">
-        <v>601</v>
+        <v>575</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13118,7 +13118,7 @@
         <v>660</v>
       </c>
       <c r="K17" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13151,7 +13151,7 @@
         <v>722</v>
       </c>
       <c r="X17" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13186,7 +13186,7 @@
         <v>662</v>
       </c>
       <c r="K18" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13219,7 +13219,7 @@
         <v>724</v>
       </c>
       <c r="X18" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="Y18">
         <v>28.478249999999999</v>
@@ -13254,7 +13254,7 @@
         <v>664</v>
       </c>
       <c r="K19" t="s">
-        <v>432</v>
+        <v>476</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13287,7 +13287,7 @@
         <v>726</v>
       </c>
       <c r="X19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Y19">
         <v>22.079249999999998</v>
@@ -13322,7 +13322,7 @@
         <v>666</v>
       </c>
       <c r="K20" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13355,7 +13355,7 @@
         <v>728</v>
       </c>
       <c r="X20" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="Y20">
         <v>29.961749999999999</v>
@@ -13390,7 +13390,7 @@
         <v>668</v>
       </c>
       <c r="K21" t="s">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13423,7 +13423,7 @@
         <v>730</v>
       </c>
       <c r="X21" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13458,7 +13458,7 @@
         <v>670</v>
       </c>
       <c r="K22" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13491,7 +13491,7 @@
         <v>732</v>
       </c>
       <c r="X22" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="Y22">
         <v>82.576499999999996</v>
@@ -13526,7 +13526,7 @@
         <v>672</v>
       </c>
       <c r="K23" t="s">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13559,7 +13559,7 @@
         <v>734</v>
       </c>
       <c r="X23" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13594,7 +13594,7 @@
         <v>674</v>
       </c>
       <c r="K24" t="s">
-        <v>469</v>
+        <v>435</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13627,7 +13627,7 @@
         <v>736</v>
       </c>
       <c r="X24" t="s">
-        <v>641</v>
+        <v>617</v>
       </c>
       <c r="Y24">
         <v>75.512249999999995</v>
@@ -13662,7 +13662,7 @@
         <v>676</v>
       </c>
       <c r="K25" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13695,7 +13695,7 @@
         <v>738</v>
       </c>
       <c r="X25" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="Y25">
         <v>28.239750000000001</v>
@@ -13730,7 +13730,7 @@
         <v>678</v>
       </c>
       <c r="K26" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13763,7 +13763,7 @@
         <v>740</v>
       </c>
       <c r="X26" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="Y26">
         <v>1.9132499999999999</v>
@@ -13798,7 +13798,7 @@
         <v>680</v>
       </c>
       <c r="K27" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -13831,7 +13831,7 @@
         <v>742</v>
       </c>
       <c r="X27" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="Y27">
         <v>63.731250000000003</v>
@@ -13866,7 +13866,7 @@
         <v>682</v>
       </c>
       <c r="K28" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -13899,7 +13899,7 @@
         <v>744</v>
       </c>
       <c r="X28" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="Y28">
         <v>38.451000000000001</v>
@@ -13934,7 +13934,7 @@
         <v>684</v>
       </c>
       <c r="K29" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -13967,7 +13967,7 @@
         <v>746</v>
       </c>
       <c r="X29" t="s">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="Y29">
         <v>64.533749999999998</v>
@@ -14002,7 +14002,7 @@
         <v>686</v>
       </c>
       <c r="K30" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14035,7 +14035,7 @@
         <v>748</v>
       </c>
       <c r="X30" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="Y30">
         <v>44.370750000000001</v>
@@ -14070,7 +14070,7 @@
         <v>688</v>
       </c>
       <c r="K31" t="s">
-        <v>485</v>
+        <v>439</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14103,7 +14103,7 @@
         <v>750</v>
       </c>
       <c r="X31" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="Y31">
         <v>38.15925</v>
@@ -14138,7 +14138,7 @@
         <v>690</v>
       </c>
       <c r="K32" t="s">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14171,7 +14171,7 @@
         <v>752</v>
       </c>
       <c r="X32" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="Y32">
         <v>3.38625</v>
@@ -14206,7 +14206,7 @@
         <v>692</v>
       </c>
       <c r="K33" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14239,7 +14239,7 @@
         <v>754</v>
       </c>
       <c r="X33" t="s">
-        <v>621</v>
+        <v>594</v>
       </c>
       <c r="Y33">
         <v>30.597750000000001</v>
@@ -14274,7 +14274,7 @@
         <v>694</v>
       </c>
       <c r="K34" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14307,7 +14307,7 @@
         <v>756</v>
       </c>
       <c r="X34" t="s">
-        <v>598</v>
+        <v>641</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14342,7 +14342,7 @@
         <v>696</v>
       </c>
       <c r="K35" t="s">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="L35">
         <v>44.894334115294185</v>
@@ -14375,7 +14375,7 @@
         <v>758</v>
       </c>
       <c r="X35" t="s">
-        <v>619</v>
+        <v>592</v>
       </c>
       <c r="Y35">
         <v>58.474499999999999</v>
@@ -14410,7 +14410,7 @@
         <v>698</v>
       </c>
       <c r="K36" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L36">
         <v>14.358494358107757</v>
@@ -14443,7 +14443,7 @@
         <v>760</v>
       </c>
       <c r="X36" t="s">
-        <v>596</v>
+        <v>639</v>
       </c>
       <c r="Y36">
         <v>18.711749999999999</v>
@@ -14478,7 +14478,7 @@
         <v>700</v>
       </c>
       <c r="K37" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14511,7 +14511,7 @@
         <v>762</v>
       </c>
       <c r="X37" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14579,7 +14579,7 @@
         <v>764</v>
       </c>
       <c r="X38" t="s">
-        <v>594</v>
+        <v>637</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14614,7 +14614,7 @@
         <v>704</v>
       </c>
       <c r="K39" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14647,7 +14647,7 @@
         <v>766</v>
       </c>
       <c r="X39" t="s">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14682,7 +14682,7 @@
         <v>706</v>
       </c>
       <c r="K40" t="s">
-        <v>438</v>
+        <v>482</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14715,7 +14715,7 @@
         <v>768</v>
       </c>
       <c r="X40" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14783,7 +14783,7 @@
         <v>770</v>
       </c>
       <c r="X41" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14818,7 +14818,7 @@
         <v>772</v>
       </c>
       <c r="X42" t="s">
-        <v>587</v>
+        <v>642</v>
       </c>
       <c r="Y42">
         <v>27.642749999999999</v>
@@ -14853,7 +14853,7 @@
         <v>774</v>
       </c>
       <c r="X43" t="s">
-        <v>644</v>
+        <v>620</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14888,7 +14888,7 @@
         <v>776</v>
       </c>
       <c r="X44" t="s">
-        <v>591</v>
+        <v>645</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14923,7 +14923,7 @@
         <v>778</v>
       </c>
       <c r="X45" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14958,7 +14958,7 @@
         <v>780</v>
       </c>
       <c r="X46" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14993,7 +14993,7 @@
         <v>782</v>
       </c>
       <c r="X47" t="s">
-        <v>625</v>
+        <v>590</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -15028,7 +15028,7 @@
         <v>784</v>
       </c>
       <c r="X48" t="s">
-        <v>589</v>
+        <v>644</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15063,7 +15063,7 @@
         <v>786</v>
       </c>
       <c r="X49" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="Y49">
         <v>16.497</v>
@@ -15098,7 +15098,7 @@
         <v>788</v>
       </c>
       <c r="X50" t="s">
-        <v>646</v>
+        <v>622</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15133,7 +15133,7 @@
         <v>790</v>
       </c>
       <c r="X51" t="s">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15168,7 +15168,7 @@
         <v>792</v>
       </c>
       <c r="X52" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15203,7 +15203,7 @@
         <v>794</v>
       </c>
       <c r="X53" t="s">
-        <v>592</v>
+        <v>646</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15238,7 +15238,7 @@
         <v>796</v>
       </c>
       <c r="X54" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15253,7 +15253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55699BF7-7831-4A5E-A972-417B9D603082}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6114EC7E-9E23-4A81-A1BA-A9590224DB7A}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17070,7 +17070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A68CF4-D4A0-46BE-8F83-94FE96DAFCD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88AEC32B-F5B0-4EAA-BC41-8537544994EC}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE3A635C-44BA-4F9C-B96E-F31F442CFBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF567A7B-C733-486A-A3FE-05534B0B66CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -961,28 +961,166 @@
     <t>daynite</t>
   </si>
   <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_015</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
     <t>distr_solelc_spv_006</t>
@@ -1003,144 +1141,6 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1150,16 +1150,79 @@
     <t>e_JP306-500,e_w215451416-500</t>
   </si>
   <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
     <t>e_JP7-275,e_JP6-275</t>
   </si>
   <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
   </si>
   <si>
     <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
@@ -1171,67 +1234,136 @@
     <t>e_JP6-275</t>
   </si>
   <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wonelc_won_005</t>
@@ -1246,16 +1378,10 @@
     <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1270,6 +1396,12 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_017</t>
   </si>
   <si>
@@ -1288,136 +1420,124 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
   </si>
   <si>
     <t>elc_won_005</t>
@@ -1429,16 +1549,10 @@
     <t>elc_won_029</t>
   </si>
   <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -1453,6 +1567,12 @@
     <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
     <t>elc_won_017</t>
   </si>
   <si>
@@ -1471,124 +1591,124 @@
     <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wofelc_wof_006</t>
@@ -1609,36 +1729,36 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_018</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_029</t>
   </si>
   <si>
@@ -1663,24 +1783,6 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_013</t>
   </si>
   <si>
@@ -1705,22 +1807,22 @@
     <t>connecting wind offshore to buses in cluster 35</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wofelc_wof_010</t>
@@ -1741,66 +1843,6 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_031</t>
   </si>
   <si>
@@ -1813,46 +1855,94 @@
     <t>connecting wind offshore to buses in cluster 39</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
   </si>
   <si>
     <t>elc_wof_006</t>
@@ -1870,30 +1960,30 @@
     <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
   </si>
   <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
     <t>elc_wof_018</t>
   </si>
   <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
     <t>elc_wof_029</t>
   </si>
   <si>
@@ -1918,18 +2008,6 @@
     <t>e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
     <t>elc_wof_013</t>
   </si>
   <si>
@@ -1951,16 +2029,19 @@
     <t>e_JP132-500,e_w105298089-500</t>
   </si>
   <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
   </si>
   <si>
     <t>elc_wof_010</t>
@@ -1981,54 +2062,6 @@
     <t>e_JP7-275</t>
   </si>
   <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
     <t>elc_wof_031</t>
   </si>
   <si>
@@ -2039,39 +2072,6 @@
   </si>
   <si>
     <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7396,7 +7396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43C71B8-EBCF-4EDA-89B6-F3E9ECF971CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73D9166C-63FC-4794-8214-8F51C3596875}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7676,10 +7676,10 @@
         <v>431</v>
       </c>
       <c r="AO11">
-        <v>0.99827635377245738</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP11">
-        <v>31.600180838280902</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR11" t="s">
         <v>272</v>
@@ -7709,13 +7709,13 @@
         <v>575</v>
       </c>
       <c r="BB11" t="s">
-        <v>352</v>
+        <v>459</v>
       </c>
       <c r="BC11">
-        <v>0.95957195194316591</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD11">
-        <v>741.18088104195795</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7780,16 +7780,16 @@
         <v>277</v>
       </c>
       <c r="Y12" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="Z12" t="s">
         <v>340</v>
       </c>
       <c r="AA12">
-        <v>0.97905685820454003</v>
+        <v>0.99592928381702117</v>
       </c>
       <c r="AB12">
-        <v>383.95759958343297</v>
+        <v>74.629796687944193</v>
       </c>
       <c r="AD12" t="s">
         <v>272</v>
@@ -7819,13 +7819,13 @@
         <v>432</v>
       </c>
       <c r="AN12" t="s">
-        <v>340</v>
+        <v>433</v>
       </c>
       <c r="AO12">
-        <v>0.98949004263841422</v>
+        <v>0.99627181657233566</v>
       </c>
       <c r="AP12">
-        <v>192.68255162907312</v>
+        <v>68.350029507179471</v>
       </c>
       <c r="AR12" t="s">
         <v>272</v>
@@ -7858,10 +7858,10 @@
         <v>577</v>
       </c>
       <c r="BC12">
-        <v>0.98627205860840139</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD12">
-        <v>251.67892551264018</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7926,16 +7926,16 @@
         <v>279</v>
       </c>
       <c r="Y13" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Z13" t="s">
         <v>341</v>
       </c>
       <c r="AA13">
-        <v>0.99592928381702117</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB13">
-        <v>74.629796687944193</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD13" t="s">
         <v>272</v>
@@ -7962,16 +7962,16 @@
         <v>372</v>
       </c>
       <c r="AM13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO13">
-        <v>0.99841760060377538</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP13">
-        <v>29.010655597451841</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR13" t="s">
         <v>272</v>
@@ -8004,10 +8004,10 @@
         <v>579</v>
       </c>
       <c r="BC13">
-        <v>0.99504061303190972</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD13">
-        <v>90.922094414988095</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8072,16 +8072,16 @@
         <v>281</v>
       </c>
       <c r="Y14" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="Z14" t="s">
         <v>342</v>
       </c>
       <c r="AA14">
-        <v>0.99726055556014181</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB14">
-        <v>50.223148064066145</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD14" t="s">
         <v>272</v>
@@ -8108,16 +8108,16 @@
         <v>374</v>
       </c>
       <c r="AM14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO14">
-        <v>0.99781438034778358</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP14">
-        <v>40.069693623967019</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR14" t="s">
         <v>272</v>
@@ -8147,13 +8147,13 @@
         <v>580</v>
       </c>
       <c r="BB14" t="s">
-        <v>581</v>
+        <v>343</v>
       </c>
       <c r="BC14">
-        <v>0.98822137145239475</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD14">
-        <v>215.94152337276336</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8218,16 +8218,16 @@
         <v>283</v>
       </c>
       <c r="Y15" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="Z15" t="s">
         <v>343</v>
       </c>
       <c r="AA15">
-        <v>0.98968917222400854</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB15">
-        <v>189.03184255984442</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD15" t="s">
         <v>272</v>
@@ -8254,16 +8254,16 @@
         <v>376</v>
       </c>
       <c r="AM15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN15" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO15">
-        <v>0.99870022163576544</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP15">
-        <v>23.829270010966344</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR15" t="s">
         <v>272</v>
@@ -8290,16 +8290,16 @@
         <v>495</v>
       </c>
       <c r="BA15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BB15" t="s">
-        <v>583</v>
+        <v>343</v>
       </c>
       <c r="BC15">
-        <v>0.99284590877035406</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD15">
-        <v>131.158339210175</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8364,16 +8364,16 @@
         <v>285</v>
       </c>
       <c r="Y16" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="Z16" t="s">
         <v>344</v>
       </c>
       <c r="AA16">
-        <v>0.99852430677621173</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB16">
-        <v>27.054375769451152</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD16" t="s">
         <v>272</v>
@@ -8400,16 +8400,16 @@
         <v>378</v>
       </c>
       <c r="AM16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN16" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO16">
-        <v>0.99807466477127271</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP16">
-        <v>35.297812526667357</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR16" t="s">
         <v>272</v>
@@ -8436,16 +8436,16 @@
         <v>497</v>
       </c>
       <c r="BA16" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="BB16" t="s">
-        <v>585</v>
+        <v>343</v>
       </c>
       <c r="BC16">
-        <v>0.99302778580016682</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD16">
-        <v>127.82392699694152</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8510,16 +8510,16 @@
         <v>287</v>
       </c>
       <c r="Y17" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Z17" t="s">
         <v>345</v>
       </c>
       <c r="AA17">
-        <v>0.9975431479552237</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB17">
-        <v>45.042287487565297</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD17" t="s">
         <v>272</v>
@@ -8546,16 +8546,16 @@
         <v>380</v>
       </c>
       <c r="AM17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO17">
-        <v>0.99804155179341392</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP17">
-        <v>35.904883787411507</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR17" t="s">
         <v>272</v>
@@ -8582,16 +8582,16 @@
         <v>499</v>
       </c>
       <c r="BA17" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="BB17" t="s">
-        <v>340</v>
+        <v>584</v>
       </c>
       <c r="BC17">
-        <v>0.98180592470173533</v>
+        <v>0.99272888574049079</v>
       </c>
       <c r="BD17">
-        <v>333.55804713485287</v>
+        <v>133.30376142433548</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8656,16 +8656,16 @@
         <v>289</v>
       </c>
       <c r="Y18" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="Z18" t="s">
         <v>346</v>
       </c>
       <c r="AA18">
-        <v>0.98179245618315802</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB18">
-        <v>333.80496997543548</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD18" t="s">
         <v>272</v>
@@ -8692,16 +8692,16 @@
         <v>382</v>
       </c>
       <c r="AM18" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN18" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO18">
-        <v>0.99508023417818925</v>
+        <v>0.99771335854027388</v>
       </c>
       <c r="AP18">
-        <v>90.195706733197795</v>
+        <v>41.921760094978509</v>
       </c>
       <c r="AR18" t="s">
         <v>272</v>
@@ -8728,16 +8728,16 @@
         <v>501</v>
       </c>
       <c r="BA18" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="BB18" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="BC18">
-        <v>0.99547930517021377</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD18">
-        <v>82.879405212747869</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8838,16 +8838,16 @@
         <v>384</v>
       </c>
       <c r="AM19" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN19" t="s">
-        <v>446</v>
+        <v>354</v>
       </c>
       <c r="AO19">
-        <v>0.99940622505963084</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP19">
-        <v>10.885873906767051</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR19" t="s">
         <v>272</v>
@@ -8874,16 +8874,16 @@
         <v>503</v>
       </c>
       <c r="BA19" t="s">
+        <v>587</v>
+      </c>
+      <c r="BB19" t="s">
         <v>588</v>
       </c>
-      <c r="BB19" t="s">
-        <v>589</v>
-      </c>
       <c r="BC19">
-        <v>0.99234935324205875</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD19">
-        <v>140.26185722892211</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9020,16 +9020,16 @@
         <v>505</v>
       </c>
       <c r="BA20" t="s">
+        <v>589</v>
+      </c>
+      <c r="BB20" t="s">
         <v>590</v>
       </c>
-      <c r="BB20" t="s">
-        <v>591</v>
-      </c>
       <c r="BC20">
-        <v>0.9205295464439136</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD20">
-        <v>1456.9583151949184</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9094,16 +9094,16 @@
         <v>295</v>
       </c>
       <c r="Y21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Z21" t="s">
         <v>349</v>
       </c>
       <c r="AA21">
-        <v>0.9977500892185478</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB21">
-        <v>41.248364326622962</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD21" t="s">
         <v>272</v>
@@ -9166,16 +9166,16 @@
         <v>507</v>
       </c>
       <c r="BA21" t="s">
+        <v>591</v>
+      </c>
+      <c r="BB21" t="s">
         <v>592</v>
       </c>
-      <c r="BB21" t="s">
-        <v>593</v>
-      </c>
       <c r="BC21">
-        <v>0.99015836110796274</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD21">
-        <v>180.43004635401576</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9240,16 +9240,16 @@
         <v>297</v>
       </c>
       <c r="Y22" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="Z22" t="s">
         <v>350</v>
       </c>
       <c r="AA22">
-        <v>0.99788758639511588</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB22">
-        <v>38.727582756208619</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD22" t="s">
         <v>272</v>
@@ -9279,13 +9279,13 @@
         <v>451</v>
       </c>
       <c r="AN22" t="s">
-        <v>343</v>
+        <v>452</v>
       </c>
       <c r="AO22">
-        <v>0.99192535126433146</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP22">
-        <v>148.0352268205892</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR22" t="s">
         <v>272</v>
@@ -9312,16 +9312,16 @@
         <v>509</v>
       </c>
       <c r="BA22" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="BB22" t="s">
-        <v>595</v>
+        <v>437</v>
       </c>
       <c r="BC22">
-        <v>0.97803702976044449</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD22">
-        <v>402.65445439185123</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9386,16 +9386,16 @@
         <v>299</v>
       </c>
       <c r="Y23" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="Z23" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AA23">
-        <v>0.99841742239430997</v>
+        <v>0.96340341594909085</v>
       </c>
       <c r="AB23">
-        <v>29.013922770983669</v>
+        <v>670.93737426666792</v>
       </c>
       <c r="AD23" t="s">
         <v>272</v>
@@ -9422,16 +9422,16 @@
         <v>392</v>
       </c>
       <c r="AM23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN23" t="s">
-        <v>340</v>
+        <v>454</v>
       </c>
       <c r="AO23">
-        <v>0.98092693557487454</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP23">
-        <v>349.67284779396647</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR23" t="s">
         <v>272</v>
@@ -9458,16 +9458,16 @@
         <v>511</v>
       </c>
       <c r="BA23" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="BB23" t="s">
-        <v>473</v>
+        <v>595</v>
       </c>
       <c r="BC23">
-        <v>0.95726256957223688</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD23">
-        <v>783.51955784232393</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9532,16 +9532,16 @@
         <v>301</v>
       </c>
       <c r="Y24" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Z24" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA24">
-        <v>0.96340341594909085</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB24">
-        <v>670.93737426666792</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD24" t="s">
         <v>272</v>
@@ -9568,16 +9568,16 @@
         <v>394</v>
       </c>
       <c r="AM24" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN24" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO24">
-        <v>0.99762356494824644</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP24">
-        <v>43.567975948815601</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR24" t="s">
         <v>272</v>
@@ -9604,10 +9604,10 @@
         <v>513</v>
       </c>
       <c r="BA24" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="BB24" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="BC24">
         <v>0.99536692897647694</v>
@@ -9678,16 +9678,16 @@
         <v>303</v>
       </c>
       <c r="Y25" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Z25" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AA25">
-        <v>0.99838604658336239</v>
+        <v>0.99864010607905451</v>
       </c>
       <c r="AB25">
-        <v>29.589145971689483</v>
+        <v>24.931388550667378</v>
       </c>
       <c r="AD25" t="s">
         <v>272</v>
@@ -9714,16 +9714,16 @@
         <v>396</v>
       </c>
       <c r="AM25" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AN25" t="s">
-        <v>456</v>
+        <v>343</v>
       </c>
       <c r="AO25">
-        <v>0.99669176136177262</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP25">
-        <v>60.651041700835236</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR25" t="s">
         <v>272</v>
@@ -9750,10 +9750,10 @@
         <v>515</v>
       </c>
       <c r="BA25" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="BB25" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="BC25">
         <v>0.93089405249526469</v>
@@ -9824,16 +9824,16 @@
         <v>305</v>
       </c>
       <c r="Y26" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="Z26" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA26">
-        <v>0.99809153006866247</v>
+        <v>0.99706930328635524</v>
       </c>
       <c r="AB26">
-        <v>34.98861540785537</v>
+        <v>53.729439750153354</v>
       </c>
       <c r="AD26" t="s">
         <v>272</v>
@@ -9860,16 +9860,16 @@
         <v>398</v>
       </c>
       <c r="AM26" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO26">
-        <v>0.99710631799330929</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP26">
-        <v>53.050836789329388</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR26" t="s">
         <v>272</v>
@@ -9896,16 +9896,16 @@
         <v>517</v>
       </c>
       <c r="BA26" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="BB26" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="BC26">
-        <v>0.9973402418125219</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD26">
-        <v>48.762233437098502</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9970,16 +9970,16 @@
         <v>307</v>
       </c>
       <c r="Y27" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA27">
-        <v>0.99323944641370343</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB27">
-        <v>123.94348241543759</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD27" t="s">
         <v>272</v>
@@ -10006,16 +10006,16 @@
         <v>400</v>
       </c>
       <c r="AM27" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO27">
-        <v>0.99627181657233566</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP27">
-        <v>68.350029507179471</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR27" t="s">
         <v>272</v>
@@ -10042,16 +10042,16 @@
         <v>519</v>
       </c>
       <c r="BA27" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="BB27" t="s">
-        <v>603</v>
+        <v>345</v>
       </c>
       <c r="BC27">
-        <v>0.99519319222421976</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD27">
-        <v>88.124809222638589</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10116,16 +10116,16 @@
         <v>309</v>
       </c>
       <c r="Y28" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="Z28" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AA28">
-        <v>0.99864010607905451</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB28">
-        <v>24.931388550667378</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD28" t="s">
         <v>272</v>
@@ -10152,16 +10152,16 @@
         <v>402</v>
       </c>
       <c r="AM28" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN28" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO28">
-        <v>0.99550555557680764</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP28">
-        <v>82.398147758527074</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR28" t="s">
         <v>272</v>
@@ -10188,16 +10188,16 @@
         <v>521</v>
       </c>
       <c r="BA28" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="BB28" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="BC28">
-        <v>0.98605307635189521</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD28">
-        <v>255.693600215255</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10262,16 +10262,16 @@
         <v>311</v>
       </c>
       <c r="Y29" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="Z29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA29">
-        <v>0.99706930328635524</v>
+        <v>0.99809153006866247</v>
       </c>
       <c r="AB29">
-        <v>53.729439750153354</v>
+        <v>34.98861540785537</v>
       </c>
       <c r="AD29" t="s">
         <v>272</v>
@@ -10298,16 +10298,16 @@
         <v>404</v>
       </c>
       <c r="AM29" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN29" t="s">
-        <v>464</v>
+        <v>342</v>
       </c>
       <c r="AO29">
-        <v>0.93896180472603763</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP29">
-        <v>1119.0335800226442</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR29" t="s">
         <v>272</v>
@@ -10334,16 +10334,16 @@
         <v>523</v>
       </c>
       <c r="BA29" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="BB29" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="BC29">
-        <v>0.88199812838352587</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD29">
-        <v>2163.367646302027</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10408,16 +10408,16 @@
         <v>313</v>
       </c>
       <c r="Y30" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="Z30" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA30">
-        <v>0.99116451092312863</v>
+        <v>0.99323944641370343</v>
       </c>
       <c r="AB30">
-        <v>161.98396640930775</v>
+        <v>123.94348241543759</v>
       </c>
       <c r="AD30" t="s">
         <v>272</v>
@@ -10447,13 +10447,13 @@
         <v>465</v>
       </c>
       <c r="AN30" t="s">
-        <v>466</v>
+        <v>345</v>
       </c>
       <c r="AO30">
-        <v>0.99682717865030179</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP30">
-        <v>58.168391411134159</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR30" t="s">
         <v>272</v>
@@ -10480,16 +10480,16 @@
         <v>525</v>
       </c>
       <c r="BA30" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="BB30" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="BC30">
-        <v>0.96140381292129873</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD30">
-        <v>707.59676310952364</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10554,16 +10554,16 @@
         <v>315</v>
       </c>
       <c r="Y31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z31" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA31">
-        <v>0.9488788277802801</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB31">
-        <v>937.22149069486488</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD31" t="s">
         <v>272</v>
@@ -10590,16 +10590,16 @@
         <v>408</v>
       </c>
       <c r="AM31" t="s">
+        <v>466</v>
+      </c>
+      <c r="AN31" t="s">
         <v>467</v>
       </c>
-      <c r="AN31" t="s">
-        <v>468</v>
-      </c>
       <c r="AO31">
-        <v>0.99686124252542985</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP31">
-        <v>57.543887033786262</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR31" t="s">
         <v>272</v>
@@ -10626,16 +10626,16 @@
         <v>527</v>
       </c>
       <c r="BA31" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="BB31" t="s">
-        <v>609</v>
+        <v>343</v>
       </c>
       <c r="BC31">
-        <v>0.99490784156958001</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD31">
-        <v>93.356237891033686</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10700,16 +10700,16 @@
         <v>317</v>
       </c>
       <c r="Y32" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="Z32" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA32">
-        <v>0.9982812149336332</v>
+        <v>0.99788758639511588</v>
       </c>
       <c r="AB32">
-        <v>31.51105955005805</v>
+        <v>38.727582756208619</v>
       </c>
       <c r="AD32" t="s">
         <v>272</v>
@@ -10736,16 +10736,16 @@
         <v>410</v>
       </c>
       <c r="AM32" t="s">
+        <v>468</v>
+      </c>
+      <c r="AN32" t="s">
         <v>469</v>
       </c>
-      <c r="AN32" t="s">
-        <v>470</v>
-      </c>
       <c r="AO32">
-        <v>0.99869874972548245</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP32">
-        <v>23.856255032822389</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR32" t="s">
         <v>272</v>
@@ -10772,16 +10772,16 @@
         <v>529</v>
       </c>
       <c r="BA32" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="BB32" t="s">
-        <v>346</v>
+        <v>607</v>
       </c>
       <c r="BC32">
-        <v>0.97902641975794957</v>
+        <v>0.98627205860840139</v>
       </c>
       <c r="BD32">
-        <v>384.51563777092457</v>
+        <v>251.67892551264018</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10846,16 +10846,16 @@
         <v>319</v>
       </c>
       <c r="Y33" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="Z33" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AA33">
-        <v>0.99782703065964284</v>
+        <v>0.99841742239430997</v>
       </c>
       <c r="AB33">
-        <v>39.837771239882208</v>
+        <v>29.013922770983669</v>
       </c>
       <c r="AD33" t="s">
         <v>272</v>
@@ -10882,16 +10882,16 @@
         <v>412</v>
       </c>
       <c r="AM33" t="s">
+        <v>470</v>
+      </c>
+      <c r="AN33" t="s">
         <v>471</v>
       </c>
-      <c r="AN33" t="s">
-        <v>352</v>
-      </c>
       <c r="AO33">
-        <v>0.93717435218793788</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP33">
-        <v>1151.8035432211395</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR33" t="s">
         <v>272</v>
@@ -10918,16 +10918,16 @@
         <v>531</v>
       </c>
       <c r="BA33" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="BB33" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="BC33">
-        <v>0.99366677237144974</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD33">
-        <v>116.10917319008783</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -10992,16 +10992,16 @@
         <v>321</v>
       </c>
       <c r="Y34" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="Z34" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="AA34">
-        <v>0.99756610784588629</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB34">
-        <v>44.621356158751233</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD34" t="s">
         <v>272</v>
@@ -11031,13 +11031,13 @@
         <v>472</v>
       </c>
       <c r="AN34" t="s">
-        <v>473</v>
+        <v>345</v>
       </c>
       <c r="AO34">
-        <v>0.96551955124232614</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP34">
-        <v>632.14156055735509</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR34" t="s">
         <v>272</v>
@@ -11064,16 +11064,16 @@
         <v>533</v>
       </c>
       <c r="BA34" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="BB34" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="BC34">
-        <v>0.99623532634854861</v>
+        <v>0.99547930517021377</v>
       </c>
       <c r="BD34">
-        <v>69.01901694327529</v>
+        <v>82.879405212747869</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11138,16 +11138,16 @@
         <v>323</v>
       </c>
       <c r="Y35" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="Z35" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AA35">
-        <v>0.99636728996375623</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB35">
-        <v>66.599683997802714</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD35" t="s">
         <v>272</v>
@@ -11174,16 +11174,16 @@
         <v>416</v>
       </c>
       <c r="AM35" t="s">
+        <v>473</v>
+      </c>
+      <c r="AN35" t="s">
         <v>474</v>
       </c>
-      <c r="AN35" t="s">
-        <v>475</v>
-      </c>
       <c r="AO35">
-        <v>0.99693456929731861</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP35">
-        <v>56.199562882493169</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR35" t="s">
         <v>272</v>
@@ -11210,16 +11210,16 @@
         <v>535</v>
       </c>
       <c r="BA35" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="BB35" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="BC35">
-        <v>0.99895994357772033</v>
+        <v>0.99220908762204307</v>
       </c>
       <c r="BD35">
-        <v>19.067701075126294</v>
+        <v>142.83339359587785</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11284,16 +11284,16 @@
         <v>325</v>
       </c>
       <c r="Y36" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="Z36" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="AA36">
-        <v>0.94069903208664407</v>
+        <v>0.99866775225229476</v>
       </c>
       <c r="AB36">
-        <v>1087.1844117448593</v>
+        <v>24.424542041262942</v>
       </c>
       <c r="AD36" t="s">
         <v>272</v>
@@ -11320,16 +11320,16 @@
         <v>418</v>
       </c>
       <c r="AM36" t="s">
+        <v>475</v>
+      </c>
+      <c r="AN36" t="s">
         <v>476</v>
       </c>
-      <c r="AN36" t="s">
-        <v>477</v>
-      </c>
       <c r="AO36">
-        <v>0.99811838305018963</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP36">
-        <v>34.496310746523356</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR36" t="s">
         <v>272</v>
@@ -11356,16 +11356,16 @@
         <v>537</v>
       </c>
       <c r="BA36" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="BB36" t="s">
-        <v>618</v>
+        <v>343</v>
       </c>
       <c r="BC36">
-        <v>0.99220908762204307</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD36">
-        <v>142.83339359587785</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11430,16 +11430,16 @@
         <v>327</v>
       </c>
       <c r="Y37" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="Z37" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA37">
-        <v>0.99900168239190124</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB37">
-        <v>18.302489481810518</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD37" t="s">
         <v>272</v>
@@ -11466,16 +11466,16 @@
         <v>420</v>
       </c>
       <c r="AM37" t="s">
+        <v>477</v>
+      </c>
+      <c r="AN37" t="s">
         <v>478</v>
       </c>
-      <c r="AN37" t="s">
-        <v>479</v>
-      </c>
       <c r="AO37">
-        <v>0.9985928182686985</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP37">
-        <v>25.798331740528162</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR37" t="s">
         <v>272</v>
@@ -11502,16 +11502,16 @@
         <v>539</v>
       </c>
       <c r="BA37" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="BB37" t="s">
-        <v>352</v>
+        <v>615</v>
       </c>
       <c r="BC37">
-        <v>0.97591598065988894</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD37">
-        <v>441.54035456870389</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11576,16 +11576,16 @@
         <v>329</v>
       </c>
       <c r="Y38" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="Z38" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="AA38">
-        <v>0.98833720780868572</v>
+        <v>0.99782703065964284</v>
       </c>
       <c r="AB38">
-        <v>213.8178568407609</v>
+        <v>39.837771239882208</v>
       </c>
       <c r="AD38" t="s">
         <v>272</v>
@@ -11612,16 +11612,16 @@
         <v>422</v>
       </c>
       <c r="AM38" t="s">
+        <v>479</v>
+      </c>
+      <c r="AN38" t="s">
         <v>480</v>
       </c>
-      <c r="AN38" t="s">
-        <v>481</v>
-      </c>
       <c r="AO38">
-        <v>0.99771335854027388</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP38">
-        <v>41.921760094978509</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR38" t="s">
         <v>272</v>
@@ -11648,16 +11648,16 @@
         <v>541</v>
       </c>
       <c r="BA38" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="BB38" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="BC38">
-        <v>0.99412039195829205</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD38">
-        <v>107.79281409797902</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11722,16 +11722,16 @@
         <v>331</v>
       </c>
       <c r="Y39" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="Z39" t="s">
         <v>365</v>
       </c>
       <c r="AA39">
-        <v>0.99856748800713691</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB39">
-        <v>26.26271986915707</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD39" t="s">
         <v>272</v>
@@ -11758,16 +11758,16 @@
         <v>424</v>
       </c>
       <c r="AM39" t="s">
+        <v>481</v>
+      </c>
+      <c r="AN39" t="s">
         <v>482</v>
       </c>
-      <c r="AN39" t="s">
-        <v>358</v>
-      </c>
       <c r="AO39">
-        <v>0.98814178187791379</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP39">
-        <v>217.40066557158059</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR39" t="s">
         <v>272</v>
@@ -11794,16 +11794,16 @@
         <v>543</v>
       </c>
       <c r="BA39" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="BB39" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="BC39">
-        <v>0.98881218539944515</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD39">
-        <v>205.10993434350485</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11868,16 +11868,16 @@
         <v>333</v>
       </c>
       <c r="Y40" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="Z40" t="s">
         <v>366</v>
       </c>
       <c r="AA40">
-        <v>0.99850557699173803</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB40">
-        <v>27.397755151469518</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD40" t="s">
         <v>272</v>
@@ -11910,10 +11910,10 @@
         <v>484</v>
       </c>
       <c r="AO40">
-        <v>0.99750949182367343</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP40">
-        <v>45.659316565986806</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR40" t="s">
         <v>272</v>
@@ -11940,16 +11940,16 @@
         <v>545</v>
       </c>
       <c r="BA40" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="BB40" t="s">
-        <v>352</v>
+        <v>621</v>
       </c>
       <c r="BC40">
-        <v>0.934538160869965</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD40">
-        <v>1200.1337173839754</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12014,16 +12014,16 @@
         <v>335</v>
       </c>
       <c r="Y41" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Z41" t="s">
         <v>367</v>
       </c>
       <c r="AA41">
-        <v>0.99866775225229476</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB41">
-        <v>24.424542041262942</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD41" t="s">
         <v>272</v>
@@ -12056,10 +12056,10 @@
         <v>486</v>
       </c>
       <c r="AO41">
-        <v>0.99863922747017897</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP41">
-        <v>24.947496380053089</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR41" t="s">
         <v>272</v>
@@ -12086,16 +12086,16 @@
         <v>547</v>
       </c>
       <c r="BA41" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="BB41" t="s">
-        <v>352</v>
+        <v>623</v>
       </c>
       <c r="BC41">
-        <v>0.94616153753972931</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD41">
-        <v>987.03847843829612</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12124,16 +12124,16 @@
         <v>549</v>
       </c>
       <c r="BA42" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="BB42" t="s">
-        <v>352</v>
+        <v>625</v>
       </c>
       <c r="BC42">
-        <v>0.97218956380622079</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD42">
-        <v>509.85799688595205</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12162,16 +12162,16 @@
         <v>551</v>
       </c>
       <c r="BA43" t="s">
+        <v>626</v>
+      </c>
+      <c r="BB43" t="s">
         <v>627</v>
       </c>
-      <c r="BB43" t="s">
-        <v>628</v>
-      </c>
       <c r="BC43">
-        <v>0.99272888574049079</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD43">
-        <v>133.30376142433548</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12200,16 +12200,16 @@
         <v>553</v>
       </c>
       <c r="BA44" t="s">
+        <v>628</v>
+      </c>
+      <c r="BB44" t="s">
         <v>629</v>
       </c>
-      <c r="BB44" t="s">
-        <v>630</v>
-      </c>
       <c r="BC44">
-        <v>0.99662747375050009</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD44">
-        <v>61.829647907498845</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12238,16 +12238,16 @@
         <v>555</v>
       </c>
       <c r="BA45" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BB45" t="s">
-        <v>632</v>
+        <v>354</v>
       </c>
       <c r="BC45">
-        <v>0.99637036284424008</v>
+        <v>0.98605307635189521</v>
       </c>
       <c r="BD45">
-        <v>66.543347855598327</v>
+        <v>255.693600215255</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12276,16 +12276,16 @@
         <v>557</v>
       </c>
       <c r="BA46" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="BB46" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="BC46">
-        <v>0.98779966071713954</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD46">
-        <v>223.67288685244134</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12314,16 +12314,16 @@
         <v>559</v>
       </c>
       <c r="BA47" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="BB47" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="BC47">
-        <v>0.99681267676383467</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD47">
-        <v>58.434259329697142</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12352,16 +12352,16 @@
         <v>561</v>
       </c>
       <c r="BA48" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="BB48" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="BC48">
-        <v>0.99114508565756532</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD48">
-        <v>162.34009627796874</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12390,16 +12390,16 @@
         <v>563</v>
       </c>
       <c r="BA49" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="BB49" t="s">
-        <v>640</v>
+        <v>354</v>
       </c>
       <c r="BC49">
-        <v>0.99561586640696276</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD49">
-        <v>80.375782539015233</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12428,16 +12428,16 @@
         <v>565</v>
       </c>
       <c r="BA50" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="BB50" t="s">
-        <v>358</v>
+        <v>639</v>
       </c>
       <c r="BC50">
-        <v>0.98235584693125277</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD50">
-        <v>323.47613959369914</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12466,16 +12466,16 @@
         <v>567</v>
       </c>
       <c r="BA51" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="BB51" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="BC51">
-        <v>0.99603667376986049</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD51">
-        <v>72.660980885890424</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12504,16 +12504,16 @@
         <v>569</v>
       </c>
       <c r="BA52" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="BB52" t="s">
-        <v>599</v>
+        <v>643</v>
       </c>
       <c r="BC52">
-        <v>0.97589985979527272</v>
+        <v>0.99895994357772033</v>
       </c>
       <c r="BD52">
-        <v>441.83590375333313</v>
+        <v>19.067701075126294</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12542,16 +12542,16 @@
         <v>571</v>
       </c>
       <c r="BA53" t="s">
+        <v>644</v>
+      </c>
+      <c r="BB53" t="s">
         <v>645</v>
       </c>
-      <c r="BB53" t="s">
-        <v>464</v>
-      </c>
       <c r="BC53">
-        <v>0.9437657388784082</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD53">
-        <v>1030.9614538958492</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12586,10 +12586,10 @@
         <v>647</v>
       </c>
       <c r="BC54">
-        <v>0.99602290686668338</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD54">
-        <v>72.91337411080552</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
   </sheetData>
@@ -12598,7 +12598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EBE32DF-24D2-424B-AEA1-59E91761AEBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CCF7BD-D128-45B6-B975-44F4545374E4}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12743,7 +12743,7 @@
         <v>710</v>
       </c>
       <c r="X11" t="s">
-        <v>624</v>
+        <v>580</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12778,7 +12778,7 @@
         <v>650</v>
       </c>
       <c r="K12" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12811,7 +12811,7 @@
         <v>712</v>
       </c>
       <c r="X12" t="s">
-        <v>625</v>
+        <v>581</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12846,7 +12846,7 @@
         <v>652</v>
       </c>
       <c r="K13" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -12879,7 +12879,7 @@
         <v>714</v>
       </c>
       <c r="X13" t="s">
-        <v>626</v>
+        <v>582</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12914,7 +12914,7 @@
         <v>654</v>
       </c>
       <c r="K14" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -12947,7 +12947,7 @@
         <v>716</v>
       </c>
       <c r="X14" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12982,7 +12982,7 @@
         <v>656</v>
       </c>
       <c r="K15" t="s">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13015,7 +13015,7 @@
         <v>718</v>
       </c>
       <c r="X15" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13050,7 +13050,7 @@
         <v>658</v>
       </c>
       <c r="K16" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13083,7 +13083,7 @@
         <v>720</v>
       </c>
       <c r="X16" t="s">
-        <v>575</v>
+        <v>605</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13118,7 +13118,7 @@
         <v>660</v>
       </c>
       <c r="K17" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13151,7 +13151,7 @@
         <v>722</v>
       </c>
       <c r="X17" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13186,7 +13186,7 @@
         <v>662</v>
       </c>
       <c r="K18" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13219,7 +13219,7 @@
         <v>724</v>
       </c>
       <c r="X18" t="s">
-        <v>629</v>
+        <v>585</v>
       </c>
       <c r="Y18">
         <v>28.478249999999999</v>
@@ -13254,7 +13254,7 @@
         <v>664</v>
       </c>
       <c r="K19" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13287,7 +13287,7 @@
         <v>726</v>
       </c>
       <c r="X19" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Y19">
         <v>22.079249999999998</v>
@@ -13355,7 +13355,7 @@
         <v>728</v>
       </c>
       <c r="X20" t="s">
-        <v>611</v>
+        <v>638</v>
       </c>
       <c r="Y20">
         <v>29.961749999999999</v>
@@ -13390,7 +13390,7 @@
         <v>668</v>
       </c>
       <c r="K21" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13423,7 +13423,7 @@
         <v>730</v>
       </c>
       <c r="X21" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13458,7 +13458,7 @@
         <v>670</v>
       </c>
       <c r="K22" t="s">
-        <v>445</v>
+        <v>485</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13491,7 +13491,7 @@
         <v>732</v>
       </c>
       <c r="X22" t="s">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="Y22">
         <v>82.576499999999996</v>
@@ -13526,7 +13526,7 @@
         <v>672</v>
       </c>
       <c r="K23" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13559,7 +13559,7 @@
         <v>734</v>
       </c>
       <c r="X23" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13594,7 +13594,7 @@
         <v>674</v>
       </c>
       <c r="K24" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13627,7 +13627,7 @@
         <v>736</v>
       </c>
       <c r="X24" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="Y24">
         <v>75.512249999999995</v>
@@ -13662,7 +13662,7 @@
         <v>676</v>
       </c>
       <c r="K25" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13695,7 +13695,7 @@
         <v>738</v>
       </c>
       <c r="X25" t="s">
-        <v>602</v>
+        <v>628</v>
       </c>
       <c r="Y25">
         <v>28.239750000000001</v>
@@ -13730,7 +13730,7 @@
         <v>678</v>
       </c>
       <c r="K26" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13763,7 +13763,7 @@
         <v>740</v>
       </c>
       <c r="X26" t="s">
-        <v>615</v>
+        <v>642</v>
       </c>
       <c r="Y26">
         <v>1.9132499999999999</v>
@@ -13798,7 +13798,7 @@
         <v>680</v>
       </c>
       <c r="K27" t="s">
-        <v>441</v>
+        <v>481</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -13831,7 +13831,7 @@
         <v>742</v>
       </c>
       <c r="X27" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="Y27">
         <v>63.731250000000003</v>
@@ -13866,7 +13866,7 @@
         <v>682</v>
       </c>
       <c r="K28" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -13899,7 +13899,7 @@
         <v>744</v>
       </c>
       <c r="X28" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="Y28">
         <v>38.451000000000001</v>
@@ -13934,7 +13934,7 @@
         <v>684</v>
       </c>
       <c r="K29" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -13967,7 +13967,7 @@
         <v>746</v>
       </c>
       <c r="X29" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="Y29">
         <v>64.533749999999998</v>
@@ -14002,7 +14002,7 @@
         <v>686</v>
       </c>
       <c r="K30" t="s">
-        <v>443</v>
+        <v>483</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14035,7 +14035,7 @@
         <v>748</v>
       </c>
       <c r="X30" t="s">
-        <v>604</v>
+        <v>630</v>
       </c>
       <c r="Y30">
         <v>44.370750000000001</v>
@@ -14070,7 +14070,7 @@
         <v>688</v>
       </c>
       <c r="K31" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14103,7 +14103,7 @@
         <v>750</v>
       </c>
       <c r="X31" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="Y31">
         <v>38.15925</v>
@@ -14138,7 +14138,7 @@
         <v>690</v>
       </c>
       <c r="K32" t="s">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14171,7 +14171,7 @@
         <v>752</v>
       </c>
       <c r="X32" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="Y32">
         <v>3.38625</v>
@@ -14206,7 +14206,7 @@
         <v>692</v>
       </c>
       <c r="K33" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14239,7 +14239,7 @@
         <v>754</v>
       </c>
       <c r="X33" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="Y33">
         <v>30.597750000000001</v>
@@ -14274,7 +14274,7 @@
         <v>694</v>
       </c>
       <c r="K34" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14307,7 +14307,7 @@
         <v>756</v>
       </c>
       <c r="X34" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14342,7 +14342,7 @@
         <v>696</v>
       </c>
       <c r="K35" t="s">
-        <v>480</v>
+        <v>444</v>
       </c>
       <c r="L35">
         <v>44.894334115294185</v>
@@ -14375,7 +14375,7 @@
         <v>758</v>
       </c>
       <c r="X35" t="s">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="Y35">
         <v>58.474499999999999</v>
@@ -14410,7 +14410,7 @@
         <v>698</v>
       </c>
       <c r="K36" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="L36">
         <v>14.358494358107757</v>
@@ -14443,7 +14443,7 @@
         <v>760</v>
       </c>
       <c r="X36" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="Y36">
         <v>18.711749999999999</v>
@@ -14478,7 +14478,7 @@
         <v>700</v>
       </c>
       <c r="K37" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14511,7 +14511,7 @@
         <v>762</v>
       </c>
       <c r="X37" t="s">
-        <v>631</v>
+        <v>587</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14546,7 +14546,7 @@
         <v>702</v>
       </c>
       <c r="K38" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14579,7 +14579,7 @@
         <v>764</v>
       </c>
       <c r="X38" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14614,7 +14614,7 @@
         <v>704</v>
       </c>
       <c r="K39" t="s">
-        <v>432</v>
+        <v>472</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14647,7 +14647,7 @@
         <v>766</v>
       </c>
       <c r="X39" t="s">
-        <v>588</v>
+        <v>618</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14682,7 +14682,7 @@
         <v>706</v>
       </c>
       <c r="K40" t="s">
-        <v>482</v>
+        <v>446</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14715,7 +14715,7 @@
         <v>768</v>
       </c>
       <c r="X40" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14750,7 +14750,7 @@
         <v>708</v>
       </c>
       <c r="K41" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14783,7 +14783,7 @@
         <v>770</v>
       </c>
       <c r="X41" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14818,7 +14818,7 @@
         <v>772</v>
       </c>
       <c r="X42" t="s">
-        <v>642</v>
+        <v>589</v>
       </c>
       <c r="Y42">
         <v>27.642749999999999</v>
@@ -14853,7 +14853,7 @@
         <v>774</v>
       </c>
       <c r="X43" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14888,7 +14888,7 @@
         <v>776</v>
       </c>
       <c r="X44" t="s">
-        <v>645</v>
+        <v>593</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14923,7 +14923,7 @@
         <v>778</v>
       </c>
       <c r="X45" t="s">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14958,7 +14958,7 @@
         <v>780</v>
       </c>
       <c r="X46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14993,7 +14993,7 @@
         <v>782</v>
       </c>
       <c r="X47" t="s">
-        <v>590</v>
+        <v>620</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -15028,7 +15028,7 @@
         <v>784</v>
       </c>
       <c r="X48" t="s">
-        <v>644</v>
+        <v>591</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15063,7 +15063,7 @@
         <v>786</v>
       </c>
       <c r="X49" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="Y49">
         <v>16.497</v>
@@ -15098,7 +15098,7 @@
         <v>788</v>
       </c>
       <c r="X50" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15133,7 +15133,7 @@
         <v>790</v>
       </c>
       <c r="X51" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15168,7 +15168,7 @@
         <v>792</v>
       </c>
       <c r="X52" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15203,7 +15203,7 @@
         <v>794</v>
       </c>
       <c r="X53" t="s">
-        <v>646</v>
+        <v>594</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15238,7 +15238,7 @@
         <v>796</v>
       </c>
       <c r="X54" t="s">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15253,7 +15253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6114EC7E-9E23-4A81-A1BA-A9590224DB7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457AA5E0-40FE-4507-9BD7-926A1CA579F7}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17070,7 +17070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88AEC32B-F5B0-4EAA-BC41-8537544994EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCAA29D-8F39-4225-BF15-012818DAF427}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF567A7B-C733-486A-A3FE-05534B0B66CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CC9E05C-3449-4D22-B94C-25535F4AEBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -961,6 +961,126 @@
     <t>daynite</t>
   </si>
   <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_027</t>
   </si>
   <si>
@@ -979,40 +1099,34 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_solelc_spv_008</t>
@@ -1027,120 +1141,6 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1150,6 +1150,60 @@
     <t>e_JP306-500,e_w215451416-500</t>
   </si>
   <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
   </si>
   <si>
@@ -1159,22 +1213,19 @@
     <t>e_w179863079-275,e_JP6-275</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
   </si>
   <si>
     <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
@@ -1183,55 +1234,82 @@
     <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wonelc_won_007</t>
@@ -1258,166 +1336,163 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_015</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
   </si>
   <si>
     <t>elc_won_007</t>
@@ -1444,151 +1519,220 @@
     <t>e_JP219-500,e_JP132-500</t>
   </si>
   <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
     <t>elc_won_015</t>
   </si>
   <si>
     <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
   </si>
   <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_wofelc_wof_005</t>
@@ -1597,6 +1741,108 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_011</t>
   </si>
   <si>
@@ -1609,255 +1855,213 @@
     <t>connecting wind offshore to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
     <t>elc_wof_005</t>
   </si>
   <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
     <t>elc_wof_011</t>
   </si>
   <si>
@@ -1868,210 +2072,6 @@
   </si>
   <si>
     <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7396,7 +7396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73D9166C-63FC-4794-8214-8F51C3596875}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DAE232-BA6D-4415-9141-46E570191AA1}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7676,10 +7676,10 @@
         <v>431</v>
       </c>
       <c r="AO11">
-        <v>0.99710631799330929</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP11">
-        <v>53.050836789329388</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR11" t="s">
         <v>272</v>
@@ -7709,13 +7709,13 @@
         <v>575</v>
       </c>
       <c r="BB11" t="s">
-        <v>459</v>
+        <v>576</v>
       </c>
       <c r="BC11">
-        <v>0.95726256957223688</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD11">
-        <v>783.51955784232393</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7780,16 +7780,16 @@
         <v>277</v>
       </c>
       <c r="Y12" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="Z12" t="s">
         <v>340</v>
       </c>
       <c r="AA12">
-        <v>0.99592928381702117</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB12">
-        <v>74.629796687944193</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD12" t="s">
         <v>272</v>
@@ -7819,13 +7819,13 @@
         <v>432</v>
       </c>
       <c r="AN12" t="s">
-        <v>433</v>
+        <v>352</v>
       </c>
       <c r="AO12">
-        <v>0.99627181657233566</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP12">
-        <v>68.350029507179471</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR12" t="s">
         <v>272</v>
@@ -7852,16 +7852,16 @@
         <v>489</v>
       </c>
       <c r="BA12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="BB12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="BC12">
-        <v>0.98822137145239475</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD12">
-        <v>215.94152337276336</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7926,16 +7926,16 @@
         <v>279</v>
       </c>
       <c r="Y13" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Z13" t="s">
         <v>341</v>
       </c>
       <c r="AA13">
-        <v>0.99726055556014181</v>
+        <v>0.99788758639511588</v>
       </c>
       <c r="AB13">
-        <v>50.223148064066145</v>
+        <v>38.727582756208619</v>
       </c>
       <c r="AD13" t="s">
         <v>272</v>
@@ -7962,16 +7962,16 @@
         <v>372</v>
       </c>
       <c r="AM13" t="s">
+        <v>433</v>
+      </c>
+      <c r="AN13" t="s">
         <v>434</v>
       </c>
-      <c r="AN13" t="s">
-        <v>435</v>
-      </c>
       <c r="AO13">
-        <v>0.99550555557680764</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP13">
-        <v>82.398147758527074</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR13" t="s">
         <v>272</v>
@@ -7998,16 +7998,16 @@
         <v>491</v>
       </c>
       <c r="BA13" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="BB13" t="s">
-        <v>579</v>
+        <v>462</v>
       </c>
       <c r="BC13">
-        <v>0.99284590877035406</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD13">
-        <v>131.158339210175</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8072,16 +8072,16 @@
         <v>281</v>
       </c>
       <c r="Y14" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Z14" t="s">
         <v>342</v>
       </c>
       <c r="AA14">
-        <v>0.98968917222400854</v>
+        <v>0.99841742239430997</v>
       </c>
       <c r="AB14">
-        <v>189.03184255984442</v>
+        <v>29.013922770983669</v>
       </c>
       <c r="AD14" t="s">
         <v>272</v>
@@ -8108,16 +8108,16 @@
         <v>374</v>
       </c>
       <c r="AM14" t="s">
+        <v>435</v>
+      </c>
+      <c r="AN14" t="s">
         <v>436</v>
       </c>
-      <c r="AN14" t="s">
-        <v>437</v>
-      </c>
       <c r="AO14">
-        <v>0.93896180472603763</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP14">
-        <v>1119.0335800226442</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR14" t="s">
         <v>272</v>
@@ -8147,13 +8147,13 @@
         <v>580</v>
       </c>
       <c r="BB14" t="s">
-        <v>343</v>
+        <v>581</v>
       </c>
       <c r="BC14">
-        <v>0.934538160869965</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD14">
-        <v>1200.1337173839754</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8218,16 +8218,16 @@
         <v>283</v>
       </c>
       <c r="Y15" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="Z15" t="s">
         <v>343</v>
       </c>
       <c r="AA15">
-        <v>0.94069903208664407</v>
+        <v>0.99809153006866247</v>
       </c>
       <c r="AB15">
-        <v>1087.1844117448593</v>
+        <v>34.98861540785537</v>
       </c>
       <c r="AD15" t="s">
         <v>272</v>
@@ -8254,16 +8254,16 @@
         <v>376</v>
       </c>
       <c r="AM15" t="s">
+        <v>437</v>
+      </c>
+      <c r="AN15" t="s">
         <v>438</v>
       </c>
-      <c r="AN15" t="s">
-        <v>439</v>
-      </c>
       <c r="AO15">
-        <v>0.99686124252542985</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP15">
-        <v>57.543887033786262</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR15" t="s">
         <v>272</v>
@@ -8290,16 +8290,16 @@
         <v>495</v>
       </c>
       <c r="BA15" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="BB15" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="BC15">
-        <v>0.94616153753972931</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD15">
-        <v>987.03847843829612</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8364,16 +8364,16 @@
         <v>285</v>
       </c>
       <c r="Y16" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="Z16" t="s">
         <v>344</v>
       </c>
       <c r="AA16">
-        <v>0.99900168239190124</v>
+        <v>0.99323944641370343</v>
       </c>
       <c r="AB16">
-        <v>18.302489481810518</v>
+        <v>123.94348241543759</v>
       </c>
       <c r="AD16" t="s">
         <v>272</v>
@@ -8400,16 +8400,16 @@
         <v>378</v>
       </c>
       <c r="AM16" t="s">
+        <v>439</v>
+      </c>
+      <c r="AN16" t="s">
         <v>440</v>
       </c>
-      <c r="AN16" t="s">
-        <v>441</v>
-      </c>
       <c r="AO16">
-        <v>0.99811838305018963</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP16">
-        <v>34.496310746523356</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR16" t="s">
         <v>272</v>
@@ -8436,16 +8436,16 @@
         <v>497</v>
       </c>
       <c r="BA16" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="BB16" t="s">
-        <v>343</v>
+        <v>584</v>
       </c>
       <c r="BC16">
-        <v>0.97218956380622079</v>
+        <v>0.98627205860840139</v>
       </c>
       <c r="BD16">
-        <v>509.85799688595205</v>
+        <v>251.67892551264018</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8510,16 +8510,16 @@
         <v>287</v>
       </c>
       <c r="Y17" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="Z17" t="s">
         <v>345</v>
       </c>
       <c r="AA17">
-        <v>0.98833720780868572</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB17">
-        <v>213.8178568407609</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD17" t="s">
         <v>272</v>
@@ -8546,16 +8546,16 @@
         <v>380</v>
       </c>
       <c r="AM17" t="s">
+        <v>441</v>
+      </c>
+      <c r="AN17" t="s">
         <v>442</v>
       </c>
-      <c r="AN17" t="s">
-        <v>443</v>
-      </c>
       <c r="AO17">
-        <v>0.9985928182686985</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP17">
-        <v>25.798331740528162</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR17" t="s">
         <v>272</v>
@@ -8582,16 +8582,16 @@
         <v>499</v>
       </c>
       <c r="BA17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="BB17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="BC17">
-        <v>0.99272888574049079</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD17">
-        <v>133.30376142433548</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8656,16 +8656,16 @@
         <v>289</v>
       </c>
       <c r="Y18" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Z18" t="s">
         <v>346</v>
       </c>
       <c r="AA18">
-        <v>0.99856748800713691</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB18">
-        <v>26.26271986915707</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD18" t="s">
         <v>272</v>
@@ -8692,16 +8692,16 @@
         <v>382</v>
       </c>
       <c r="AM18" t="s">
+        <v>443</v>
+      </c>
+      <c r="AN18" t="s">
         <v>444</v>
       </c>
-      <c r="AN18" t="s">
-        <v>445</v>
-      </c>
       <c r="AO18">
-        <v>0.99771335854027388</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP18">
-        <v>41.921760094978509</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR18" t="s">
         <v>272</v>
@@ -8728,16 +8728,16 @@
         <v>501</v>
       </c>
       <c r="BA18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="BB18" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="BC18">
-        <v>0.99662747375050009</v>
+        <v>0.99547930517021377</v>
       </c>
       <c r="BD18">
-        <v>61.829647907498845</v>
+        <v>82.879405212747869</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8802,16 +8802,16 @@
         <v>291</v>
       </c>
       <c r="Y19" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="Z19" t="s">
         <v>347</v>
       </c>
       <c r="AA19">
-        <v>0.9981032549815434</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB19">
-        <v>34.773658671704098</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD19" t="s">
         <v>272</v>
@@ -8838,16 +8838,16 @@
         <v>384</v>
       </c>
       <c r="AM19" t="s">
+        <v>445</v>
+      </c>
+      <c r="AN19" t="s">
         <v>446</v>
       </c>
-      <c r="AN19" t="s">
-        <v>354</v>
-      </c>
       <c r="AO19">
-        <v>0.98814178187791379</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP19">
-        <v>217.40066557158059</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR19" t="s">
         <v>272</v>
@@ -8874,16 +8874,16 @@
         <v>503</v>
       </c>
       <c r="BA19" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="BB19" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="BC19">
-        <v>0.99637036284424008</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD19">
-        <v>66.543347855598327</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8948,16 +8948,16 @@
         <v>293</v>
       </c>
       <c r="Y20" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="Z20" t="s">
         <v>348</v>
       </c>
       <c r="AA20">
-        <v>0.99894650606645485</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB20">
-        <v>19.314055448326833</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD20" t="s">
         <v>272</v>
@@ -8990,10 +8990,10 @@
         <v>448</v>
       </c>
       <c r="AO20">
-        <v>0.99013353407586135</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP20">
-        <v>180.88520860920943</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR20" t="s">
         <v>272</v>
@@ -9020,16 +9020,16 @@
         <v>505</v>
       </c>
       <c r="BA20" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="BB20" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="BC20">
-        <v>0.99603667376986049</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD20">
-        <v>72.660980885890424</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9094,16 +9094,16 @@
         <v>295</v>
       </c>
       <c r="Y21" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="Z21" t="s">
         <v>349</v>
       </c>
       <c r="AA21">
-        <v>0.99756610784588629</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB21">
-        <v>44.621356158751233</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD21" t="s">
         <v>272</v>
@@ -9136,10 +9136,10 @@
         <v>450</v>
       </c>
       <c r="AO21">
-        <v>0.99869589057011365</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP21">
-        <v>23.908672881248773</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR21" t="s">
         <v>272</v>
@@ -9166,16 +9166,16 @@
         <v>507</v>
       </c>
       <c r="BA21" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="BB21" t="s">
-        <v>592</v>
+        <v>365</v>
       </c>
       <c r="BC21">
-        <v>0.97589985979527272</v>
+        <v>0.98605307635189521</v>
       </c>
       <c r="BD21">
-        <v>441.83590375333313</v>
+        <v>255.693600215255</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9240,16 +9240,16 @@
         <v>297</v>
       </c>
       <c r="Y22" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Z22" t="s">
         <v>350</v>
       </c>
       <c r="AA22">
-        <v>0.99636728996375623</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB22">
-        <v>66.599683997802714</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD22" t="s">
         <v>272</v>
@@ -9282,10 +9282,10 @@
         <v>452</v>
       </c>
       <c r="AO22">
-        <v>0.99841760060377538</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP22">
-        <v>29.010655597451841</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR22" t="s">
         <v>272</v>
@@ -9315,13 +9315,13 @@
         <v>593</v>
       </c>
       <c r="BB22" t="s">
-        <v>437</v>
+        <v>594</v>
       </c>
       <c r="BC22">
-        <v>0.9437657388784082</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD22">
-        <v>1030.9614538958492</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9386,16 +9386,16 @@
         <v>299</v>
       </c>
       <c r="Y23" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AA23">
-        <v>0.96340341594909085</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB23">
-        <v>670.93737426666792</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD23" t="s">
         <v>272</v>
@@ -9428,10 +9428,10 @@
         <v>454</v>
       </c>
       <c r="AO23">
-        <v>0.99781438034778358</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP23">
-        <v>40.069693623967019</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR23" t="s">
         <v>272</v>
@@ -9458,16 +9458,16 @@
         <v>511</v>
       </c>
       <c r="BA23" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="BB23" t="s">
-        <v>595</v>
+        <v>352</v>
       </c>
       <c r="BC23">
-        <v>0.99602290686668338</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD23">
-        <v>72.91337411080552</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9532,16 +9532,16 @@
         <v>301</v>
       </c>
       <c r="Y24" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Z24" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA24">
-        <v>0.99838604658336239</v>
+        <v>0.96340341594909085</v>
       </c>
       <c r="AB24">
-        <v>29.589145971689483</v>
+        <v>670.93737426666792</v>
       </c>
       <c r="AD24" t="s">
         <v>272</v>
@@ -9574,10 +9574,10 @@
         <v>456</v>
       </c>
       <c r="AO24">
-        <v>0.99869874972548245</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP24">
-        <v>23.856255032822389</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR24" t="s">
         <v>272</v>
@@ -9607,13 +9607,13 @@
         <v>596</v>
       </c>
       <c r="BB24" t="s">
-        <v>351</v>
+        <v>597</v>
       </c>
       <c r="BC24">
-        <v>0.99536692897647694</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD24">
-        <v>84.939635431255269</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9678,16 +9678,16 @@
         <v>303</v>
       </c>
       <c r="Y25" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="Z25" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA25">
-        <v>0.99864010607905451</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB25">
-        <v>24.931388550667378</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD25" t="s">
         <v>272</v>
@@ -9717,13 +9717,13 @@
         <v>457</v>
       </c>
       <c r="AN25" t="s">
-        <v>343</v>
+        <v>458</v>
       </c>
       <c r="AO25">
-        <v>0.93717435218793788</v>
+        <v>0.99627181657233566</v>
       </c>
       <c r="AP25">
-        <v>1151.8035432211395</v>
+        <v>68.350029507179471</v>
       </c>
       <c r="AR25" t="s">
         <v>272</v>
@@ -9750,16 +9750,16 @@
         <v>515</v>
       </c>
       <c r="BA25" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="BB25" t="s">
-        <v>592</v>
+        <v>347</v>
       </c>
       <c r="BC25">
-        <v>0.93089405249526469</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD25">
-        <v>1266.9423709201483</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9824,16 +9824,16 @@
         <v>305</v>
       </c>
       <c r="Y26" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="Z26" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA26">
-        <v>0.99706930328635524</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB26">
-        <v>53.729439750153354</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD26" t="s">
         <v>272</v>
@@ -9860,16 +9860,16 @@
         <v>398</v>
       </c>
       <c r="AM26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN26" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO26">
-        <v>0.96551955124232614</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP26">
-        <v>632.14156055735509</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR26" t="s">
         <v>272</v>
@@ -9896,10 +9896,10 @@
         <v>517</v>
       </c>
       <c r="BA26" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="BB26" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="BC26">
         <v>0.99302778580016682</v>
@@ -9970,16 +9970,16 @@
         <v>307</v>
       </c>
       <c r="Y27" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="Z27" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AA27">
-        <v>0.99116451092312863</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB27">
-        <v>161.98396640930775</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD27" t="s">
         <v>272</v>
@@ -10006,16 +10006,16 @@
         <v>400</v>
       </c>
       <c r="AM27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO27">
-        <v>0.99693456929731861</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP27">
-        <v>56.199562882493169</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR27" t="s">
         <v>272</v>
@@ -10042,10 +10042,10 @@
         <v>519</v>
       </c>
       <c r="BA27" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="BB27" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="BC27">
         <v>0.98180592470173533</v>
@@ -10116,16 +10116,16 @@
         <v>309</v>
       </c>
       <c r="Y28" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="Z28" t="s">
         <v>355</v>
       </c>
       <c r="AA28">
-        <v>0.9488788277802801</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB28">
-        <v>937.22149069486488</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD28" t="s">
         <v>272</v>
@@ -10152,16 +10152,16 @@
         <v>402</v>
       </c>
       <c r="AM28" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO28">
-        <v>0.99863922747017897</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP28">
-        <v>24.947496380053089</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR28" t="s">
         <v>272</v>
@@ -10188,16 +10188,16 @@
         <v>521</v>
       </c>
       <c r="BA28" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="BB28" t="s">
-        <v>343</v>
+        <v>603</v>
       </c>
       <c r="BC28">
-        <v>0.96140381292129873</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD28">
-        <v>707.59676310952364</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10262,16 +10262,16 @@
         <v>311</v>
       </c>
       <c r="Y29" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Z29" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="AA29">
-        <v>0.99809153006866247</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB29">
-        <v>34.98861540785537</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD29" t="s">
         <v>272</v>
@@ -10298,16 +10298,16 @@
         <v>404</v>
       </c>
       <c r="AM29" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN29" t="s">
-        <v>342</v>
+        <v>466</v>
       </c>
       <c r="AO29">
-        <v>0.99192535126433146</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP29">
-        <v>148.0352268205892</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR29" t="s">
         <v>272</v>
@@ -10334,16 +10334,16 @@
         <v>523</v>
       </c>
       <c r="BA29" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="BB29" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="BC29">
-        <v>0.99490784156958001</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD29">
-        <v>93.356237891033686</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10408,16 +10408,16 @@
         <v>313</v>
       </c>
       <c r="Y30" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="Z30" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA30">
-        <v>0.99323944641370343</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB30">
-        <v>123.94348241543759</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD30" t="s">
         <v>272</v>
@@ -10444,16 +10444,16 @@
         <v>406</v>
       </c>
       <c r="AM30" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN30" t="s">
-        <v>345</v>
+        <v>468</v>
       </c>
       <c r="AO30">
-        <v>0.98092693557487454</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP30">
-        <v>349.67284779396647</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR30" t="s">
         <v>272</v>
@@ -10480,16 +10480,16 @@
         <v>525</v>
       </c>
       <c r="BA30" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="BB30" t="s">
-        <v>367</v>
+        <v>607</v>
       </c>
       <c r="BC30">
-        <v>0.97902641975794957</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD30">
-        <v>384.51563777092457</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10554,16 +10554,16 @@
         <v>315</v>
       </c>
       <c r="Y31" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="Z31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA31">
-        <v>0.9977500892185478</v>
+        <v>0.99782703065964284</v>
       </c>
       <c r="AB31">
-        <v>41.248364326622962</v>
+        <v>39.837771239882208</v>
       </c>
       <c r="AD31" t="s">
         <v>272</v>
@@ -10590,16 +10590,16 @@
         <v>408</v>
       </c>
       <c r="AM31" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AN31" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AO31">
-        <v>0.99762356494824644</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP31">
-        <v>43.567975948815601</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR31" t="s">
         <v>272</v>
@@ -10626,16 +10626,16 @@
         <v>527</v>
       </c>
       <c r="BA31" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="BB31" t="s">
-        <v>343</v>
+        <v>609</v>
       </c>
       <c r="BC31">
-        <v>0.95957195194316591</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD31">
-        <v>741.18088104195795</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10700,16 +10700,16 @@
         <v>317</v>
       </c>
       <c r="Y32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Z32" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA32">
-        <v>0.99788758639511588</v>
+        <v>0.99592928381702117</v>
       </c>
       <c r="AB32">
-        <v>38.727582756208619</v>
+        <v>74.629796687944193</v>
       </c>
       <c r="AD32" t="s">
         <v>272</v>
@@ -10736,16 +10736,16 @@
         <v>410</v>
       </c>
       <c r="AM32" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AN32" t="s">
-        <v>469</v>
+        <v>360</v>
       </c>
       <c r="AO32">
-        <v>0.99669176136177262</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP32">
-        <v>60.651041700835236</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR32" t="s">
         <v>272</v>
@@ -10772,16 +10772,16 @@
         <v>529</v>
       </c>
       <c r="BA32" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="BB32" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="BC32">
-        <v>0.98627205860840139</v>
+        <v>0.99895994357772033</v>
       </c>
       <c r="BD32">
-        <v>251.67892551264018</v>
+        <v>19.067701075126294</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10846,16 +10846,16 @@
         <v>319</v>
       </c>
       <c r="Y33" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="Z33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA33">
-        <v>0.99841742239430997</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB33">
-        <v>29.013922770983669</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD33" t="s">
         <v>272</v>
@@ -10882,16 +10882,16 @@
         <v>412</v>
       </c>
       <c r="AM33" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN33" t="s">
-        <v>471</v>
+        <v>349</v>
       </c>
       <c r="AO33">
-        <v>0.99827635377245738</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP33">
-        <v>31.600180838280902</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR33" t="s">
         <v>272</v>
@@ -10918,16 +10918,16 @@
         <v>531</v>
       </c>
       <c r="BA33" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="BB33" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="BC33">
-        <v>0.99504061303190972</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD33">
-        <v>90.922094414988095</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -10992,16 +10992,16 @@
         <v>321</v>
       </c>
       <c r="Y34" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Z34" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="AA34">
-        <v>0.97905685820454003</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB34">
-        <v>383.95759958343297</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD34" t="s">
         <v>272</v>
@@ -11028,16 +11028,16 @@
         <v>414</v>
       </c>
       <c r="AM34" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN34" t="s">
-        <v>345</v>
+        <v>474</v>
       </c>
       <c r="AO34">
-        <v>0.98949004263841422</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP34">
-        <v>192.68255162907312</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR34" t="s">
         <v>272</v>
@@ -11064,16 +11064,16 @@
         <v>533</v>
       </c>
       <c r="BA34" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="BB34" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="BC34">
-        <v>0.99547930517021377</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD34">
-        <v>82.879405212747869</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11174,16 +11174,16 @@
         <v>416</v>
       </c>
       <c r="AM35" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN35" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO35">
-        <v>0.99750949182367343</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP35">
-        <v>45.659316565986806</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR35" t="s">
         <v>272</v>
@@ -11210,16 +11210,16 @@
         <v>535</v>
       </c>
       <c r="BA35" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="BB35" t="s">
-        <v>612</v>
+        <v>434</v>
       </c>
       <c r="BC35">
-        <v>0.99220908762204307</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD35">
-        <v>142.83339359587785</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11320,16 +11320,16 @@
         <v>418</v>
       </c>
       <c r="AM36" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN36" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO36">
-        <v>0.99870022163576544</v>
+        <v>0.99771335854027388</v>
       </c>
       <c r="AP36">
-        <v>23.829270010966344</v>
+        <v>41.921760094978509</v>
       </c>
       <c r="AR36" t="s">
         <v>272</v>
@@ -11356,16 +11356,16 @@
         <v>537</v>
       </c>
       <c r="BA36" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="BB36" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="BC36">
-        <v>0.97591598065988894</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD36">
-        <v>441.54035456870389</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11430,16 +11430,16 @@
         <v>327</v>
       </c>
       <c r="Y37" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Z37" t="s">
         <v>363</v>
       </c>
       <c r="AA37">
-        <v>0.9982812149336332</v>
+        <v>0.99864010607905451</v>
       </c>
       <c r="AB37">
-        <v>31.51105955005805</v>
+        <v>24.931388550667378</v>
       </c>
       <c r="AD37" t="s">
         <v>272</v>
@@ -11466,16 +11466,16 @@
         <v>420</v>
       </c>
       <c r="AM37" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN37" t="s">
-        <v>478</v>
+        <v>365</v>
       </c>
       <c r="AO37">
-        <v>0.99807466477127271</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP37">
-        <v>35.297812526667357</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR37" t="s">
         <v>272</v>
@@ -11502,16 +11502,16 @@
         <v>539</v>
       </c>
       <c r="BA37" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="BB37" t="s">
-        <v>615</v>
+        <v>352</v>
       </c>
       <c r="BC37">
-        <v>0.99412039195829205</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD37">
-        <v>107.79281409797902</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11576,16 +11576,16 @@
         <v>329</v>
       </c>
       <c r="Y38" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Z38" t="s">
         <v>364</v>
       </c>
       <c r="AA38">
-        <v>0.99782703065964284</v>
+        <v>0.99706930328635524</v>
       </c>
       <c r="AB38">
-        <v>39.837771239882208</v>
+        <v>53.729439750153354</v>
       </c>
       <c r="AD38" t="s">
         <v>272</v>
@@ -11612,10 +11612,10 @@
         <v>422</v>
       </c>
       <c r="AM38" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN38" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO38">
         <v>0.99682717865030179</v>
@@ -11648,16 +11648,16 @@
         <v>541</v>
       </c>
       <c r="BA38" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="BB38" t="s">
-        <v>617</v>
+        <v>352</v>
       </c>
       <c r="BC38">
-        <v>0.98881218539944515</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD38">
-        <v>205.10993434350485</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11722,16 +11722,16 @@
         <v>331</v>
       </c>
       <c r="Y39" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="Z39" t="s">
         <v>365</v>
       </c>
       <c r="AA39">
-        <v>0.99852430677621173</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB39">
-        <v>27.054375769451152</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD39" t="s">
         <v>272</v>
@@ -11758,16 +11758,16 @@
         <v>424</v>
       </c>
       <c r="AM39" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN39" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO39">
-        <v>0.99804155179341392</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP39">
-        <v>35.904883787411507</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR39" t="s">
         <v>272</v>
@@ -11794,16 +11794,16 @@
         <v>543</v>
       </c>
       <c r="BA39" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="BB39" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="BC39">
-        <v>0.99234935324205875</v>
+        <v>0.99272888574049079</v>
       </c>
       <c r="BD39">
-        <v>140.26185722892211</v>
+        <v>133.30376142433548</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11868,16 +11868,16 @@
         <v>333</v>
       </c>
       <c r="Y40" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="Z40" t="s">
         <v>366</v>
       </c>
       <c r="AA40">
-        <v>0.9975431479552237</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB40">
-        <v>45.042287487565297</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD40" t="s">
         <v>272</v>
@@ -11904,16 +11904,16 @@
         <v>426</v>
       </c>
       <c r="AM40" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN40" t="s">
-        <v>484</v>
+        <v>349</v>
       </c>
       <c r="AO40">
-        <v>0.99508023417818925</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP40">
-        <v>90.195706733197795</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR40" t="s">
         <v>272</v>
@@ -11940,16 +11940,16 @@
         <v>545</v>
       </c>
       <c r="BA40" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="BB40" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="BC40">
-        <v>0.9205295464439136</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD40">
-        <v>1456.9583151949184</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12014,16 +12014,16 @@
         <v>335</v>
       </c>
       <c r="Y41" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Z41" t="s">
         <v>367</v>
       </c>
       <c r="AA41">
-        <v>0.98179245618315802</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB41">
-        <v>333.80496997543548</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD41" t="s">
         <v>272</v>
@@ -12056,10 +12056,10 @@
         <v>486</v>
       </c>
       <c r="AO41">
-        <v>0.99940622505963084</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP41">
-        <v>10.885873906767051</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR41" t="s">
         <v>272</v>
@@ -12086,16 +12086,16 @@
         <v>547</v>
       </c>
       <c r="BA41" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="BB41" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="BC41">
-        <v>0.99015836110796274</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD41">
-        <v>180.43004635401576</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12124,16 +12124,16 @@
         <v>549</v>
       </c>
       <c r="BA42" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="BB42" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="BC42">
-        <v>0.97803702976044449</v>
+        <v>0.99220908762204307</v>
       </c>
       <c r="BD42">
-        <v>402.65445439185123</v>
+        <v>142.83339359587785</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12162,16 +12162,16 @@
         <v>551</v>
       </c>
       <c r="BA43" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="BB43" t="s">
-        <v>627</v>
+        <v>352</v>
       </c>
       <c r="BC43">
-        <v>0.9973402418125219</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD43">
-        <v>48.762233437098502</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12200,16 +12200,16 @@
         <v>553</v>
       </c>
       <c r="BA44" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="BB44" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="BC44">
-        <v>0.99519319222421976</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD44">
-        <v>88.124809222638589</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12238,16 +12238,16 @@
         <v>555</v>
       </c>
       <c r="BA45" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="BB45" t="s">
-        <v>354</v>
+        <v>632</v>
       </c>
       <c r="BC45">
-        <v>0.98605307635189521</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD45">
-        <v>255.693600215255</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12276,16 +12276,16 @@
         <v>557</v>
       </c>
       <c r="BA46" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="BB46" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="BC46">
-        <v>0.88199812838352587</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD46">
-        <v>2163.367646302027</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12314,16 +12314,16 @@
         <v>559</v>
       </c>
       <c r="BA47" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="BB47" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="BC47">
-        <v>0.99114508565756532</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD47">
-        <v>162.34009627796874</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12352,16 +12352,16 @@
         <v>561</v>
       </c>
       <c r="BA48" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="BB48" t="s">
-        <v>636</v>
+        <v>365</v>
       </c>
       <c r="BC48">
-        <v>0.99561586640696276</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD48">
-        <v>80.375782539015233</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12390,16 +12390,16 @@
         <v>563</v>
       </c>
       <c r="BA49" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="BB49" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="BC49">
-        <v>0.98235584693125277</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD49">
-        <v>323.47613959369914</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12428,16 +12428,16 @@
         <v>565</v>
       </c>
       <c r="BA50" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="BB50" t="s">
-        <v>639</v>
+        <v>578</v>
       </c>
       <c r="BC50">
-        <v>0.99366677237144974</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD50">
-        <v>116.10917319008783</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12472,10 +12472,10 @@
         <v>641</v>
       </c>
       <c r="BC51">
-        <v>0.99623532634854861</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD51">
-        <v>69.01901694327529</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12510,10 +12510,10 @@
         <v>643</v>
       </c>
       <c r="BC52">
-        <v>0.99895994357772033</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD52">
-        <v>19.067701075126294</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12548,10 +12548,10 @@
         <v>645</v>
       </c>
       <c r="BC53">
-        <v>0.98779966071713954</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD53">
-        <v>223.67288685244134</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12586,10 +12586,10 @@
         <v>647</v>
       </c>
       <c r="BC54">
-        <v>0.99681267676383467</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD54">
-        <v>58.434259329697142</v>
+        <v>131.158339210175</v>
       </c>
     </row>
   </sheetData>
@@ -12598,7 +12598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CCF7BD-D128-45B6-B975-44F4545374E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C7FEF9-605A-44A4-9C7F-294606135449}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12710,7 +12710,7 @@
         <v>648</v>
       </c>
       <c r="K11" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12743,7 +12743,7 @@
         <v>710</v>
       </c>
       <c r="X11" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12778,7 +12778,7 @@
         <v>650</v>
       </c>
       <c r="K12" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12811,7 +12811,7 @@
         <v>712</v>
       </c>
       <c r="X12" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12846,7 +12846,7 @@
         <v>652</v>
       </c>
       <c r="K13" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -12879,7 +12879,7 @@
         <v>714</v>
       </c>
       <c r="X13" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12914,7 +12914,7 @@
         <v>654</v>
       </c>
       <c r="K14" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -12947,7 +12947,7 @@
         <v>716</v>
       </c>
       <c r="X14" t="s">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12982,7 +12982,7 @@
         <v>656</v>
       </c>
       <c r="K15" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13015,7 +13015,7 @@
         <v>718</v>
       </c>
       <c r="X15" t="s">
-        <v>575</v>
+        <v>616</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13050,7 +13050,7 @@
         <v>658</v>
       </c>
       <c r="K16" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13083,7 +13083,7 @@
         <v>720</v>
       </c>
       <c r="X16" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13118,7 +13118,7 @@
         <v>660</v>
       </c>
       <c r="K17" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13151,7 +13151,7 @@
         <v>722</v>
       </c>
       <c r="X17" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13186,7 +13186,7 @@
         <v>662</v>
       </c>
       <c r="K18" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13219,7 +13219,7 @@
         <v>724</v>
       </c>
       <c r="X18" t="s">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="Y18">
         <v>28.478249999999999</v>
@@ -13254,7 +13254,7 @@
         <v>664</v>
       </c>
       <c r="K19" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13287,7 +13287,7 @@
         <v>726</v>
       </c>
       <c r="X19" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
       <c r="Y19">
         <v>22.079249999999998</v>
@@ -13322,7 +13322,7 @@
         <v>666</v>
       </c>
       <c r="K20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13355,7 +13355,7 @@
         <v>728</v>
       </c>
       <c r="X20" t="s">
-        <v>638</v>
+        <v>606</v>
       </c>
       <c r="Y20">
         <v>29.961749999999999</v>
@@ -13390,7 +13390,7 @@
         <v>668</v>
       </c>
       <c r="K21" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13423,7 +13423,7 @@
         <v>730</v>
       </c>
       <c r="X21" t="s">
-        <v>576</v>
+        <v>644</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13458,7 +13458,7 @@
         <v>670</v>
       </c>
       <c r="K22" t="s">
-        <v>485</v>
+        <v>445</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13491,7 +13491,7 @@
         <v>732</v>
       </c>
       <c r="X22" t="s">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="Y22">
         <v>82.576499999999996</v>
@@ -13526,7 +13526,7 @@
         <v>672</v>
       </c>
       <c r="K23" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13559,7 +13559,7 @@
         <v>734</v>
       </c>
       <c r="X23" t="s">
-        <v>626</v>
+        <v>588</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13594,7 +13594,7 @@
         <v>674</v>
       </c>
       <c r="K24" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13627,7 +13627,7 @@
         <v>736</v>
       </c>
       <c r="X24" t="s">
-        <v>611</v>
+        <v>626</v>
       </c>
       <c r="Y24">
         <v>75.512249999999995</v>
@@ -13662,7 +13662,7 @@
         <v>676</v>
       </c>
       <c r="K25" t="s">
-        <v>438</v>
+        <v>485</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13695,7 +13695,7 @@
         <v>738</v>
       </c>
       <c r="X25" t="s">
-        <v>628</v>
+        <v>590</v>
       </c>
       <c r="Y25">
         <v>28.239750000000001</v>
@@ -13730,7 +13730,7 @@
         <v>678</v>
       </c>
       <c r="K26" t="s">
-        <v>473</v>
+        <v>430</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13763,7 +13763,7 @@
         <v>740</v>
       </c>
       <c r="X26" t="s">
-        <v>642</v>
+        <v>610</v>
       </c>
       <c r="Y26">
         <v>1.9132499999999999</v>
@@ -13798,7 +13798,7 @@
         <v>680</v>
       </c>
       <c r="K27" t="s">
-        <v>481</v>
+        <v>441</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -13831,7 +13831,7 @@
         <v>742</v>
       </c>
       <c r="X27" t="s">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="Y27">
         <v>63.731250000000003</v>
@@ -13866,7 +13866,7 @@
         <v>682</v>
       </c>
       <c r="K28" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -13899,7 +13899,7 @@
         <v>744</v>
       </c>
       <c r="X28" t="s">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="Y28">
         <v>38.451000000000001</v>
@@ -13934,7 +13934,7 @@
         <v>684</v>
       </c>
       <c r="K29" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -13967,7 +13967,7 @@
         <v>746</v>
       </c>
       <c r="X29" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="Y29">
         <v>64.533749999999998</v>
@@ -14002,7 +14002,7 @@
         <v>686</v>
       </c>
       <c r="K30" t="s">
-        <v>483</v>
+        <v>443</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14035,7 +14035,7 @@
         <v>748</v>
       </c>
       <c r="X30" t="s">
-        <v>630</v>
+        <v>592</v>
       </c>
       <c r="Y30">
         <v>44.370750000000001</v>
@@ -14070,7 +14070,7 @@
         <v>688</v>
       </c>
       <c r="K31" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14103,7 +14103,7 @@
         <v>750</v>
       </c>
       <c r="X31" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Y31">
         <v>38.15925</v>
@@ -14138,7 +14138,7 @@
         <v>690</v>
       </c>
       <c r="K32" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14171,7 +14171,7 @@
         <v>752</v>
       </c>
       <c r="X32" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="Y32">
         <v>3.38625</v>
@@ -14206,7 +14206,7 @@
         <v>692</v>
       </c>
       <c r="K33" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14239,7 +14239,7 @@
         <v>754</v>
       </c>
       <c r="X33" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="Y33">
         <v>30.597750000000001</v>
@@ -14274,7 +14274,7 @@
         <v>694</v>
       </c>
       <c r="K34" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14342,7 +14342,7 @@
         <v>696</v>
       </c>
       <c r="K35" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="L35">
         <v>44.894334115294185</v>
@@ -14375,7 +14375,7 @@
         <v>758</v>
       </c>
       <c r="X35" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="Y35">
         <v>58.474499999999999</v>
@@ -14410,7 +14410,7 @@
         <v>698</v>
       </c>
       <c r="K36" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="L36">
         <v>14.358494358107757</v>
@@ -14478,7 +14478,7 @@
         <v>700</v>
       </c>
       <c r="K37" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14511,7 +14511,7 @@
         <v>762</v>
       </c>
       <c r="X37" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14546,7 +14546,7 @@
         <v>702</v>
       </c>
       <c r="K38" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14614,7 +14614,7 @@
         <v>704</v>
       </c>
       <c r="K39" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14647,7 +14647,7 @@
         <v>766</v>
       </c>
       <c r="X39" t="s">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14682,7 +14682,7 @@
         <v>706</v>
       </c>
       <c r="K40" t="s">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14715,7 +14715,7 @@
         <v>768</v>
       </c>
       <c r="X40" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14750,7 +14750,7 @@
         <v>708</v>
       </c>
       <c r="K41" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14783,7 +14783,7 @@
         <v>770</v>
       </c>
       <c r="X41" t="s">
-        <v>644</v>
+        <v>602</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14818,7 +14818,7 @@
         <v>772</v>
       </c>
       <c r="X42" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="Y42">
         <v>27.642749999999999</v>
@@ -14853,7 +14853,7 @@
         <v>774</v>
       </c>
       <c r="X43" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14888,7 +14888,7 @@
         <v>776</v>
       </c>
       <c r="X44" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14923,7 +14923,7 @@
         <v>778</v>
       </c>
       <c r="X45" t="s">
-        <v>631</v>
+        <v>593</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14958,7 +14958,7 @@
         <v>780</v>
       </c>
       <c r="X46" t="s">
-        <v>597</v>
+        <v>639</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14993,7 +14993,7 @@
         <v>782</v>
       </c>
       <c r="X47" t="s">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -15028,7 +15028,7 @@
         <v>784</v>
       </c>
       <c r="X48" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15063,7 +15063,7 @@
         <v>786</v>
       </c>
       <c r="X49" t="s">
-        <v>646</v>
+        <v>604</v>
       </c>
       <c r="Y49">
         <v>16.497</v>
@@ -15098,7 +15098,7 @@
         <v>788</v>
       </c>
       <c r="X50" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15133,7 +15133,7 @@
         <v>790</v>
       </c>
       <c r="X51" t="s">
-        <v>578</v>
+        <v>646</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15168,7 +15168,7 @@
         <v>792</v>
       </c>
       <c r="X52" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15203,7 +15203,7 @@
         <v>794</v>
       </c>
       <c r="X53" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15238,7 +15238,7 @@
         <v>796</v>
       </c>
       <c r="X54" t="s">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15253,7 +15253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457AA5E0-40FE-4507-9BD7-926A1CA579F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7925130-F1BE-4AB5-87DF-0DBDE148EA26}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17070,7 +17070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCAA29D-8F39-4225-BF15-012818DAF427}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83EE9BD1-C4BA-4A24-B7B7-C7F927D1F4FA}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CC9E05C-3449-4D22-B94C-25535F4AEBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE8AF64-5B0F-4EF4-956D-87CA7AE9B3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,34 +949,184 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_solelc_spv_013</t>
@@ -991,172 +1141,91 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
     <t>e_JP306-500,e_w215451416-500</t>
   </si>
   <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
   </si>
   <si>
     <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
@@ -1165,73 +1234,160 @@
     <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
   </si>
   <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_016</t>
@@ -1240,58 +1396,22 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wonelc_won_013</t>
@@ -1300,124 +1420,145 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
   </si>
   <si>
     <t>elc_won_016</t>
@@ -1426,55 +1567,22 @@
     <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
   </si>
   <si>
     <t>elc_won_013</t>
@@ -1483,114 +1591,6 @@
     <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_032</t>
   </si>
   <si>
@@ -1615,6 +1615,180 @@
     <t>connecting wind offshore to buses in cluster 43</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
@@ -1639,70 +1813,22 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wofelc_wof_010</t>
@@ -1723,138 +1849,12 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_005</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
     <t>elc_wof_032</t>
   </si>
   <si>
@@ -1876,6 +1876,150 @@
     <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
   </si>
   <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
@@ -1894,58 +2038,19 @@
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
   </si>
   <si>
     <t>elc_wof_010</t>
@@ -1966,112 +2071,7 @@
     <t>e_JP7-275</t>
   </si>
   <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
     <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7396,7 +7396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DAE232-BA6D-4415-9141-46E570191AA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F73964C-B005-4C75-8B79-A49358225FE7}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7634,16 +7634,16 @@
         <v>273</v>
       </c>
       <c r="Y11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Z11" t="s">
         <v>339</v>
       </c>
       <c r="AA11">
-        <v>0.99391268208184824</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB11">
-        <v>111.60082849944791</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD11" t="s">
         <v>272</v>
@@ -7676,10 +7676,10 @@
         <v>431</v>
       </c>
       <c r="AO11">
-        <v>0.99750949182367343</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP11">
-        <v>45.659316565986806</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR11" t="s">
         <v>272</v>
@@ -7780,16 +7780,16 @@
         <v>277</v>
       </c>
       <c r="Y12" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="Z12" t="s">
         <v>340</v>
       </c>
       <c r="AA12">
-        <v>0.9977500892185478</v>
+        <v>0.99782703065964284</v>
       </c>
       <c r="AB12">
-        <v>41.248364326622962</v>
+        <v>39.837771239882208</v>
       </c>
       <c r="AD12" t="s">
         <v>272</v>
@@ -7819,13 +7819,13 @@
         <v>432</v>
       </c>
       <c r="AN12" t="s">
-        <v>352</v>
+        <v>433</v>
       </c>
       <c r="AO12">
-        <v>0.93717435218793788</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP12">
-        <v>1151.8035432211395</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR12" t="s">
         <v>272</v>
@@ -7926,16 +7926,16 @@
         <v>279</v>
       </c>
       <c r="Y13" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="Z13" t="s">
         <v>341</v>
       </c>
       <c r="AA13">
-        <v>0.99788758639511588</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB13">
-        <v>38.727582756208619</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD13" t="s">
         <v>272</v>
@@ -7962,16 +7962,16 @@
         <v>372</v>
       </c>
       <c r="AM13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO13">
-        <v>0.96551955124232614</v>
+        <v>0.99771335854027388</v>
       </c>
       <c r="AP13">
-        <v>632.14156055735509</v>
+        <v>41.921760094978509</v>
       </c>
       <c r="AR13" t="s">
         <v>272</v>
@@ -8001,7 +8001,7 @@
         <v>579</v>
       </c>
       <c r="BB13" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="BC13">
         <v>0.9437657388784082</v>
@@ -8072,16 +8072,16 @@
         <v>281</v>
       </c>
       <c r="Y14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Z14" t="s">
         <v>342</v>
       </c>
       <c r="AA14">
-        <v>0.99841742239430997</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB14">
-        <v>29.013922770983669</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD14" t="s">
         <v>272</v>
@@ -8108,16 +8108,16 @@
         <v>374</v>
       </c>
       <c r="AM14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN14" t="s">
-        <v>436</v>
+        <v>347</v>
       </c>
       <c r="AO14">
-        <v>0.99693456929731861</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP14">
-        <v>56.199562882493169</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR14" t="s">
         <v>272</v>
@@ -8218,16 +8218,16 @@
         <v>283</v>
       </c>
       <c r="Y15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Z15" t="s">
         <v>343</v>
       </c>
       <c r="AA15">
-        <v>0.99809153006866247</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB15">
-        <v>34.98861540785537</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD15" t="s">
         <v>272</v>
@@ -8260,10 +8260,10 @@
         <v>438</v>
       </c>
       <c r="AO15">
-        <v>0.99841760060377538</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP15">
-        <v>29.010655597451841</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR15" t="s">
         <v>272</v>
@@ -8293,13 +8293,13 @@
         <v>582</v>
       </c>
       <c r="BB15" t="s">
-        <v>352</v>
+        <v>583</v>
       </c>
       <c r="BC15">
-        <v>0.95957195194316591</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD15">
-        <v>741.18088104195795</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8364,16 +8364,16 @@
         <v>285</v>
       </c>
       <c r="Y16" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="Z16" t="s">
         <v>344</v>
       </c>
       <c r="AA16">
-        <v>0.99323944641370343</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB16">
-        <v>123.94348241543759</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD16" t="s">
         <v>272</v>
@@ -8406,10 +8406,10 @@
         <v>440</v>
       </c>
       <c r="AO16">
-        <v>0.99781438034778358</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP16">
-        <v>40.069693623967019</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR16" t="s">
         <v>272</v>
@@ -8436,16 +8436,16 @@
         <v>497</v>
       </c>
       <c r="BA16" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="BB16" t="s">
-        <v>584</v>
+        <v>343</v>
       </c>
       <c r="BC16">
-        <v>0.98627205860840139</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD16">
-        <v>251.67892551264018</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8510,16 +8510,16 @@
         <v>287</v>
       </c>
       <c r="Y17" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Z17" t="s">
         <v>345</v>
       </c>
       <c r="AA17">
-        <v>0.99852430677621173</v>
+        <v>0.99864010607905451</v>
       </c>
       <c r="AB17">
-        <v>27.054375769451152</v>
+        <v>24.931388550667378</v>
       </c>
       <c r="AD17" t="s">
         <v>272</v>
@@ -8552,10 +8552,10 @@
         <v>442</v>
       </c>
       <c r="AO17">
-        <v>0.99804155179341392</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP17">
-        <v>35.904883787411507</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR17" t="s">
         <v>272</v>
@@ -8585,13 +8585,13 @@
         <v>585</v>
       </c>
       <c r="BB17" t="s">
-        <v>586</v>
+        <v>341</v>
       </c>
       <c r="BC17">
-        <v>0.99504061303190972</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD17">
-        <v>90.922094414988095</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8656,16 +8656,16 @@
         <v>289</v>
       </c>
       <c r="Y18" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="Z18" t="s">
         <v>346</v>
       </c>
       <c r="AA18">
-        <v>0.9975431479552237</v>
+        <v>0.99706930328635524</v>
       </c>
       <c r="AB18">
-        <v>45.042287487565297</v>
+        <v>53.729439750153354</v>
       </c>
       <c r="AD18" t="s">
         <v>272</v>
@@ -8698,10 +8698,10 @@
         <v>444</v>
       </c>
       <c r="AO18">
-        <v>0.99508023417818925</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP18">
-        <v>90.195706733197795</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR18" t="s">
         <v>272</v>
@@ -8728,16 +8728,16 @@
         <v>501</v>
       </c>
       <c r="BA18" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="BB18" t="s">
-        <v>584</v>
+        <v>341</v>
       </c>
       <c r="BC18">
-        <v>0.99547930517021377</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD18">
-        <v>82.879405212747869</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8802,16 +8802,16 @@
         <v>291</v>
       </c>
       <c r="Y19" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z19" t="s">
         <v>347</v>
       </c>
       <c r="AA19">
-        <v>0.98179245618315802</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB19">
-        <v>333.80496997543548</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD19" t="s">
         <v>272</v>
@@ -8844,10 +8844,10 @@
         <v>446</v>
       </c>
       <c r="AO19">
-        <v>0.99940622505963084</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP19">
-        <v>10.885873906767051</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR19" t="s">
         <v>272</v>
@@ -8874,16 +8874,16 @@
         <v>503</v>
       </c>
       <c r="BA19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="BB19" t="s">
-        <v>589</v>
+        <v>341</v>
       </c>
       <c r="BC19">
-        <v>0.9973402418125219</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD19">
-        <v>48.762233437098502</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8948,16 +8948,16 @@
         <v>293</v>
       </c>
       <c r="Y20" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="Z20" t="s">
         <v>348</v>
       </c>
       <c r="AA20">
-        <v>0.9488788277802801</v>
+        <v>0.99592928381702117</v>
       </c>
       <c r="AB20">
-        <v>937.22149069486488</v>
+        <v>74.629796687944193</v>
       </c>
       <c r="AD20" t="s">
         <v>272</v>
@@ -8990,10 +8990,10 @@
         <v>448</v>
       </c>
       <c r="AO20">
-        <v>0.99869874972548245</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP20">
-        <v>23.856255032822389</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR20" t="s">
         <v>272</v>
@@ -9020,16 +9020,16 @@
         <v>505</v>
       </c>
       <c r="BA20" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="BB20" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="BC20">
-        <v>0.99519319222421976</v>
+        <v>0.99272888574049079</v>
       </c>
       <c r="BD20">
-        <v>88.124809222638589</v>
+        <v>133.30376142433548</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9094,16 +9094,16 @@
         <v>295</v>
       </c>
       <c r="Y21" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="Z21" t="s">
         <v>349</v>
       </c>
       <c r="AA21">
-        <v>0.97905685820454003</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB21">
-        <v>383.95759958343297</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD21" t="s">
         <v>272</v>
@@ -9136,10 +9136,10 @@
         <v>450</v>
       </c>
       <c r="AO21">
-        <v>0.99863922747017897</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP21">
-        <v>24.947496380053089</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR21" t="s">
         <v>272</v>
@@ -9166,16 +9166,16 @@
         <v>507</v>
       </c>
       <c r="BA21" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="BB21" t="s">
-        <v>365</v>
+        <v>591</v>
       </c>
       <c r="BC21">
-        <v>0.98605307635189521</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD21">
-        <v>255.693600215255</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9240,16 +9240,16 @@
         <v>297</v>
       </c>
       <c r="Y22" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="Z22" t="s">
         <v>350</v>
       </c>
       <c r="AA22">
-        <v>0.9981032549815434</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB22">
-        <v>34.773658671704098</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD22" t="s">
         <v>272</v>
@@ -9282,10 +9282,10 @@
         <v>452</v>
       </c>
       <c r="AO22">
-        <v>0.99013353407586135</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP22">
-        <v>180.88520860920943</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR22" t="s">
         <v>272</v>
@@ -9312,16 +9312,16 @@
         <v>509</v>
       </c>
       <c r="BA22" t="s">
+        <v>592</v>
+      </c>
+      <c r="BB22" t="s">
         <v>593</v>
       </c>
-      <c r="BB22" t="s">
-        <v>594</v>
-      </c>
       <c r="BC22">
-        <v>0.88199812838352587</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD22">
-        <v>2163.367646302027</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9386,16 +9386,16 @@
         <v>299</v>
       </c>
       <c r="Y23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s">
         <v>351</v>
       </c>
       <c r="AA23">
-        <v>0.99894650606645485</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB23">
-        <v>19.314055448326833</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD23" t="s">
         <v>272</v>
@@ -9428,10 +9428,10 @@
         <v>454</v>
       </c>
       <c r="AO23">
-        <v>0.99869589057011365</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP23">
-        <v>23.908672881248773</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR23" t="s">
         <v>272</v>
@@ -9458,16 +9458,16 @@
         <v>511</v>
       </c>
       <c r="BA23" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="BB23" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="BC23">
-        <v>0.96140381292129873</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD23">
-        <v>707.59676310952364</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9532,16 +9532,16 @@
         <v>301</v>
       </c>
       <c r="Y24" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s">
         <v>352</v>
       </c>
       <c r="AA24">
-        <v>0.96340341594909085</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB24">
-        <v>670.93737426666792</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD24" t="s">
         <v>272</v>
@@ -9571,13 +9571,13 @@
         <v>455</v>
       </c>
       <c r="AN24" t="s">
-        <v>456</v>
+        <v>350</v>
       </c>
       <c r="AO24">
-        <v>0.99710631799330929</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP24">
-        <v>53.050836789329388</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR24" t="s">
         <v>272</v>
@@ -9604,16 +9604,16 @@
         <v>513</v>
       </c>
       <c r="BA24" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="BB24" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="BC24">
-        <v>0.99490784156958001</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD24">
-        <v>93.356237891033686</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9678,16 +9678,16 @@
         <v>303</v>
       </c>
       <c r="Y25" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Z25" t="s">
         <v>353</v>
       </c>
       <c r="AA25">
-        <v>0.99838604658336239</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB25">
-        <v>29.589145971689483</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD25" t="s">
         <v>272</v>
@@ -9714,16 +9714,16 @@
         <v>396</v>
       </c>
       <c r="AM25" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AN25" t="s">
-        <v>458</v>
+        <v>343</v>
       </c>
       <c r="AO25">
-        <v>0.99627181657233566</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP25">
-        <v>68.350029507179471</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR25" t="s">
         <v>272</v>
@@ -9750,16 +9750,16 @@
         <v>515</v>
       </c>
       <c r="BA25" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="BB25" t="s">
-        <v>347</v>
+        <v>597</v>
       </c>
       <c r="BC25">
-        <v>0.97902641975794957</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD25">
-        <v>384.51563777092457</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9824,16 +9824,16 @@
         <v>305</v>
       </c>
       <c r="Y26" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="Z26" t="s">
         <v>354</v>
       </c>
       <c r="AA26">
-        <v>0.99856748800713691</v>
+        <v>0.99866775225229476</v>
       </c>
       <c r="AB26">
-        <v>26.26271986915707</v>
+        <v>24.424542041262942</v>
       </c>
       <c r="AD26" t="s">
         <v>272</v>
@@ -9860,16 +9860,16 @@
         <v>398</v>
       </c>
       <c r="AM26" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AN26" t="s">
-        <v>460</v>
+        <v>341</v>
       </c>
       <c r="AO26">
-        <v>0.99550555557680764</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP26">
-        <v>82.398147758527074</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR26" t="s">
         <v>272</v>
@@ -9896,16 +9896,16 @@
         <v>517</v>
       </c>
       <c r="BA26" t="s">
+        <v>598</v>
+      </c>
+      <c r="BB26" t="s">
         <v>599</v>
       </c>
-      <c r="BB26" t="s">
-        <v>600</v>
-      </c>
       <c r="BC26">
-        <v>0.99302778580016682</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD26">
-        <v>127.82392699694152</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9970,16 +9970,16 @@
         <v>307</v>
       </c>
       <c r="Y27" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="Z27" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AA27">
-        <v>0.94069903208664407</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB27">
-        <v>1087.1844117448593</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD27" t="s">
         <v>272</v>
@@ -10006,16 +10006,16 @@
         <v>400</v>
       </c>
       <c r="AM27" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AN27" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AO27">
-        <v>0.93896180472603763</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP27">
-        <v>1119.0335800226442</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR27" t="s">
         <v>272</v>
@@ -10042,16 +10042,16 @@
         <v>519</v>
       </c>
       <c r="BA27" t="s">
+        <v>600</v>
+      </c>
+      <c r="BB27" t="s">
         <v>601</v>
       </c>
-      <c r="BB27" t="s">
-        <v>349</v>
-      </c>
       <c r="BC27">
-        <v>0.98180592470173533</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD27">
-        <v>333.55804713485287</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10116,16 +10116,16 @@
         <v>309</v>
       </c>
       <c r="Y28" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="Z28" t="s">
         <v>355</v>
       </c>
       <c r="AA28">
-        <v>0.99900168239190124</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB28">
-        <v>18.302489481810518</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD28" t="s">
         <v>272</v>
@@ -10152,16 +10152,16 @@
         <v>402</v>
       </c>
       <c r="AM28" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AN28" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AO28">
-        <v>0.99870022163576544</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP28">
-        <v>23.829270010966344</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR28" t="s">
         <v>272</v>
@@ -10194,10 +10194,10 @@
         <v>603</v>
       </c>
       <c r="BC28">
-        <v>0.98779966071713954</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD28">
-        <v>223.67288685244134</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10262,16 +10262,16 @@
         <v>311</v>
       </c>
       <c r="Y29" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="Z29" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="AA29">
-        <v>0.98833720780868572</v>
+        <v>0.99788758639511588</v>
       </c>
       <c r="AB29">
-        <v>213.8178568407609</v>
+        <v>38.727582756208619</v>
       </c>
       <c r="AD29" t="s">
         <v>272</v>
@@ -10298,16 +10298,16 @@
         <v>404</v>
       </c>
       <c r="AM29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AN29" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AO29">
-        <v>0.99807466477127271</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP29">
-        <v>35.297812526667357</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR29" t="s">
         <v>272</v>
@@ -10337,13 +10337,13 @@
         <v>604</v>
       </c>
       <c r="BB29" t="s">
-        <v>605</v>
+        <v>347</v>
       </c>
       <c r="BC29">
-        <v>0.99681267676383467</v>
+        <v>0.98605307635189521</v>
       </c>
       <c r="BD29">
-        <v>58.434259329697142</v>
+        <v>255.693600215255</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10408,16 +10408,16 @@
         <v>313</v>
       </c>
       <c r="Y30" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="Z30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA30">
-        <v>0.9982812149336332</v>
+        <v>0.99841742239430997</v>
       </c>
       <c r="AB30">
-        <v>31.51105955005805</v>
+        <v>29.013922770983669</v>
       </c>
       <c r="AD30" t="s">
         <v>272</v>
@@ -10444,16 +10444,16 @@
         <v>406</v>
       </c>
       <c r="AM30" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AN30" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AO30">
-        <v>0.99762356494824644</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP30">
-        <v>43.567975948815601</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR30" t="s">
         <v>272</v>
@@ -10480,16 +10480,16 @@
         <v>525</v>
       </c>
       <c r="BA30" t="s">
+        <v>605</v>
+      </c>
+      <c r="BB30" t="s">
         <v>606</v>
       </c>
-      <c r="BB30" t="s">
-        <v>607</v>
-      </c>
       <c r="BC30">
-        <v>0.99366677237144974</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD30">
-        <v>116.10917319008783</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10554,16 +10554,16 @@
         <v>315</v>
       </c>
       <c r="Y31" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="Z31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA31">
-        <v>0.99782703065964284</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB31">
-        <v>39.837771239882208</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD31" t="s">
         <v>272</v>
@@ -10590,16 +10590,16 @@
         <v>408</v>
       </c>
       <c r="AM31" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AN31" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AO31">
-        <v>0.99669176136177262</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP31">
-        <v>60.651041700835236</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR31" t="s">
         <v>272</v>
@@ -10626,16 +10626,16 @@
         <v>527</v>
       </c>
       <c r="BA31" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="BB31" t="s">
-        <v>609</v>
+        <v>341</v>
       </c>
       <c r="BC31">
-        <v>0.99623532634854861</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD31">
-        <v>69.01901694327529</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10700,16 +10700,16 @@
         <v>317</v>
       </c>
       <c r="Y32" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="Z32" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA32">
-        <v>0.99592928381702117</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB32">
-        <v>74.629796687944193</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD32" t="s">
         <v>272</v>
@@ -10736,16 +10736,16 @@
         <v>410</v>
       </c>
       <c r="AM32" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AN32" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="AO32">
-        <v>0.99192535126433146</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP32">
-        <v>148.0352268205892</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR32" t="s">
         <v>272</v>
@@ -10772,16 +10772,16 @@
         <v>529</v>
       </c>
       <c r="BA32" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="BB32" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="BC32">
-        <v>0.99895994357772033</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD32">
-        <v>19.067701075126294</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10846,16 +10846,16 @@
         <v>319</v>
       </c>
       <c r="Y33" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="Z33" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA33">
-        <v>0.99726055556014181</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB33">
-        <v>50.223148064066145</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD33" t="s">
         <v>272</v>
@@ -10882,16 +10882,16 @@
         <v>412</v>
       </c>
       <c r="AM33" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AN33" t="s">
-        <v>349</v>
+        <v>470</v>
       </c>
       <c r="AO33">
-        <v>0.98092693557487454</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP33">
-        <v>349.67284779396647</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR33" t="s">
         <v>272</v>
@@ -10918,16 +10918,16 @@
         <v>531</v>
       </c>
       <c r="BA33" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="BB33" t="s">
-        <v>613</v>
+        <v>360</v>
       </c>
       <c r="BC33">
-        <v>0.99015836110796274</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD33">
-        <v>180.43004635401576</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -10992,16 +10992,16 @@
         <v>321</v>
       </c>
       <c r="Y34" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="Z34" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="AA34">
-        <v>0.98968917222400854</v>
+        <v>0.96340341594909085</v>
       </c>
       <c r="AB34">
-        <v>189.03184255984442</v>
+        <v>670.93737426666792</v>
       </c>
       <c r="AD34" t="s">
         <v>272</v>
@@ -11028,16 +11028,16 @@
         <v>414</v>
       </c>
       <c r="AM34" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AN34" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AO34">
-        <v>0.99811838305018963</v>
+        <v>0.99627181657233566</v>
       </c>
       <c r="AP34">
-        <v>34.496310746523356</v>
+        <v>68.350029507179471</v>
       </c>
       <c r="AR34" t="s">
         <v>272</v>
@@ -11064,16 +11064,16 @@
         <v>533</v>
       </c>
       <c r="BA34" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="BB34" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="BC34">
-        <v>0.97803702976044449</v>
+        <v>0.99220908762204307</v>
       </c>
       <c r="BD34">
-        <v>402.65445439185123</v>
+        <v>142.83339359587785</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11138,16 +11138,16 @@
         <v>323</v>
       </c>
       <c r="Y35" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Z35" t="s">
         <v>361</v>
       </c>
       <c r="AA35">
-        <v>0.99850557699173803</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB35">
-        <v>27.397755151469518</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD35" t="s">
         <v>272</v>
@@ -11174,16 +11174,16 @@
         <v>416</v>
       </c>
       <c r="AM35" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AN35" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AO35">
-        <v>0.9985928182686985</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP35">
-        <v>25.798331740528162</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR35" t="s">
         <v>272</v>
@@ -11210,16 +11210,16 @@
         <v>535</v>
       </c>
       <c r="BA35" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="BB35" t="s">
-        <v>434</v>
+        <v>341</v>
       </c>
       <c r="BC35">
-        <v>0.95726256957223688</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD35">
-        <v>783.51955784232393</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11284,16 +11284,16 @@
         <v>325</v>
       </c>
       <c r="Y36" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Z36" t="s">
         <v>362</v>
       </c>
       <c r="AA36">
-        <v>0.99866775225229476</v>
+        <v>0.99756610784588629</v>
       </c>
       <c r="AB36">
-        <v>24.424542041262942</v>
+        <v>44.621356158751233</v>
       </c>
       <c r="AD36" t="s">
         <v>272</v>
@@ -11320,16 +11320,16 @@
         <v>418</v>
       </c>
       <c r="AM36" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AN36" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AO36">
-        <v>0.99771335854027388</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP36">
-        <v>41.921760094978509</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR36" t="s">
         <v>272</v>
@@ -11356,16 +11356,16 @@
         <v>537</v>
       </c>
       <c r="BA36" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="BB36" t="s">
-        <v>352</v>
+        <v>615</v>
       </c>
       <c r="BC36">
-        <v>0.934538160869965</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD36">
-        <v>1200.1337173839754</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11430,16 +11430,16 @@
         <v>327</v>
       </c>
       <c r="Y37" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="Z37" t="s">
         <v>363</v>
       </c>
       <c r="AA37">
-        <v>0.99864010607905451</v>
+        <v>0.99636728996375623</v>
       </c>
       <c r="AB37">
-        <v>24.931388550667378</v>
+        <v>66.599683997802714</v>
       </c>
       <c r="AD37" t="s">
         <v>272</v>
@@ -11466,16 +11466,16 @@
         <v>420</v>
       </c>
       <c r="AM37" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AN37" t="s">
-        <v>365</v>
+        <v>478</v>
       </c>
       <c r="AO37">
-        <v>0.98814178187791379</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP37">
-        <v>217.40066557158059</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR37" t="s">
         <v>272</v>
@@ -11502,16 +11502,16 @@
         <v>539</v>
       </c>
       <c r="BA37" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="BB37" t="s">
-        <v>352</v>
+        <v>617</v>
       </c>
       <c r="BC37">
-        <v>0.94616153753972931</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD37">
-        <v>987.03847843829612</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11576,16 +11576,16 @@
         <v>329</v>
       </c>
       <c r="Y38" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="Z38" t="s">
         <v>364</v>
       </c>
       <c r="AA38">
-        <v>0.99706930328635524</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB38">
-        <v>53.729439750153354</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD38" t="s">
         <v>272</v>
@@ -11612,16 +11612,16 @@
         <v>422</v>
       </c>
       <c r="AM38" t="s">
+        <v>479</v>
+      </c>
+      <c r="AN38" t="s">
         <v>480</v>
       </c>
-      <c r="AN38" t="s">
-        <v>481</v>
-      </c>
       <c r="AO38">
-        <v>0.99682717865030179</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP38">
-        <v>58.168391411134159</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR38" t="s">
         <v>272</v>
@@ -11648,16 +11648,16 @@
         <v>541</v>
       </c>
       <c r="BA38" t="s">
+        <v>618</v>
+      </c>
+      <c r="BB38" t="s">
         <v>619</v>
       </c>
-      <c r="BB38" t="s">
-        <v>352</v>
-      </c>
       <c r="BC38">
-        <v>0.97218956380622079</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD38">
-        <v>509.85799688595205</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11722,16 +11722,16 @@
         <v>331</v>
       </c>
       <c r="Y39" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="Z39" t="s">
         <v>365</v>
       </c>
       <c r="AA39">
-        <v>0.99116451092312863</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB39">
-        <v>161.98396640930775</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD39" t="s">
         <v>272</v>
@@ -11758,16 +11758,16 @@
         <v>424</v>
       </c>
       <c r="AM39" t="s">
+        <v>481</v>
+      </c>
+      <c r="AN39" t="s">
         <v>482</v>
       </c>
-      <c r="AN39" t="s">
-        <v>483</v>
-      </c>
       <c r="AO39">
-        <v>0.99827635377245738</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP39">
-        <v>31.600180838280902</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR39" t="s">
         <v>272</v>
@@ -11800,10 +11800,10 @@
         <v>621</v>
       </c>
       <c r="BC39">
-        <v>0.99272888574049079</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD39">
-        <v>133.30376142433548</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11868,16 +11868,16 @@
         <v>333</v>
       </c>
       <c r="Y40" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Z40" t="s">
         <v>366</v>
       </c>
       <c r="AA40">
-        <v>0.99756610784588629</v>
+        <v>0.99809153006866247</v>
       </c>
       <c r="AB40">
-        <v>44.621356158751233</v>
+        <v>34.98861540785537</v>
       </c>
       <c r="AD40" t="s">
         <v>272</v>
@@ -11904,16 +11904,16 @@
         <v>426</v>
       </c>
       <c r="AM40" t="s">
+        <v>483</v>
+      </c>
+      <c r="AN40" t="s">
         <v>484</v>
       </c>
-      <c r="AN40" t="s">
-        <v>349</v>
-      </c>
       <c r="AO40">
-        <v>0.98949004263841422</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP40">
-        <v>192.68255162907312</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR40" t="s">
         <v>272</v>
@@ -11946,10 +11946,10 @@
         <v>623</v>
       </c>
       <c r="BC40">
-        <v>0.99662747375050009</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD40">
-        <v>61.829647907498845</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12014,16 +12014,16 @@
         <v>335</v>
       </c>
       <c r="Y41" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="Z41" t="s">
         <v>367</v>
       </c>
       <c r="AA41">
-        <v>0.99636728996375623</v>
+        <v>0.99323944641370343</v>
       </c>
       <c r="AB41">
-        <v>66.599683997802714</v>
+        <v>123.94348241543759</v>
       </c>
       <c r="AD41" t="s">
         <v>272</v>
@@ -12056,10 +12056,10 @@
         <v>486</v>
       </c>
       <c r="AO41">
-        <v>0.99686124252542985</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP41">
-        <v>57.543887033786262</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR41" t="s">
         <v>272</v>
@@ -12092,10 +12092,10 @@
         <v>625</v>
       </c>
       <c r="BC41">
-        <v>0.99637036284424008</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD41">
-        <v>66.543347855598327</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12130,10 +12130,10 @@
         <v>627</v>
       </c>
       <c r="BC42">
-        <v>0.99220908762204307</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD42">
-        <v>142.83339359587785</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12165,13 +12165,13 @@
         <v>628</v>
       </c>
       <c r="BB43" t="s">
-        <v>352</v>
+        <v>629</v>
       </c>
       <c r="BC43">
-        <v>0.97591598065988894</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD43">
-        <v>441.54035456870389</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12200,16 +12200,16 @@
         <v>553</v>
       </c>
       <c r="BA44" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="BB44" t="s">
-        <v>630</v>
+        <v>341</v>
       </c>
       <c r="BC44">
-        <v>0.99412039195829205</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD44">
-        <v>107.79281409797902</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12244,10 +12244,10 @@
         <v>632</v>
       </c>
       <c r="BC45">
-        <v>0.98881218539944515</v>
+        <v>0.98627205860840139</v>
       </c>
       <c r="BD45">
-        <v>205.10993434350485</v>
+        <v>251.67892551264018</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12282,10 +12282,10 @@
         <v>634</v>
       </c>
       <c r="BC46">
-        <v>0.99114508565756532</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD46">
-        <v>162.34009627796874</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12317,13 +12317,13 @@
         <v>635</v>
       </c>
       <c r="BB47" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="BC47">
-        <v>0.99561586640696276</v>
+        <v>0.99547930517021377</v>
       </c>
       <c r="BD47">
-        <v>80.375782539015233</v>
+        <v>82.879405212747869</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12352,16 +12352,16 @@
         <v>561</v>
       </c>
       <c r="BA48" t="s">
+        <v>636</v>
+      </c>
+      <c r="BB48" t="s">
         <v>637</v>
       </c>
-      <c r="BB48" t="s">
-        <v>365</v>
-      </c>
       <c r="BC48">
-        <v>0.98235584693125277</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD48">
-        <v>323.47613959369914</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12393,13 +12393,13 @@
         <v>638</v>
       </c>
       <c r="BB49" t="s">
-        <v>353</v>
+        <v>639</v>
       </c>
       <c r="BC49">
-        <v>0.99536692897647694</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD49">
-        <v>84.939635431255269</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12428,16 +12428,16 @@
         <v>565</v>
       </c>
       <c r="BA50" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="BB50" t="s">
-        <v>578</v>
+        <v>347</v>
       </c>
       <c r="BC50">
-        <v>0.93089405249526469</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD50">
-        <v>1266.9423709201483</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12466,16 +12466,16 @@
         <v>567</v>
       </c>
       <c r="BA51" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB51" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="BC51">
-        <v>0.99234935324205875</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD51">
-        <v>140.26185722892211</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12504,16 +12504,16 @@
         <v>569</v>
       </c>
       <c r="BA52" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BB52" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="BC52">
-        <v>0.9205295464439136</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD52">
-        <v>1456.9583151949184</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12542,16 +12542,16 @@
         <v>571</v>
       </c>
       <c r="BA53" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="BB53" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="BC53">
-        <v>0.98822137145239475</v>
+        <v>0.99895994357772033</v>
       </c>
       <c r="BD53">
-        <v>215.94152337276336</v>
+        <v>19.067701075126294</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12580,16 +12580,16 @@
         <v>573</v>
       </c>
       <c r="BA54" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="BB54" t="s">
-        <v>647</v>
+        <v>459</v>
       </c>
       <c r="BC54">
-        <v>0.99284590877035406</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD54">
-        <v>131.158339210175</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
   </sheetData>
@@ -12598,7 +12598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C7FEF9-605A-44A4-9C7F-294606135449}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C218208C-CD4D-42B6-A4F5-A8562FD85B9E}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12710,7 +12710,7 @@
         <v>648</v>
       </c>
       <c r="K11" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12743,7 +12743,7 @@
         <v>710</v>
       </c>
       <c r="X11" t="s">
-        <v>617</v>
+        <v>585</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12778,7 +12778,7 @@
         <v>650</v>
       </c>
       <c r="K12" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12811,7 +12811,7 @@
         <v>712</v>
       </c>
       <c r="X12" t="s">
-        <v>618</v>
+        <v>586</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12846,7 +12846,7 @@
         <v>652</v>
       </c>
       <c r="K13" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -12879,7 +12879,7 @@
         <v>714</v>
       </c>
       <c r="X13" t="s">
-        <v>619</v>
+        <v>587</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12914,7 +12914,7 @@
         <v>654</v>
       </c>
       <c r="K14" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -12947,7 +12947,7 @@
         <v>716</v>
       </c>
       <c r="X14" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12982,7 +12982,7 @@
         <v>656</v>
       </c>
       <c r="K15" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13015,7 +13015,7 @@
         <v>718</v>
       </c>
       <c r="X15" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13050,7 +13050,7 @@
         <v>658</v>
       </c>
       <c r="K16" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13083,7 +13083,7 @@
         <v>720</v>
       </c>
       <c r="X16" t="s">
-        <v>582</v>
+        <v>630</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13118,7 +13118,7 @@
         <v>660</v>
       </c>
       <c r="K17" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13151,7 +13151,7 @@
         <v>722</v>
       </c>
       <c r="X17" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13186,7 +13186,7 @@
         <v>662</v>
       </c>
       <c r="K18" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13219,7 +13219,7 @@
         <v>724</v>
       </c>
       <c r="X18" t="s">
-        <v>622</v>
+        <v>590</v>
       </c>
       <c r="Y18">
         <v>28.478249999999999</v>
@@ -13254,7 +13254,7 @@
         <v>664</v>
       </c>
       <c r="K19" t="s">
-        <v>473</v>
+        <v>430</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13287,7 +13287,7 @@
         <v>726</v>
       </c>
       <c r="X19" t="s">
-        <v>638</v>
+        <v>594</v>
       </c>
       <c r="Y19">
         <v>22.079249999999998</v>
@@ -13322,7 +13322,7 @@
         <v>666</v>
       </c>
       <c r="K20" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13355,7 +13355,7 @@
         <v>728</v>
       </c>
       <c r="X20" t="s">
-        <v>606</v>
+        <v>641</v>
       </c>
       <c r="Y20">
         <v>29.961749999999999</v>
@@ -13390,7 +13390,7 @@
         <v>668</v>
       </c>
       <c r="K21" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13423,7 +13423,7 @@
         <v>730</v>
       </c>
       <c r="X21" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13458,7 +13458,7 @@
         <v>670</v>
       </c>
       <c r="K22" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13491,7 +13491,7 @@
         <v>732</v>
       </c>
       <c r="X22" t="s">
-        <v>620</v>
+        <v>588</v>
       </c>
       <c r="Y22">
         <v>82.576499999999996</v>
@@ -13526,7 +13526,7 @@
         <v>672</v>
       </c>
       <c r="K23" t="s">
-        <v>449</v>
+        <v>485</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13559,7 +13559,7 @@
         <v>734</v>
       </c>
       <c r="X23" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13594,7 +13594,7 @@
         <v>674</v>
       </c>
       <c r="K24" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13627,7 +13627,7 @@
         <v>736</v>
       </c>
       <c r="X24" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="Y24">
         <v>75.512249999999995</v>
@@ -13662,7 +13662,7 @@
         <v>676</v>
       </c>
       <c r="K25" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13695,7 +13695,7 @@
         <v>738</v>
       </c>
       <c r="X25" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="Y25">
         <v>28.239750000000001</v>
@@ -13730,7 +13730,7 @@
         <v>678</v>
       </c>
       <c r="K26" t="s">
-        <v>430</v>
+        <v>477</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13763,7 +13763,7 @@
         <v>740</v>
       </c>
       <c r="X26" t="s">
-        <v>610</v>
+        <v>645</v>
       </c>
       <c r="Y26">
         <v>1.9132499999999999</v>
@@ -13798,7 +13798,7 @@
         <v>680</v>
       </c>
       <c r="K27" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -13831,7 +13831,7 @@
         <v>742</v>
       </c>
       <c r="X27" t="s">
-        <v>585</v>
+        <v>633</v>
       </c>
       <c r="Y27">
         <v>63.731250000000003</v>
@@ -13866,7 +13866,7 @@
         <v>682</v>
       </c>
       <c r="K28" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -13899,7 +13899,7 @@
         <v>744</v>
       </c>
       <c r="X28" t="s">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="Y28">
         <v>38.451000000000001</v>
@@ -13934,7 +13934,7 @@
         <v>684</v>
       </c>
       <c r="K29" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -13967,7 +13967,7 @@
         <v>746</v>
       </c>
       <c r="X29" t="s">
-        <v>583</v>
+        <v>631</v>
       </c>
       <c r="Y29">
         <v>64.533749999999998</v>
@@ -14002,7 +14002,7 @@
         <v>686</v>
       </c>
       <c r="K30" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14035,7 +14035,7 @@
         <v>748</v>
       </c>
       <c r="X30" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="Y30">
         <v>44.370750000000001</v>
@@ -14070,7 +14070,7 @@
         <v>688</v>
       </c>
       <c r="K31" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14103,7 +14103,7 @@
         <v>750</v>
       </c>
       <c r="X31" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="Y31">
         <v>38.15925</v>
@@ -14138,7 +14138,7 @@
         <v>690</v>
       </c>
       <c r="K32" t="s">
-        <v>475</v>
+        <v>432</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14171,7 +14171,7 @@
         <v>752</v>
       </c>
       <c r="X32" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="Y32">
         <v>3.38625</v>
@@ -14206,7 +14206,7 @@
         <v>692</v>
       </c>
       <c r="K33" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14239,7 +14239,7 @@
         <v>754</v>
       </c>
       <c r="X33" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="Y33">
         <v>30.597750000000001</v>
@@ -14274,7 +14274,7 @@
         <v>694</v>
       </c>
       <c r="K34" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14307,7 +14307,7 @@
         <v>756</v>
       </c>
       <c r="X34" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14342,7 +14342,7 @@
         <v>696</v>
       </c>
       <c r="K35" t="s">
-        <v>477</v>
+        <v>434</v>
       </c>
       <c r="L35">
         <v>44.894334115294185</v>
@@ -14375,7 +14375,7 @@
         <v>758</v>
       </c>
       <c r="X35" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="Y35">
         <v>58.474499999999999</v>
@@ -14410,7 +14410,7 @@
         <v>698</v>
       </c>
       <c r="K36" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="L36">
         <v>14.358494358107757</v>
@@ -14443,7 +14443,7 @@
         <v>760</v>
       </c>
       <c r="X36" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="Y36">
         <v>18.711749999999999</v>
@@ -14478,7 +14478,7 @@
         <v>700</v>
       </c>
       <c r="K37" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14511,7 +14511,7 @@
         <v>762</v>
       </c>
       <c r="X37" t="s">
-        <v>624</v>
+        <v>592</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14546,7 +14546,7 @@
         <v>702</v>
       </c>
       <c r="K38" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14579,7 +14579,7 @@
         <v>764</v>
       </c>
       <c r="X38" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14614,7 +14614,7 @@
         <v>704</v>
       </c>
       <c r="K39" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14647,7 +14647,7 @@
         <v>766</v>
       </c>
       <c r="X39" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14682,7 +14682,7 @@
         <v>706</v>
       </c>
       <c r="K40" t="s">
-        <v>479</v>
+        <v>436</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14715,7 +14715,7 @@
         <v>768</v>
       </c>
       <c r="X40" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14750,7 +14750,7 @@
         <v>708</v>
       </c>
       <c r="K41" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14783,7 +14783,7 @@
         <v>770</v>
       </c>
       <c r="X41" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14853,7 +14853,7 @@
         <v>774</v>
       </c>
       <c r="X43" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14923,7 +14923,7 @@
         <v>778</v>
       </c>
       <c r="X45" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14958,7 +14958,7 @@
         <v>780</v>
       </c>
       <c r="X46" t="s">
-        <v>639</v>
+        <v>595</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14993,7 +14993,7 @@
         <v>782</v>
       </c>
       <c r="X47" t="s">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -15063,7 +15063,7 @@
         <v>786</v>
       </c>
       <c r="X49" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="Y49">
         <v>16.497</v>
@@ -15098,7 +15098,7 @@
         <v>788</v>
       </c>
       <c r="X50" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15133,7 +15133,7 @@
         <v>790</v>
       </c>
       <c r="X51" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15168,7 +15168,7 @@
         <v>792</v>
       </c>
       <c r="X52" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15238,7 +15238,7 @@
         <v>796</v>
       </c>
       <c r="X54" t="s">
-        <v>608</v>
+        <v>643</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15253,7 +15253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7925130-F1BE-4AB5-87DF-0DBDE148EA26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122393BE-ABF0-409E-B923-32B20B73E95E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17070,7 +17070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83EE9BD1-C4BA-4A24-B7B7-C7F927D1F4FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15EB3827-7995-4E62-BC93-B8B4E6FB313E}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE8AF64-5B0F-4EF4-956D-87CA7AE9B3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6F3BBEF-DA8F-4839-BC60-0F810763EB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,40 +949,172 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_030</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_solelc_spv_023</t>
@@ -991,52 +1123,10 @@
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_solelc_spv_012</t>
@@ -1051,142 +1141,91 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
     <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
   </si>
   <si>
     <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
+    <t>e_JP306-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
     <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
   </si>
   <si>
-    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
   </si>
   <si>
     <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
@@ -1195,43 +1234,82 @@
     <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
   </si>
   <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wonelc_won_009</t>
@@ -1258,12 +1336,6 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_011</t>
   </si>
   <si>
@@ -1276,22 +1348,40 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wonelc_won_017</t>
@@ -1312,6 +1402,12 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_028</t>
   </si>
   <si>
@@ -1324,100 +1420,76 @@
     <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
   </si>
   <si>
     <t>elc_won_009</t>
@@ -1441,12 +1513,6 @@
     <t>elc_won_030</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
-  </si>
-  <si>
     <t>elc_won_011</t>
   </si>
   <si>
@@ -1459,22 +1525,40 @@
     <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
   </si>
   <si>
     <t>elc_won_017</t>
@@ -1495,100 +1579,244 @@
     <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
   </si>
   <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
     <t>elc_won_028</t>
   </si>
   <si>
     <t>elc_won_031</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_032</t>
@@ -1615,168 +1843,6 @@
     <t>connecting wind offshore to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_011</t>
   </si>
   <si>
@@ -1789,70 +1855,193 @@
     <t>connecting wind offshore to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
   </si>
   <si>
     <t>elc_wof_032</t>
@@ -1864,9 +2053,6 @@
     <t>elc_wof_038</t>
   </si>
   <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
     <t>elc_wof_034</t>
   </si>
   <si>
@@ -1876,138 +2062,6 @@
     <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
   </si>
   <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
     <t>elc_wof_011</t>
   </si>
   <si>
@@ -2018,60 +2072,6 @@
   </si>
   <si>
     <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7396,7 +7396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F73964C-B005-4C75-8B79-A49358225FE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC1FD7C-FCEC-47DC-87AE-356E3DF741DF}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7634,16 +7634,16 @@
         <v>273</v>
       </c>
       <c r="Y11" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Z11" t="s">
         <v>339</v>
       </c>
       <c r="AA11">
-        <v>0.9982812149336332</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB11">
-        <v>31.51105955005805</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD11" t="s">
         <v>272</v>
@@ -7676,10 +7676,10 @@
         <v>431</v>
       </c>
       <c r="AO11">
-        <v>0.99811838305018963</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP11">
-        <v>34.496310746523356</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR11" t="s">
         <v>272</v>
@@ -7709,13 +7709,13 @@
         <v>575</v>
       </c>
       <c r="BB11" t="s">
-        <v>576</v>
+        <v>345</v>
       </c>
       <c r="BC11">
-        <v>0.99603667376986049</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD11">
-        <v>72.660980885890424</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7780,16 +7780,16 @@
         <v>277</v>
       </c>
       <c r="Y12" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="Z12" t="s">
         <v>340</v>
       </c>
       <c r="AA12">
-        <v>0.99782703065964284</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB12">
-        <v>39.837771239882208</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD12" t="s">
         <v>272</v>
@@ -7822,10 +7822,10 @@
         <v>433</v>
       </c>
       <c r="AO12">
-        <v>0.9985928182686985</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP12">
-        <v>25.798331740528162</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR12" t="s">
         <v>272</v>
@@ -7852,16 +7852,16 @@
         <v>489</v>
       </c>
       <c r="BA12" t="s">
+        <v>576</v>
+      </c>
+      <c r="BB12" t="s">
         <v>577</v>
       </c>
-      <c r="BB12" t="s">
-        <v>578</v>
-      </c>
       <c r="BC12">
-        <v>0.97589985979527272</v>
+        <v>0.98627205860840139</v>
       </c>
       <c r="BD12">
-        <v>441.83590375333313</v>
+        <v>251.67892551264018</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7926,16 +7926,16 @@
         <v>279</v>
       </c>
       <c r="Y13" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="Z13" t="s">
         <v>341</v>
       </c>
       <c r="AA13">
-        <v>0.94069903208664407</v>
+        <v>0.9975431479552237</v>
       </c>
       <c r="AB13">
-        <v>1087.1844117448593</v>
+        <v>45.042287487565297</v>
       </c>
       <c r="AD13" t="s">
         <v>272</v>
@@ -7965,13 +7965,13 @@
         <v>434</v>
       </c>
       <c r="AN13" t="s">
-        <v>435</v>
+        <v>345</v>
       </c>
       <c r="AO13">
-        <v>0.99771335854027388</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP13">
-        <v>41.921760094978509</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR13" t="s">
         <v>272</v>
@@ -7998,16 +7998,16 @@
         <v>491</v>
       </c>
       <c r="BA13" t="s">
+        <v>578</v>
+      </c>
+      <c r="BB13" t="s">
         <v>579</v>
       </c>
-      <c r="BB13" t="s">
-        <v>476</v>
-      </c>
       <c r="BC13">
-        <v>0.9437657388784082</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD13">
-        <v>1030.9614538958492</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8072,16 +8072,16 @@
         <v>281</v>
       </c>
       <c r="Y14" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="Z14" t="s">
         <v>342</v>
       </c>
       <c r="AA14">
-        <v>0.99900168239190124</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB14">
-        <v>18.302489481810518</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD14" t="s">
         <v>272</v>
@@ -8108,16 +8108,16 @@
         <v>374</v>
       </c>
       <c r="AM14" t="s">
+        <v>435</v>
+      </c>
+      <c r="AN14" t="s">
         <v>436</v>
       </c>
-      <c r="AN14" t="s">
-        <v>347</v>
-      </c>
       <c r="AO14">
-        <v>0.98814178187791379</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP14">
-        <v>217.40066557158059</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR14" t="s">
         <v>272</v>
@@ -8147,13 +8147,13 @@
         <v>580</v>
       </c>
       <c r="BB14" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="BC14">
-        <v>0.99602290686668338</v>
+        <v>0.99547930517021377</v>
       </c>
       <c r="BD14">
-        <v>72.91337411080552</v>
+        <v>82.879405212747869</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8218,16 +8218,16 @@
         <v>283</v>
       </c>
       <c r="Y15" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="Z15" t="s">
         <v>343</v>
       </c>
       <c r="AA15">
-        <v>0.98833720780868572</v>
+        <v>0.9981032549815434</v>
       </c>
       <c r="AB15">
-        <v>213.8178568407609</v>
+        <v>34.773658671704098</v>
       </c>
       <c r="AD15" t="s">
         <v>272</v>
@@ -8260,10 +8260,10 @@
         <v>438</v>
       </c>
       <c r="AO15">
-        <v>0.99869874972548245</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP15">
-        <v>23.856255032822389</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR15" t="s">
         <v>272</v>
@@ -8290,16 +8290,16 @@
         <v>495</v>
       </c>
       <c r="BA15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BB15" t="s">
-        <v>583</v>
+        <v>350</v>
       </c>
       <c r="BC15">
-        <v>0.99302778580016682</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD15">
-        <v>127.82392699694152</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8364,16 +8364,16 @@
         <v>285</v>
       </c>
       <c r="Y16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z16" t="s">
         <v>344</v>
       </c>
       <c r="AA16">
-        <v>0.99856748800713691</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB16">
-        <v>26.26271986915707</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD16" t="s">
         <v>272</v>
@@ -8406,10 +8406,10 @@
         <v>440</v>
       </c>
       <c r="AO16">
-        <v>0.99870022163576544</v>
+        <v>0.99710631799330929</v>
       </c>
       <c r="AP16">
-        <v>23.829270010966344</v>
+        <v>53.050836789329388</v>
       </c>
       <c r="AR16" t="s">
         <v>272</v>
@@ -8436,16 +8436,16 @@
         <v>497</v>
       </c>
       <c r="BA16" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="BB16" t="s">
-        <v>343</v>
+        <v>583</v>
       </c>
       <c r="BC16">
-        <v>0.98180592470173533</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD16">
-        <v>333.55804713485287</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8510,16 +8510,16 @@
         <v>287</v>
       </c>
       <c r="Y17" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="Z17" t="s">
         <v>345</v>
       </c>
       <c r="AA17">
-        <v>0.99864010607905451</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB17">
-        <v>24.931388550667378</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD17" t="s">
         <v>272</v>
@@ -8552,10 +8552,10 @@
         <v>442</v>
       </c>
       <c r="AO17">
-        <v>0.99807466477127271</v>
+        <v>0.99627181657233566</v>
       </c>
       <c r="AP17">
-        <v>35.297812526667357</v>
+        <v>68.350029507179471</v>
       </c>
       <c r="AR17" t="s">
         <v>272</v>
@@ -8582,16 +8582,16 @@
         <v>499</v>
       </c>
       <c r="BA17" t="s">
+        <v>584</v>
+      </c>
+      <c r="BB17" t="s">
         <v>585</v>
       </c>
-      <c r="BB17" t="s">
-        <v>341</v>
-      </c>
       <c r="BC17">
-        <v>0.934538160869965</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD17">
-        <v>1200.1337173839754</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8656,16 +8656,16 @@
         <v>289</v>
       </c>
       <c r="Y18" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="Z18" t="s">
         <v>346</v>
       </c>
       <c r="AA18">
-        <v>0.99706930328635524</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB18">
-        <v>53.729439750153354</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD18" t="s">
         <v>272</v>
@@ -8698,10 +8698,10 @@
         <v>444</v>
       </c>
       <c r="AO18">
-        <v>0.99686124252542985</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP18">
-        <v>57.543887033786262</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR18" t="s">
         <v>272</v>
@@ -8731,13 +8731,13 @@
         <v>586</v>
       </c>
       <c r="BB18" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="BC18">
-        <v>0.94616153753972931</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD18">
-        <v>987.03847843829612</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8802,16 +8802,16 @@
         <v>291</v>
       </c>
       <c r="Y19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z19" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AA19">
-        <v>0.99116451092312863</v>
+        <v>0.98833720780868572</v>
       </c>
       <c r="AB19">
-        <v>161.98396640930775</v>
+        <v>213.8178568407609</v>
       </c>
       <c r="AD19" t="s">
         <v>272</v>
@@ -8844,10 +8844,10 @@
         <v>446</v>
       </c>
       <c r="AO19">
-        <v>0.99762356494824644</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP19">
-        <v>43.567975948815601</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR19" t="s">
         <v>272</v>
@@ -8877,13 +8877,13 @@
         <v>587</v>
       </c>
       <c r="BB19" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="BC19">
-        <v>0.97218956380622079</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD19">
-        <v>509.85799688595205</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8948,16 +8948,16 @@
         <v>293</v>
       </c>
       <c r="Y20" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="Z20" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA20">
-        <v>0.99592928381702117</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB20">
-        <v>74.629796687944193</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD20" t="s">
         <v>272</v>
@@ -8990,10 +8990,10 @@
         <v>448</v>
       </c>
       <c r="AO20">
-        <v>0.99669176136177262</v>
+        <v>0.99827635377245738</v>
       </c>
       <c r="AP20">
-        <v>60.651041700835236</v>
+        <v>31.600180838280902</v>
       </c>
       <c r="AR20" t="s">
         <v>272</v>
@@ -9023,13 +9023,13 @@
         <v>588</v>
       </c>
       <c r="BB20" t="s">
-        <v>589</v>
+        <v>345</v>
       </c>
       <c r="BC20">
-        <v>0.99272888574049079</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD20">
-        <v>133.30376142433548</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9094,16 +9094,16 @@
         <v>295</v>
       </c>
       <c r="Y21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Z21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AA21">
-        <v>0.99726055556014181</v>
+        <v>0.99782703065964284</v>
       </c>
       <c r="AB21">
-        <v>50.223148064066145</v>
+        <v>39.837771239882208</v>
       </c>
       <c r="AD21" t="s">
         <v>272</v>
@@ -9133,13 +9133,13 @@
         <v>449</v>
       </c>
       <c r="AN21" t="s">
-        <v>450</v>
+        <v>339</v>
       </c>
       <c r="AO21">
-        <v>0.99804155179341392</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP21">
-        <v>35.904883787411507</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR21" t="s">
         <v>272</v>
@@ -9166,16 +9166,16 @@
         <v>507</v>
       </c>
       <c r="BA21" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="BB21" t="s">
-        <v>591</v>
+        <v>345</v>
       </c>
       <c r="BC21">
-        <v>0.99662747375050009</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD21">
-        <v>61.829647907498845</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9240,16 +9240,16 @@
         <v>297</v>
       </c>
       <c r="Y22" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="Z22" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA22">
-        <v>0.98968917222400854</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB22">
-        <v>189.03184255984442</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD22" t="s">
         <v>272</v>
@@ -9276,16 +9276,16 @@
         <v>390</v>
       </c>
       <c r="AM22" t="s">
+        <v>450</v>
+      </c>
+      <c r="AN22" t="s">
         <v>451</v>
       </c>
-      <c r="AN22" t="s">
-        <v>452</v>
-      </c>
       <c r="AO22">
-        <v>0.99508023417818925</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP22">
-        <v>90.195706733197795</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR22" t="s">
         <v>272</v>
@@ -9312,16 +9312,16 @@
         <v>509</v>
       </c>
       <c r="BA22" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="BB22" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="BC22">
-        <v>0.99637036284424008</v>
+        <v>0.99272888574049079</v>
       </c>
       <c r="BD22">
-        <v>66.543347855598327</v>
+        <v>133.30376142433548</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9386,16 +9386,16 @@
         <v>299</v>
       </c>
       <c r="Y23" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="Z23" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AA23">
-        <v>0.9981032549815434</v>
+        <v>0.96340341594909085</v>
       </c>
       <c r="AB23">
-        <v>34.773658671704098</v>
+        <v>670.93737426666792</v>
       </c>
       <c r="AD23" t="s">
         <v>272</v>
@@ -9422,16 +9422,16 @@
         <v>392</v>
       </c>
       <c r="AM23" t="s">
+        <v>452</v>
+      </c>
+      <c r="AN23" t="s">
         <v>453</v>
       </c>
-      <c r="AN23" t="s">
-        <v>454</v>
-      </c>
       <c r="AO23">
-        <v>0.99940622505963084</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP23">
-        <v>10.885873906767051</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR23" t="s">
         <v>272</v>
@@ -9458,16 +9458,16 @@
         <v>511</v>
       </c>
       <c r="BA23" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="BB23" t="s">
-        <v>361</v>
+        <v>593</v>
       </c>
       <c r="BC23">
-        <v>0.99536692897647694</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD23">
-        <v>84.939635431255269</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9532,16 +9532,16 @@
         <v>301</v>
       </c>
       <c r="Y24" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="Z24" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AA24">
-        <v>0.99894650606645485</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB24">
-        <v>19.314055448326833</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD24" t="s">
         <v>272</v>
@@ -9568,16 +9568,16 @@
         <v>394</v>
       </c>
       <c r="AM24" t="s">
+        <v>454</v>
+      </c>
+      <c r="AN24" t="s">
         <v>455</v>
       </c>
-      <c r="AN24" t="s">
-        <v>350</v>
-      </c>
       <c r="AO24">
-        <v>0.99192535126433146</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP24">
-        <v>148.0352268205892</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR24" t="s">
         <v>272</v>
@@ -9604,16 +9604,16 @@
         <v>513</v>
       </c>
       <c r="BA24" t="s">
+        <v>594</v>
+      </c>
+      <c r="BB24" t="s">
         <v>595</v>
       </c>
-      <c r="BB24" t="s">
-        <v>578</v>
-      </c>
       <c r="BC24">
-        <v>0.93089405249526469</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD24">
-        <v>1266.9423709201483</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9678,16 +9678,16 @@
         <v>303</v>
       </c>
       <c r="Y25" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z25" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AA25">
-        <v>0.99850557699173803</v>
+        <v>0.99809153006866247</v>
       </c>
       <c r="AB25">
-        <v>27.397755151469518</v>
+        <v>34.98861540785537</v>
       </c>
       <c r="AD25" t="s">
         <v>272</v>
@@ -9717,13 +9717,13 @@
         <v>456</v>
       </c>
       <c r="AN25" t="s">
-        <v>343</v>
+        <v>457</v>
       </c>
       <c r="AO25">
-        <v>0.98092693557487454</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP25">
-        <v>349.67284779396647</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR25" t="s">
         <v>272</v>
@@ -9756,10 +9756,10 @@
         <v>597</v>
       </c>
       <c r="BC25">
-        <v>0.99015836110796274</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD25">
-        <v>180.43004635401576</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9824,16 +9824,16 @@
         <v>305</v>
       </c>
       <c r="Y26" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="Z26" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AA26">
-        <v>0.99866775225229476</v>
+        <v>0.99323944641370343</v>
       </c>
       <c r="AB26">
-        <v>24.424542041262942</v>
+        <v>123.94348241543759</v>
       </c>
       <c r="AD26" t="s">
         <v>272</v>
@@ -9860,16 +9860,16 @@
         <v>398</v>
       </c>
       <c r="AM26" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN26" t="s">
-        <v>341</v>
+        <v>459</v>
       </c>
       <c r="AO26">
-        <v>0.93717435218793788</v>
+        <v>0.99771335854027388</v>
       </c>
       <c r="AP26">
-        <v>1151.8035432211395</v>
+        <v>41.921760094978509</v>
       </c>
       <c r="AR26" t="s">
         <v>272</v>
@@ -9902,10 +9902,10 @@
         <v>599</v>
       </c>
       <c r="BC26">
-        <v>0.97803702976044449</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD26">
-        <v>402.65445439185123</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9970,16 +9970,16 @@
         <v>307</v>
       </c>
       <c r="Y27" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="Z27" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="AA27">
-        <v>0.97905685820454003</v>
+        <v>0.99592928381702117</v>
       </c>
       <c r="AB27">
-        <v>383.95759958343297</v>
+        <v>74.629796687944193</v>
       </c>
       <c r="AD27" t="s">
         <v>272</v>
@@ -10006,16 +10006,16 @@
         <v>400</v>
       </c>
       <c r="AM27" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN27" t="s">
-        <v>459</v>
+        <v>358</v>
       </c>
       <c r="AO27">
-        <v>0.96551955124232614</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP27">
-        <v>632.14156055735509</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR27" t="s">
         <v>272</v>
@@ -10116,16 +10116,16 @@
         <v>309</v>
       </c>
       <c r="Y28" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="Z28" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA28">
-        <v>0.9977500892185478</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB28">
-        <v>41.248364326622962</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD28" t="s">
         <v>272</v>
@@ -10152,16 +10152,16 @@
         <v>402</v>
       </c>
       <c r="AM28" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN28" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO28">
-        <v>0.99693456929731861</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP28">
-        <v>56.199562882493169</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR28" t="s">
         <v>272</v>
@@ -10262,16 +10262,16 @@
         <v>311</v>
       </c>
       <c r="Y29" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="Z29" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AA29">
-        <v>0.99788758639511588</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB29">
-        <v>38.727582756208619</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD29" t="s">
         <v>272</v>
@@ -10298,16 +10298,16 @@
         <v>404</v>
       </c>
       <c r="AM29" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN29" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO29">
-        <v>0.99841760060377538</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP29">
-        <v>29.010655597451841</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR29" t="s">
         <v>272</v>
@@ -10337,7 +10337,7 @@
         <v>604</v>
       </c>
       <c r="BB29" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BC29">
         <v>0.98605307635189521</v>
@@ -10408,16 +10408,16 @@
         <v>313</v>
       </c>
       <c r="Y30" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="Z30" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA30">
-        <v>0.99841742239430997</v>
+        <v>0.99864010607905451</v>
       </c>
       <c r="AB30">
-        <v>29.013922770983669</v>
+        <v>24.931388550667378</v>
       </c>
       <c r="AD30" t="s">
         <v>272</v>
@@ -10444,16 +10444,16 @@
         <v>406</v>
       </c>
       <c r="AM30" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN30" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO30">
-        <v>0.99781438034778358</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP30">
-        <v>40.069693623967019</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR30" t="s">
         <v>272</v>
@@ -10554,16 +10554,16 @@
         <v>315</v>
       </c>
       <c r="Y31" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="Z31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA31">
-        <v>0.99852430677621173</v>
+        <v>0.99706930328635524</v>
       </c>
       <c r="AB31">
-        <v>27.054375769451152</v>
+        <v>53.729439750153354</v>
       </c>
       <c r="AD31" t="s">
         <v>272</v>
@@ -10590,16 +10590,16 @@
         <v>408</v>
       </c>
       <c r="AM31" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN31" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO31">
-        <v>0.99827635377245738</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP31">
-        <v>31.600180838280902</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR31" t="s">
         <v>272</v>
@@ -10629,7 +10629,7 @@
         <v>607</v>
       </c>
       <c r="BB31" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="BC31">
         <v>0.96140381292129873</v>
@@ -10700,16 +10700,16 @@
         <v>317</v>
       </c>
       <c r="Y32" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Z32" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA32">
-        <v>0.9975431479552237</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB32">
-        <v>45.042287487565297</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD32" t="s">
         <v>272</v>
@@ -10736,16 +10736,16 @@
         <v>410</v>
       </c>
       <c r="AM32" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN32" t="s">
-        <v>343</v>
+        <v>470</v>
       </c>
       <c r="AO32">
-        <v>0.98949004263841422</v>
+        <v>0.99869589057011365</v>
       </c>
       <c r="AP32">
-        <v>192.68255162907312</v>
+        <v>23.908672881248773</v>
       </c>
       <c r="AR32" t="s">
         <v>272</v>
@@ -10846,16 +10846,16 @@
         <v>319</v>
       </c>
       <c r="Y33" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="Z33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA33">
-        <v>0.98179245618315802</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB33">
-        <v>333.80496997543548</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD33" t="s">
         <v>272</v>
@@ -10882,16 +10882,16 @@
         <v>412</v>
       </c>
       <c r="AM33" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN33" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO33">
-        <v>0.99710631799330929</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP33">
-        <v>53.050836789329388</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR33" t="s">
         <v>272</v>
@@ -10921,7 +10921,7 @@
         <v>610</v>
       </c>
       <c r="BB33" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="BC33">
         <v>0.97902641975794957</v>
@@ -10992,16 +10992,16 @@
         <v>321</v>
       </c>
       <c r="Y34" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="Z34" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="AA34">
-        <v>0.96340341594909085</v>
+        <v>0.99788758639511588</v>
       </c>
       <c r="AB34">
-        <v>670.93737426666792</v>
+        <v>38.727582756208619</v>
       </c>
       <c r="AD34" t="s">
         <v>272</v>
@@ -11028,16 +11028,16 @@
         <v>414</v>
       </c>
       <c r="AM34" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AN34" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AO34">
-        <v>0.99627181657233566</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP34">
-        <v>68.350029507179471</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR34" t="s">
         <v>272</v>
@@ -11070,10 +11070,10 @@
         <v>612</v>
       </c>
       <c r="BC34">
-        <v>0.99220908762204307</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD34">
-        <v>142.83339359587785</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11138,16 +11138,16 @@
         <v>323</v>
       </c>
       <c r="Y35" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="Z35" t="s">
         <v>361</v>
       </c>
       <c r="AA35">
-        <v>0.99838604658336239</v>
+        <v>0.99841742239430997</v>
       </c>
       <c r="AB35">
-        <v>29.589145971689483</v>
+        <v>29.013922770983669</v>
       </c>
       <c r="AD35" t="s">
         <v>272</v>
@@ -11174,16 +11174,16 @@
         <v>416</v>
       </c>
       <c r="AM35" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN35" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO35">
-        <v>0.99550555557680764</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP35">
-        <v>82.398147758527074</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR35" t="s">
         <v>272</v>
@@ -11213,13 +11213,13 @@
         <v>613</v>
       </c>
       <c r="BB35" t="s">
-        <v>341</v>
+        <v>614</v>
       </c>
       <c r="BC35">
-        <v>0.97591598065988894</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD35">
-        <v>441.54035456870389</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11320,16 +11320,16 @@
         <v>418</v>
       </c>
       <c r="AM36" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN36" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO36">
-        <v>0.93896180472603763</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP36">
-        <v>1119.0335800226442</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR36" t="s">
         <v>272</v>
@@ -11356,16 +11356,16 @@
         <v>537</v>
       </c>
       <c r="BA36" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="BB36" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="BC36">
-        <v>0.99412039195829205</v>
+        <v>0.99895994357772033</v>
       </c>
       <c r="BD36">
-        <v>107.79281409797902</v>
+        <v>19.067701075126294</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11466,16 +11466,16 @@
         <v>420</v>
       </c>
       <c r="AM37" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN37" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO37">
-        <v>0.99750949182367343</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP37">
-        <v>45.659316565986806</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR37" t="s">
         <v>272</v>
@@ -11502,16 +11502,16 @@
         <v>539</v>
       </c>
       <c r="BA37" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="BB37" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="BC37">
-        <v>0.98881218539944515</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD37">
-        <v>205.10993434350485</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11576,16 +11576,16 @@
         <v>329</v>
       </c>
       <c r="Y38" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="Z38" t="s">
         <v>364</v>
       </c>
       <c r="AA38">
-        <v>0.99391268208184824</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB38">
-        <v>111.60082849944791</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD38" t="s">
         <v>272</v>
@@ -11612,16 +11612,16 @@
         <v>422</v>
       </c>
       <c r="AM38" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AN38" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AO38">
-        <v>0.99013353407586135</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP38">
-        <v>180.88520860920943</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR38" t="s">
         <v>272</v>
@@ -11648,16 +11648,16 @@
         <v>541</v>
       </c>
       <c r="BA38" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="BB38" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="BC38">
-        <v>0.98779966071713954</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD38">
-        <v>223.67288685244134</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11758,16 +11758,16 @@
         <v>424</v>
       </c>
       <c r="AM39" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN39" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AO39">
-        <v>0.99869589057011365</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP39">
-        <v>23.908672881248773</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR39" t="s">
         <v>272</v>
@@ -11794,16 +11794,16 @@
         <v>543</v>
       </c>
       <c r="BA39" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="BB39" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="BC39">
-        <v>0.99681267676383467</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD39">
-        <v>58.434259329697142</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11868,16 +11868,16 @@
         <v>333</v>
       </c>
       <c r="Y40" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Z40" t="s">
         <v>366</v>
       </c>
       <c r="AA40">
-        <v>0.99809153006866247</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB40">
-        <v>34.98861540785537</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD40" t="s">
         <v>272</v>
@@ -11904,16 +11904,16 @@
         <v>426</v>
       </c>
       <c r="AM40" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AN40" t="s">
-        <v>484</v>
+        <v>355</v>
       </c>
       <c r="AO40">
-        <v>0.99682717865030179</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP40">
-        <v>58.168391411134159</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR40" t="s">
         <v>272</v>
@@ -11940,16 +11940,16 @@
         <v>545</v>
       </c>
       <c r="BA40" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="BB40" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="BC40">
-        <v>0.99234935324205875</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD40">
-        <v>140.26185722892211</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12014,16 +12014,16 @@
         <v>335</v>
       </c>
       <c r="Y41" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="Z41" t="s">
         <v>367</v>
       </c>
       <c r="AA41">
-        <v>0.99323944641370343</v>
+        <v>0.99866775225229476</v>
       </c>
       <c r="AB41">
-        <v>123.94348241543759</v>
+        <v>24.424542041262942</v>
       </c>
       <c r="AD41" t="s">
         <v>272</v>
@@ -12050,16 +12050,16 @@
         <v>428</v>
       </c>
       <c r="AM41" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN41" t="s">
-        <v>486</v>
+        <v>339</v>
       </c>
       <c r="AO41">
-        <v>0.99863922747017897</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP41">
-        <v>24.947496380053089</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR41" t="s">
         <v>272</v>
@@ -12086,16 +12086,16 @@
         <v>547</v>
       </c>
       <c r="BA41" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="BB41" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="BC41">
-        <v>0.9205295464439136</v>
+        <v>0.99220908762204307</v>
       </c>
       <c r="BD41">
-        <v>1456.9583151949184</v>
+        <v>142.83339359587785</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12124,16 +12124,16 @@
         <v>549</v>
       </c>
       <c r="BA42" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="BB42" t="s">
-        <v>627</v>
+        <v>345</v>
       </c>
       <c r="BC42">
-        <v>0.98822137145239475</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD42">
-        <v>215.94152337276336</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12168,10 +12168,10 @@
         <v>629</v>
       </c>
       <c r="BC43">
-        <v>0.99284590877035406</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD43">
-        <v>131.158339210175</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12203,13 +12203,13 @@
         <v>630</v>
       </c>
       <c r="BB44" t="s">
-        <v>341</v>
+        <v>631</v>
       </c>
       <c r="BC44">
-        <v>0.95957195194316591</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD44">
-        <v>741.18088104195795</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12238,16 +12238,16 @@
         <v>555</v>
       </c>
       <c r="BA45" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="BB45" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="BC45">
-        <v>0.98627205860840139</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD45">
-        <v>251.67892551264018</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12276,16 +12276,16 @@
         <v>557</v>
       </c>
       <c r="BA46" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="BB46" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="BC46">
-        <v>0.99504061303190972</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD46">
-        <v>90.922094414988095</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12314,16 +12314,16 @@
         <v>559</v>
       </c>
       <c r="BA47" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="BB47" t="s">
-        <v>632</v>
+        <v>358</v>
       </c>
       <c r="BC47">
-        <v>0.99547930517021377</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD47">
-        <v>82.879405212747869</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12352,16 +12352,16 @@
         <v>561</v>
       </c>
       <c r="BA48" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="BB48" t="s">
-        <v>637</v>
+        <v>436</v>
       </c>
       <c r="BC48">
-        <v>0.99114508565756532</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD48">
-        <v>162.34009627796874</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12396,10 +12396,10 @@
         <v>639</v>
       </c>
       <c r="BC49">
-        <v>0.99561586640696276</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD49">
-        <v>80.375782539015233</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12431,13 +12431,13 @@
         <v>640</v>
       </c>
       <c r="BB50" t="s">
-        <v>347</v>
+        <v>583</v>
       </c>
       <c r="BC50">
-        <v>0.98235584693125277</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD50">
-        <v>323.47613959369914</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12469,13 +12469,13 @@
         <v>641</v>
       </c>
       <c r="BB51" t="s">
-        <v>642</v>
+        <v>446</v>
       </c>
       <c r="BC51">
-        <v>0.99366677237144974</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD51">
-        <v>116.10917319008783</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12504,16 +12504,16 @@
         <v>569</v>
       </c>
       <c r="BA52" t="s">
+        <v>642</v>
+      </c>
+      <c r="BB52" t="s">
         <v>643</v>
       </c>
-      <c r="BB52" t="s">
-        <v>644</v>
-      </c>
       <c r="BC52">
-        <v>0.99623532634854861</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD52">
-        <v>69.01901694327529</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12542,16 +12542,16 @@
         <v>571</v>
       </c>
       <c r="BA53" t="s">
+        <v>644</v>
+      </c>
+      <c r="BB53" t="s">
         <v>645</v>
       </c>
-      <c r="BB53" t="s">
-        <v>646</v>
-      </c>
       <c r="BC53">
-        <v>0.99895994357772033</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD53">
-        <v>19.067701075126294</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12580,16 +12580,16 @@
         <v>573</v>
       </c>
       <c r="BA54" t="s">
+        <v>646</v>
+      </c>
+      <c r="BB54" t="s">
         <v>647</v>
       </c>
-      <c r="BB54" t="s">
-        <v>459</v>
-      </c>
       <c r="BC54">
-        <v>0.95726256957223688</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD54">
-        <v>783.51955784232393</v>
+        <v>131.158339210175</v>
       </c>
     </row>
   </sheetData>
@@ -12598,7 +12598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C218208C-CD4D-42B6-A4F5-A8562FD85B9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E16207-4280-4960-B7A6-FFEABF17BBB8}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12710,7 +12710,7 @@
         <v>648</v>
       </c>
       <c r="K11" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="L11">
         <v>6.1151684514715345</v>
@@ -12743,7 +12743,7 @@
         <v>710</v>
       </c>
       <c r="X11" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12778,7 +12778,7 @@
         <v>650</v>
       </c>
       <c r="K12" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="L12">
         <v>4.1221966299799098</v>
@@ -12811,7 +12811,7 @@
         <v>712</v>
       </c>
       <c r="X12" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12846,7 +12846,7 @@
         <v>652</v>
       </c>
       <c r="K13" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="L13">
         <v>6.7028485191473308E-2</v>
@@ -12879,7 +12879,7 @@
         <v>714</v>
       </c>
       <c r="X13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12914,7 +12914,7 @@
         <v>654</v>
       </c>
       <c r="K14" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
       <c r="L14">
         <v>1.3102559495532347</v>
@@ -12947,7 +12947,7 @@
         <v>716</v>
       </c>
       <c r="X14" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12982,7 +12982,7 @@
         <v>656</v>
       </c>
       <c r="K15" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="L15">
         <v>51.171736048895305</v>
@@ -13015,7 +13015,7 @@
         <v>718</v>
       </c>
       <c r="X15" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13050,7 +13050,7 @@
         <v>658</v>
       </c>
       <c r="K16" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="L16">
         <v>27.131882337818411</v>
@@ -13083,7 +13083,7 @@
         <v>720</v>
       </c>
       <c r="X16" t="s">
-        <v>630</v>
+        <v>575</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13118,7 +13118,7 @@
         <v>660</v>
       </c>
       <c r="K17" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="L17">
         <v>8.7915989873091043</v>
@@ -13186,7 +13186,7 @@
         <v>662</v>
       </c>
       <c r="K18" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13219,7 +13219,7 @@
         <v>724</v>
       </c>
       <c r="X18" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="Y18">
         <v>28.478249999999999</v>
@@ -13254,7 +13254,7 @@
         <v>664</v>
       </c>
       <c r="K19" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13287,7 +13287,7 @@
         <v>726</v>
       </c>
       <c r="X19" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="Y19">
         <v>22.079249999999998</v>
@@ -13322,7 +13322,7 @@
         <v>666</v>
       </c>
       <c r="K20" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="L20">
         <v>21.853336570084423</v>
@@ -13355,7 +13355,7 @@
         <v>728</v>
       </c>
       <c r="X20" t="s">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="Y20">
         <v>29.961749999999999</v>
@@ -13390,7 +13390,7 @@
         <v>668</v>
       </c>
       <c r="K21" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="L21">
         <v>40.036304639772588</v>
@@ -13423,7 +13423,7 @@
         <v>730</v>
       </c>
       <c r="X21" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13458,7 +13458,7 @@
         <v>670</v>
       </c>
       <c r="K22" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13491,7 +13491,7 @@
         <v>732</v>
       </c>
       <c r="X22" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="Y22">
         <v>82.576499999999996</v>
@@ -13526,7 +13526,7 @@
         <v>672</v>
       </c>
       <c r="K23" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L23">
         <v>16.970662525397827</v>
@@ -13594,7 +13594,7 @@
         <v>674</v>
       </c>
       <c r="K24" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13627,7 +13627,7 @@
         <v>736</v>
       </c>
       <c r="X24" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="Y24">
         <v>75.512249999999995</v>
@@ -13662,7 +13662,7 @@
         <v>676</v>
       </c>
       <c r="K25" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="L25">
         <v>5.5071261071764246</v>
@@ -13730,7 +13730,7 @@
         <v>678</v>
       </c>
       <c r="K26" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="L26">
         <v>8.4886449615793467</v>
@@ -13763,7 +13763,7 @@
         <v>740</v>
       </c>
       <c r="X26" t="s">
-        <v>645</v>
+        <v>615</v>
       </c>
       <c r="Y26">
         <v>1.9132499999999999</v>
@@ -13798,7 +13798,7 @@
         <v>680</v>
       </c>
       <c r="K27" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="L27">
         <v>8.4075540995285696</v>
@@ -13831,7 +13831,7 @@
         <v>742</v>
       </c>
       <c r="X27" t="s">
-        <v>633</v>
+        <v>578</v>
       </c>
       <c r="Y27">
         <v>63.731250000000003</v>
@@ -13866,7 +13866,7 @@
         <v>682</v>
       </c>
       <c r="K28" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="L28">
         <v>15.703622047270191</v>
@@ -13899,7 +13899,7 @@
         <v>744</v>
       </c>
       <c r="X28" t="s">
-        <v>635</v>
+        <v>580</v>
       </c>
       <c r="Y28">
         <v>38.451000000000001</v>
@@ -13934,7 +13934,7 @@
         <v>684</v>
       </c>
       <c r="K29" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="L29">
         <v>24.074478129461852</v>
@@ -13967,7 +13967,7 @@
         <v>746</v>
       </c>
       <c r="X29" t="s">
-        <v>631</v>
+        <v>576</v>
       </c>
       <c r="Y29">
         <v>64.533749999999998</v>
@@ -14002,7 +14002,7 @@
         <v>686</v>
       </c>
       <c r="K30" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="L30">
         <v>12.527007796473459</v>
@@ -14070,7 +14070,7 @@
         <v>688</v>
       </c>
       <c r="K31" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="L31">
         <v>22.322239264526591</v>
@@ -14103,7 +14103,7 @@
         <v>750</v>
       </c>
       <c r="X31" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="Y31">
         <v>38.15925</v>
@@ -14138,7 +14138,7 @@
         <v>690</v>
       </c>
       <c r="K32" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="L32">
         <v>13.047413180463023</v>
@@ -14206,7 +14206,7 @@
         <v>692</v>
       </c>
       <c r="K33" t="s">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="L33">
         <v>23.637816650626842</v>
@@ -14239,7 +14239,7 @@
         <v>754</v>
       </c>
       <c r="X33" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="Y33">
         <v>30.597750000000001</v>
@@ -14274,7 +14274,7 @@
         <v>694</v>
       </c>
       <c r="K34" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14307,7 +14307,7 @@
         <v>756</v>
       </c>
       <c r="X34" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14342,7 +14342,7 @@
         <v>696</v>
       </c>
       <c r="K35" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="L35">
         <v>44.894334115294185</v>
@@ -14375,7 +14375,7 @@
         <v>758</v>
       </c>
       <c r="X35" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="Y35">
         <v>58.474499999999999</v>
@@ -14410,7 +14410,7 @@
         <v>698</v>
       </c>
       <c r="K36" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="L36">
         <v>14.358494358107757</v>
@@ -14443,7 +14443,7 @@
         <v>760</v>
       </c>
       <c r="X36" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="Y36">
         <v>18.711749999999999</v>
@@ -14478,7 +14478,7 @@
         <v>700</v>
       </c>
       <c r="K37" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="L37">
         <v>39.022668784713879</v>
@@ -14511,7 +14511,7 @@
         <v>762</v>
       </c>
       <c r="X37" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14546,7 +14546,7 @@
         <v>702</v>
       </c>
       <c r="K38" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14579,7 +14579,7 @@
         <v>764</v>
       </c>
       <c r="X38" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14614,7 +14614,7 @@
         <v>704</v>
       </c>
       <c r="K39" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14647,7 +14647,7 @@
         <v>766</v>
       </c>
       <c r="X39" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14682,7 +14682,7 @@
         <v>706</v>
       </c>
       <c r="K40" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="L40">
         <v>26.081770464705624</v>
@@ -14750,7 +14750,7 @@
         <v>708</v>
       </c>
       <c r="K41" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="L41">
         <v>28.326303899090867</v>
@@ -14783,7 +14783,7 @@
         <v>770</v>
       </c>
       <c r="X41" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14818,7 +14818,7 @@
         <v>772</v>
       </c>
       <c r="X42" t="s">
-        <v>575</v>
+        <v>638</v>
       </c>
       <c r="Y42">
         <v>27.642749999999999</v>
@@ -14853,7 +14853,7 @@
         <v>774</v>
       </c>
       <c r="X43" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14888,7 +14888,7 @@
         <v>776</v>
       </c>
       <c r="X44" t="s">
-        <v>579</v>
+        <v>641</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14958,7 +14958,7 @@
         <v>780</v>
       </c>
       <c r="X46" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14993,7 +14993,7 @@
         <v>782</v>
       </c>
       <c r="X47" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -15028,7 +15028,7 @@
         <v>784</v>
       </c>
       <c r="X48" t="s">
-        <v>577</v>
+        <v>640</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15063,7 +15063,7 @@
         <v>786</v>
       </c>
       <c r="X49" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="Y49">
         <v>16.497</v>
@@ -15098,7 +15098,7 @@
         <v>788</v>
       </c>
       <c r="X50" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15133,7 +15133,7 @@
         <v>790</v>
       </c>
       <c r="X51" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15168,7 +15168,7 @@
         <v>792</v>
       </c>
       <c r="X52" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15203,7 +15203,7 @@
         <v>794</v>
       </c>
       <c r="X53" t="s">
-        <v>580</v>
+        <v>642</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15238,7 +15238,7 @@
         <v>796</v>
       </c>
       <c r="X54" t="s">
-        <v>643</v>
+        <v>613</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15253,7 +15253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122393BE-ABF0-409E-B923-32B20B73E95E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E0B3C01-F851-4F68-A884-5562D216C6C2}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17070,7 +17070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15EB3827-7995-4E62-BC93-B8B4E6FB313E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835DE53C-393F-4F3B-AF64-C16882EA2F97}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6F3BBEF-DA8F-4839-BC60-0F810763EB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4CFD238-CC26-4A50-AD5F-086DF4DB40D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="851">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -949,34 +949,142 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_015</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_solelc_spv_025</t>
@@ -985,10 +1093,46 @@
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_solelc_spv_002</t>
@@ -997,196 +1141,88 @@
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w216956620-500,e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP3-275,e_JP1-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
     <t>e_JP7-275,e_JP6-275</t>
   </si>
   <si>
+    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
+  </si>
+  <si>
     <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
   </si>
   <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500,e_JP3-275,e_JP1-275</t>
-  </si>
-  <si>
     <t>e_JP6-275</t>
   </si>
   <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
   </si>
   <si>
     <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
   </si>
   <si>
-    <t>e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w204258596-500,e_w216778426-500,e_w242253500-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
   </si>
   <si>
     <t>e_JP306-500,e_w215451416-500</t>
   </si>
   <si>
-    <t>e_w216956620-500,e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
   </si>
   <si>
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
@@ -1195,43 +1231,28 @@
     <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
   </si>
   <si>
-    <t>e_w179863079-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_w307942220-500,e_JP175-500,e_JP137-500,e_w291678103-500,e_w170605907-500,e_JP135-500,e_JP120-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_w785319805-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>e_w253566674-500,e_JP19-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w216778426-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_JP249-500,e_w1038584990-500,e_w109834508-500,e_w169031998-500</t>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_019</t>
@@ -1240,58 +1261,130 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_026</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wonelc_won_029</t>
@@ -1300,34 +1393,22 @@
     <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wonelc_won_030</t>
@@ -1336,259 +1417,295 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
   </si>
   <si>
     <t>elc_won_019</t>
   </si>
   <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w216778426-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w170974371-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_w170589736-500,e_JP156-500,e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w116559939-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
     <t>e_JP292-500,e_JP269-500,e_w186510275-500,e_JP306-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
   </si>
   <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
     <t>elc_won_018</t>
   </si>
   <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
     <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_w170247312-500,e_w116559939-500</t>
-  </si>
-  <si>
     <t>elc_won_026</t>
   </si>
   <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
   </si>
   <si>
     <t>e_JP219-500,e_JP132-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w172907196-500,e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_JP218-500</t>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
   </si>
   <si>
     <t>elc_won_029</t>
   </si>
   <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_w170537514-500,e_JP96-500,e_w170850727-500,e_w142662111-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
   </si>
   <si>
     <t>elc_won_030</t>
   </si>
   <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
     <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
   </si>
   <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
+    <t>distr_wofelc_wof_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
   </si>
   <si>
     <t>distr_wofelc_wof_006</t>
@@ -1609,16 +1726,88 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
   </si>
   <si>
     <t>distr_wofelc_wof_036</t>
@@ -1627,106 +1816,28 @@
     <t>connecting wind offshore to buses in cluster 36</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wofelc_wof_010</t>
@@ -1735,337 +1846,220 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_041</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 41</t>
   </si>
   <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
+  </si>
+  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
     <t>elc_wof_019</t>
   </si>
   <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
     <t>elc_wof_017</t>
   </si>
   <si>
     <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
   </si>
   <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
   </si>
   <si>
     <t>elc_wof_036</t>
   </si>
   <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w106076988-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
   </si>
   <si>
     <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_JP8-275,e_w801582512-275,e_JP9-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500,e_JP117-500,e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP120-500,e_JP25-500</t>
-  </si>
-  <si>
-    <t>elc_wof_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
   </si>
   <si>
     <t>elc_wof_041</t>
@@ -7396,7 +7390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC1FD7C-FCEC-47DC-87AE-356E3DF741DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73079A1-D90B-45B6-8649-266F177945D0}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7601,10 +7595,10 @@
         <v>240</v>
       </c>
       <c r="L11">
-        <v>1.0868475837211775</v>
+        <v>1.2695492135139217</v>
       </c>
       <c r="M11">
-        <v>0.18525666908653099</v>
+        <v>0.1768982238146152</v>
       </c>
       <c r="O11" t="s">
         <v>272</v>
@@ -7634,25 +7628,25 @@
         <v>273</v>
       </c>
       <c r="Y11" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="Z11" t="s">
         <v>339</v>
       </c>
       <c r="AA11">
-        <v>0.97905685820454003</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB11">
-        <v>383.95759958343297</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD11" t="s">
         <v>272</v>
       </c>
       <c r="AE11" t="s">
+        <v>367</v>
+      </c>
+      <c r="AF11" t="s">
         <v>368</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>369</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -7667,28 +7661,28 @@
         <v>175</v>
       </c>
       <c r="AL11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AM11" t="s">
+        <v>429</v>
+      </c>
+      <c r="AN11" t="s">
         <v>430</v>
       </c>
-      <c r="AN11" t="s">
-        <v>431</v>
-      </c>
       <c r="AO11">
-        <v>0.99762356494824644</v>
+        <v>0.99829313447340673</v>
       </c>
       <c r="AP11">
-        <v>43.567975948815601</v>
+        <v>31.292534654209355</v>
       </c>
       <c r="AR11" t="s">
         <v>272</v>
       </c>
       <c r="AS11" t="s">
+        <v>486</v>
+      </c>
+      <c r="AT11" t="s">
         <v>487</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>488</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -7703,19 +7697,19 @@
         <v>175</v>
       </c>
       <c r="AZ11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="BA11" t="s">
+        <v>574</v>
+      </c>
+      <c r="BB11" t="s">
         <v>575</v>
       </c>
-      <c r="BB11" t="s">
-        <v>345</v>
-      </c>
       <c r="BC11">
-        <v>0.95957195194316591</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD11">
-        <v>741.18088104195795</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7747,10 +7741,10 @@
         <v>241</v>
       </c>
       <c r="L12">
-        <v>0.49620812665820685</v>
+        <v>11.170148024550075</v>
       </c>
       <c r="M12">
-        <v>0.18139311086660159</v>
+        <v>0.17820812772092209</v>
       </c>
       <c r="O12" t="s">
         <v>272</v>
@@ -7780,25 +7774,25 @@
         <v>277</v>
       </c>
       <c r="Y12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Z12" t="s">
         <v>340</v>
       </c>
       <c r="AA12">
-        <v>0.99852430677621173</v>
+        <v>0.99690397462165847</v>
       </c>
       <c r="AB12">
-        <v>27.054375769451152</v>
+        <v>56.760465269594654</v>
       </c>
       <c r="AD12" t="s">
         <v>272</v>
       </c>
       <c r="AE12" t="s">
+        <v>369</v>
+      </c>
+      <c r="AF12" t="s">
         <v>370</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>371</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -7813,28 +7807,28 @@
         <v>175</v>
       </c>
       <c r="AL12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AM12" t="s">
+        <v>431</v>
+      </c>
+      <c r="AN12" t="s">
         <v>432</v>
       </c>
-      <c r="AN12" t="s">
-        <v>433</v>
-      </c>
       <c r="AO12">
-        <v>0.99669176136177262</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP12">
-        <v>60.651041700835236</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR12" t="s">
         <v>272</v>
       </c>
       <c r="AS12" t="s">
+        <v>488</v>
+      </c>
+      <c r="AT12" t="s">
         <v>489</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>490</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -7849,19 +7843,19 @@
         <v>175</v>
       </c>
       <c r="AZ12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="BA12" t="s">
         <v>576</v>
       </c>
       <c r="BB12" t="s">
-        <v>577</v>
+        <v>355</v>
       </c>
       <c r="BC12">
-        <v>0.98627205860840139</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD12">
-        <v>251.67892551264018</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7893,10 +7887,10 @@
         <v>242</v>
       </c>
       <c r="L13">
-        <v>4.0441125317019988E-2</v>
+        <v>6.0583925239792951</v>
       </c>
       <c r="M13">
-        <v>0.20223864817792889</v>
+        <v>0.17190415393703271</v>
       </c>
       <c r="O13" t="s">
         <v>272</v>
@@ -7926,25 +7920,25 @@
         <v>279</v>
       </c>
       <c r="Y13" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Z13" t="s">
         <v>341</v>
       </c>
       <c r="AA13">
-        <v>0.9975431479552237</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB13">
-        <v>45.042287487565297</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD13" t="s">
         <v>272</v>
       </c>
       <c r="AE13" t="s">
+        <v>371</v>
+      </c>
+      <c r="AF13" t="s">
         <v>372</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>373</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -7959,28 +7953,28 @@
         <v>175</v>
       </c>
       <c r="AL13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AM13" t="s">
+        <v>433</v>
+      </c>
+      <c r="AN13" t="s">
         <v>434</v>
       </c>
-      <c r="AN13" t="s">
-        <v>345</v>
-      </c>
       <c r="AO13">
-        <v>0.93717435218793788</v>
+        <v>0.9985842216283608</v>
       </c>
       <c r="AP13">
-        <v>1151.8035432211395</v>
+        <v>25.9559368133853</v>
       </c>
       <c r="AR13" t="s">
         <v>272</v>
       </c>
       <c r="AS13" t="s">
+        <v>490</v>
+      </c>
+      <c r="AT13" t="s">
         <v>491</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>492</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -7995,19 +7989,19 @@
         <v>175</v>
       </c>
       <c r="AZ13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="BA13" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="BB13" t="s">
-        <v>579</v>
+        <v>343</v>
       </c>
       <c r="BC13">
-        <v>0.99504061303190972</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD13">
-        <v>90.922094414988095</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8039,10 +8033,10 @@
         <v>243</v>
       </c>
       <c r="L14">
-        <v>3.1156738745546861</v>
+        <v>4.9429022151581998</v>
       </c>
       <c r="M14">
-        <v>0.1844401710515986</v>
+        <v>0.17623300047483759</v>
       </c>
       <c r="O14" t="s">
         <v>272</v>
@@ -8072,25 +8066,25 @@
         <v>281</v>
       </c>
       <c r="Y14" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="Z14" t="s">
         <v>342</v>
       </c>
       <c r="AA14">
-        <v>0.98179245618315802</v>
+        <v>0.9967423148539083</v>
       </c>
       <c r="AB14">
-        <v>333.80496997543548</v>
+        <v>59.724227678348747</v>
       </c>
       <c r="AD14" t="s">
         <v>272</v>
       </c>
       <c r="AE14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AF14" t="s">
         <v>374</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>375</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -8105,7 +8099,7 @@
         <v>175</v>
       </c>
       <c r="AL14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AM14" t="s">
         <v>435</v>
@@ -8123,10 +8117,10 @@
         <v>272</v>
       </c>
       <c r="AS14" t="s">
+        <v>492</v>
+      </c>
+      <c r="AT14" t="s">
         <v>493</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>494</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -8141,19 +8135,19 @@
         <v>175</v>
       </c>
       <c r="AZ14" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="BA14" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="BB14" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="BC14">
-        <v>0.99547930517021377</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD14">
-        <v>82.879405212747869</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8185,10 +8179,10 @@
         <v>244</v>
       </c>
       <c r="L15">
-        <v>1.0095122884700507</v>
+        <v>3.1087651703643377</v>
       </c>
       <c r="M15">
-        <v>0.18575864794618849</v>
+        <v>0.1713626664711283</v>
       </c>
       <c r="O15" t="s">
         <v>272</v>
@@ -8218,25 +8212,25 @@
         <v>283</v>
       </c>
       <c r="Y15" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="Z15" t="s">
         <v>343</v>
       </c>
       <c r="AA15">
-        <v>0.9981032549815434</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB15">
-        <v>34.773658671704098</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD15" t="s">
         <v>272</v>
       </c>
       <c r="AE15" t="s">
+        <v>375</v>
+      </c>
+      <c r="AF15" t="s">
         <v>376</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>377</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -8251,7 +8245,7 @@
         <v>175</v>
       </c>
       <c r="AL15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM15" t="s">
         <v>437</v>
@@ -8260,19 +8254,19 @@
         <v>438</v>
       </c>
       <c r="AO15">
-        <v>0.99693456929731861</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP15">
-        <v>56.199562882493169</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR15" t="s">
         <v>272</v>
       </c>
       <c r="AS15" t="s">
+        <v>494</v>
+      </c>
+      <c r="AT15" t="s">
         <v>495</v>
-      </c>
-      <c r="AT15" t="s">
-        <v>496</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -8287,19 +8281,19 @@
         <v>175</v>
       </c>
       <c r="AZ15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="BA15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="BB15" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="BC15">
-        <v>0.99536692897647694</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD15">
-        <v>84.939635431255269</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8331,10 +8325,10 @@
         <v>245</v>
       </c>
       <c r="L16">
-        <v>9.6014343718961292</v>
+        <v>7.6858099243981899</v>
       </c>
       <c r="M16">
-        <v>0.1799742763899051</v>
+        <v>0.16962307707337801</v>
       </c>
       <c r="O16" t="s">
         <v>272</v>
@@ -8364,25 +8358,25 @@
         <v>285</v>
       </c>
       <c r="Y16" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Z16" t="s">
         <v>344</v>
       </c>
       <c r="AA16">
-        <v>0.99894650606645485</v>
+        <v>0.99818924951829635</v>
       </c>
       <c r="AB16">
-        <v>19.314055448326833</v>
+        <v>33.197092164567515</v>
       </c>
       <c r="AD16" t="s">
         <v>272</v>
       </c>
       <c r="AE16" t="s">
+        <v>377</v>
+      </c>
+      <c r="AF16" t="s">
         <v>378</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>379</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -8397,7 +8391,7 @@
         <v>175</v>
       </c>
       <c r="AL16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AM16" t="s">
         <v>439</v>
@@ -8406,19 +8400,19 @@
         <v>440</v>
       </c>
       <c r="AO16">
-        <v>0.99710631799330929</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP16">
-        <v>53.050836789329388</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR16" t="s">
         <v>272</v>
       </c>
       <c r="AS16" t="s">
+        <v>496</v>
+      </c>
+      <c r="AT16" t="s">
         <v>497</v>
-      </c>
-      <c r="AT16" t="s">
-        <v>498</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -8433,19 +8427,19 @@
         <v>175</v>
       </c>
       <c r="AZ16" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="BA16" t="s">
+        <v>581</v>
+      </c>
+      <c r="BB16" t="s">
         <v>582</v>
       </c>
-      <c r="BB16" t="s">
-        <v>583</v>
-      </c>
       <c r="BC16">
-        <v>0.93089405249526469</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD16">
-        <v>1266.9423709201483</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8477,10 +8471,10 @@
         <v>246</v>
       </c>
       <c r="L17">
-        <v>2.0672282720381219</v>
+        <v>6.8708538922649831</v>
       </c>
       <c r="M17">
-        <v>0.1897242685700597</v>
+        <v>0.17252690554813149</v>
       </c>
       <c r="O17" t="s">
         <v>272</v>
@@ -8510,25 +8504,25 @@
         <v>287</v>
       </c>
       <c r="Y17" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="Z17" t="s">
         <v>345</v>
       </c>
       <c r="AA17">
-        <v>0.94069903208664407</v>
+        <v>0.99794776600687107</v>
       </c>
       <c r="AB17">
-        <v>1087.1844117448593</v>
+        <v>37.624289874031113</v>
       </c>
       <c r="AD17" t="s">
         <v>272</v>
       </c>
       <c r="AE17" t="s">
+        <v>379</v>
+      </c>
+      <c r="AF17" t="s">
         <v>380</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>381</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -8543,7 +8537,7 @@
         <v>175</v>
       </c>
       <c r="AL17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM17" t="s">
         <v>441</v>
@@ -8552,19 +8546,19 @@
         <v>442</v>
       </c>
       <c r="AO17">
-        <v>0.99627181657233566</v>
+        <v>0.99835408615028387</v>
       </c>
       <c r="AP17">
-        <v>68.350029507179471</v>
+        <v>30.175087244796281</v>
       </c>
       <c r="AR17" t="s">
         <v>272</v>
       </c>
       <c r="AS17" t="s">
+        <v>498</v>
+      </c>
+      <c r="AT17" t="s">
         <v>499</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>500</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -8579,19 +8573,19 @@
         <v>175</v>
       </c>
       <c r="AZ17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="BA17" t="s">
+        <v>583</v>
+      </c>
+      <c r="BB17" t="s">
         <v>584</v>
       </c>
-      <c r="BB17" t="s">
-        <v>585</v>
-      </c>
       <c r="BC17">
-        <v>0.99302778580016682</v>
+        <v>0.99547930517021377</v>
       </c>
       <c r="BD17">
-        <v>127.82392699694152</v>
+        <v>82.879405212747869</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8623,10 +8617,10 @@
         <v>247</v>
       </c>
       <c r="L18">
-        <v>5.3002505298606302</v>
+        <v>1.8808781416844131</v>
       </c>
       <c r="M18">
-        <v>0.19067081479710349</v>
+        <v>0.17266493010223849</v>
       </c>
       <c r="O18" t="s">
         <v>272</v>
@@ -8656,25 +8650,25 @@
         <v>289</v>
       </c>
       <c r="Y18" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="Z18" t="s">
         <v>346</v>
       </c>
       <c r="AA18">
-        <v>0.99900168239190124</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB18">
-        <v>18.302489481810518</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD18" t="s">
         <v>272</v>
       </c>
       <c r="AE18" t="s">
+        <v>381</v>
+      </c>
+      <c r="AF18" t="s">
         <v>382</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>383</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -8689,7 +8683,7 @@
         <v>175</v>
       </c>
       <c r="AL18" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AM18" t="s">
         <v>443</v>
@@ -8698,19 +8692,19 @@
         <v>444</v>
       </c>
       <c r="AO18">
-        <v>0.99550555557680764</v>
+        <v>0.99627181657233566</v>
       </c>
       <c r="AP18">
-        <v>82.398147758527074</v>
+        <v>68.350029507179471</v>
       </c>
       <c r="AR18" t="s">
         <v>272</v>
       </c>
       <c r="AS18" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT18" t="s">
         <v>501</v>
-      </c>
-      <c r="AT18" t="s">
-        <v>502</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -8725,19 +8719,19 @@
         <v>175</v>
       </c>
       <c r="AZ18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="BA18" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="BB18" t="s">
-        <v>339</v>
+        <v>436</v>
       </c>
       <c r="BC18">
-        <v>0.98180592470173533</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD18">
-        <v>333.55804713485287</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8769,10 +8763,10 @@
         <v>248</v>
       </c>
       <c r="L19">
-        <v>1.7148461776183934</v>
+        <v>2.234130084558998</v>
       </c>
       <c r="M19">
-        <v>0.1988962714532147</v>
+        <v>0.17375166762337191</v>
       </c>
       <c r="O19" t="s">
         <v>272</v>
@@ -8802,25 +8796,25 @@
         <v>291</v>
       </c>
       <c r="Y19" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Z19" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="AA19">
-        <v>0.98833720780868572</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB19">
-        <v>213.8178568407609</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD19" t="s">
         <v>272</v>
       </c>
       <c r="AE19" t="s">
+        <v>383</v>
+      </c>
+      <c r="AF19" t="s">
         <v>384</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>385</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -8835,28 +8829,28 @@
         <v>175</v>
       </c>
       <c r="AL19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AM19" t="s">
         <v>445</v>
       </c>
       <c r="AN19" t="s">
-        <v>446</v>
+        <v>355</v>
       </c>
       <c r="AO19">
-        <v>0.93896180472603763</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP19">
-        <v>1119.0335800226442</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR19" t="s">
         <v>272</v>
       </c>
       <c r="AS19" t="s">
+        <v>502</v>
+      </c>
+      <c r="AT19" t="s">
         <v>503</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>504</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -8871,19 +8865,19 @@
         <v>175</v>
       </c>
       <c r="AZ19" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="BA19" t="s">
+        <v>586</v>
+      </c>
+      <c r="BB19" t="s">
         <v>587</v>
       </c>
-      <c r="BB19" t="s">
-        <v>345</v>
-      </c>
       <c r="BC19">
-        <v>0.934538160869965</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD19">
-        <v>1200.1337173839754</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8915,10 +8909,10 @@
         <v>249</v>
       </c>
       <c r="L20">
-        <v>11.664406830498095</v>
+        <v>8.2308495959667809</v>
       </c>
       <c r="M20">
-        <v>0.20214793379564561</v>
+        <v>0.1872946834989149</v>
       </c>
       <c r="O20" t="s">
         <v>272</v>
@@ -8951,22 +8945,22 @@
         <v>249</v>
       </c>
       <c r="Z20" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA20">
-        <v>0.9982812149336332</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB20">
-        <v>31.51105955005805</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD20" t="s">
         <v>272</v>
       </c>
       <c r="AE20" t="s">
+        <v>385</v>
+      </c>
+      <c r="AF20" t="s">
         <v>386</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>387</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -8981,28 +8975,28 @@
         <v>175</v>
       </c>
       <c r="AL20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AM20" t="s">
+        <v>446</v>
+      </c>
+      <c r="AN20" t="s">
         <v>447</v>
       </c>
-      <c r="AN20" t="s">
-        <v>448</v>
-      </c>
       <c r="AO20">
-        <v>0.99827635377245738</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP20">
-        <v>31.600180838280902</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR20" t="s">
         <v>272</v>
       </c>
       <c r="AS20" t="s">
+        <v>504</v>
+      </c>
+      <c r="AT20" t="s">
         <v>505</v>
-      </c>
-      <c r="AT20" t="s">
-        <v>506</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -9017,19 +9011,19 @@
         <v>175</v>
       </c>
       <c r="AZ20" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BA20" t="s">
         <v>588</v>
       </c>
       <c r="BB20" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="BC20">
-        <v>0.94616153753972931</v>
+        <v>0.99895994357772033</v>
       </c>
       <c r="BD20">
-        <v>987.03847843829612</v>
+        <v>19.067701075126294</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9061,10 +9055,10 @@
         <v>250</v>
       </c>
       <c r="L21">
-        <v>11.527434284891411</v>
+        <v>12.207707960945804</v>
       </c>
       <c r="M21">
-        <v>0.19218189271120059</v>
+        <v>0.1885277185926072</v>
       </c>
       <c r="O21" t="s">
         <v>272</v>
@@ -9097,22 +9091,22 @@
         <v>269</v>
       </c>
       <c r="Z21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA21">
-        <v>0.99782703065964284</v>
+        <v>0.99829848799221066</v>
       </c>
       <c r="AB21">
-        <v>39.837771239882208</v>
+        <v>31.194386809470345</v>
       </c>
       <c r="AD21" t="s">
         <v>272</v>
       </c>
       <c r="AE21" t="s">
+        <v>387</v>
+      </c>
+      <c r="AF21" t="s">
         <v>388</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>389</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -9127,28 +9121,28 @@
         <v>175</v>
       </c>
       <c r="AL21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AM21" t="s">
+        <v>448</v>
+      </c>
+      <c r="AN21" t="s">
         <v>449</v>
       </c>
-      <c r="AN21" t="s">
-        <v>339</v>
-      </c>
       <c r="AO21">
-        <v>0.98949004263841422</v>
+        <v>0.99826201627849442</v>
       </c>
       <c r="AP21">
-        <v>192.68255162907312</v>
+        <v>31.863034894267944</v>
       </c>
       <c r="AR21" t="s">
         <v>272</v>
       </c>
       <c r="AS21" t="s">
+        <v>506</v>
+      </c>
+      <c r="AT21" t="s">
         <v>507</v>
-      </c>
-      <c r="AT21" t="s">
-        <v>508</v>
       </c>
       <c r="AU21" t="s">
         <v>10</v>
@@ -9163,19 +9157,19 @@
         <v>175</v>
       </c>
       <c r="AZ21" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BA21" t="s">
         <v>589</v>
       </c>
       <c r="BB21" t="s">
-        <v>345</v>
+        <v>590</v>
       </c>
       <c r="BC21">
-        <v>0.97218956380622079</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD21">
-        <v>509.85799688595205</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9207,10 +9201,10 @@
         <v>251</v>
       </c>
       <c r="L22">
-        <v>6.3183450599935256</v>
+        <v>11.84836321250885</v>
       </c>
       <c r="M22">
-        <v>0.19209496103447071</v>
+        <v>0.18764376746668049</v>
       </c>
       <c r="O22" t="s">
         <v>272</v>
@@ -9240,25 +9234,25 @@
         <v>297</v>
       </c>
       <c r="Y22" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="Z22" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA22">
-        <v>0.99391268208184824</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB22">
-        <v>111.60082849944791</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD22" t="s">
         <v>272</v>
       </c>
       <c r="AE22" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF22" t="s">
         <v>390</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>391</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -9273,7 +9267,7 @@
         <v>175</v>
       </c>
       <c r="AL22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AM22" t="s">
         <v>450</v>
@@ -9282,19 +9276,19 @@
         <v>451</v>
       </c>
       <c r="AO22">
-        <v>0.99686124252542985</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP22">
-        <v>57.543887033786262</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR22" t="s">
         <v>272</v>
       </c>
       <c r="AS22" t="s">
+        <v>508</v>
+      </c>
+      <c r="AT22" t="s">
         <v>509</v>
-      </c>
-      <c r="AT22" t="s">
-        <v>510</v>
       </c>
       <c r="AU22" t="s">
         <v>10</v>
@@ -9309,19 +9303,19 @@
         <v>175</v>
       </c>
       <c r="AZ22" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="BA22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="BB22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="BC22">
-        <v>0.99272888574049079</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD22">
-        <v>133.30376142433548</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9353,10 +9347,10 @@
         <v>252</v>
       </c>
       <c r="L23">
-        <v>4.3872020218935068</v>
+        <v>6.311418285235062</v>
       </c>
       <c r="M23">
-        <v>0.18593850300475309</v>
+        <v>0.1693068332707558</v>
       </c>
       <c r="O23" t="s">
         <v>272</v>
@@ -9386,25 +9380,25 @@
         <v>299</v>
       </c>
       <c r="Y23" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="Z23" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AA23">
-        <v>0.96340341594909085</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB23">
-        <v>670.93737426666792</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD23" t="s">
         <v>272</v>
       </c>
       <c r="AE23" t="s">
+        <v>391</v>
+      </c>
+      <c r="AF23" t="s">
         <v>392</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>393</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -9419,7 +9413,7 @@
         <v>175</v>
       </c>
       <c r="AL23" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AM23" t="s">
         <v>452</v>
@@ -9428,19 +9422,19 @@
         <v>453</v>
       </c>
       <c r="AO23">
-        <v>0.99869874972548245</v>
+        <v>0.99771335854027388</v>
       </c>
       <c r="AP23">
-        <v>23.856255032822389</v>
+        <v>41.921760094978509</v>
       </c>
       <c r="AR23" t="s">
         <v>272</v>
       </c>
       <c r="AS23" t="s">
+        <v>510</v>
+      </c>
+      <c r="AT23" t="s">
         <v>511</v>
-      </c>
-      <c r="AT23" t="s">
-        <v>512</v>
       </c>
       <c r="AU23" t="s">
         <v>10</v>
@@ -9455,19 +9449,19 @@
         <v>175</v>
       </c>
       <c r="AZ23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="BA23" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="BB23" t="s">
-        <v>593</v>
+        <v>470</v>
       </c>
       <c r="BC23">
-        <v>0.99662747375050009</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD23">
-        <v>61.829647907498845</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9499,10 +9493,10 @@
         <v>253</v>
       </c>
       <c r="L24">
-        <v>4.9429022151581998</v>
+        <v>7.2071728047478238</v>
       </c>
       <c r="M24">
-        <v>0.17623300047483759</v>
+        <v>0.18922795314163121</v>
       </c>
       <c r="O24" t="s">
         <v>272</v>
@@ -9535,22 +9529,22 @@
         <v>246</v>
       </c>
       <c r="Z24" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA24">
-        <v>0.99838604658336239</v>
+        <v>0.99824746199801306</v>
       </c>
       <c r="AB24">
-        <v>29.589145971689483</v>
+        <v>32.129863369760315</v>
       </c>
       <c r="AD24" t="s">
         <v>272</v>
       </c>
       <c r="AE24" t="s">
+        <v>393</v>
+      </c>
+      <c r="AF24" t="s">
         <v>394</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>395</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -9565,7 +9559,7 @@
         <v>175</v>
       </c>
       <c r="AL24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AM24" t="s">
         <v>454</v>
@@ -9574,19 +9568,19 @@
         <v>455</v>
       </c>
       <c r="AO24">
-        <v>0.99811838305018963</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP24">
-        <v>34.496310746523356</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR24" t="s">
         <v>272</v>
       </c>
       <c r="AS24" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT24" t="s">
         <v>513</v>
-      </c>
-      <c r="AT24" t="s">
-        <v>514</v>
       </c>
       <c r="AU24" t="s">
         <v>10</v>
@@ -9601,7 +9595,7 @@
         <v>175</v>
       </c>
       <c r="AZ24" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="BA24" t="s">
         <v>594</v>
@@ -9610,10 +9604,10 @@
         <v>595</v>
       </c>
       <c r="BC24">
-        <v>0.99637036284424008</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD24">
-        <v>66.543347855598327</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9645,10 +9639,10 @@
         <v>254</v>
       </c>
       <c r="L25">
-        <v>6.0583925239792951</v>
+        <v>9.4700882153505201</v>
       </c>
       <c r="M25">
-        <v>0.17190415393703271</v>
+        <v>0.17932962385242079</v>
       </c>
       <c r="O25" t="s">
         <v>272</v>
@@ -9678,25 +9672,25 @@
         <v>303</v>
       </c>
       <c r="Y25" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Z25" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AA25">
-        <v>0.99809153006866247</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB25">
-        <v>34.98861540785537</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD25" t="s">
         <v>272</v>
       </c>
       <c r="AE25" t="s">
+        <v>395</v>
+      </c>
+      <c r="AF25" t="s">
         <v>396</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>397</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -9711,28 +9705,28 @@
         <v>175</v>
       </c>
       <c r="AL25" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AM25" t="s">
         <v>456</v>
       </c>
       <c r="AN25" t="s">
-        <v>457</v>
+        <v>355</v>
       </c>
       <c r="AO25">
-        <v>0.9985928182686985</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP25">
-        <v>25.798331740528162</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR25" t="s">
         <v>272</v>
       </c>
       <c r="AS25" t="s">
+        <v>514</v>
+      </c>
+      <c r="AT25" t="s">
         <v>515</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>516</v>
       </c>
       <c r="AU25" t="s">
         <v>10</v>
@@ -9747,19 +9741,19 @@
         <v>175</v>
       </c>
       <c r="AZ25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="BA25" t="s">
         <v>596</v>
       </c>
       <c r="BB25" t="s">
-        <v>597</v>
+        <v>339</v>
       </c>
       <c r="BC25">
-        <v>0.98779966071713954</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD25">
-        <v>223.67288685244134</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9791,10 +9785,10 @@
         <v>255</v>
       </c>
       <c r="L26">
-        <v>8.8562728829669233</v>
+        <v>5.819871101459503</v>
       </c>
       <c r="M26">
-        <v>0.17852540925562671</v>
+        <v>0.1668865544761739</v>
       </c>
       <c r="O26" t="s">
         <v>272</v>
@@ -9824,25 +9818,25 @@
         <v>305</v>
       </c>
       <c r="Y26" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA26">
-        <v>0.99323944641370343</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB26">
-        <v>123.94348241543759</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD26" t="s">
         <v>272</v>
       </c>
       <c r="AE26" t="s">
+        <v>397</v>
+      </c>
+      <c r="AF26" t="s">
         <v>398</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>399</v>
       </c>
       <c r="AG26" t="s">
         <v>10</v>
@@ -9857,28 +9851,28 @@
         <v>175</v>
       </c>
       <c r="AL26" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AM26" t="s">
+        <v>457</v>
+      </c>
+      <c r="AN26" t="s">
         <v>458</v>
       </c>
-      <c r="AN26" t="s">
-        <v>459</v>
-      </c>
       <c r="AO26">
-        <v>0.99771335854027388</v>
+        <v>0.99804155179341392</v>
       </c>
       <c r="AP26">
-        <v>41.921760094978509</v>
+        <v>35.904883787411507</v>
       </c>
       <c r="AR26" t="s">
         <v>272</v>
       </c>
       <c r="AS26" t="s">
+        <v>516</v>
+      </c>
+      <c r="AT26" t="s">
         <v>517</v>
-      </c>
-      <c r="AT26" t="s">
-        <v>518</v>
       </c>
       <c r="AU26" t="s">
         <v>10</v>
@@ -9893,19 +9887,19 @@
         <v>175</v>
       </c>
       <c r="AZ26" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="BA26" t="s">
+        <v>597</v>
+      </c>
+      <c r="BB26" t="s">
         <v>598</v>
       </c>
-      <c r="BB26" t="s">
-        <v>599</v>
-      </c>
       <c r="BC26">
-        <v>0.99681267676383467</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD26">
-        <v>58.434259329697142</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9937,10 +9931,10 @@
         <v>256</v>
       </c>
       <c r="L27">
-        <v>3.1087651703643377</v>
+        <v>7.4335447943742894</v>
       </c>
       <c r="M27">
-        <v>0.1713626664711283</v>
+        <v>0.17297840533466791</v>
       </c>
       <c r="O27" t="s">
         <v>272</v>
@@ -9970,25 +9964,25 @@
         <v>307</v>
       </c>
       <c r="Y27" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="Z27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA27">
-        <v>0.99592928381702117</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB27">
-        <v>74.629796687944193</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD27" t="s">
         <v>272</v>
       </c>
       <c r="AE27" t="s">
+        <v>399</v>
+      </c>
+      <c r="AF27" t="s">
         <v>400</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>401</v>
       </c>
       <c r="AG27" t="s">
         <v>10</v>
@@ -10003,28 +9997,28 @@
         <v>175</v>
       </c>
       <c r="AL27" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AM27" t="s">
+        <v>459</v>
+      </c>
+      <c r="AN27" t="s">
         <v>460</v>
       </c>
-      <c r="AN27" t="s">
-        <v>358</v>
-      </c>
       <c r="AO27">
-        <v>0.98814178187791379</v>
+        <v>0.99686124252542985</v>
       </c>
       <c r="AP27">
-        <v>217.40066557158059</v>
+        <v>57.543887033786262</v>
       </c>
       <c r="AR27" t="s">
         <v>272</v>
       </c>
       <c r="AS27" t="s">
+        <v>518</v>
+      </c>
+      <c r="AT27" t="s">
         <v>519</v>
-      </c>
-      <c r="AT27" t="s">
-        <v>520</v>
       </c>
       <c r="AU27" t="s">
         <v>10</v>
@@ -10039,19 +10033,19 @@
         <v>175</v>
       </c>
       <c r="AZ27" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="BA27" t="s">
+        <v>599</v>
+      </c>
+      <c r="BB27" t="s">
         <v>600</v>
       </c>
-      <c r="BB27" t="s">
-        <v>601</v>
-      </c>
       <c r="BC27">
-        <v>0.9973402418125219</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD27">
-        <v>48.762233437098502</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10083,10 +10077,10 @@
         <v>257</v>
       </c>
       <c r="L28">
-        <v>7.6858099243981899</v>
+        <v>0.11366418204482304</v>
       </c>
       <c r="M28">
-        <v>0.16962307707337801</v>
+        <v>0.18364651891835679</v>
       </c>
       <c r="O28" t="s">
         <v>272</v>
@@ -10116,25 +10110,25 @@
         <v>309</v>
       </c>
       <c r="Y28" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="Z28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA28">
-        <v>0.99726055556014181</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB28">
-        <v>50.223148064066145</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD28" t="s">
         <v>272</v>
       </c>
       <c r="AE28" t="s">
+        <v>401</v>
+      </c>
+      <c r="AF28" t="s">
         <v>402</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>403</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
@@ -10149,7 +10143,7 @@
         <v>175</v>
       </c>
       <c r="AL28" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AM28" t="s">
         <v>461</v>
@@ -10158,19 +10152,19 @@
         <v>462</v>
       </c>
       <c r="AO28">
-        <v>0.99870022163576544</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP28">
-        <v>23.829270010966344</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR28" t="s">
         <v>272</v>
       </c>
       <c r="AS28" t="s">
+        <v>520</v>
+      </c>
+      <c r="AT28" t="s">
         <v>521</v>
-      </c>
-      <c r="AT28" t="s">
-        <v>522</v>
       </c>
       <c r="AU28" t="s">
         <v>10</v>
@@ -10185,19 +10179,19 @@
         <v>175</v>
       </c>
       <c r="AZ28" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="BA28" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="BB28" t="s">
-        <v>603</v>
+        <v>343</v>
       </c>
       <c r="BC28">
-        <v>0.99519319222421976</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD28">
-        <v>88.124809222638589</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10229,10 +10223,10 @@
         <v>258</v>
       </c>
       <c r="L29">
-        <v>8.8290491423659851</v>
+        <v>0.97318340167635442</v>
       </c>
       <c r="M29">
-        <v>0.17384629516416941</v>
+        <v>0.18544472860493169</v>
       </c>
       <c r="O29" t="s">
         <v>272</v>
@@ -10262,25 +10256,25 @@
         <v>311</v>
       </c>
       <c r="Y29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Z29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA29">
-        <v>0.98968917222400854</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB29">
-        <v>189.03184255984442</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD29" t="s">
         <v>272</v>
       </c>
       <c r="AE29" t="s">
+        <v>403</v>
+      </c>
+      <c r="AF29" t="s">
         <v>404</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>405</v>
       </c>
       <c r="AG29" t="s">
         <v>10</v>
@@ -10295,7 +10289,7 @@
         <v>175</v>
       </c>
       <c r="AL29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AM29" t="s">
         <v>463</v>
@@ -10304,19 +10298,19 @@
         <v>464</v>
       </c>
       <c r="AO29">
-        <v>0.99807466477127271</v>
+        <v>0.99693456929731861</v>
       </c>
       <c r="AP29">
-        <v>35.297812526667357</v>
+        <v>56.199562882493169</v>
       </c>
       <c r="AR29" t="s">
         <v>272</v>
       </c>
       <c r="AS29" t="s">
+        <v>522</v>
+      </c>
+      <c r="AT29" t="s">
         <v>523</v>
-      </c>
-      <c r="AT29" t="s">
-        <v>524</v>
       </c>
       <c r="AU29" t="s">
         <v>10</v>
@@ -10331,19 +10325,19 @@
         <v>175</v>
       </c>
       <c r="AZ29" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="BA29" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="BB29" t="s">
-        <v>358</v>
+        <v>603</v>
       </c>
       <c r="BC29">
-        <v>0.98605307635189521</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD29">
-        <v>255.693600215255</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10375,10 +10369,10 @@
         <v>259</v>
       </c>
       <c r="L30">
-        <v>3.8593591895550672</v>
+        <v>0.49620812665820685</v>
       </c>
       <c r="M30">
-        <v>0.17433358698743889</v>
+        <v>0.18139311086660159</v>
       </c>
       <c r="O30" t="s">
         <v>272</v>
@@ -10408,25 +10402,25 @@
         <v>313</v>
       </c>
       <c r="Y30" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="Z30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA30">
-        <v>0.99864010607905451</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB30">
-        <v>24.931388550667378</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD30" t="s">
         <v>272</v>
       </c>
       <c r="AE30" t="s">
+        <v>405</v>
+      </c>
+      <c r="AF30" t="s">
         <v>406</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>407</v>
       </c>
       <c r="AG30" t="s">
         <v>10</v>
@@ -10441,7 +10435,7 @@
         <v>175</v>
       </c>
       <c r="AL30" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AM30" t="s">
         <v>465</v>
@@ -10450,19 +10444,19 @@
         <v>466</v>
       </c>
       <c r="AO30">
-        <v>0.99750949182367343</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP30">
-        <v>45.659316565986806</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR30" t="s">
         <v>272</v>
       </c>
       <c r="AS30" t="s">
+        <v>524</v>
+      </c>
+      <c r="AT30" t="s">
         <v>525</v>
-      </c>
-      <c r="AT30" t="s">
-        <v>526</v>
       </c>
       <c r="AU30" t="s">
         <v>10</v>
@@ -10477,19 +10471,19 @@
         <v>175</v>
       </c>
       <c r="AZ30" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="BA30" t="s">
+        <v>604</v>
+      </c>
+      <c r="BB30" t="s">
         <v>605</v>
       </c>
-      <c r="BB30" t="s">
-        <v>606</v>
-      </c>
       <c r="BC30">
-        <v>0.88199812838352587</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD30">
-        <v>2163.367646302027</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10521,10 +10515,10 @@
         <v>260</v>
       </c>
       <c r="L31">
-        <v>8.2308495959667809</v>
+        <v>4.0441125317019988E-2</v>
       </c>
       <c r="M31">
-        <v>0.1872946834989149</v>
+        <v>0.20223864817792889</v>
       </c>
       <c r="O31" t="s">
         <v>272</v>
@@ -10554,25 +10548,25 @@
         <v>315</v>
       </c>
       <c r="Y31" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="Z31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA31">
-        <v>0.99706930328635524</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB31">
-        <v>53.729439750153354</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD31" t="s">
         <v>272</v>
       </c>
       <c r="AE31" t="s">
+        <v>407</v>
+      </c>
+      <c r="AF31" t="s">
         <v>408</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>409</v>
       </c>
       <c r="AG31" t="s">
         <v>10</v>
@@ -10587,7 +10581,7 @@
         <v>175</v>
       </c>
       <c r="AL31" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AM31" t="s">
         <v>467</v>
@@ -10596,19 +10590,19 @@
         <v>468</v>
       </c>
       <c r="AO31">
-        <v>0.99013353407586135</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP31">
-        <v>180.88520860920943</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR31" t="s">
         <v>272</v>
       </c>
       <c r="AS31" t="s">
+        <v>526</v>
+      </c>
+      <c r="AT31" t="s">
         <v>527</v>
-      </c>
-      <c r="AT31" t="s">
-        <v>528</v>
       </c>
       <c r="AU31" t="s">
         <v>10</v>
@@ -10623,19 +10617,19 @@
         <v>175</v>
       </c>
       <c r="AZ31" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BA31" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="BB31" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BC31">
-        <v>0.96140381292129873</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD31">
-        <v>707.59676310952364</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10667,10 +10661,10 @@
         <v>261</v>
       </c>
       <c r="L32">
-        <v>4.1919248573917418</v>
+        <v>3.1156738745546861</v>
       </c>
       <c r="M32">
-        <v>0.1839798063486249</v>
+        <v>0.1844401710515986</v>
       </c>
       <c r="O32" t="s">
         <v>272</v>
@@ -10700,25 +10694,25 @@
         <v>317</v>
       </c>
       <c r="Y32" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="Z32" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA32">
-        <v>0.99116451092312863</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB32">
-        <v>161.98396640930775</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD32" t="s">
         <v>272</v>
       </c>
       <c r="AE32" t="s">
+        <v>409</v>
+      </c>
+      <c r="AF32" t="s">
         <v>410</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>411</v>
       </c>
       <c r="AG32" t="s">
         <v>10</v>
@@ -10733,7 +10727,7 @@
         <v>175</v>
       </c>
       <c r="AL32" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AM32" t="s">
         <v>469</v>
@@ -10742,19 +10736,19 @@
         <v>470</v>
       </c>
       <c r="AO32">
-        <v>0.99869589057011365</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP32">
-        <v>23.908672881248773</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR32" t="s">
         <v>272</v>
       </c>
       <c r="AS32" t="s">
+        <v>528</v>
+      </c>
+      <c r="AT32" t="s">
         <v>529</v>
-      </c>
-      <c r="AT32" t="s">
-        <v>530</v>
       </c>
       <c r="AU32" t="s">
         <v>10</v>
@@ -10769,19 +10763,19 @@
         <v>175</v>
       </c>
       <c r="AZ32" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BA32" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="BB32" t="s">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="BC32">
-        <v>0.99490784156958001</v>
+        <v>0.98627205860840139</v>
       </c>
       <c r="BD32">
-        <v>93.356237891033686</v>
+        <v>251.67892551264018</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10813,10 +10807,10 @@
         <v>262</v>
       </c>
       <c r="L33">
-        <v>12.207707960945804</v>
+        <v>1.0095122884700507</v>
       </c>
       <c r="M33">
-        <v>0.1885277185926072</v>
+        <v>0.18575864794618849</v>
       </c>
       <c r="O33" t="s">
         <v>272</v>
@@ -10846,25 +10840,25 @@
         <v>319</v>
       </c>
       <c r="Y33" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="Z33" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA33">
-        <v>0.9977500892185478</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB33">
-        <v>41.248364326622962</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD33" t="s">
         <v>272</v>
       </c>
       <c r="AE33" t="s">
+        <v>411</v>
+      </c>
+      <c r="AF33" t="s">
         <v>412</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>413</v>
       </c>
       <c r="AG33" t="s">
         <v>10</v>
@@ -10879,7 +10873,7 @@
         <v>175</v>
       </c>
       <c r="AL33" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AM33" t="s">
         <v>471</v>
@@ -10888,19 +10882,19 @@
         <v>472</v>
       </c>
       <c r="AO33">
-        <v>0.99841760060377538</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP33">
-        <v>29.010655597451841</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR33" t="s">
         <v>272</v>
       </c>
       <c r="AS33" t="s">
+        <v>530</v>
+      </c>
+      <c r="AT33" t="s">
         <v>531</v>
-      </c>
-      <c r="AT33" t="s">
-        <v>532</v>
       </c>
       <c r="AU33" t="s">
         <v>10</v>
@@ -10915,19 +10909,19 @@
         <v>175</v>
       </c>
       <c r="AZ33" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="BA33" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="BB33" t="s">
-        <v>342</v>
+        <v>609</v>
       </c>
       <c r="BC33">
-        <v>0.97902641975794957</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD33">
-        <v>384.51563777092457</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -10959,10 +10953,10 @@
         <v>263</v>
       </c>
       <c r="L34">
-        <v>11.84836321250885</v>
+        <v>9.6014343718961292</v>
       </c>
       <c r="M34">
-        <v>0.18764376746668049</v>
+        <v>0.1799742763899051</v>
       </c>
       <c r="O34" t="s">
         <v>272</v>
@@ -10992,25 +10986,25 @@
         <v>321</v>
       </c>
       <c r="Y34" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="Z34" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="AA34">
-        <v>0.99788758639511588</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB34">
-        <v>38.727582756208619</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD34" t="s">
         <v>272</v>
       </c>
       <c r="AE34" t="s">
+        <v>413</v>
+      </c>
+      <c r="AF34" t="s">
         <v>414</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>415</v>
       </c>
       <c r="AG34" t="s">
         <v>10</v>
@@ -11025,28 +11019,28 @@
         <v>175</v>
       </c>
       <c r="AL34" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AM34" t="s">
         <v>473</v>
       </c>
       <c r="AN34" t="s">
-        <v>474</v>
+        <v>354</v>
       </c>
       <c r="AO34">
-        <v>0.99781438034778358</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP34">
-        <v>40.069693623967019</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR34" t="s">
         <v>272</v>
       </c>
       <c r="AS34" t="s">
+        <v>532</v>
+      </c>
+      <c r="AT34" t="s">
         <v>533</v>
-      </c>
-      <c r="AT34" t="s">
-        <v>534</v>
       </c>
       <c r="AU34" t="s">
         <v>10</v>
@@ -11061,19 +11055,19 @@
         <v>175</v>
       </c>
       <c r="AZ34" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="BA34" t="s">
+        <v>610</v>
+      </c>
+      <c r="BB34" t="s">
         <v>611</v>
       </c>
-      <c r="BB34" t="s">
-        <v>612</v>
-      </c>
       <c r="BC34">
-        <v>0.99366677237144974</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD34">
-        <v>116.10917319008783</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11105,10 +11099,10 @@
         <v>264</v>
       </c>
       <c r="L35">
-        <v>6.614368021654732</v>
+        <v>11.664406830498095</v>
       </c>
       <c r="M35">
-        <v>0.1892871810641478</v>
+        <v>0.20214793379564561</v>
       </c>
       <c r="O35" t="s">
         <v>272</v>
@@ -11144,19 +11138,19 @@
         <v>361</v>
       </c>
       <c r="AA35">
-        <v>0.99841742239430997</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB35">
-        <v>29.013922770983669</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD35" t="s">
         <v>272</v>
       </c>
       <c r="AE35" t="s">
+        <v>415</v>
+      </c>
+      <c r="AF35" t="s">
         <v>416</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>417</v>
       </c>
       <c r="AG35" t="s">
         <v>10</v>
@@ -11171,28 +11165,28 @@
         <v>175</v>
       </c>
       <c r="AL35" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AM35" t="s">
+        <v>474</v>
+      </c>
+      <c r="AN35" t="s">
         <v>475</v>
       </c>
-      <c r="AN35" t="s">
-        <v>476</v>
-      </c>
       <c r="AO35">
-        <v>0.99682717865030179</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP35">
-        <v>58.168391411134159</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR35" t="s">
         <v>272</v>
       </c>
       <c r="AS35" t="s">
+        <v>534</v>
+      </c>
+      <c r="AT35" t="s">
         <v>535</v>
-      </c>
-      <c r="AT35" t="s">
-        <v>536</v>
       </c>
       <c r="AU35" t="s">
         <v>10</v>
@@ -11207,19 +11201,19 @@
         <v>175</v>
       </c>
       <c r="AZ35" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="BA35" t="s">
+        <v>612</v>
+      </c>
+      <c r="BB35" t="s">
         <v>613</v>
       </c>
-      <c r="BB35" t="s">
-        <v>614</v>
-      </c>
       <c r="BC35">
-        <v>0.99623532634854861</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD35">
-        <v>69.01901694327529</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11251,10 +11245,10 @@
         <v>265</v>
       </c>
       <c r="L36">
-        <v>2.2140559413717158</v>
+        <v>11.049590277797785</v>
       </c>
       <c r="M36">
-        <v>0.17924996447431779</v>
+        <v>0.19454864451673889</v>
       </c>
       <c r="O36" t="s">
         <v>272</v>
@@ -11284,25 +11278,25 @@
         <v>325</v>
       </c>
       <c r="Y36" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="Z36" t="s">
         <v>362</v>
       </c>
       <c r="AA36">
-        <v>0.99756610784588629</v>
+        <v>0.99759093327931103</v>
       </c>
       <c r="AB36">
-        <v>44.621356158751233</v>
+        <v>44.16622321263192</v>
       </c>
       <c r="AD36" t="s">
         <v>272</v>
       </c>
       <c r="AE36" t="s">
+        <v>417</v>
+      </c>
+      <c r="AF36" t="s">
         <v>418</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>419</v>
       </c>
       <c r="AG36" t="s">
         <v>10</v>
@@ -11317,28 +11311,28 @@
         <v>175</v>
       </c>
       <c r="AL36" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AM36" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AN36" t="s">
-        <v>478</v>
+        <v>343</v>
       </c>
       <c r="AO36">
-        <v>0.99804155179341392</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP36">
-        <v>35.904883787411507</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR36" t="s">
         <v>272</v>
       </c>
       <c r="AS36" t="s">
+        <v>536</v>
+      </c>
+      <c r="AT36" t="s">
         <v>537</v>
-      </c>
-      <c r="AT36" t="s">
-        <v>538</v>
       </c>
       <c r="AU36" t="s">
         <v>10</v>
@@ -11353,19 +11347,19 @@
         <v>175</v>
       </c>
       <c r="AZ36" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="BA36" t="s">
+        <v>614</v>
+      </c>
+      <c r="BB36" t="s">
         <v>615</v>
       </c>
-      <c r="BB36" t="s">
-        <v>616</v>
-      </c>
       <c r="BC36">
-        <v>0.99895994357772033</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD36">
-        <v>19.067701075126294</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11397,10 +11391,10 @@
         <v>266</v>
       </c>
       <c r="L37">
-        <v>6.2355425421755246</v>
+        <v>2.0672282720381219</v>
       </c>
       <c r="M37">
-        <v>0.1685465489224991</v>
+        <v>0.1897242685700597</v>
       </c>
       <c r="O37" t="s">
         <v>272</v>
@@ -11430,25 +11424,25 @@
         <v>327</v>
       </c>
       <c r="Y37" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Z37" t="s">
         <v>363</v>
       </c>
       <c r="AA37">
-        <v>0.99636728996375623</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB37">
-        <v>66.599683997802714</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD37" t="s">
         <v>272</v>
       </c>
       <c r="AE37" t="s">
+        <v>419</v>
+      </c>
+      <c r="AF37" t="s">
         <v>420</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>421</v>
       </c>
       <c r="AG37" t="s">
         <v>10</v>
@@ -11463,13 +11457,13 @@
         <v>175</v>
       </c>
       <c r="AL37" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AM37" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AN37" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AO37">
         <v>0.99508023417818925</v>
@@ -11481,10 +11475,10 @@
         <v>272</v>
       </c>
       <c r="AS37" t="s">
+        <v>538</v>
+      </c>
+      <c r="AT37" t="s">
         <v>539</v>
-      </c>
-      <c r="AT37" t="s">
-        <v>540</v>
       </c>
       <c r="AU37" t="s">
         <v>10</v>
@@ -11499,19 +11493,19 @@
         <v>175</v>
       </c>
       <c r="AZ37" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="BA37" t="s">
+        <v>616</v>
+      </c>
+      <c r="BB37" t="s">
         <v>617</v>
       </c>
-      <c r="BB37" t="s">
-        <v>618</v>
-      </c>
       <c r="BC37">
-        <v>0.99015836110796274</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD37">
-        <v>180.43004635401576</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11543,10 +11537,10 @@
         <v>267</v>
       </c>
       <c r="L38">
-        <v>8.5054017076497139</v>
+        <v>6.2367051121823778</v>
       </c>
       <c r="M38">
-        <v>0.1737818205315152</v>
+        <v>0.19008013066509069</v>
       </c>
       <c r="O38" t="s">
         <v>272</v>
@@ -11576,25 +11570,25 @@
         <v>329</v>
       </c>
       <c r="Y38" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Z38" t="s">
         <v>364</v>
       </c>
       <c r="AA38">
-        <v>0.99856748800713691</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB38">
-        <v>26.26271986915707</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD38" t="s">
         <v>272</v>
       </c>
       <c r="AE38" t="s">
+        <v>421</v>
+      </c>
+      <c r="AF38" t="s">
         <v>422</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>423</v>
       </c>
       <c r="AG38" t="s">
         <v>10</v>
@@ -11609,28 +11603,28 @@
         <v>175</v>
       </c>
       <c r="AL38" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AM38" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AN38" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AO38">
-        <v>0.99940622505963084</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP38">
-        <v>10.885873906767051</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR38" t="s">
         <v>272</v>
       </c>
       <c r="AS38" t="s">
+        <v>540</v>
+      </c>
+      <c r="AT38" t="s">
         <v>541</v>
-      </c>
-      <c r="AT38" t="s">
-        <v>542</v>
       </c>
       <c r="AU38" t="s">
         <v>10</v>
@@ -11645,19 +11639,19 @@
         <v>175</v>
       </c>
       <c r="AZ38" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BA38" t="s">
+        <v>618</v>
+      </c>
+      <c r="BB38" t="s">
         <v>619</v>
       </c>
-      <c r="BB38" t="s">
-        <v>620</v>
-      </c>
       <c r="BC38">
-        <v>0.97803702976044449</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD38">
-        <v>402.65445439185123</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11689,10 +11683,10 @@
         <v>268</v>
       </c>
       <c r="L39">
-        <v>4.3103819501195213</v>
+        <v>3.4507474395717592</v>
       </c>
       <c r="M39">
-        <v>0.16638536910986701</v>
+        <v>0.18572183333239789</v>
       </c>
       <c r="O39" t="s">
         <v>272</v>
@@ -11722,25 +11716,25 @@
         <v>331</v>
       </c>
       <c r="Y39" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="Z39" t="s">
         <v>365</v>
       </c>
       <c r="AA39">
-        <v>0.9488788277802801</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB39">
-        <v>937.22149069486488</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD39" t="s">
         <v>272</v>
       </c>
       <c r="AE39" t="s">
+        <v>423</v>
+      </c>
+      <c r="AF39" t="s">
         <v>424</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>425</v>
       </c>
       <c r="AG39" t="s">
         <v>10</v>
@@ -11755,28 +11749,28 @@
         <v>175</v>
       </c>
       <c r="AL39" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AM39" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AN39" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AO39">
-        <v>0.99863922747017897</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP39">
-        <v>24.947496380053089</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR39" t="s">
         <v>272</v>
       </c>
       <c r="AS39" t="s">
+        <v>542</v>
+      </c>
+      <c r="AT39" t="s">
         <v>543</v>
-      </c>
-      <c r="AT39" t="s">
-        <v>544</v>
       </c>
       <c r="AU39" t="s">
         <v>10</v>
@@ -11791,19 +11785,19 @@
         <v>175</v>
       </c>
       <c r="AZ39" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="BA39" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="BB39" t="s">
-        <v>622</v>
+        <v>354</v>
       </c>
       <c r="BC39">
-        <v>0.99234935324205875</v>
+        <v>0.98605307635189521</v>
       </c>
       <c r="BD39">
-        <v>140.26185722892211</v>
+        <v>255.693600215255</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11835,10 +11829,10 @@
         <v>269</v>
       </c>
       <c r="L40">
-        <v>4.1704201808042445</v>
+        <v>2.1926901847120215</v>
       </c>
       <c r="M40">
-        <v>0.1729732681063105</v>
+        <v>0.18550629799122259</v>
       </c>
       <c r="O40" t="s">
         <v>272</v>
@@ -11868,25 +11862,25 @@
         <v>333</v>
       </c>
       <c r="Y40" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Z40" t="s">
         <v>366</v>
       </c>
       <c r="AA40">
-        <v>0.99850557699173803</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB40">
-        <v>27.397755151469518</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD40" t="s">
         <v>272</v>
       </c>
       <c r="AE40" t="s">
+        <v>425</v>
+      </c>
+      <c r="AF40" t="s">
         <v>426</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>427</v>
       </c>
       <c r="AG40" t="s">
         <v>10</v>
@@ -11901,13 +11895,13 @@
         <v>175</v>
       </c>
       <c r="AL40" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AM40" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AN40" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="AO40">
         <v>0.99192535126433146</v>
@@ -11919,10 +11913,10 @@
         <v>272</v>
       </c>
       <c r="AS40" t="s">
+        <v>544</v>
+      </c>
+      <c r="AT40" t="s">
         <v>545</v>
-      </c>
-      <c r="AT40" t="s">
-        <v>546</v>
       </c>
       <c r="AU40" t="s">
         <v>10</v>
@@ -11937,19 +11931,19 @@
         <v>175</v>
       </c>
       <c r="AZ40" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="BA40" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="BB40" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="BC40">
-        <v>0.9205295464439136</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD40">
-        <v>1456.9583151949184</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -11981,10 +11975,10 @@
         <v>270</v>
       </c>
       <c r="L41">
-        <v>1.8808781416844131</v>
+        <v>6.3183450599935256</v>
       </c>
       <c r="M41">
-        <v>0.17266493010223849</v>
+        <v>0.19209496103447071</v>
       </c>
       <c r="O41" t="s">
         <v>272</v>
@@ -12014,25 +12008,25 @@
         <v>335</v>
       </c>
       <c r="Y41" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="Z41" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="AA41">
-        <v>0.99866775225229476</v>
+        <v>0.98910041547393335</v>
       </c>
       <c r="AB41">
-        <v>24.424542041262942</v>
+        <v>199.82571631122156</v>
       </c>
       <c r="AD41" t="s">
         <v>272</v>
       </c>
       <c r="AE41" t="s">
+        <v>427</v>
+      </c>
+      <c r="AF41" t="s">
         <v>428</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>429</v>
       </c>
       <c r="AG41" t="s">
         <v>10</v>
@@ -12047,28 +12041,28 @@
         <v>175</v>
       </c>
       <c r="AL41" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AM41" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AN41" t="s">
-        <v>339</v>
+        <v>485</v>
       </c>
       <c r="AO41">
-        <v>0.98092693557487454</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP41">
-        <v>349.67284779396647</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR41" t="s">
         <v>272</v>
       </c>
       <c r="AS41" t="s">
+        <v>546</v>
+      </c>
+      <c r="AT41" t="s">
         <v>547</v>
-      </c>
-      <c r="AT41" t="s">
-        <v>548</v>
       </c>
       <c r="AU41" t="s">
         <v>10</v>
@@ -12083,19 +12077,19 @@
         <v>175</v>
       </c>
       <c r="AZ41" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="BA41" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="BB41" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="BC41">
-        <v>0.99220908762204307</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD41">
-        <v>142.83339359587785</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12103,10 +12097,10 @@
         <v>272</v>
       </c>
       <c r="AS42" t="s">
+        <v>548</v>
+      </c>
+      <c r="AT42" t="s">
         <v>549</v>
-      </c>
-      <c r="AT42" t="s">
-        <v>550</v>
       </c>
       <c r="AU42" t="s">
         <v>10</v>
@@ -12121,19 +12115,19 @@
         <v>175</v>
       </c>
       <c r="AZ42" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="BA42" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="BB42" t="s">
-        <v>345</v>
+        <v>626</v>
       </c>
       <c r="BC42">
-        <v>0.97591598065988894</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD42">
-        <v>441.54035456870389</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12141,10 +12135,10 @@
         <v>272</v>
       </c>
       <c r="AS43" t="s">
+        <v>550</v>
+      </c>
+      <c r="AT43" t="s">
         <v>551</v>
-      </c>
-      <c r="AT43" t="s">
-        <v>552</v>
       </c>
       <c r="AU43" t="s">
         <v>10</v>
@@ -12159,19 +12153,19 @@
         <v>175</v>
       </c>
       <c r="AZ43" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="BA43" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="BB43" t="s">
-        <v>629</v>
+        <v>343</v>
       </c>
       <c r="BC43">
-        <v>0.99412039195829205</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD43">
-        <v>107.79281409797902</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12179,10 +12173,10 @@
         <v>272</v>
       </c>
       <c r="AS44" t="s">
+        <v>552</v>
+      </c>
+      <c r="AT44" t="s">
         <v>553</v>
-      </c>
-      <c r="AT44" t="s">
-        <v>554</v>
       </c>
       <c r="AU44" t="s">
         <v>10</v>
@@ -12197,19 +12191,19 @@
         <v>175</v>
       </c>
       <c r="AZ44" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BA44" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="BB44" t="s">
-        <v>631</v>
+        <v>343</v>
       </c>
       <c r="BC44">
-        <v>0.98881218539944515</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD44">
-        <v>205.10993434350485</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12217,10 +12211,10 @@
         <v>272</v>
       </c>
       <c r="AS45" t="s">
+        <v>554</v>
+      </c>
+      <c r="AT45" t="s">
         <v>555</v>
-      </c>
-      <c r="AT45" t="s">
-        <v>556</v>
       </c>
       <c r="AU45" t="s">
         <v>10</v>
@@ -12235,19 +12229,19 @@
         <v>175</v>
       </c>
       <c r="AZ45" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BA45" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="BB45" t="s">
-        <v>633</v>
+        <v>343</v>
       </c>
       <c r="BC45">
-        <v>0.99114508565756532</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD45">
-        <v>162.34009627796874</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12255,10 +12249,10 @@
         <v>272</v>
       </c>
       <c r="AS46" t="s">
+        <v>556</v>
+      </c>
+      <c r="AT46" t="s">
         <v>557</v>
-      </c>
-      <c r="AT46" t="s">
-        <v>558</v>
       </c>
       <c r="AU46" t="s">
         <v>10</v>
@@ -12273,19 +12267,19 @@
         <v>175</v>
       </c>
       <c r="AZ46" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="BA46" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="BB46" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="BC46">
-        <v>0.99561586640696276</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD46">
-        <v>80.375782539015233</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12293,10 +12287,10 @@
         <v>272</v>
       </c>
       <c r="AS47" t="s">
+        <v>558</v>
+      </c>
+      <c r="AT47" t="s">
         <v>559</v>
-      </c>
-      <c r="AT47" t="s">
-        <v>560</v>
       </c>
       <c r="AU47" t="s">
         <v>10</v>
@@ -12311,19 +12305,19 @@
         <v>175</v>
       </c>
       <c r="AZ47" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="BA47" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="BB47" t="s">
-        <v>358</v>
+        <v>633</v>
       </c>
       <c r="BC47">
-        <v>0.98235584693125277</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD47">
-        <v>323.47613959369914</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12331,10 +12325,10 @@
         <v>272</v>
       </c>
       <c r="AS48" t="s">
+        <v>560</v>
+      </c>
+      <c r="AT48" t="s">
         <v>561</v>
-      </c>
-      <c r="AT48" t="s">
-        <v>562</v>
       </c>
       <c r="AU48" t="s">
         <v>10</v>
@@ -12349,19 +12343,19 @@
         <v>175</v>
       </c>
       <c r="AZ48" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="BA48" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="BB48" t="s">
-        <v>436</v>
+        <v>592</v>
       </c>
       <c r="BC48">
-        <v>0.95726256957223688</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD48">
-        <v>783.51955784232393</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12369,10 +12363,10 @@
         <v>272</v>
       </c>
       <c r="AS49" t="s">
+        <v>562</v>
+      </c>
+      <c r="AT49" t="s">
         <v>563</v>
-      </c>
-      <c r="AT49" t="s">
-        <v>564</v>
       </c>
       <c r="AU49" t="s">
         <v>10</v>
@@ -12387,19 +12381,19 @@
         <v>175</v>
       </c>
       <c r="AZ49" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="BA49" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="BB49" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="BC49">
-        <v>0.99603667376986049</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD49">
-        <v>72.660980885890424</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12407,10 +12401,10 @@
         <v>272</v>
       </c>
       <c r="AS50" t="s">
+        <v>564</v>
+      </c>
+      <c r="AT50" t="s">
         <v>565</v>
-      </c>
-      <c r="AT50" t="s">
-        <v>566</v>
       </c>
       <c r="AU50" t="s">
         <v>10</v>
@@ -12425,19 +12419,19 @@
         <v>175</v>
       </c>
       <c r="AZ50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="BA50" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="BB50" t="s">
-        <v>583</v>
+        <v>638</v>
       </c>
       <c r="BC50">
-        <v>0.97589985979527272</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD50">
-        <v>441.83590375333313</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12445,10 +12439,10 @@
         <v>272</v>
       </c>
       <c r="AS51" t="s">
+        <v>566</v>
+      </c>
+      <c r="AT51" t="s">
         <v>567</v>
-      </c>
-      <c r="AT51" t="s">
-        <v>568</v>
       </c>
       <c r="AU51" t="s">
         <v>10</v>
@@ -12463,19 +12457,19 @@
         <v>175</v>
       </c>
       <c r="AZ51" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="BA51" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="BB51" t="s">
-        <v>446</v>
+        <v>354</v>
       </c>
       <c r="BC51">
-        <v>0.9437657388784082</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD51">
-        <v>1030.9614538958492</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12483,10 +12477,10 @@
         <v>272</v>
       </c>
       <c r="AS52" t="s">
+        <v>568</v>
+      </c>
+      <c r="AT52" t="s">
         <v>569</v>
-      </c>
-      <c r="AT52" t="s">
-        <v>570</v>
       </c>
       <c r="AU52" t="s">
         <v>10</v>
@@ -12501,19 +12495,19 @@
         <v>175</v>
       </c>
       <c r="AZ52" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="BA52" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="BB52" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="BC52">
-        <v>0.99602290686668338</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD52">
-        <v>72.91337411080552</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12521,10 +12515,10 @@
         <v>272</v>
       </c>
       <c r="AS53" t="s">
+        <v>570</v>
+      </c>
+      <c r="AT53" t="s">
         <v>571</v>
-      </c>
-      <c r="AT53" t="s">
-        <v>572</v>
       </c>
       <c r="AU53" t="s">
         <v>10</v>
@@ -12539,19 +12533,19 @@
         <v>175</v>
       </c>
       <c r="AZ53" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BA53" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="BB53" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="BC53">
-        <v>0.98822137145239475</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD53">
-        <v>215.94152337276336</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12559,10 +12553,10 @@
         <v>272</v>
       </c>
       <c r="AS54" t="s">
+        <v>572</v>
+      </c>
+      <c r="AT54" t="s">
         <v>573</v>
-      </c>
-      <c r="AT54" t="s">
-        <v>574</v>
       </c>
       <c r="AU54" t="s">
         <v>10</v>
@@ -12577,13 +12571,13 @@
         <v>175</v>
       </c>
       <c r="AZ54" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BA54" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="BB54" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="BC54">
         <v>0.99284590877035406</v>
@@ -12598,7 +12592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E16207-4280-4960-B7A6-FFEABF17BBB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0107827A-9ACA-401A-A512-26E747AA4C17}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12689,10 +12683,10 @@
         <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D11" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -12707,25 +12701,25 @@
         <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="K11" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="L11">
-        <v>6.1151684514715345</v>
+        <v>27.131882337818411</v>
       </c>
       <c r="M11">
-        <v>0.44244733217755411</v>
+        <v>0.13421919246645389</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
       </c>
       <c r="P11" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="Q11" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -12740,10 +12734,10 @@
         <v>175</v>
       </c>
       <c r="W11" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="X11" t="s">
-        <v>587</v>
+        <v>627</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12757,10 +12751,10 @@
         <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -12775,25 +12769,25 @@
         <v>175</v>
       </c>
       <c r="J12" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="K12" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="L12">
-        <v>4.1221966299799098</v>
+        <v>30.590093860622108</v>
       </c>
       <c r="M12">
-        <v>0.47272019788829328</v>
+        <v>0.1625792625494113</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
       </c>
       <c r="P12" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="Q12" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -12808,10 +12802,10 @@
         <v>175</v>
       </c>
       <c r="W12" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="X12" t="s">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12825,10 +12819,10 @@
         <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D13" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -12843,25 +12837,25 @@
         <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="K13" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="L13">
-        <v>6.7028485191473308E-2</v>
+        <v>27.017887629498883</v>
       </c>
       <c r="M13">
-        <v>0.41432793234675691</v>
+        <v>0.20595237107142639</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
       </c>
       <c r="P13" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="Q13" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -12876,10 +12870,10 @@
         <v>175</v>
       </c>
       <c r="W13" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="X13" t="s">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12893,10 +12887,10 @@
         <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D14" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -12911,25 +12905,25 @@
         <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="K14" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="L14">
-        <v>1.3102559495532347</v>
+        <v>15.703622047270191</v>
       </c>
       <c r="M14">
-        <v>0.51823166137173471</v>
+        <v>0.2902999058993756</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
       </c>
       <c r="P14" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="Q14" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -12944,10 +12938,10 @@
         <v>175</v>
       </c>
       <c r="W14" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="X14" t="s">
-        <v>627</v>
+        <v>601</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12961,10 +12955,10 @@
         <v>171</v>
       </c>
       <c r="C15" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D15" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -12979,25 +12973,25 @@
         <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="K15" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="L15">
-        <v>51.171736048895305</v>
+        <v>24.074478129461852</v>
       </c>
       <c r="M15">
-        <v>0.1753269736233318</v>
+        <v>0.32175887833734967</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
       </c>
       <c r="P15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="Q15" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -13012,10 +13006,10 @@
         <v>175</v>
       </c>
       <c r="W15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="X15" t="s">
-        <v>637</v>
+        <v>585</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13029,10 +13023,10 @@
         <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D16" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -13047,25 +13041,25 @@
         <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="K16" t="s">
         <v>471</v>
       </c>
       <c r="L16">
-        <v>27.131882337818411</v>
+        <v>6.1151684514715345</v>
       </c>
       <c r="M16">
-        <v>0.13421919246645389</v>
+        <v>0.44244733217755411</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
       </c>
       <c r="P16" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="Q16" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -13080,10 +13074,10 @@
         <v>175</v>
       </c>
       <c r="W16" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="X16" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13097,10 +13091,10 @@
         <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D17" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -13115,25 +13109,25 @@
         <v>175</v>
       </c>
       <c r="J17" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K17" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="L17">
-        <v>8.7915989873091043</v>
+        <v>4.1221966299799098</v>
       </c>
       <c r="M17">
-        <v>0.33157900311052629</v>
+        <v>0.47272019788829328</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
       </c>
       <c r="P17" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="Q17" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -13148,10 +13142,10 @@
         <v>175</v>
       </c>
       <c r="W17" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="X17" t="s">
-        <v>607</v>
+        <v>577</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13165,10 +13159,10 @@
         <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D18" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -13183,25 +13177,25 @@
         <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K18" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="L18">
-        <v>26.915511431987859</v>
+        <v>6.7028485191473308E-2</v>
       </c>
       <c r="M18">
-        <v>0.17204244166879709</v>
+        <v>0.41432793234675691</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
       </c>
       <c r="P18" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="Q18" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -13216,16 +13210,16 @@
         <v>175</v>
       </c>
       <c r="W18" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="X18" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="Y18">
-        <v>28.478249999999999</v>
+        <v>22.079249999999998</v>
       </c>
       <c r="Z18">
-        <v>0.31013048721759129</v>
+        <v>0.3223061905611202</v>
       </c>
     </row>
     <row r="19" spans="2:26">
@@ -13233,10 +13227,10 @@
         <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D19" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -13251,25 +13245,25 @@
         <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="K19" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="L19">
-        <v>7.5025171344716721</v>
+        <v>1.3102559495532347</v>
       </c>
       <c r="M19">
-        <v>0.102078386690078</v>
+        <v>0.51823166137173471</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
       </c>
       <c r="P19" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="Q19" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -13284,16 +13278,16 @@
         <v>175</v>
       </c>
       <c r="W19" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="X19" t="s">
         <v>581</v>
       </c>
       <c r="Y19">
-        <v>22.079249999999998</v>
+        <v>29.961749999999999</v>
       </c>
       <c r="Z19">
-        <v>0.3223061905611202</v>
+        <v>0.33421489525964382</v>
       </c>
     </row>
     <row r="20" spans="2:26">
@@ -13301,10 +13295,10 @@
         <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D20" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -13319,25 +13313,25 @@
         <v>175</v>
       </c>
       <c r="J20" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="K20" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="L20">
-        <v>21.853336570084423</v>
+        <v>44.894334115294185</v>
       </c>
       <c r="M20">
-        <v>0.2470260197032213</v>
+        <v>0.26214900595896268</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
       </c>
       <c r="P20" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="Q20" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -13352,16 +13346,16 @@
         <v>175</v>
       </c>
       <c r="W20" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="X20" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="Y20">
-        <v>29.961749999999999</v>
+        <v>28.478249999999999</v>
       </c>
       <c r="Z20">
-        <v>0.33421489525964382</v>
+        <v>0.31013048721759129</v>
       </c>
     </row>
     <row r="21" spans="2:26">
@@ -13369,10 +13363,10 @@
         <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D21" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -13387,25 +13381,25 @@
         <v>175</v>
       </c>
       <c r="J21" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="K21" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="L21">
-        <v>40.036304639772588</v>
+        <v>14.358494358107757</v>
       </c>
       <c r="M21">
-        <v>0.22158847806059459</v>
+        <v>0.48737624583080358</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
       </c>
       <c r="P21" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="Q21" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -13420,10 +13414,10 @@
         <v>175</v>
       </c>
       <c r="W21" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="X21" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13437,10 +13431,10 @@
         <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D22" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -13455,25 +13449,25 @@
         <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="K22" t="s">
-        <v>481</v>
+        <v>431</v>
       </c>
       <c r="L22">
-        <v>7.0903888161806279</v>
+        <v>39.022668784713879</v>
       </c>
       <c r="M22">
-        <v>0.126349887785319</v>
+        <v>0.30226720130549178</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
       </c>
       <c r="P22" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="Q22" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -13488,16 +13482,16 @@
         <v>175</v>
       </c>
       <c r="W22" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="X22" t="s">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="Y22">
-        <v>82.576499999999996</v>
+        <v>75.481499999999997</v>
       </c>
       <c r="Z22">
-        <v>0.3946475348851019</v>
+        <v>0.39947482218024288</v>
       </c>
     </row>
     <row r="23" spans="2:26">
@@ -13505,10 +13499,10 @@
         <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D23" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -13523,25 +13517,25 @@
         <v>175</v>
       </c>
       <c r="J23" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="K23" t="s">
         <v>483</v>
       </c>
       <c r="L23">
-        <v>16.970662525397827</v>
+        <v>33.851015501811965</v>
       </c>
       <c r="M23">
-        <v>0.2876476609673595</v>
+        <v>0.17836569756942919</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
       </c>
       <c r="P23" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="Q23" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -13556,10 +13550,10 @@
         <v>175</v>
       </c>
       <c r="W23" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="X23" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13573,10 +13567,10 @@
         <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D24" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -13591,25 +13585,25 @@
         <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="K24" t="s">
-        <v>473</v>
+        <v>445</v>
       </c>
       <c r="L24">
-        <v>2.5242004930684354</v>
+        <v>29.76120824924126</v>
       </c>
       <c r="M24">
-        <v>9.3541201112904898E-2</v>
+        <v>0.1835874284667649</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
       </c>
       <c r="P24" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="Q24" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -13624,16 +13618,16 @@
         <v>175</v>
       </c>
       <c r="W24" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="X24" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="Y24">
-        <v>75.512249999999995</v>
+        <v>82.607249999999993</v>
       </c>
       <c r="Z24">
-        <v>0.42052864752994251</v>
+        <v>0.4138948789420363</v>
       </c>
     </row>
     <row r="25" spans="2:26">
@@ -13641,10 +13635,10 @@
         <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D25" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -13659,25 +13653,25 @@
         <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="K25" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="L25">
-        <v>5.5071261071764246</v>
+        <v>26.081770464705624</v>
       </c>
       <c r="M25">
-        <v>0.34206800892605482</v>
+        <v>0.33938741610056822</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
       </c>
       <c r="P25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Q25" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -13692,10 +13686,10 @@
         <v>175</v>
       </c>
       <c r="W25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="X25" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="Y25">
         <v>28.239750000000001</v>
@@ -13709,10 +13703,10 @@
         <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D26" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -13727,25 +13721,25 @@
         <v>175</v>
       </c>
       <c r="J26" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="K26" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="L26">
-        <v>8.4886449615793467</v>
+        <v>28.326303899090867</v>
       </c>
       <c r="M26">
-        <v>0.33231574315319728</v>
+        <v>0.31672699232591051</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
       </c>
       <c r="P26" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Q26" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -13760,10 +13754,10 @@
         <v>175</v>
       </c>
       <c r="W26" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="X26" t="s">
-        <v>615</v>
+        <v>588</v>
       </c>
       <c r="Y26">
         <v>1.9132499999999999</v>
@@ -13777,10 +13771,10 @@
         <v>171</v>
       </c>
       <c r="C27" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D27" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -13795,25 +13789,25 @@
         <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K27" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="L27">
-        <v>8.4075540995285696</v>
+        <v>13.047413180463023</v>
       </c>
       <c r="M27">
-        <v>0.28011366210530497</v>
+        <v>0.11846842726897321</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
       </c>
       <c r="P27" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="Q27" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -13828,10 +13822,10 @@
         <v>175</v>
       </c>
       <c r="W27" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="X27" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="Y27">
         <v>63.731250000000003</v>
@@ -13845,10 +13839,10 @@
         <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D28" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -13863,25 +13857,25 @@
         <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K28" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="L28">
-        <v>15.703622047270191</v>
+        <v>23.637816650626842</v>
       </c>
       <c r="M28">
-        <v>0.2902999058993756</v>
+        <v>0.1537391571572389</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
       </c>
       <c r="P28" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="Q28" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="R28" t="s">
         <v>10</v>
@@ -13896,10 +13890,10 @@
         <v>175</v>
       </c>
       <c r="W28" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="X28" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="Y28">
         <v>38.451000000000001</v>
@@ -13913,10 +13907,10 @@
         <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D29" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -13931,25 +13925,25 @@
         <v>175</v>
       </c>
       <c r="J29" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K29" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="L29">
-        <v>24.074478129461852</v>
+        <v>50.076680799526407</v>
       </c>
       <c r="M29">
-        <v>0.32175887833734967</v>
+        <v>0.19002505627190239</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
       </c>
       <c r="P29" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="Q29" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="R29" t="s">
         <v>10</v>
@@ -13964,10 +13958,10 @@
         <v>175</v>
       </c>
       <c r="W29" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="X29" t="s">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="Y29">
         <v>64.533749999999998</v>
@@ -13981,10 +13975,10 @@
         <v>171</v>
       </c>
       <c r="C30" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D30" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -13999,25 +13993,25 @@
         <v>175</v>
       </c>
       <c r="J30" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="K30" t="s">
         <v>479</v>
       </c>
       <c r="L30">
-        <v>12.527007796473459</v>
+        <v>8.4886449615793467</v>
       </c>
       <c r="M30">
-        <v>0.26335249621019208</v>
+        <v>0.33231574315319728</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
       </c>
       <c r="P30" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="Q30" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="R30" t="s">
         <v>10</v>
@@ -14032,10 +14026,10 @@
         <v>175</v>
       </c>
       <c r="W30" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="X30" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="Y30">
         <v>44.370750000000001</v>
@@ -14049,10 +14043,10 @@
         <v>171</v>
       </c>
       <c r="C31" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D31" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -14067,25 +14061,25 @@
         <v>175</v>
       </c>
       <c r="J31" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="K31" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="L31">
-        <v>22.322239264526591</v>
+        <v>8.4075540995285696</v>
       </c>
       <c r="M31">
-        <v>0.24546553943130331</v>
+        <v>0.28011366210530497</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
       </c>
       <c r="P31" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Q31" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="R31" t="s">
         <v>10</v>
@@ -14100,10 +14094,10 @@
         <v>175</v>
       </c>
       <c r="W31" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="X31" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="Y31">
         <v>38.15925</v>
@@ -14117,10 +14111,10 @@
         <v>171</v>
       </c>
       <c r="C32" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D32" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -14135,25 +14129,25 @@
         <v>175</v>
       </c>
       <c r="J32" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="K32" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="L32">
-        <v>13.047413180463023</v>
+        <v>7.5025171344716721</v>
       </c>
       <c r="M32">
-        <v>0.11846842726897321</v>
+        <v>0.102078386690078</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
       </c>
       <c r="P32" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="Q32" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="R32" t="s">
         <v>10</v>
@@ -14168,10 +14162,10 @@
         <v>175</v>
       </c>
       <c r="W32" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="X32" t="s">
-        <v>610</v>
+        <v>580</v>
       </c>
       <c r="Y32">
         <v>3.38625</v>
@@ -14185,10 +14179,10 @@
         <v>171</v>
       </c>
       <c r="C33" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D33" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -14203,25 +14197,25 @@
         <v>175</v>
       </c>
       <c r="J33" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="K33" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="L33">
-        <v>23.637816650626842</v>
+        <v>25.978158470265569</v>
       </c>
       <c r="M33">
-        <v>0.1537391571572389</v>
+        <v>0.22366609886397831</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
       </c>
       <c r="P33" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="Q33" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="R33" t="s">
         <v>10</v>
@@ -14236,10 +14230,10 @@
         <v>175</v>
       </c>
       <c r="W33" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="X33" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="Y33">
         <v>30.597750000000001</v>
@@ -14253,10 +14247,10 @@
         <v>171</v>
       </c>
       <c r="C34" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D34" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -14271,25 +14265,25 @@
         <v>175</v>
       </c>
       <c r="J34" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K34" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="L34">
-        <v>50.076680799526407</v>
+        <v>40.036304639772588</v>
       </c>
       <c r="M34">
-        <v>0.19002505627190239</v>
+        <v>0.22158847806059459</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
       </c>
       <c r="P34" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="Q34" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="R34" t="s">
         <v>10</v>
@@ -14304,10 +14298,10 @@
         <v>175</v>
       </c>
       <c r="W34" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="X34" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14321,10 +14315,10 @@
         <v>171</v>
       </c>
       <c r="C35" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D35" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -14339,25 +14333,25 @@
         <v>175</v>
       </c>
       <c r="J35" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K35" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="L35">
-        <v>44.894334115294185</v>
+        <v>7.0903888161806279</v>
       </c>
       <c r="M35">
-        <v>0.26214900595896268</v>
+        <v>0.126349887785319</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
       </c>
       <c r="P35" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="Q35" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="R35" t="s">
         <v>10</v>
@@ -14372,10 +14366,10 @@
         <v>175</v>
       </c>
       <c r="W35" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="X35" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="Y35">
         <v>58.474499999999999</v>
@@ -14389,10 +14383,10 @@
         <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D36" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -14407,25 +14401,25 @@
         <v>175</v>
       </c>
       <c r="J36" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K36" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="L36">
-        <v>14.358494358107757</v>
+        <v>16.970662525397827</v>
       </c>
       <c r="M36">
-        <v>0.48737624583080358</v>
+        <v>0.2876476609673595</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
       </c>
       <c r="P36" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="Q36" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="R36" t="s">
         <v>10</v>
@@ -14440,10 +14434,10 @@
         <v>175</v>
       </c>
       <c r="W36" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="X36" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="Y36">
         <v>18.711749999999999</v>
@@ -14457,10 +14451,10 @@
         <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D37" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -14475,25 +14469,25 @@
         <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="K37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="L37">
-        <v>39.022668784713879</v>
+        <v>2.5242004930684354</v>
       </c>
       <c r="M37">
-        <v>0.30226720130549178</v>
+        <v>9.3541201112904898E-2</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
       </c>
       <c r="P37" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="Q37" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="R37" t="s">
         <v>10</v>
@@ -14508,10 +14502,10 @@
         <v>175</v>
       </c>
       <c r="W37" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="X37" t="s">
-        <v>594</v>
+        <v>632</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14525,10 +14519,10 @@
         <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D38" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -14543,25 +14537,25 @@
         <v>175</v>
       </c>
       <c r="J38" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K38" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="L38">
-        <v>33.851015501811965</v>
+        <v>5.5071261071764246</v>
       </c>
       <c r="M38">
-        <v>0.17836569756942919</v>
+        <v>0.34206800892605482</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
       </c>
       <c r="P38" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="Q38" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="R38" t="s">
         <v>10</v>
@@ -14576,10 +14570,10 @@
         <v>175</v>
       </c>
       <c r="W38" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="X38" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14593,10 +14587,10 @@
         <v>171</v>
       </c>
       <c r="C39" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D39" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -14611,25 +14605,25 @@
         <v>175</v>
       </c>
       <c r="J39" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K39" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="L39">
-        <v>29.76120824924126</v>
+        <v>12.527007796473459</v>
       </c>
       <c r="M39">
-        <v>0.1835874284667649</v>
+        <v>0.26335249621019208</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
       </c>
       <c r="P39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="Q39" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="R39" t="s">
         <v>10</v>
@@ -14644,10 +14638,10 @@
         <v>175</v>
       </c>
       <c r="W39" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="X39" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14661,10 +14655,10 @@
         <v>171</v>
       </c>
       <c r="C40" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D40" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -14679,25 +14673,25 @@
         <v>175</v>
       </c>
       <c r="J40" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K40" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="L40">
-        <v>26.081770464705624</v>
+        <v>22.322239264526591</v>
       </c>
       <c r="M40">
-        <v>0.33938741610056822</v>
+        <v>0.24546553943130331</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
       </c>
       <c r="P40" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="Q40" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="R40" t="s">
         <v>10</v>
@@ -14712,10 +14706,10 @@
         <v>175</v>
       </c>
       <c r="W40" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="X40" t="s">
-        <v>608</v>
+        <v>578</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14729,10 +14723,10 @@
         <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D41" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -14747,25 +14741,25 @@
         <v>175</v>
       </c>
       <c r="J41" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K41" t="s">
-        <v>486</v>
+        <v>448</v>
       </c>
       <c r="L41">
-        <v>28.326303899090867</v>
+        <v>25.14604307789013</v>
       </c>
       <c r="M41">
-        <v>0.31672699232591051</v>
+        <v>0.2214146377764582</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
       </c>
       <c r="P41" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="Q41" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="R41" t="s">
         <v>10</v>
@@ -14780,10 +14774,10 @@
         <v>175</v>
       </c>
       <c r="W41" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="X41" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14797,10 +14791,10 @@
         <v>171</v>
       </c>
       <c r="P42" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="Q42" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="R42" t="s">
         <v>10</v>
@@ -14815,10 +14809,10 @@
         <v>175</v>
       </c>
       <c r="W42" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="X42" t="s">
-        <v>638</v>
+        <v>589</v>
       </c>
       <c r="Y42">
         <v>27.642749999999999</v>
@@ -14832,10 +14826,10 @@
         <v>171</v>
       </c>
       <c r="P43" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="Q43" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="R43" t="s">
         <v>10</v>
@@ -14850,10 +14844,10 @@
         <v>175</v>
       </c>
       <c r="W43" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="X43" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14867,10 +14861,10 @@
         <v>171</v>
       </c>
       <c r="P44" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="Q44" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="R44" t="s">
         <v>10</v>
@@ -14885,10 +14879,10 @@
         <v>175</v>
       </c>
       <c r="W44" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="X44" t="s">
-        <v>641</v>
+        <v>593</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14902,10 +14896,10 @@
         <v>171</v>
       </c>
       <c r="P45" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="Q45" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="R45" t="s">
         <v>10</v>
@@ -14920,10 +14914,10 @@
         <v>175</v>
       </c>
       <c r="W45" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="X45" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14937,10 +14931,10 @@
         <v>171</v>
       </c>
       <c r="P46" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="Q46" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="R46" t="s">
         <v>10</v>
@@ -14955,10 +14949,10 @@
         <v>175</v>
       </c>
       <c r="W46" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="X46" t="s">
-        <v>582</v>
+        <v>634</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14972,10 +14966,10 @@
         <v>171</v>
       </c>
       <c r="P47" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="Q47" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="R47" t="s">
         <v>10</v>
@@ -14990,10 +14984,10 @@
         <v>175</v>
       </c>
       <c r="W47" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="X47" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -15007,10 +15001,10 @@
         <v>171</v>
       </c>
       <c r="P48" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="Q48" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="R48" t="s">
         <v>10</v>
@@ -15025,10 +15019,10 @@
         <v>175</v>
       </c>
       <c r="W48" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="X48" t="s">
-        <v>640</v>
+        <v>591</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15042,10 +15036,10 @@
         <v>171</v>
       </c>
       <c r="P49" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="Q49" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="R49" t="s">
         <v>10</v>
@@ -15060,10 +15054,10 @@
         <v>175</v>
       </c>
       <c r="W49" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="X49" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Y49">
         <v>16.497</v>
@@ -15077,10 +15071,10 @@
         <v>171</v>
       </c>
       <c r="P50" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="Q50" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="R50" t="s">
         <v>10</v>
@@ -15095,10 +15089,10 @@
         <v>175</v>
       </c>
       <c r="W50" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="X50" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15112,10 +15106,10 @@
         <v>171</v>
       </c>
       <c r="P51" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="Q51" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="R51" t="s">
         <v>10</v>
@@ -15130,10 +15124,10 @@
         <v>175</v>
       </c>
       <c r="W51" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="X51" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15147,10 +15141,10 @@
         <v>171</v>
       </c>
       <c r="P52" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="Q52" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="R52" t="s">
         <v>10</v>
@@ -15165,10 +15159,10 @@
         <v>175</v>
       </c>
       <c r="W52" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="X52" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15182,10 +15176,10 @@
         <v>171</v>
       </c>
       <c r="P53" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="Q53" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="R53" t="s">
         <v>10</v>
@@ -15200,10 +15194,10 @@
         <v>175</v>
       </c>
       <c r="W53" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="X53" t="s">
-        <v>642</v>
+        <v>594</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15217,10 +15211,10 @@
         <v>171</v>
       </c>
       <c r="P54" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="Q54" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="R54" t="s">
         <v>10</v>
@@ -15235,10 +15229,10 @@
         <v>175</v>
       </c>
       <c r="W54" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="X54" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15253,7 +15247,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E0B3C01-F851-4F68-A884-5562D216C6C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD0FB8D-38A6-4ADA-89E5-A612BB39B57F}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15311,7 +15305,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -15335,7 +15329,7 @@
         <v>171</v>
       </c>
       <c r="K11" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -15347,12 +15341,12 @@
         <v>276</v>
       </c>
       <c r="P11" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -15370,13 +15364,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="J12" t="s">
         <v>171</v>
       </c>
       <c r="K12" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -15388,12 +15382,12 @@
         <v>276</v>
       </c>
       <c r="P12" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -15411,13 +15405,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="J13" t="s">
         <v>171</v>
       </c>
       <c r="K13" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -15429,12 +15423,12 @@
         <v>276</v>
       </c>
       <c r="P13" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -15452,13 +15446,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="J14" t="s">
         <v>171</v>
       </c>
       <c r="K14" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -15470,12 +15464,12 @@
         <v>276</v>
       </c>
       <c r="P14" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -15493,13 +15487,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="J15" t="s">
         <v>171</v>
       </c>
       <c r="K15" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -15511,12 +15505,12 @@
         <v>276</v>
       </c>
       <c r="P15" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -15540,7 +15534,7 @@
         <v>171</v>
       </c>
       <c r="K16" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -15552,12 +15546,12 @@
         <v>276</v>
       </c>
       <c r="P16" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -15575,13 +15569,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="J17" t="s">
         <v>171</v>
       </c>
       <c r="K17" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -15593,12 +15587,12 @@
         <v>276</v>
       </c>
       <c r="P17" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -15616,13 +15610,13 @@
         <v>2250</v>
       </c>
       <c r="H18" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="J18" t="s">
         <v>171</v>
       </c>
       <c r="K18" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -15634,12 +15628,12 @@
         <v>276</v>
       </c>
       <c r="P18" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -15657,13 +15651,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="J19" t="s">
         <v>171</v>
       </c>
       <c r="K19" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -15675,12 +15669,12 @@
         <v>276</v>
       </c>
       <c r="P19" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -15698,13 +15692,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="J20" t="s">
         <v>171</v>
       </c>
       <c r="K20" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -15716,12 +15710,12 @@
         <v>276</v>
       </c>
       <c r="P20" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -15745,7 +15739,7 @@
         <v>171</v>
       </c>
       <c r="K21" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -15757,12 +15751,12 @@
         <v>276</v>
       </c>
       <c r="P21" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -15780,13 +15774,13 @@
         <v>1100</v>
       </c>
       <c r="H22" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="J22" t="s">
         <v>171</v>
       </c>
       <c r="K22" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -15798,12 +15792,12 @@
         <v>276</v>
       </c>
       <c r="P22" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -15821,13 +15815,13 @@
         <v>30</v>
       </c>
       <c r="H23" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="J23" t="s">
         <v>171</v>
       </c>
       <c r="K23" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -15839,12 +15833,12 @@
         <v>276</v>
       </c>
       <c r="P23" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -15868,7 +15862,7 @@
         <v>171</v>
       </c>
       <c r="K24" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -15880,12 +15874,12 @@
         <v>276</v>
       </c>
       <c r="P24" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -15903,13 +15897,13 @@
         <v>2500</v>
       </c>
       <c r="H25" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="J25" t="s">
         <v>171</v>
       </c>
       <c r="K25" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -15921,12 +15915,12 @@
         <v>276</v>
       </c>
       <c r="P25" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -15944,13 +15938,13 @@
         <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="J26" t="s">
         <v>171</v>
       </c>
       <c r="K26" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -15962,12 +15956,12 @@
         <v>276</v>
       </c>
       <c r="P26" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -15991,7 +15985,7 @@
         <v>171</v>
       </c>
       <c r="K27" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -16003,12 +15997,12 @@
         <v>276</v>
       </c>
       <c r="P27" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -16026,12 +16020,12 @@
         <v>4750</v>
       </c>
       <c r="H28" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -16049,12 +16043,12 @@
         <v>140</v>
       </c>
       <c r="H29" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -16077,7 +16071,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -16095,12 +16089,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -16118,12 +16112,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -16146,7 +16140,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -16164,12 +16158,12 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -16187,12 +16181,12 @@
         <v>2400</v>
       </c>
       <c r="H35" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -16210,12 +16204,12 @@
         <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -16233,12 +16227,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -16261,7 +16255,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -16279,12 +16273,12 @@
         <v>2700</v>
       </c>
       <c r="H39" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -16302,12 +16296,12 @@
         <v>95</v>
       </c>
       <c r="H40" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -16330,7 +16324,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -16348,12 +16342,12 @@
         <v>5500</v>
       </c>
       <c r="H42" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -16371,12 +16365,12 @@
         <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -16399,7 +16393,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -16417,12 +16411,12 @@
         <v>4000</v>
       </c>
       <c r="H45" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -16440,12 +16434,12 @@
         <v>225</v>
       </c>
       <c r="H46" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -16468,7 +16462,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -16486,12 +16480,12 @@
         <v>5500</v>
       </c>
       <c r="H48" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -16509,12 +16503,12 @@
         <v>165</v>
       </c>
       <c r="H49" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -16537,7 +16531,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -16555,12 +16549,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -16578,12 +16572,12 @@
         <v>940</v>
       </c>
       <c r="H52" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -16601,12 +16595,12 @@
         <v>24</v>
       </c>
       <c r="H53" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -16624,12 +16618,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -16652,7 +16646,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -16670,12 +16664,12 @@
         <v>2100</v>
       </c>
       <c r="H56" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -16693,12 +16687,12 @@
         <v>55</v>
       </c>
       <c r="H57" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -16721,7 +16715,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -16739,12 +16733,12 @@
         <v>2400</v>
       </c>
       <c r="H59" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -16762,12 +16756,12 @@
         <v>70</v>
       </c>
       <c r="H60" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -16790,7 +16784,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -16808,12 +16802,12 @@
         <v>2600</v>
       </c>
       <c r="H62" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -16831,15 +16825,15 @@
         <v>80</v>
       </c>
       <c r="H63" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C64" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -16859,10 +16853,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C65" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -16877,15 +16871,15 @@
         <v>0.46</v>
       </c>
       <c r="H65" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C66" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -16900,15 +16894,15 @@
         <v>2760</v>
       </c>
       <c r="H66" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C67" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -16923,15 +16917,15 @@
         <v>85</v>
       </c>
       <c r="H67" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C68" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -16946,15 +16940,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C69" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -16974,10 +16968,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C70" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -16992,15 +16986,15 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H70" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C71" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -17015,15 +17009,15 @@
         <v>2140</v>
       </c>
       <c r="H71" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C72" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -17038,15 +17032,15 @@
         <v>56</v>
       </c>
       <c r="H72" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C73" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -17061,7 +17055,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -17070,7 +17064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835DE53C-393F-4F3B-AF64-C16882EA2F97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E48C342F-7C1D-4678-A1BC-8E67415C451F}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17105,10 +17099,10 @@
         <v>166</v>
       </c>
       <c r="K3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="L3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="M3" t="s">
         <v>169</v>
@@ -17116,13 +17110,13 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" t="s">
+        <v>819</v>
+      </c>
+      <c r="C4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D4" t="s">
         <v>821</v>
-      </c>
-      <c r="C4" t="s">
-        <v>822</v>
-      </c>
-      <c r="D4" t="s">
-        <v>823</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -17131,10 +17125,10 @@
         <v>272</v>
       </c>
       <c r="I4" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="J4" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -17148,13 +17142,13 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C5" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D5" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -17163,10 +17157,10 @@
         <v>272</v>
       </c>
       <c r="I5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="J5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
@@ -17180,13 +17174,13 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
+        <v>823</v>
+      </c>
+      <c r="C6" t="s">
+        <v>824</v>
+      </c>
+      <c r="D6" t="s">
         <v>825</v>
-      </c>
-      <c r="C6" t="s">
-        <v>826</v>
-      </c>
-      <c r="D6" t="s">
-        <v>827</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -17195,10 +17189,10 @@
         <v>272</v>
       </c>
       <c r="I6" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="J6" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -17212,13 +17206,13 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C7" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D7" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -17227,10 +17221,10 @@
         <v>272</v>
       </c>
       <c r="I7" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="J7" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -17244,13 +17238,13 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" t="s">
+        <v>827</v>
+      </c>
+      <c r="C8" t="s">
+        <v>828</v>
+      </c>
+      <c r="D8" t="s">
         <v>829</v>
-      </c>
-      <c r="C8" t="s">
-        <v>830</v>
-      </c>
-      <c r="D8" t="s">
-        <v>831</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -17259,10 +17253,10 @@
         <v>272</v>
       </c>
       <c r="I8" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="J8" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -17276,13 +17270,13 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C9" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D9" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -17291,10 +17285,10 @@
         <v>272</v>
       </c>
       <c r="I9" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="J9" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -17308,13 +17302,13 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
+        <v>831</v>
+      </c>
+      <c r="C10" t="s">
+        <v>832</v>
+      </c>
+      <c r="D10" t="s">
         <v>833</v>
-      </c>
-      <c r="C10" t="s">
-        <v>834</v>
-      </c>
-      <c r="D10" t="s">
-        <v>835</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -17323,10 +17317,10 @@
         <v>272</v>
       </c>
       <c r="I10" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="J10" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -17340,13 +17334,13 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C11" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D11" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -17355,10 +17349,10 @@
         <v>272</v>
       </c>
       <c r="I11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="J11" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="K11" t="s">
         <v>21</v>
@@ -17372,13 +17366,13 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
+        <v>835</v>
+      </c>
+      <c r="C12" t="s">
+        <v>836</v>
+      </c>
+      <c r="D12" t="s">
         <v>837</v>
-      </c>
-      <c r="C12" t="s">
-        <v>838</v>
-      </c>
-      <c r="D12" t="s">
-        <v>839</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -17387,10 +17381,10 @@
         <v>272</v>
       </c>
       <c r="I12" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="J12" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -17404,13 +17398,13 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C13" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D13" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -17419,10 +17413,10 @@
         <v>272</v>
       </c>
       <c r="I13" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="J13" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4CFD238-CC26-4A50-AD5F-086DF4DB40D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EDA2BD3-5A31-4430-B6C7-52FDF84BFFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,24 +949,90 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_027</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_009</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_016</t>
   </si>
   <si>
@@ -979,34 +1045,94 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_solelc_spv_010</t>
@@ -1015,220 +1141,160 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
+  </si>
+  <si>
     <t>e_w216956620-500,e_w216953915-500</t>
   </si>
   <si>
     <t>e_w801582512-275,e_JP4-275,e_JP5-275,e_JP9-500</t>
   </si>
   <si>
+    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
+  </si>
+  <si>
+    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP3-275,e_JP1-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP306-500</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275,e_JP6-275</t>
+  </si>
+  <si>
     <t>e_w106076988-500,e_w174636874-500,e_JP10-500</t>
   </si>
   <si>
     <t>e_JP7-275</t>
   </si>
   <si>
-    <t>e_JP306-500</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w242253500-500,e_w317416612-500,e_w193544791-500,e_JP117-500,e_w242103481-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>e_w315618377-500,e_w256682313-500,e_JP74-500,e_JP25-500,e_w975217734-500,e_JP57-500,e_r17013811-500,e_w315662839-500,e_JP28-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500,e_JP132-500</t>
+    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
+  </si>
+  <si>
+    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w204258596-500,e_w216778426-500,e_w242253500-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
+  </si>
+  <si>
+    <t>e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
+  </si>
+  <si>
+    <t>e_w179863079-275</t>
+  </si>
+  <si>
+    <t>e_JP7-275,e_JP6-275</t>
+  </si>
+  <si>
+    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500</t>
   </si>
   <si>
     <t>e_JP219-500,e_w150065045-500,e_w149843487-500,e_w145079972-500,e_w315461259-500,e_r2269992-500,e_JP132-500</t>
   </si>
   <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500</t>
-  </si>
-  <si>
-    <t>e_w150035494-500,e_JP73-500,e_w66098469-500,e_w315434358-500,e_w250540807-500,e_r15580570-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_w168727982-500,e_w132913106-500,e_w168839127-500,e_w105298089-500,e_w104391636-500,e_JP23-500</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP3-275,e_JP1-275,e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w174636874-500,e_JP10-500,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>e_w179863079-275</t>
-  </si>
-  <si>
-    <t>e_JP7-275,e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500,e_w659138214-500,e_w253566674-500,e_JP19-500,e_w785319805-500,e_w106076988-500,e_w104173570-500,e_w901872431-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_JP292-500,e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500</t>
-  </si>
-  <si>
-    <t>e_JP6-275</t>
-  </si>
-  <si>
-    <t>e_w170974371-500,e_w171066843-500,e_w241828221-500,e_w87538349-500,e_w102958903-500,e_w241822623-500,e_w307942220-500,e_JP218-500</t>
-  </si>
-  <si>
-    <t>e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w170366035-500,e_w116559939-500,e_w142662111-500,e_w209429410-500,e_w315662839-500,e_w210090094-500,e_w459476442-500,e_w209726348-500</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_w186510275-500,e_w185029969-500,e_w172601929-500,e_w187988970-500,e_w204258596-500</t>
-  </si>
-  <si>
-    <t>e_JP296-500,e_w405626236-500,e_w201293312-500,e_w204258596-500,e_w216778426-500,e_w242253500-500,e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>e_JP248-500,e_w307942220-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w421647841-500,e_JP116-500,e_w169031998-500,e_w170589736-500,e_JP156-500,e_JP122-500</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>e_JP9-500,e_JP8-275,e_w1028554758-500</t>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_002</t>
@@ -1243,70 +1309,100 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_023</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wonelc_won_005</t>
@@ -1321,100 +1417,61 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_w170589736-500,e_JP156-500,e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w116559939-500,e_w142662111-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
   </si>
   <si>
     <t>elc_won_002</t>
@@ -1429,67 +1486,97 @@
     <t>e_w174636874-500,e_JP10-500,e_JP9-500,e_w714627759-500</t>
   </si>
   <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w459476442-500,e_w150065045-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w201293312-500,e_w204258596-500,e_w216778426-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w170974371-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
+  </si>
+  <si>
     <t>elc_won_023</t>
   </si>
   <si>
     <t>e_w307942220-500,e_JP248-500,e_JP175-500,e_JP249-500,e_w291678103-500,e_w170605907-500,e_w1038584990-500,e_w109834508-500,e_w161727149-500,e_w169031998-500</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w106076988-500,e_w785319805-500,e_w174636874-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_w216953915-500,e_JP296-500,e_w1037299172-500,e_w172907196-500,e_w722673849-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w201293312-500,e_w204258596-500,e_w216778426-500,e_w242253500-500,e_w1037299172-500,e_w193544791-500,e_w317416612-500,e_w170974371-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP4-275,e_JP8-275,e_JP9-500,e_w1028554758-500,e_w179863079-275,e_JP7-275</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_JP294-500,e_w172601929-500,e_w215451416-500,e_w216502300-500,e_w405626236-500,e_w172144358-500,e_JP296-500</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_w170589736-500,e_JP156-500,e_w169031998-500,e_w170537514-500,e_JP96-500,e_w170247312-500,e_w170850727-500,e_w116559939-500,e_w142662111-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w315434358-500,e_w250540807-500,e_JP41-500,e_JP29-500,e_JP30-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w801582512-275,e_JP5-275,e_JP4-275,e_JP9-500,e_JP3-275,e_JP1-275,e_JP7-275,e_JP6-275,e_w179863079-275</t>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_JP219-500,e_JP132-500</t>
   </si>
   <si>
     <t>elc_won_005</t>
@@ -1501,91 +1588,166 @@
     <t>elc_won_016</t>
   </si>
   <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w256682313-500,e_JP25-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w210090094-500,e_JP219-500,e_w150065045-500,e_w149843487-500,e_w315461259-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w459476442-500,e_w150065045-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w1030329139-500,e_w659138214-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_r2269992-500,e_JP132-500,e_w168727982-500,e_w132913106-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w145079972-500,e_r15580570-500,e_w168839127-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_JP219-500,e_JP132-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w215451416-500,e_w216956620-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_JP74-500,e_w975217734-500,e_JP57-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w659138214-500,e_w106076988-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w204258596-500,e_w317416612-500,e_JP117-500,e_w317511904-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w242103481-500,e_w242253537-500,e_JP137-500,e_JP135-500,e_JP120-500,e_w421647841-500,e_JP116-500,e_w1029010255-500,e_JP122-500,e_w315618377-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_w168839127-500,e_w104391636-500,e_w253566674-500,e_JP19-500,e_JP23-500,e_w104173570-500,e_w901872431-500,e_w106076988-500</t>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wofelc_wof_042</t>
@@ -1600,78 +1762,6 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
@@ -1690,6 +1780,24 @@
     <t>connecting wind offshore to buses in cluster 39</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
@@ -1708,40 +1816,16 @@
     <t>connecting wind offshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_wofelc_wof_013</t>
@@ -1768,88 +1852,136 @@
     <t>connecting wind offshore to buses in cluster 35</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500,e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500,e_JP117-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500,e_JP21-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
   </si>
   <si>
     <t>elc_wof_042</t>
@@ -1861,63 +1993,6 @@
     <t>elc_wof_021</t>
   </si>
   <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500,e_JP117-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500,e_w172907196-500,e_w171066843-500,e_w722673849-500,e_w1037516198-500,e_JP249-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_JP4-275,e_JP1-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500,e_w315461259-500,e_JP132-500,e_w151379730-500,e_w168727982-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500,e_w1029010255-500,e_w315618377-500,e_w256682313-500</t>
-  </si>
-  <si>
-    <t>elc_wof_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>elc_wof_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500,e_JP23-500,e_w104173570-500</t>
-  </si>
-  <si>
     <t>elc_wof_008</t>
   </si>
   <si>
@@ -1933,6 +2008,18 @@
     <t>e_w170247312-500,e_JP219-500</t>
   </si>
   <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
+  </si>
+  <si>
     <t>elc_wof_004</t>
   </si>
   <si>
@@ -1948,34 +2035,16 @@
     <t>e_JP219-500,e_w149843487-500,e_JP132-500,e_w315461259-500</t>
   </si>
   <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500,e_JP9-500,e_JP5-275,e_JP7-275,e_w714627759-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_JP269-500,e_JP292-500,e_w186510275-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500,e_w204258596-500,e_w317416612-500</t>
-  </si>
-  <si>
-    <t>elc_wof_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500,e_JP219-500</t>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_JP6-275,e_w179863079-275</t>
   </si>
   <si>
     <t>elc_wof_013</t>
@@ -1997,75 +2066,6 @@
   </si>
   <si>
     <t>e_JP132-500,e_w105298089-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500,e_w174636874-500,e_w659138214-500,e_w106076988-500,e_JP10-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_JP6-275,e_w179863079-275</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_JP292-500,e_JP269-500,e_JP306-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_w256682313-500,e_r17013811-500</t>
-  </si>
-  <si>
-    <t>elc_wof_036</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500,e_JP21-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_JP306-500,e_w216956620-500,e_w215451416-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500,e_w1037299172-500,e_w722673849-500,e_w1037516198-500,e_w291678103-500,e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>elc_wof_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500,e_w901872431-500,e_w104173570-500,e_w106076988-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7390,7 +7390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73079A1-D90B-45B6-8649-266F177945D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B0FE73-449A-4120-981F-AAF37E033782}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7628,16 +7628,16 @@
         <v>273</v>
       </c>
       <c r="Y11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Z11" t="s">
         <v>339</v>
       </c>
       <c r="AA11">
-        <v>0.99838604658336239</v>
+        <v>0.99850557699173803</v>
       </c>
       <c r="AB11">
-        <v>29.589145971689483</v>
+        <v>27.397755151469518</v>
       </c>
       <c r="AD11" t="s">
         <v>272</v>
@@ -7670,10 +7670,10 @@
         <v>430</v>
       </c>
       <c r="AO11">
-        <v>0.99829313447340673</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP11">
-        <v>31.292534654209355</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR11" t="s">
         <v>272</v>
@@ -7706,10 +7706,10 @@
         <v>575</v>
       </c>
       <c r="BC11">
-        <v>0.99302778580016682</v>
+        <v>0.99253849155603513</v>
       </c>
       <c r="BD11">
-        <v>127.82392699694152</v>
+        <v>136.79432147269009</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7774,16 +7774,16 @@
         <v>277</v>
       </c>
       <c r="Y12" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="Z12" t="s">
         <v>340</v>
       </c>
       <c r="AA12">
-        <v>0.99690397462165847</v>
+        <v>0.99838604658336239</v>
       </c>
       <c r="AB12">
-        <v>56.760465269594654</v>
+        <v>29.589145971689483</v>
       </c>
       <c r="AD12" t="s">
         <v>272</v>
@@ -7813,13 +7813,13 @@
         <v>431</v>
       </c>
       <c r="AN12" t="s">
-        <v>432</v>
+        <v>348</v>
       </c>
       <c r="AO12">
-        <v>0.99550555557680764</v>
+        <v>0.93717435218793788</v>
       </c>
       <c r="AP12">
-        <v>82.398147758527074</v>
+        <v>1151.8035432211395</v>
       </c>
       <c r="AR12" t="s">
         <v>272</v>
@@ -7849,13 +7849,13 @@
         <v>576</v>
       </c>
       <c r="BB12" t="s">
-        <v>355</v>
+        <v>577</v>
       </c>
       <c r="BC12">
-        <v>0.98180592470173533</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD12">
-        <v>333.55804713485287</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7920,16 +7920,16 @@
         <v>279</v>
       </c>
       <c r="Y13" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="Z13" t="s">
         <v>341</v>
       </c>
       <c r="AA13">
-        <v>0.99410594174368461</v>
+        <v>0.99690397462165847</v>
       </c>
       <c r="AB13">
-        <v>108.05773469911641</v>
+        <v>56.760465269594654</v>
       </c>
       <c r="AD13" t="s">
         <v>272</v>
@@ -7956,16 +7956,16 @@
         <v>371</v>
       </c>
       <c r="AM13" t="s">
+        <v>432</v>
+      </c>
+      <c r="AN13" t="s">
         <v>433</v>
       </c>
-      <c r="AN13" t="s">
-        <v>434</v>
-      </c>
       <c r="AO13">
-        <v>0.9985842216283608</v>
+        <v>0.99508023417818925</v>
       </c>
       <c r="AP13">
-        <v>25.9559368133853</v>
+        <v>90.195706733197795</v>
       </c>
       <c r="AR13" t="s">
         <v>272</v>
@@ -7992,16 +7992,16 @@
         <v>490</v>
       </c>
       <c r="BA13" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="BB13" t="s">
-        <v>343</v>
+        <v>579</v>
       </c>
       <c r="BC13">
-        <v>0.96140381292129873</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD13">
-        <v>707.59676310952364</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8066,16 +8066,16 @@
         <v>281</v>
       </c>
       <c r="Y14" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="Z14" t="s">
         <v>342</v>
       </c>
       <c r="AA14">
-        <v>0.9967423148539083</v>
+        <v>0.99798824264234642</v>
       </c>
       <c r="AB14">
-        <v>59.724227678348747</v>
+        <v>36.882218223648351</v>
       </c>
       <c r="AD14" t="s">
         <v>272</v>
@@ -8102,16 +8102,16 @@
         <v>373</v>
       </c>
       <c r="AM14" t="s">
+        <v>434</v>
+      </c>
+      <c r="AN14" t="s">
         <v>435</v>
       </c>
-      <c r="AN14" t="s">
-        <v>436</v>
-      </c>
       <c r="AO14">
-        <v>0.96551955124232614</v>
+        <v>0.99771335854027388</v>
       </c>
       <c r="AP14">
-        <v>632.14156055735509</v>
+        <v>41.921760094978509</v>
       </c>
       <c r="AR14" t="s">
         <v>272</v>
@@ -8138,16 +8138,16 @@
         <v>492</v>
       </c>
       <c r="BA14" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="BB14" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="BC14">
-        <v>0.99490784156958001</v>
+        <v>0.99623532634854861</v>
       </c>
       <c r="BD14">
-        <v>93.356237891033686</v>
+        <v>69.01901694327529</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8212,16 +8212,16 @@
         <v>283</v>
       </c>
       <c r="Y15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z15" t="s">
         <v>343</v>
       </c>
       <c r="AA15">
-        <v>0.94069903208664407</v>
+        <v>0.9488788277802801</v>
       </c>
       <c r="AB15">
-        <v>1087.1844117448593</v>
+        <v>937.22149069486488</v>
       </c>
       <c r="AD15" t="s">
         <v>272</v>
@@ -8248,16 +8248,16 @@
         <v>375</v>
       </c>
       <c r="AM15" t="s">
+        <v>436</v>
+      </c>
+      <c r="AN15" t="s">
         <v>437</v>
       </c>
-      <c r="AN15" t="s">
-        <v>438</v>
-      </c>
       <c r="AO15">
-        <v>0.99682717865030179</v>
+        <v>0.99841760060377538</v>
       </c>
       <c r="AP15">
-        <v>58.168391411134159</v>
+        <v>29.010655597451841</v>
       </c>
       <c r="AR15" t="s">
         <v>272</v>
@@ -8284,16 +8284,16 @@
         <v>494</v>
       </c>
       <c r="BA15" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="BB15" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="BC15">
-        <v>0.97902641975794957</v>
+        <v>0.99895994357772033</v>
       </c>
       <c r="BD15">
-        <v>384.51563777092457</v>
+        <v>19.067701075126294</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8358,16 +8358,16 @@
         <v>285</v>
       </c>
       <c r="Y16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z16" t="s">
         <v>344</v>
       </c>
       <c r="AA16">
-        <v>0.99818924951829635</v>
+        <v>0.99829848799221066</v>
       </c>
       <c r="AB16">
-        <v>33.197092164567515</v>
+        <v>31.194386809470345</v>
       </c>
       <c r="AD16" t="s">
         <v>272</v>
@@ -8394,16 +8394,16 @@
         <v>377</v>
       </c>
       <c r="AM16" t="s">
+        <v>438</v>
+      </c>
+      <c r="AN16" t="s">
         <v>439</v>
       </c>
-      <c r="AN16" t="s">
-        <v>440</v>
-      </c>
       <c r="AO16">
-        <v>0.99669176136177262</v>
+        <v>0.99826201627849442</v>
       </c>
       <c r="AP16">
-        <v>60.651041700835236</v>
+        <v>31.863034894267944</v>
       </c>
       <c r="AR16" t="s">
         <v>272</v>
@@ -8430,16 +8430,16 @@
         <v>496</v>
       </c>
       <c r="BA16" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="BB16" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="BC16">
-        <v>0.99366677237144974</v>
+        <v>0.99603667376986049</v>
       </c>
       <c r="BD16">
-        <v>116.10917319008783</v>
+        <v>72.660980885890424</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8504,16 +8504,16 @@
         <v>287</v>
       </c>
       <c r="Y17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Z17" t="s">
         <v>345</v>
       </c>
       <c r="AA17">
-        <v>0.99794776600687107</v>
+        <v>0.99894650606645485</v>
       </c>
       <c r="AB17">
-        <v>37.624289874031113</v>
+        <v>19.314055448326833</v>
       </c>
       <c r="AD17" t="s">
         <v>272</v>
@@ -8540,16 +8540,16 @@
         <v>379</v>
       </c>
       <c r="AM17" t="s">
+        <v>440</v>
+      </c>
+      <c r="AN17" t="s">
         <v>441</v>
       </c>
-      <c r="AN17" t="s">
-        <v>442</v>
-      </c>
       <c r="AO17">
-        <v>0.99835408615028387</v>
+        <v>0.9985928182686985</v>
       </c>
       <c r="AP17">
-        <v>30.175087244796281</v>
+        <v>25.798331740528162</v>
       </c>
       <c r="AR17" t="s">
         <v>272</v>
@@ -8576,16 +8576,16 @@
         <v>498</v>
       </c>
       <c r="BA17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="BB17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="BC17">
-        <v>0.99547930517021377</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD17">
-        <v>82.879405212747869</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8650,16 +8650,16 @@
         <v>289</v>
       </c>
       <c r="Y18" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Z18" t="s">
         <v>346</v>
       </c>
       <c r="AA18">
-        <v>0.98968917222400854</v>
+        <v>0.99856748800713691</v>
       </c>
       <c r="AB18">
-        <v>189.03184255984442</v>
+        <v>26.26271986915707</v>
       </c>
       <c r="AD18" t="s">
         <v>272</v>
@@ -8686,16 +8686,16 @@
         <v>381</v>
       </c>
       <c r="AM18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AN18" t="s">
-        <v>444</v>
+        <v>361</v>
       </c>
       <c r="AO18">
-        <v>0.99627181657233566</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP18">
-        <v>68.350029507179471</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR18" t="s">
         <v>272</v>
@@ -8722,16 +8722,16 @@
         <v>500</v>
       </c>
       <c r="BA18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="BB18" t="s">
-        <v>436</v>
+        <v>482</v>
       </c>
       <c r="BC18">
-        <v>0.95726256957223688</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD18">
-        <v>783.51955784232393</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8796,16 +8796,16 @@
         <v>291</v>
       </c>
       <c r="Y19" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="Z19" t="s">
         <v>347</v>
       </c>
       <c r="AA19">
-        <v>0.9488788277802801</v>
+        <v>0.99824746199801306</v>
       </c>
       <c r="AB19">
-        <v>937.22149069486488</v>
+        <v>32.129863369760315</v>
       </c>
       <c r="AD19" t="s">
         <v>272</v>
@@ -8832,16 +8832,16 @@
         <v>383</v>
       </c>
       <c r="AM19" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AN19" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="AO19">
-        <v>0.98949004263841422</v>
+        <v>0.99807466477127271</v>
       </c>
       <c r="AP19">
-        <v>192.68255162907312</v>
+        <v>35.297812526667357</v>
       </c>
       <c r="AR19" t="s">
         <v>272</v>
@@ -8868,16 +8868,16 @@
         <v>502</v>
       </c>
       <c r="BA19" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="BB19" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="BC19">
-        <v>0.99623532634854861</v>
+        <v>0.99602290686668338</v>
       </c>
       <c r="BD19">
-        <v>69.01901694327529</v>
+        <v>72.91337411080552</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8942,16 +8942,16 @@
         <v>293</v>
       </c>
       <c r="Y20" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="Z20" t="s">
         <v>348</v>
       </c>
       <c r="AA20">
-        <v>0.99900168239190124</v>
+        <v>0.94069903208664407</v>
       </c>
       <c r="AB20">
-        <v>18.302489481810518</v>
+        <v>1087.1844117448593</v>
       </c>
       <c r="AD20" t="s">
         <v>272</v>
@@ -8978,16 +8978,16 @@
         <v>385</v>
       </c>
       <c r="AM20" t="s">
+        <v>445</v>
+      </c>
+      <c r="AN20" t="s">
         <v>446</v>
       </c>
-      <c r="AN20" t="s">
-        <v>447</v>
-      </c>
       <c r="AO20">
-        <v>0.99841760060377538</v>
+        <v>0.99013353407586135</v>
       </c>
       <c r="AP20">
-        <v>29.010655597451841</v>
+        <v>180.88520860920943</v>
       </c>
       <c r="AR20" t="s">
         <v>272</v>
@@ -9014,16 +9014,16 @@
         <v>504</v>
       </c>
       <c r="BA20" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="BB20" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="BC20">
-        <v>0.99895994357772033</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD20">
-        <v>19.067701075126294</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9088,16 +9088,16 @@
         <v>295</v>
       </c>
       <c r="Y21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Z21" t="s">
         <v>349</v>
       </c>
       <c r="AA21">
-        <v>0.99829848799221066</v>
+        <v>0.99818924951829635</v>
       </c>
       <c r="AB21">
-        <v>31.194386809470345</v>
+        <v>33.197092164567515</v>
       </c>
       <c r="AD21" t="s">
         <v>272</v>
@@ -9124,16 +9124,16 @@
         <v>387</v>
       </c>
       <c r="AM21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AN21" t="s">
-        <v>449</v>
+        <v>360</v>
       </c>
       <c r="AO21">
-        <v>0.99826201627849442</v>
+        <v>0.98814178187791379</v>
       </c>
       <c r="AP21">
-        <v>31.863034894267944</v>
+        <v>217.40066557158059</v>
       </c>
       <c r="AR21" t="s">
         <v>272</v>
@@ -9160,16 +9160,16 @@
         <v>506</v>
       </c>
       <c r="BA21" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="BB21" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="BC21">
-        <v>0.99603667376986049</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD21">
-        <v>72.660980885890424</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9234,16 +9234,16 @@
         <v>297</v>
       </c>
       <c r="Y22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Z22" t="s">
         <v>350</v>
       </c>
       <c r="AA22">
-        <v>0.99894650606645485</v>
+        <v>0.99794776600687107</v>
       </c>
       <c r="AB22">
-        <v>19.314055448326833</v>
+        <v>37.624289874031113</v>
       </c>
       <c r="AD22" t="s">
         <v>272</v>
@@ -9270,16 +9270,16 @@
         <v>389</v>
       </c>
       <c r="AM22" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AN22" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AO22">
-        <v>0.9985928182686985</v>
+        <v>0.99829313447340673</v>
       </c>
       <c r="AP22">
-        <v>25.798331740528162</v>
+        <v>31.292534654209355</v>
       </c>
       <c r="AR22" t="s">
         <v>272</v>
@@ -9306,16 +9306,16 @@
         <v>508</v>
       </c>
       <c r="BA22" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="BB22" t="s">
-        <v>592</v>
+        <v>357</v>
       </c>
       <c r="BC22">
-        <v>0.97589985979527272</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD22">
-        <v>441.83590375333313</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9380,16 +9380,16 @@
         <v>299</v>
       </c>
       <c r="Y23" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Z23" t="s">
         <v>351</v>
       </c>
       <c r="AA23">
-        <v>0.99856748800713691</v>
+        <v>0.98968917222400854</v>
       </c>
       <c r="AB23">
-        <v>26.26271986915707</v>
+        <v>189.03184255984442</v>
       </c>
       <c r="AD23" t="s">
         <v>272</v>
@@ -9416,16 +9416,16 @@
         <v>391</v>
       </c>
       <c r="AM23" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AN23" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AO23">
-        <v>0.99771335854027388</v>
+        <v>0.99550555557680764</v>
       </c>
       <c r="AP23">
-        <v>41.921760094978509</v>
+        <v>82.398147758527074</v>
       </c>
       <c r="AR23" t="s">
         <v>272</v>
@@ -9452,16 +9452,16 @@
         <v>510</v>
       </c>
       <c r="BA23" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="BB23" t="s">
-        <v>470</v>
+        <v>348</v>
       </c>
       <c r="BC23">
-        <v>0.9437657388784082</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD23">
-        <v>1030.9614538958492</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9526,16 +9526,16 @@
         <v>301</v>
       </c>
       <c r="Y24" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="Z24" t="s">
         <v>352</v>
       </c>
       <c r="AA24">
-        <v>0.99824746199801306</v>
+        <v>0.99410594174368461</v>
       </c>
       <c r="AB24">
-        <v>32.129863369760315</v>
+        <v>108.05773469911641</v>
       </c>
       <c r="AD24" t="s">
         <v>272</v>
@@ -9562,16 +9562,16 @@
         <v>393</v>
       </c>
       <c r="AM24" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN24" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AO24">
-        <v>0.99762356494824644</v>
+        <v>0.96551955124232614</v>
       </c>
       <c r="AP24">
-        <v>43.567975948815601</v>
+        <v>632.14156055735509</v>
       </c>
       <c r="AR24" t="s">
         <v>272</v>
@@ -9598,16 +9598,16 @@
         <v>512</v>
       </c>
       <c r="BA24" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="BB24" t="s">
-        <v>595</v>
+        <v>348</v>
       </c>
       <c r="BC24">
-        <v>0.99602290686668338</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD24">
-        <v>72.91337411080552</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9672,16 +9672,16 @@
         <v>303</v>
       </c>
       <c r="Y25" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="Z25" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="AA25">
-        <v>0.96189283472138964</v>
+        <v>0.9967423148539083</v>
       </c>
       <c r="AB25">
-        <v>698.63136344118936</v>
+        <v>59.724227678348747</v>
       </c>
       <c r="AD25" t="s">
         <v>272</v>
@@ -9708,16 +9708,16 @@
         <v>395</v>
       </c>
       <c r="AM25" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AN25" t="s">
-        <v>355</v>
+        <v>455</v>
       </c>
       <c r="AO25">
-        <v>0.98092693557487454</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP25">
-        <v>349.67284779396647</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR25" t="s">
         <v>272</v>
@@ -9747,13 +9747,13 @@
         <v>596</v>
       </c>
       <c r="BB25" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="BC25">
-        <v>0.99536692897647694</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD25">
-        <v>84.939635431255269</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9818,16 +9818,16 @@
         <v>305</v>
       </c>
       <c r="Y26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z26" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AA26">
-        <v>0.9972084849335241</v>
+        <v>0.97633688849282452</v>
       </c>
       <c r="AB26">
-        <v>51.177776218725121</v>
+        <v>433.82371096488447</v>
       </c>
       <c r="AD26" t="s">
         <v>272</v>
@@ -9854,10 +9854,10 @@
         <v>397</v>
       </c>
       <c r="AM26" t="s">
+        <v>456</v>
+      </c>
+      <c r="AN26" t="s">
         <v>457</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>458</v>
       </c>
       <c r="AO26">
         <v>0.99804155179341392</v>
@@ -9896,10 +9896,10 @@
         <v>598</v>
       </c>
       <c r="BC26">
-        <v>0.98779966071713954</v>
+        <v>0.9924172440074055</v>
       </c>
       <c r="BD26">
-        <v>223.67288685244134</v>
+        <v>139.01719319756617</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9964,16 +9964,16 @@
         <v>307</v>
       </c>
       <c r="Y27" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s">
         <v>354</v>
       </c>
       <c r="AA27">
-        <v>0.99116451092312863</v>
+        <v>0.9977500892185478</v>
       </c>
       <c r="AB27">
-        <v>161.98396640930775</v>
+        <v>41.248364326622962</v>
       </c>
       <c r="AD27" t="s">
         <v>272</v>
@@ -10000,10 +10000,10 @@
         <v>399</v>
       </c>
       <c r="AM27" t="s">
+        <v>458</v>
+      </c>
+      <c r="AN27" t="s">
         <v>459</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>460</v>
       </c>
       <c r="AO27">
         <v>0.99686124252542985</v>
@@ -10042,10 +10042,10 @@
         <v>600</v>
       </c>
       <c r="BC27">
-        <v>0.99681267676383467</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD27">
-        <v>58.434259329697142</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10110,16 +10110,16 @@
         <v>309</v>
       </c>
       <c r="Y28" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s">
         <v>355</v>
       </c>
       <c r="AA28">
-        <v>0.97905685820454003</v>
+        <v>0.99759093327931103</v>
       </c>
       <c r="AB28">
-        <v>383.95759958343297</v>
+        <v>44.16622321263192</v>
       </c>
       <c r="AD28" t="s">
         <v>272</v>
@@ -10146,10 +10146,10 @@
         <v>401</v>
       </c>
       <c r="AM28" t="s">
+        <v>460</v>
+      </c>
+      <c r="AN28" t="s">
         <v>461</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>462</v>
       </c>
       <c r="AO28">
         <v>0.99781438034778358</v>
@@ -10185,13 +10185,13 @@
         <v>601</v>
       </c>
       <c r="BB28" t="s">
-        <v>343</v>
+        <v>453</v>
       </c>
       <c r="BC28">
-        <v>0.97591598065988894</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD28">
-        <v>441.54035456870389</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10256,16 +10256,16 @@
         <v>311</v>
       </c>
       <c r="Y29" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Z29" t="s">
         <v>356</v>
       </c>
       <c r="AA29">
-        <v>0.99798824264234642</v>
+        <v>0.99852430677621173</v>
       </c>
       <c r="AB29">
-        <v>36.882218223648351</v>
+        <v>27.054375769451152</v>
       </c>
       <c r="AD29" t="s">
         <v>272</v>
@@ -10292,10 +10292,10 @@
         <v>403</v>
       </c>
       <c r="AM29" t="s">
+        <v>462</v>
+      </c>
+      <c r="AN29" t="s">
         <v>463</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>464</v>
       </c>
       <c r="AO29">
         <v>0.99693456929731861</v>
@@ -10331,13 +10331,13 @@
         <v>602</v>
       </c>
       <c r="BB29" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="BC29">
-        <v>0.99412039195829205</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD29">
-        <v>107.79281409797902</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10402,16 +10402,16 @@
         <v>313</v>
       </c>
       <c r="Y30" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="Z30" t="s">
         <v>357</v>
       </c>
       <c r="AA30">
-        <v>0.99852430677621173</v>
+        <v>0.98179245618315802</v>
       </c>
       <c r="AB30">
-        <v>27.054375769451152</v>
+        <v>333.80496997543548</v>
       </c>
       <c r="AD30" t="s">
         <v>272</v>
@@ -10438,16 +10438,16 @@
         <v>405</v>
       </c>
       <c r="AM30" t="s">
+        <v>464</v>
+      </c>
+      <c r="AN30" t="s">
         <v>465</v>
       </c>
-      <c r="AN30" t="s">
-        <v>466</v>
-      </c>
       <c r="AO30">
-        <v>0.99863922747017897</v>
+        <v>0.99669176136177262</v>
       </c>
       <c r="AP30">
-        <v>24.947496380053089</v>
+        <v>60.651041700835236</v>
       </c>
       <c r="AR30" t="s">
         <v>272</v>
@@ -10474,16 +10474,16 @@
         <v>524</v>
       </c>
       <c r="BA30" t="s">
+        <v>603</v>
+      </c>
+      <c r="BB30" t="s">
         <v>604</v>
       </c>
-      <c r="BB30" t="s">
-        <v>605</v>
-      </c>
       <c r="BC30">
-        <v>0.98881218539944515</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD30">
-        <v>205.10993434350485</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10548,16 +10548,16 @@
         <v>315</v>
       </c>
       <c r="Y31" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="Z31" t="s">
         <v>358</v>
       </c>
       <c r="AA31">
-        <v>0.98179245618315802</v>
+        <v>0.9982812149336332</v>
       </c>
       <c r="AB31">
-        <v>333.80496997543548</v>
+        <v>31.51105955005805</v>
       </c>
       <c r="AD31" t="s">
         <v>272</v>
@@ -10584,16 +10584,16 @@
         <v>407</v>
       </c>
       <c r="AM31" t="s">
+        <v>466</v>
+      </c>
+      <c r="AN31" t="s">
         <v>467</v>
       </c>
-      <c r="AN31" t="s">
-        <v>468</v>
-      </c>
       <c r="AO31">
-        <v>0.99940622505963084</v>
+        <v>0.99835408615028387</v>
       </c>
       <c r="AP31">
-        <v>10.885873906767051</v>
+        <v>30.175087244796281</v>
       </c>
       <c r="AR31" t="s">
         <v>272</v>
@@ -10620,16 +10620,16 @@
         <v>526</v>
       </c>
       <c r="BA31" t="s">
+        <v>605</v>
+      </c>
+      <c r="BB31" t="s">
         <v>606</v>
       </c>
-      <c r="BB31" t="s">
-        <v>343</v>
-      </c>
       <c r="BC31">
-        <v>0.95957195194316591</v>
+        <v>0.99561586640696276</v>
       </c>
       <c r="BD31">
-        <v>741.18088104195795</v>
+        <v>80.375782539015233</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10694,16 +10694,16 @@
         <v>317</v>
       </c>
       <c r="Y32" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="Z32" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="AA32">
-        <v>0.99850557699173803</v>
+        <v>0.96189283472138964</v>
       </c>
       <c r="AB32">
-        <v>27.397755151469518</v>
+        <v>698.63136344118936</v>
       </c>
       <c r="AD32" t="s">
         <v>272</v>
@@ -10730,16 +10730,16 @@
         <v>409</v>
       </c>
       <c r="AM32" t="s">
+        <v>468</v>
+      </c>
+      <c r="AN32" t="s">
         <v>469</v>
       </c>
-      <c r="AN32" t="s">
-        <v>470</v>
-      </c>
       <c r="AO32">
-        <v>0.93896180472603763</v>
+        <v>0.99627181657233566</v>
       </c>
       <c r="AP32">
-        <v>1119.0335800226442</v>
+        <v>68.350029507179471</v>
       </c>
       <c r="AR32" t="s">
         <v>272</v>
@@ -10769,13 +10769,13 @@
         <v>607</v>
       </c>
       <c r="BB32" t="s">
-        <v>584</v>
+        <v>360</v>
       </c>
       <c r="BC32">
-        <v>0.98627205860840139</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD32">
-        <v>251.67892551264018</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10840,16 +10840,16 @@
         <v>319</v>
       </c>
       <c r="Y33" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="Z33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA33">
-        <v>0.9982812149336332</v>
+        <v>0.9972084849335241</v>
       </c>
       <c r="AB33">
-        <v>31.51105955005805</v>
+        <v>51.177776218725121</v>
       </c>
       <c r="AD33" t="s">
         <v>272</v>
@@ -10876,16 +10876,16 @@
         <v>411</v>
       </c>
       <c r="AM33" t="s">
+        <v>470</v>
+      </c>
+      <c r="AN33" t="s">
         <v>471</v>
       </c>
-      <c r="AN33" t="s">
-        <v>472</v>
-      </c>
       <c r="AO33">
-        <v>0.99013353407586135</v>
+        <v>0.9985842216283608</v>
       </c>
       <c r="AP33">
-        <v>180.88520860920943</v>
+        <v>25.9559368133853</v>
       </c>
       <c r="AR33" t="s">
         <v>272</v>
@@ -10918,10 +10918,10 @@
         <v>609</v>
       </c>
       <c r="BC33">
-        <v>0.99504061303190972</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD33">
-        <v>90.922094414988095</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -10986,16 +10986,16 @@
         <v>321</v>
       </c>
       <c r="Y34" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="Z34" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="AA34">
-        <v>0.97633688849282452</v>
+        <v>0.99116451092312863</v>
       </c>
       <c r="AB34">
-        <v>433.82371096488447</v>
+        <v>161.98396640930775</v>
       </c>
       <c r="AD34" t="s">
         <v>272</v>
@@ -11022,16 +11022,16 @@
         <v>413</v>
       </c>
       <c r="AM34" t="s">
+        <v>472</v>
+      </c>
+      <c r="AN34" t="s">
         <v>473</v>
       </c>
-      <c r="AN34" t="s">
-        <v>354</v>
-      </c>
       <c r="AO34">
-        <v>0.98814178187791379</v>
+        <v>0.99750949182367343</v>
       </c>
       <c r="AP34">
-        <v>217.40066557158059</v>
+        <v>45.659316565986806</v>
       </c>
       <c r="AR34" t="s">
         <v>272</v>
@@ -11064,10 +11064,10 @@
         <v>611</v>
       </c>
       <c r="BC34">
-        <v>0.99253849155603513</v>
+        <v>0.99662747375050009</v>
       </c>
       <c r="BD34">
-        <v>136.79432147269009</v>
+        <v>61.829647907498845</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11132,16 +11132,16 @@
         <v>323</v>
       </c>
       <c r="Y35" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="Z35" t="s">
         <v>361</v>
       </c>
       <c r="AA35">
-        <v>0.9977500892185478</v>
+        <v>0.97905685820454003</v>
       </c>
       <c r="AB35">
-        <v>41.248364326622962</v>
+        <v>383.95759958343297</v>
       </c>
       <c r="AD35" t="s">
         <v>272</v>
@@ -11174,10 +11174,10 @@
         <v>475</v>
       </c>
       <c r="AO35">
-        <v>0.99811838305018963</v>
+        <v>0.99870022163576544</v>
       </c>
       <c r="AP35">
-        <v>34.496310746523356</v>
+        <v>23.829270010966344</v>
       </c>
       <c r="AR35" t="s">
         <v>272</v>
@@ -11210,10 +11210,10 @@
         <v>613</v>
       </c>
       <c r="BC35">
-        <v>0.99234935324205875</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD35">
-        <v>140.26185722892211</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11278,16 +11278,16 @@
         <v>325</v>
       </c>
       <c r="Y36" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Z36" t="s">
         <v>362</v>
       </c>
       <c r="AA36">
-        <v>0.99759093327931103</v>
+        <v>0.99871218762601011</v>
       </c>
       <c r="AB36">
-        <v>44.16622321263192</v>
+        <v>23.609893523147914</v>
       </c>
       <c r="AD36" t="s">
         <v>272</v>
@@ -11317,13 +11317,13 @@
         <v>476</v>
       </c>
       <c r="AN36" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AO36">
-        <v>0.93717435218793788</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP36">
-        <v>1151.8035432211395</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR36" t="s">
         <v>272</v>
@@ -11356,10 +11356,10 @@
         <v>615</v>
       </c>
       <c r="BC36">
-        <v>0.9205295464439136</v>
+        <v>0.99366677237144974</v>
       </c>
       <c r="BD36">
-        <v>1456.9583151949184</v>
+        <v>116.10917319008783</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11424,16 +11424,16 @@
         <v>327</v>
       </c>
       <c r="Y37" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="Z37" t="s">
         <v>363</v>
       </c>
       <c r="AA37">
-        <v>0.99391268208184824</v>
+        <v>0.99628076912917996</v>
       </c>
       <c r="AB37">
-        <v>111.60082849944791</v>
+        <v>68.185899298368355</v>
       </c>
       <c r="AD37" t="s">
         <v>272</v>
@@ -11466,10 +11466,10 @@
         <v>478</v>
       </c>
       <c r="AO37">
-        <v>0.99508023417818925</v>
+        <v>0.99863922747017897</v>
       </c>
       <c r="AP37">
-        <v>90.195706733197795</v>
+        <v>24.947496380053089</v>
       </c>
       <c r="AR37" t="s">
         <v>272</v>
@@ -11502,10 +11502,10 @@
         <v>617</v>
       </c>
       <c r="BC37">
-        <v>0.9973402418125219</v>
+        <v>0.99547930517021377</v>
       </c>
       <c r="BD37">
-        <v>48.762233437098502</v>
+        <v>82.879405212747869</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11570,16 +11570,16 @@
         <v>329</v>
       </c>
       <c r="Y38" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="Z38" t="s">
         <v>364</v>
       </c>
       <c r="AA38">
-        <v>0.99871218762601011</v>
+        <v>0.99726055556014181</v>
       </c>
       <c r="AB38">
-        <v>23.609893523147914</v>
+        <v>50.223148064066145</v>
       </c>
       <c r="AD38" t="s">
         <v>272</v>
@@ -11612,10 +11612,10 @@
         <v>480</v>
       </c>
       <c r="AO38">
-        <v>0.99750949182367343</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP38">
-        <v>45.659316565986806</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR38" t="s">
         <v>272</v>
@@ -11648,10 +11648,10 @@
         <v>619</v>
       </c>
       <c r="BC38">
-        <v>0.99519319222421976</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD38">
-        <v>88.124809222638589</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11716,16 +11716,16 @@
         <v>331</v>
       </c>
       <c r="Y39" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="Z39" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="AA39">
-        <v>0.99628076912917996</v>
+        <v>0.98910041547393335</v>
       </c>
       <c r="AB39">
-        <v>68.185899298368355</v>
+        <v>199.82571631122156</v>
       </c>
       <c r="AD39" t="s">
         <v>272</v>
@@ -11758,10 +11758,10 @@
         <v>482</v>
       </c>
       <c r="AO39">
-        <v>0.99870022163576544</v>
+        <v>0.93896180472603763</v>
       </c>
       <c r="AP39">
-        <v>23.829270010966344</v>
+        <v>1119.0335800226442</v>
       </c>
       <c r="AR39" t="s">
         <v>272</v>
@@ -11791,13 +11791,13 @@
         <v>620</v>
       </c>
       <c r="BB39" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="BC39">
-        <v>0.98605307635189521</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD39">
-        <v>255.693600215255</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11862,16 +11862,16 @@
         <v>333</v>
       </c>
       <c r="Y40" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="Z40" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA40">
-        <v>0.99726055556014181</v>
+        <v>0.99391268208184824</v>
       </c>
       <c r="AB40">
-        <v>50.223148064066145</v>
+        <v>111.60082849944791</v>
       </c>
       <c r="AD40" t="s">
         <v>272</v>
@@ -11901,13 +11901,13 @@
         <v>483</v>
       </c>
       <c r="AN40" t="s">
-        <v>346</v>
+        <v>484</v>
       </c>
       <c r="AO40">
-        <v>0.99192535126433146</v>
+        <v>0.99762356494824644</v>
       </c>
       <c r="AP40">
-        <v>148.0352268205892</v>
+        <v>43.567975948815601</v>
       </c>
       <c r="AR40" t="s">
         <v>272</v>
@@ -11937,13 +11937,13 @@
         <v>621</v>
       </c>
       <c r="BB40" t="s">
-        <v>622</v>
+        <v>340</v>
       </c>
       <c r="BC40">
-        <v>0.88199812838352587</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD40">
-        <v>2163.367646302027</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12008,16 +12008,16 @@
         <v>335</v>
       </c>
       <c r="Y41" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="Z41" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="AA41">
-        <v>0.98910041547393335</v>
+        <v>0.99900168239190124</v>
       </c>
       <c r="AB41">
-        <v>199.82571631122156</v>
+        <v>18.302489481810518</v>
       </c>
       <c r="AD41" t="s">
         <v>272</v>
@@ -12044,16 +12044,16 @@
         <v>427</v>
       </c>
       <c r="AM41" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN41" t="s">
-        <v>485</v>
+        <v>361</v>
       </c>
       <c r="AO41">
-        <v>0.99807466477127271</v>
+        <v>0.98092693557487454</v>
       </c>
       <c r="AP41">
-        <v>35.297812526667357</v>
+        <v>349.67284779396647</v>
       </c>
       <c r="AR41" t="s">
         <v>272</v>
@@ -12080,16 +12080,16 @@
         <v>546</v>
       </c>
       <c r="BA41" t="s">
+        <v>622</v>
+      </c>
+      <c r="BB41" t="s">
         <v>623</v>
       </c>
-      <c r="BB41" t="s">
-        <v>624</v>
-      </c>
       <c r="BC41">
-        <v>0.99015836110796274</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD41">
-        <v>180.43004635401576</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12118,16 +12118,16 @@
         <v>548</v>
       </c>
       <c r="BA42" t="s">
+        <v>624</v>
+      </c>
+      <c r="BB42" t="s">
         <v>625</v>
       </c>
-      <c r="BB42" t="s">
-        <v>626</v>
-      </c>
       <c r="BC42">
-        <v>0.97803702976044449</v>
+        <v>0.99681267676383467</v>
       </c>
       <c r="BD42">
-        <v>402.65445439185123</v>
+        <v>58.434259329697142</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12156,16 +12156,16 @@
         <v>550</v>
       </c>
       <c r="BA43" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="BB43" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="BC43">
-        <v>0.934538160869965</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD43">
-        <v>1200.1337173839754</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12194,16 +12194,16 @@
         <v>552</v>
       </c>
       <c r="BA44" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="BB44" t="s">
-        <v>343</v>
+        <v>617</v>
       </c>
       <c r="BC44">
-        <v>0.94616153753972931</v>
+        <v>0.98627205860840139</v>
       </c>
       <c r="BD44">
-        <v>987.03847843829612</v>
+        <v>251.67892551264018</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12232,16 +12232,16 @@
         <v>554</v>
       </c>
       <c r="BA45" t="s">
+        <v>628</v>
+      </c>
+      <c r="BB45" t="s">
         <v>629</v>
       </c>
-      <c r="BB45" t="s">
-        <v>343</v>
-      </c>
       <c r="BC45">
-        <v>0.97218956380622079</v>
+        <v>0.99504061303190972</v>
       </c>
       <c r="BD45">
-        <v>509.85799688595205</v>
+        <v>90.922094414988095</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12273,13 +12273,13 @@
         <v>630</v>
       </c>
       <c r="BB46" t="s">
-        <v>631</v>
+        <v>348</v>
       </c>
       <c r="BC46">
-        <v>0.9924172440074055</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD46">
-        <v>139.01719319756617</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12308,16 +12308,16 @@
         <v>558</v>
       </c>
       <c r="BA47" t="s">
+        <v>631</v>
+      </c>
+      <c r="BB47" t="s">
         <v>632</v>
       </c>
-      <c r="BB47" t="s">
-        <v>633</v>
-      </c>
       <c r="BC47">
-        <v>0.99637036284424008</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD47">
-        <v>66.543347855598327</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12346,16 +12346,16 @@
         <v>560</v>
       </c>
       <c r="BA48" t="s">
+        <v>633</v>
+      </c>
+      <c r="BB48" t="s">
         <v>634</v>
       </c>
-      <c r="BB48" t="s">
-        <v>592</v>
-      </c>
       <c r="BC48">
-        <v>0.93089405249526469</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD48">
-        <v>1266.9423709201483</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12390,10 +12390,10 @@
         <v>636</v>
       </c>
       <c r="BC49">
-        <v>0.99114508565756532</v>
+        <v>0.99015836110796274</v>
       </c>
       <c r="BD49">
-        <v>162.34009627796874</v>
+        <v>180.43004635401576</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12428,10 +12428,10 @@
         <v>638</v>
       </c>
       <c r="BC50">
-        <v>0.99561586640696276</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD50">
-        <v>80.375782539015233</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12463,13 +12463,13 @@
         <v>639</v>
       </c>
       <c r="BB51" t="s">
-        <v>354</v>
+        <v>640</v>
       </c>
       <c r="BC51">
-        <v>0.98235584693125277</v>
+        <v>0.9973402418125219</v>
       </c>
       <c r="BD51">
-        <v>323.47613959369914</v>
+        <v>48.762233437098502</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12498,16 +12498,16 @@
         <v>568</v>
       </c>
       <c r="BA52" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB52" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="BC52">
-        <v>0.98822137145239475</v>
+        <v>0.99519319222421976</v>
       </c>
       <c r="BD52">
-        <v>215.94152337276336</v>
+        <v>88.124809222638589</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12536,16 +12536,16 @@
         <v>570</v>
       </c>
       <c r="BA53" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BB53" t="s">
-        <v>643</v>
+        <v>360</v>
       </c>
       <c r="BC53">
-        <v>0.99662747375050009</v>
+        <v>0.98605307635189521</v>
       </c>
       <c r="BD53">
-        <v>61.829647907498845</v>
+        <v>255.693600215255</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12580,10 +12580,10 @@
         <v>645</v>
       </c>
       <c r="BC54">
-        <v>0.99284590877035406</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD54">
-        <v>131.158339210175</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
   </sheetData>
@@ -12592,7 +12592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0107827A-9ACA-401A-A512-26E747AA4C17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD0FE541-928E-4D8D-B35B-60002078CF88}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12704,7 +12704,7 @@
         <v>646</v>
       </c>
       <c r="K11" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="L11">
         <v>27.131882337818411</v>
@@ -12737,7 +12737,7 @@
         <v>708</v>
       </c>
       <c r="X11" t="s">
-        <v>627</v>
+        <v>594</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12772,7 +12772,7 @@
         <v>648</v>
       </c>
       <c r="K12" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="L12">
         <v>30.590093860622108</v>
@@ -12805,7 +12805,7 @@
         <v>710</v>
       </c>
       <c r="X12" t="s">
-        <v>628</v>
+        <v>595</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12840,7 +12840,7 @@
         <v>650</v>
       </c>
       <c r="K13" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="L13">
         <v>27.017887629498883</v>
@@ -12873,7 +12873,7 @@
         <v>712</v>
       </c>
       <c r="X13" t="s">
-        <v>629</v>
+        <v>596</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12908,7 +12908,7 @@
         <v>652</v>
       </c>
       <c r="K14" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="L14">
         <v>15.703622047270191</v>
@@ -12941,7 +12941,7 @@
         <v>714</v>
       </c>
       <c r="X14" t="s">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12976,7 +12976,7 @@
         <v>654</v>
       </c>
       <c r="K15" t="s">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="L15">
         <v>24.074478129461852</v>
@@ -13009,7 +13009,7 @@
         <v>716</v>
       </c>
       <c r="X15" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13044,7 +13044,7 @@
         <v>656</v>
       </c>
       <c r="K16" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="L16">
         <v>6.1151684514715345</v>
@@ -13077,7 +13077,7 @@
         <v>718</v>
       </c>
       <c r="X16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13112,7 +13112,7 @@
         <v>658</v>
       </c>
       <c r="K17" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="L17">
         <v>4.1221966299799098</v>
@@ -13145,7 +13145,7 @@
         <v>720</v>
       </c>
       <c r="X17" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13180,7 +13180,7 @@
         <v>660</v>
       </c>
       <c r="K18" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="L18">
         <v>6.7028485191473308E-2</v>
@@ -13213,7 +13213,7 @@
         <v>722</v>
       </c>
       <c r="X18" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="Y18">
         <v>22.079249999999998</v>
@@ -13248,7 +13248,7 @@
         <v>662</v>
       </c>
       <c r="K19" t="s">
-        <v>476</v>
+        <v>431</v>
       </c>
       <c r="L19">
         <v>1.3102559495532347</v>
@@ -13281,7 +13281,7 @@
         <v>724</v>
       </c>
       <c r="X19" t="s">
-        <v>581</v>
+        <v>614</v>
       </c>
       <c r="Y19">
         <v>29.961749999999999</v>
@@ -13316,7 +13316,7 @@
         <v>664</v>
       </c>
       <c r="K20" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="L20">
         <v>44.894334115294185</v>
@@ -13349,7 +13349,7 @@
         <v>726</v>
       </c>
       <c r="X20" t="s">
-        <v>642</v>
+        <v>610</v>
       </c>
       <c r="Y20">
         <v>28.478249999999999</v>
@@ -13384,7 +13384,7 @@
         <v>666</v>
       </c>
       <c r="K21" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="L21">
         <v>14.358494358107757</v>
@@ -13417,7 +13417,7 @@
         <v>728</v>
       </c>
       <c r="X21" t="s">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="Y21">
         <v>117.89700000000001</v>
@@ -13452,7 +13452,7 @@
         <v>668</v>
       </c>
       <c r="K22" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="L22">
         <v>39.022668784713879</v>
@@ -13485,7 +13485,7 @@
         <v>730</v>
       </c>
       <c r="X22" t="s">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="Y22">
         <v>75.481499999999997</v>
@@ -13520,7 +13520,7 @@
         <v>670</v>
       </c>
       <c r="K23" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="L23">
         <v>33.851015501811965</v>
@@ -13553,7 +13553,7 @@
         <v>732</v>
       </c>
       <c r="X23" t="s">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="Y23">
         <v>10.68975</v>
@@ -13588,7 +13588,7 @@
         <v>672</v>
       </c>
       <c r="K24" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="L24">
         <v>29.76120824924126</v>
@@ -13621,7 +13621,7 @@
         <v>734</v>
       </c>
       <c r="X24" t="s">
-        <v>610</v>
+        <v>574</v>
       </c>
       <c r="Y24">
         <v>82.607249999999993</v>
@@ -13656,7 +13656,7 @@
         <v>674</v>
       </c>
       <c r="K25" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="L25">
         <v>26.081770464705624</v>
@@ -13689,7 +13689,7 @@
         <v>736</v>
       </c>
       <c r="X25" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="Y25">
         <v>28.239750000000001</v>
@@ -13724,7 +13724,7 @@
         <v>676</v>
       </c>
       <c r="K26" t="s">
-        <v>456</v>
+        <v>485</v>
       </c>
       <c r="L26">
         <v>28.326303899090867</v>
@@ -13757,7 +13757,7 @@
         <v>738</v>
       </c>
       <c r="X26" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="Y26">
         <v>1.9132499999999999</v>
@@ -13792,7 +13792,7 @@
         <v>678</v>
       </c>
       <c r="K27" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="L27">
         <v>13.047413180463023</v>
@@ -13825,7 +13825,7 @@
         <v>740</v>
       </c>
       <c r="X27" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="Y27">
         <v>63.731250000000003</v>
@@ -13860,7 +13860,7 @@
         <v>680</v>
       </c>
       <c r="K28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L28">
         <v>23.637816650626842</v>
@@ -13893,7 +13893,7 @@
         <v>742</v>
       </c>
       <c r="X28" t="s">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="Y28">
         <v>38.451000000000001</v>
@@ -13928,7 +13928,7 @@
         <v>682</v>
       </c>
       <c r="K29" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="L29">
         <v>50.076680799526407</v>
@@ -13961,7 +13961,7 @@
         <v>744</v>
       </c>
       <c r="X29" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="Y29">
         <v>64.533749999999998</v>
@@ -13996,7 +13996,7 @@
         <v>684</v>
       </c>
       <c r="K30" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="L30">
         <v>8.4886449615793467</v>
@@ -14029,7 +14029,7 @@
         <v>746</v>
       </c>
       <c r="X30" t="s">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="Y30">
         <v>44.370750000000001</v>
@@ -14064,7 +14064,7 @@
         <v>686</v>
       </c>
       <c r="K31" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L31">
         <v>8.4075540995285696</v>
@@ -14097,7 +14097,7 @@
         <v>748</v>
       </c>
       <c r="X31" t="s">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="Y31">
         <v>38.15925</v>
@@ -14132,7 +14132,7 @@
         <v>688</v>
       </c>
       <c r="K32" t="s">
-        <v>474</v>
+        <v>429</v>
       </c>
       <c r="L32">
         <v>7.5025171344716721</v>
@@ -14165,7 +14165,7 @@
         <v>750</v>
       </c>
       <c r="X32" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="Y32">
         <v>3.38625</v>
@@ -14200,7 +14200,7 @@
         <v>690</v>
       </c>
       <c r="K33" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="L33">
         <v>25.978158470265569</v>
@@ -14233,7 +14233,7 @@
         <v>752</v>
       </c>
       <c r="X33" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="Y33">
         <v>30.597750000000001</v>
@@ -14268,7 +14268,7 @@
         <v>692</v>
       </c>
       <c r="K34" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="L34">
         <v>40.036304639772588</v>
@@ -14301,7 +14301,7 @@
         <v>754</v>
       </c>
       <c r="X34" t="s">
-        <v>639</v>
+        <v>607</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14336,7 +14336,7 @@
         <v>694</v>
       </c>
       <c r="K35" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="L35">
         <v>7.0903888161806279</v>
@@ -14369,7 +14369,7 @@
         <v>756</v>
       </c>
       <c r="X35" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="Y35">
         <v>58.474499999999999</v>
@@ -14404,7 +14404,7 @@
         <v>696</v>
       </c>
       <c r="K36" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="L36">
         <v>16.970662525397827</v>
@@ -14437,7 +14437,7 @@
         <v>758</v>
       </c>
       <c r="X36" t="s">
-        <v>637</v>
+        <v>605</v>
       </c>
       <c r="Y36">
         <v>18.711749999999999</v>
@@ -14472,7 +14472,7 @@
         <v>698</v>
       </c>
       <c r="K37" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L37">
         <v>2.5242004930684354</v>
@@ -14505,7 +14505,7 @@
         <v>760</v>
       </c>
       <c r="X37" t="s">
-        <v>632</v>
+        <v>599</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14540,7 +14540,7 @@
         <v>700</v>
       </c>
       <c r="K38" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L38">
         <v>5.5071261071764246</v>
@@ -14573,7 +14573,7 @@
         <v>762</v>
       </c>
       <c r="X38" t="s">
-        <v>635</v>
+        <v>603</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14608,7 +14608,7 @@
         <v>702</v>
       </c>
       <c r="K39" t="s">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="L39">
         <v>12.527007796473459</v>
@@ -14641,7 +14641,7 @@
         <v>764</v>
       </c>
       <c r="X39" t="s">
-        <v>612</v>
+        <v>576</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14676,7 +14676,7 @@
         <v>704</v>
       </c>
       <c r="K40" t="s">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="L40">
         <v>22.322239264526591</v>
@@ -14709,7 +14709,7 @@
         <v>766</v>
       </c>
       <c r="X40" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14744,7 +14744,7 @@
         <v>706</v>
       </c>
       <c r="K41" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="L41">
         <v>25.14604307789013</v>
@@ -14777,7 +14777,7 @@
         <v>768</v>
       </c>
       <c r="X41" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14812,7 +14812,7 @@
         <v>770</v>
       </c>
       <c r="X42" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="Y42">
         <v>27.642749999999999</v>
@@ -14847,7 +14847,7 @@
         <v>772</v>
       </c>
       <c r="X43" t="s">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14882,7 +14882,7 @@
         <v>774</v>
       </c>
       <c r="X44" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14917,7 +14917,7 @@
         <v>776</v>
       </c>
       <c r="X45" t="s">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14952,7 +14952,7 @@
         <v>778</v>
       </c>
       <c r="X46" t="s">
-        <v>634</v>
+        <v>602</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14987,7 +14987,7 @@
         <v>780</v>
       </c>
       <c r="X47" t="s">
-        <v>614</v>
+        <v>578</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -15022,7 +15022,7 @@
         <v>782</v>
       </c>
       <c r="X48" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15057,7 +15057,7 @@
         <v>784</v>
       </c>
       <c r="X49" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="Y49">
         <v>16.497</v>
@@ -15092,7 +15092,7 @@
         <v>786</v>
       </c>
       <c r="X50" t="s">
-        <v>604</v>
+        <v>633</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15127,7 +15127,7 @@
         <v>788</v>
       </c>
       <c r="X51" t="s">
-        <v>644</v>
+        <v>612</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15162,7 +15162,7 @@
         <v>790</v>
       </c>
       <c r="X52" t="s">
-        <v>574</v>
+        <v>618</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15197,7 +15197,7 @@
         <v>792</v>
       </c>
       <c r="X53" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="Y53">
         <v>30.527249999999999</v>
@@ -15232,7 +15232,7 @@
         <v>794</v>
       </c>
       <c r="X54" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="Y54">
         <v>17.390999999999998</v>
@@ -15247,7 +15247,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD0FB8D-38A6-4ADA-89E5-A612BB39B57F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD261B6-B3A6-41A0-AF26-BA14BFA12604}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17064,7 +17064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E48C342F-7C1D-4678-A1BC-8E67415C451F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9A6698-6A41-44F7-89AC-F571DB016F11}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EDA2BD3-5A31-4430-B6C7-52FDF84BFFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F629456-B8C3-4B73-BA0E-5CB4C8823016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,64 +949,148 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses 